--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F3" s="36" t="inlineStr">
@@ -1412,33 +1412,47 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H3" s="36" t="n">
-        <v>42</v>
-      </c>
-      <c r="I3" s="36" t="n"/>
-      <c r="J3" s="36" t="n"/>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K3" s="36" t="n">
-        <v>67.93000000000001</v>
+        <v>19.96</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M3" s="36" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="N3" s="36" t="n">
-        <v>50</v>
+      <c r="M3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O3" s="36" t="inlineStr">
         <is>
-          <t>未报告(7级量表)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="P3" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q3" s="36" t="n">
@@ -1446,12 +1460,12 @@
       </c>
       <c r="R3" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S3" s="36" t="inlineStr">
         <is>
-          <t>2-back; numerical updating; alpha-span</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="T3" s="36" t="inlineStr">
@@ -1464,33 +1478,49 @@
       </c>
       <c r="V3" s="36" t="inlineStr">
         <is>
-          <t>15-20</t>
-        </is>
-      </c>
-      <c r="W3" s="35" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W3" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X3" s="36" t="inlineStr">
         <is>
-          <t>≤30天</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y3" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" s="36" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z3" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA3" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB3" s="35" t="n"/>
+      <c r="AB3" s="35" t="inlineStr">
+        <is>
+          <t>LMM/ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC3" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD3" s="36" t="n"/>
+          <t>was app; Session 4</t>
+        </is>
+      </c>
+      <c r="AD3" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF3" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -1498,7 +1528,7 @@
       </c>
       <c r="AG3" s="36" t="inlineStr">
         <is>
-          <t>Backward Digit Span</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH3" s="36" t="inlineStr">
@@ -1508,13 +1538,17 @@
       </c>
       <c r="AI3" s="36" t="inlineStr">
         <is>
-          <t>Faces &amp; Names; Shopping List</t>
-        </is>
-      </c>
-      <c r="AJ3" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ3" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK3" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL3" s="36" t="inlineStr">
@@ -1530,19 +1564,28 @@
       <c r="AN3" s="35" t="n"/>
       <c r="AO3" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP3" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ3" s="36" t="n"/>
-      <c r="AR3" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ3" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR3" s="36" t="inlineStr">
+        <is>
+          <t>brain areas and corresponding decreased
+performance.</t>
+        </is>
+      </c>
       <c r="AS3" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AT3" s="36" t="inlineStr">
@@ -1552,10 +1595,14 @@
       </c>
       <c r="AU3" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV3" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV3" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW3" s="36" t="inlineStr">
         <is>
           <t>否</t>
@@ -1563,10 +1610,14 @@
       </c>
       <c r="AX3" s="36" t="inlineStr">
         <is>
-          <t>教育(7级量表)</t>
-        </is>
-      </c>
-      <c r="AY3" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY3" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ3" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -1574,14 +1625,22 @@
       </c>
       <c r="BA3" s="36" t="inlineStr">
         <is>
-          <t>按基线EF高/低分组分析调节效应</t>
-        </is>
-      </c>
-      <c r="BB3" s="36" t="n"/>
-      <c r="BC3" s="36" t="n"/>
+          <t>按基线EF高/低分组分析调节效应 | 待核查：无法确定对照类型 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB3" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC3" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD3" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE3" s="40" t="inlineStr">
@@ -1609,7 +1668,7 @@
       </c>
       <c r="E4" s="38" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F4" s="38" t="inlineStr">
@@ -1623,26 +1682,40 @@
         </is>
       </c>
       <c r="H4" s="38" t="n">
-        <v>72</v>
-      </c>
-      <c r="I4" s="38" t="n"/>
-      <c r="J4" s="38" t="n"/>
-      <c r="K4" s="38" t="n">
-        <v>69.23999999999999</v>
+        <v>19</v>
+      </c>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="K4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M4" s="38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N4" s="38" t="n">
-        <v>58</v>
-      </c>
-      <c r="O4" s="38" t="n">
-        <v>13.84</v>
+      <c r="M4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P4" s="38" t="inlineStr">
         <is>
@@ -1661,7 +1734,7 @@
       </c>
       <c r="S4" s="38" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>wome; engage</t>
         </is>
       </c>
       <c r="T4" s="38" t="inlineStr">
@@ -1669,34 +1742,56 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U4" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="38" t="n">
-        <v>60</v>
-      </c>
-      <c r="W4" s="37" t="n"/>
-      <c r="X4" s="38" t="n">
-        <v>2</v>
+      <c r="U4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y4" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z4" s="38" t="n"/>
+      <c r="Z4" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA4" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB4" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AC4" s="38" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
-        </is>
-      </c>
-      <c r="AD4" s="38" t="n"/>
+          <t>these program; Venezia 8</t>
+        </is>
+      </c>
+      <c r="AD4" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE4" t="n">
         <v>1.5</v>
       </c>
@@ -1707,7 +1802,7 @@
       </c>
       <c r="AG4" s="38" t="inlineStr">
         <is>
-          <t>Backward Corsi blocks</t>
+          <t>were expected only immediately after training (e</t>
         </is>
       </c>
       <c r="AH4" s="38" t="inlineStr">
@@ -1717,10 +1812,14 @@
       </c>
       <c r="AI4" s="38" t="inlineStr">
         <is>
-          <t>Verbal fluency; Raven matrices; Culture Fair</t>
-        </is>
-      </c>
-      <c r="AJ4" s="38" t="n"/>
+          <t>or follow-up (p = 0</t>
+        </is>
+      </c>
+      <c r="AJ4" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK4" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -1731,13 +1830,17 @@
       </c>
       <c r="AM4" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN4" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN4" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO4" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP4" s="38" t="inlineStr">
@@ -1745,8 +1848,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ4" s="38" t="n"/>
-      <c r="AR4" s="38" t="n"/>
+      <c r="AQ4" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR4" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS4" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1762,18 +1873,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV4" s="37" t="n"/>
+      <c r="AV4" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX4" s="38" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY4" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY4" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ4" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -1784,11 +1903,19 @@
           <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
         </is>
       </c>
-      <c r="BB4" s="38" t="n"/>
-      <c r="BC4" s="38" t="n"/>
+      <c r="BB4" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC4" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD4" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE4" s="40" t="inlineStr">
@@ -1816,7 +1943,7 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F5" s="36" t="inlineStr">
@@ -1826,36 +1953,42 @@
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>社区/大学</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H5" s="36" t="n">
-        <v>46</v>
-      </c>
-      <c r="I5" s="36" t="n"/>
-      <c r="J5" s="36" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="36" t="n">
+        <v>21</v>
+      </c>
       <c r="K5" s="36" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M5" s="36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N5" s="36" t="n">
-        <v>56</v>
-      </c>
-      <c r="O5" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M5" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N5" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O5" s="36" t="n">
+        <v>96</v>
       </c>
       <c r="P5" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q5" s="36" t="inlineStr">
@@ -1870,7 +2003,7 @@
       </c>
       <c r="S5" s="36" t="inlineStr">
         <is>
-          <t>Dual n-back (auditory-visual)</t>
+          <t>dual n-back; single n-back; engage; reading span; verbal n-back</t>
         </is>
       </c>
       <c r="T5" s="36" t="inlineStr">
@@ -1879,35 +2012,53 @@
         </is>
       </c>
       <c r="U5" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="V5" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="W5" s="35" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="V5" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W5" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X5" s="36" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y5" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z5" s="36" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA5" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB5" s="35" t="n"/>
+      <c r="AB5" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
       <c r="AC5" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD5" s="36" t="n"/>
+          <t>our platform; only 14</t>
+        </is>
+      </c>
+      <c r="AD5" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF5" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -1915,7 +2066,8 @@
       </c>
       <c r="AG5" s="36" t="inlineStr">
         <is>
-          <t>AV n-back (untrained stimuli)</t>
+          <t>and numerical 2- and 3-back tasks following
+training on a spatial 2-back task and</t>
         </is>
       </c>
       <c r="AH5" s="36" t="inlineStr">
@@ -1925,13 +2077,17 @@
       </c>
       <c r="AI5" s="36" t="inlineStr">
         <is>
-          <t>Task switching; Attentional blink (T2)</t>
-        </is>
-      </c>
-      <c r="AJ5" s="36" t="n"/>
+          <t>of verbal learning and memory, but no transfer to fluid intelligence or attention</t>
+        </is>
+      </c>
+      <c r="AJ5" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK5" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL5" s="36" t="inlineStr">
@@ -1941,13 +2097,17 @@
       </c>
       <c r="AM5" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN5" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN5" s="35" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="AO5" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP5" s="36" t="inlineStr">
@@ -1955,8 +2115,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ5" s="36" t="n"/>
-      <c r="AR5" s="36" t="n"/>
+      <c r="AQ5" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR5" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS5" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1969,10 +2137,14 @@
       </c>
       <c r="AU5" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
-        </is>
-      </c>
-      <c r="AV5" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV5" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW5" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -1983,7 +2155,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY5" s="36" t="n"/>
+      <c r="AY5" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ5" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -1991,14 +2167,22 @@
       </c>
       <c r="BA5" s="36" t="inlineStr">
         <is>
-          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
-        </is>
-      </c>
-      <c r="BB5" s="36" t="n"/>
-      <c r="BC5" s="36" t="n"/>
+          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB5" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC5" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD5" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE5" s="40" t="inlineStr">
@@ -2026,7 +2210,7 @@
       </c>
       <c r="E6" s="38" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F6" s="38" t="inlineStr">
@@ -2039,31 +2223,49 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H6" s="38" t="n">
-        <v>72</v>
-      </c>
-      <c r="I6" s="38" t="n"/>
-      <c r="J6" s="38" t="n"/>
-      <c r="K6" s="38" t="n">
-        <v>64.38</v>
+      <c r="H6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="N6" s="38" t="n">
-        <v>68</v>
-      </c>
-      <c r="O6" s="38" t="n">
-        <v>16.78</v>
+      <c r="M6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P6" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q6" s="38" t="n">
@@ -2071,47 +2273,65 @@
       </c>
       <c r="R6" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S6" s="38" t="inlineStr">
         <is>
-          <t>Verbal WM; Visuospatial WM; OSpan</t>
+          <t>engage; Operation Span</t>
         </is>
       </c>
       <c r="T6" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U6" s="38" t="n">
         <v>10</v>
       </c>
       <c r="V6" s="38" t="n">
-        <v>60</v>
-      </c>
-      <c r="W6" s="37" t="n"/>
-      <c r="X6" s="38" t="n">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="W6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y6" s="38" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z6" s="38" t="n"/>
+      <c r="Z6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA6" s="38" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB6" s="37" t="n"/>
+          <t>tDCS/TMS/tRNS/运动</t>
+        </is>
+      </c>
+      <c r="AB6" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC6" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD6" s="38" t="n"/>
+          <t>involves app</t>
+        </is>
+      </c>
+      <c r="AD6" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE6" t="n">
         <v>5</v>
       </c>
@@ -2122,7 +2342,7 @@
       </c>
       <c r="AG6" s="38" t="inlineStr">
         <is>
-          <t>Spatial 2-back</t>
+          <t>the spatial 2-back WM</t>
         </is>
       </c>
       <c r="AH6" s="38" t="inlineStr">
@@ -2132,17 +2352,23 @@
       </c>
       <c r="AI6" s="38" t="inlineStr">
         <is>
-          <t>Digit span; Stroop</t>
-        </is>
-      </c>
-      <c r="AJ6" s="38" t="n"/>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ6" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK6" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL6" s="38" t="n">
-        <v>1</v>
+      <c r="AL6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AM6" s="37" t="inlineStr">
         <is>
@@ -2152,16 +2378,24 @@
       <c r="AN6" s="37" t="n"/>
       <c r="AO6" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP6" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ6" s="38" t="n"/>
-      <c r="AR6" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ6" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR6" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS6" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2177,18 +2411,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV6" s="37" t="n"/>
+      <c r="AV6" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW6" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX6" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
-        </is>
-      </c>
-      <c r="AY6" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY6" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ6" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -2196,14 +2438,22 @@
       </c>
       <c r="BA6" s="38" t="inlineStr">
         <is>
-          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
-        </is>
-      </c>
-      <c r="BB6" s="38" t="n"/>
-      <c r="BC6" s="38" t="n"/>
+          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB6" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC6" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD6" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE6" s="40" t="inlineStr">
@@ -2231,7 +2481,7 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>Brain and behavior</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F7" s="36" t="inlineStr">
@@ -2241,16 +2491,24 @@
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H7" s="36" t="n">
-        <v>28</v>
-      </c>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="36" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J7" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K7" s="36" t="n">
-        <v>63.11</v>
+        <v>26.15</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2262,8 +2520,10 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N7" s="36" t="n">
-        <v>54</v>
+      <c r="N7" s="36" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
       </c>
       <c r="O7" s="36" t="inlineStr">
         <is>
@@ -2272,7 +2532,7 @@
       </c>
       <c r="P7" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="Q7" s="36" t="inlineStr">
@@ -2287,42 +2547,61 @@
       </c>
       <c r="S7" s="36" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>dual n-back; engage; complex span</t>
         </is>
       </c>
       <c r="T7" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U7" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="V7" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W7" s="35" t="n"/>
+      <c r="V7" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X7" s="36" t="n">
         <v>3</v>
       </c>
       <c r="Y7" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z7" s="36" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA7" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB7" s="35" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB7" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC7" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD7" s="36" t="n"/>
+          <t>Poles  
+Program</t>
+        </is>
+      </c>
+      <c r="AD7" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE7" t="n">
         <v>3.3</v>
       </c>
@@ -2333,7 +2612,7 @@
       </c>
       <c r="AG7" s="36" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH7" s="36" t="inlineStr">
@@ -2341,11 +2620,20 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI7" s="36" t="n"/>
-      <c r="AJ7" s="36" t="n"/>
+      <c r="AI7" s="36" t="inlineStr">
+        <is>
+          <t>switch‐
+ing training</t>
+        </is>
+      </c>
+      <c r="AJ7" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK7" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL7" s="36" t="inlineStr">
@@ -2355,13 +2643,17 @@
       </c>
       <c r="AM7" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN7" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN7" s="35" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
       <c r="AO7" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP7" s="36" t="inlineStr">
@@ -2371,12 +2663,13 @@
       </c>
       <c r="AQ7" s="36" t="inlineStr">
         <is>
-          <t>EEG/ERP</t>
+          <t>fMRI/EEG/ERP/PET</t>
         </is>
       </c>
       <c r="AR7" s="36" t="inlineStr">
         <is>
-          <t>训练后P300振幅变化与任务难度相关</t>
+          <t>EEG studies have noted task difficulty and age‐related changes in time‐
+locked EEG responses, called event‐related potentials (ERPs), we focused on th</t>
         </is>
       </c>
       <c r="AS7" s="36" t="inlineStr">
@@ -2394,10 +2687,14 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV7" s="35" t="n"/>
+      <c r="AV7" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW7" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX7" s="36" t="inlineStr">
@@ -2405,7 +2702,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY7" s="36" t="n"/>
+      <c r="AY7" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ7" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -2413,14 +2714,22 @@
       </c>
       <c r="BA7" s="36" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
-        </is>
-      </c>
-      <c r="BB7" s="36" t="n"/>
-      <c r="BC7" s="36" t="n"/>
+          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB7" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC7" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD7" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE7" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -712,7 +712,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:BE58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E8" s="38" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F8" s="38" t="inlineStr">
@@ -2770,33 +2770,49 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H8" s="38" t="n">
-        <v>46</v>
-      </c>
-      <c r="I8" s="38" t="n"/>
-      <c r="J8" s="38" t="n"/>
-      <c r="K8" s="38" t="n">
-        <v>67.17</v>
+      <c r="H8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M8" s="38" t="n">
-        <v>4.4</v>
+      <c r="M8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N8" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="O8" s="38" t="n">
-        <v>9.5</v>
+      <c r="O8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P8" s="38" t="inlineStr">
         <is>
-          <t>CERAD+CDT</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q8" s="38" t="inlineStr">
@@ -2806,12 +2822,12 @@
       </c>
       <c r="R8" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S8" s="38" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, Borella protocol)</t>
+          <t>dual n-back; engage</t>
         </is>
       </c>
       <c r="T8" s="38" t="inlineStr">
@@ -2822,31 +2838,52 @@
       <c r="U8" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="38" t="n">
-        <v>60</v>
-      </c>
-      <c r="W8" s="37" t="n"/>
-      <c r="X8" s="38" t="n">
-        <v>2</v>
+      <c r="V8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y8" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z8" s="38" t="n"/>
+      <c r="Z8" s="38" t="inlineStr">
+        <is>
+          <t>the assessments accord-
+ing to the same schedule</t>
+        </is>
+      </c>
       <c r="AA8" s="38" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB8" s="37" t="n"/>
+      <c r="AB8" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC8" s="38" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
-        </is>
-      </c>
-      <c r="AD8" s="38" t="n"/>
+          <t>Age Program</t>
+        </is>
+      </c>
+      <c r="AD8" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE8" t="n">
         <v>1.5</v>
       </c>
@@ -2857,7 +2894,9 @@
       </c>
       <c r="AG8" s="38" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; Visuospatial WM</t>
+          <t>measuring different
+constructs but related to WM functioning in older adults,
+for</t>
         </is>
       </c>
       <c r="AH8" s="38" t="inlineStr">
@@ -2867,10 +2906,15 @@
       </c>
       <c r="AI8" s="38" t="inlineStr">
         <is>
-          <t>Stroop; Processing speed; Fluid intelligence</t>
-        </is>
-      </c>
-      <c r="AJ8" s="38" t="n"/>
+          <t>at post-test and fol-
+low-up</t>
+        </is>
+      </c>
+      <c r="AJ8" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK8" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -2881,13 +2925,17 @@
       </c>
       <c r="AM8" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN8" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN8" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO8" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP8" s="38" t="inlineStr">
@@ -2895,8 +2943,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ8" s="38" t="n"/>
-      <c r="AR8" s="38" t="n"/>
+      <c r="AQ8" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR8" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS8" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2904,26 +2960,34 @@
       </c>
       <c r="AT8" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU8" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV8" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW8" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX8" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY8" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV8" s="37" t="n"/>
-      <c r="AW8" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX8" s="38" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY8" s="38" t="n"/>
       <c r="AZ8" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -2931,14 +2995,22 @@
       </c>
       <c r="BA8" s="38" t="inlineStr">
         <is>
-          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
-        </is>
-      </c>
-      <c r="BB8" s="38" t="n"/>
-      <c r="BC8" s="38" t="n"/>
+          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol | 待核查</t>
+        </is>
+      </c>
+      <c r="BB8" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC8" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD8" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE8" s="40" t="inlineStr">
@@ -2966,7 +3038,7 @@
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F9" s="36" t="inlineStr">
@@ -2976,14 +3048,22 @@
       </c>
       <c r="G9" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H9" s="36" t="n">
         <v>76</v>
       </c>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="n"/>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K9" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2999,14 +3079,12 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="O9" s="36" t="inlineStr">
-        <is>
-          <t>≥6年</t>
-        </is>
+      <c r="O9" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="P9" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q9" s="36" t="inlineStr">
@@ -3021,7 +3099,7 @@
       </c>
       <c r="S9" s="36" t="inlineStr">
         <is>
-          <t>Gamified N-back (fruit-cutting game)</t>
+          <t>dual n-back; Cogmed; BrainHQ; Lumosity; engage; Complex span</t>
         </is>
       </c>
       <c r="T9" s="36" t="inlineStr">
@@ -3033,9 +3111,13 @@
         <v>12</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="W9" s="35" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="W9" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X9" s="36" t="n">
         <v>6</v>
       </c>
@@ -3044,19 +3126,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="36" t="n"/>
+      <c r="Z9" s="36" t="inlineStr">
+        <is>
+          <t>cognitive assessments</t>
+        </is>
+      </c>
       <c r="AA9" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB9" s="35" t="n"/>
+      <c r="AB9" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC9" s="36" t="inlineStr">
         <is>
-          <t>自制(JavaScript游戏)</t>
-        </is>
-      </c>
-      <c r="AD9" s="36" t="n"/>
+          <t>Lumosity; effective app</t>
+        </is>
+      </c>
+      <c r="AD9" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE9" t="n">
         <v>2</v>
       </c>
@@ -3067,7 +3161,7 @@
       </c>
       <c r="AG9" s="36" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH9" s="36" t="inlineStr">
@@ -3077,10 +3171,14 @@
       </c>
       <c r="AI9" s="36" t="inlineStr">
         <is>
-          <t>Inhibitory control; Visuospatial; Episodic memory</t>
-        </is>
-      </c>
-      <c r="AJ9" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ9" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK9" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -3091,13 +3189,17 @@
       </c>
       <c r="AM9" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN9" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN9" s="35" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
       <c r="AO9" s="36" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP9" s="36" t="inlineStr">
@@ -3107,41 +3209,52 @@
       </c>
       <c r="AQ9" s="36" t="inlineStr">
         <is>
-          <t>fMRI(sMRI+rs-fMRI)</t>
+          <t>fMRI/MRI/PET</t>
         </is>
       </c>
       <c r="AR9" s="36" t="inlineStr">
         <is>
-          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
+          <t>neural changes
+are proposed to be the underlying mechanisms for the observed
+cognitive enhancements (Duda &amp; Sweet, 2020; Karbach &amp; Schubert,
+2013).</t>
         </is>
       </c>
       <c r="AS9" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT9" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU9" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV9" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW9" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY9" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV9" s="35" t="n"/>
-      <c r="AW9" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX9" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY9" s="36" t="n"/>
       <c r="AZ9" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3149,14 +3262,22 @@
       </c>
       <c r="BA9" s="36" t="inlineStr">
         <is>
-          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
-        </is>
-      </c>
-      <c r="BB9" s="36" t="n"/>
-      <c r="BC9" s="36" t="n"/>
+          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB9" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC9" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD9" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE9" s="40" t="inlineStr">
@@ -3184,7 +3305,7 @@
       </c>
       <c r="E10" s="38" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F10" s="38" t="inlineStr">
@@ -3198,10 +3319,18 @@
         </is>
       </c>
       <c r="H10" s="38" t="n">
-        <v>142</v>
-      </c>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="I10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="n">
         <v>70.34999999999999</v>
       </c>
@@ -3211,19 +3340,21 @@
         </is>
       </c>
       <c r="M10" s="38" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N10" s="38" t="n">
-        <v>48</v>
+        <v>150</v>
+      </c>
+      <c r="N10" s="38" t="inlineStr">
+        <is>
+          <t>103%</t>
+        </is>
       </c>
       <c r="O10" s="38" t="inlineStr">
         <is>
-          <t>未报告(0-7量表)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="P10" s="38" t="inlineStr">
         <is>
-          <t>MMSE+GDS</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q10" s="38" t="inlineStr">
@@ -3233,12 +3364,12 @@
       </c>
       <c r="R10" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S10" s="38" t="inlineStr">
         <is>
-          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
+          <t>engage; complex span</t>
         </is>
       </c>
       <c r="T10" s="38" t="inlineStr">
@@ -3249,33 +3380,49 @@
       <c r="U10" s="38" t="n">
         <v>25</v>
       </c>
-      <c r="V10" s="38" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="W10" s="37" t="n"/>
-      <c r="X10" s="38" t="n">
-        <v>5</v>
+      <c r="V10" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" s="37" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="X10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y10" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z10" s="38" t="n"/>
+      <c r="Z10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA10" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB10" s="37" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB10" s="37" t="inlineStr">
+        <is>
+          <t>LMM/Bayesian</t>
+        </is>
+      </c>
       <c r="AC10" s="38" t="inlineStr">
         <is>
-          <t>自制(von Bastian protocol)</t>
-        </is>
-      </c>
-      <c r="AD10" s="38" t="n"/>
+          <t>Priority Program</t>
+        </is>
+      </c>
+      <c r="AD10" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE10" t="n">
         <v>5</v>
       </c>
@@ -3286,7 +3433,8 @@
       </c>
       <c r="AG10" s="38" t="inlineStr">
         <is>
-          <t>Visuospatial WM (3 tasks)</t>
+          <t>and the absence of far transfer effects to all of the assessed 
+abilities</t>
         </is>
       </c>
       <c r="AH10" s="38" t="inlineStr">
@@ -3296,13 +3444,18 @@
       </c>
       <c r="AI10" s="38" t="inlineStr">
         <is>
-          <t>Fluid intelligence; Inhibition; Shifting</t>
-        </is>
-      </c>
-      <c r="AJ10" s="38" t="n"/>
+          <t>ed 
+abilities</t>
+        </is>
+      </c>
+      <c r="AJ10" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK10" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL10" s="38" t="inlineStr">
@@ -3312,13 +3465,17 @@
       </c>
       <c r="AM10" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN10" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN10" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO10" s="38" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP10" s="38" t="inlineStr">
@@ -3326,8 +3483,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ10" s="38" t="n"/>
-      <c r="AR10" s="38" t="n"/>
+      <c r="AQ10" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR10" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS10" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -3335,26 +3500,34 @@
       </c>
       <c r="AT10" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU10" s="38" t="inlineStr">
         <is>
-          <t>未检验</t>
-        </is>
-      </c>
-      <c r="AV10" s="37" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV10" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW10" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX10" s="38" t="inlineStr">
         <is>
-          <t>教育(0-7量表)</t>
-        </is>
-      </c>
-      <c r="AY10" s="38" t="n"/>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY10" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ10" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3362,14 +3535,22 @@
       </c>
       <c r="BA10" s="38" t="inlineStr">
         <is>
-          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
-        </is>
-      </c>
-      <c r="BB10" s="38" t="n"/>
-      <c r="BC10" s="38" t="n"/>
+          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移 | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB10" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC10" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD10" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE10" s="40" t="inlineStr">
@@ -3397,7 +3578,7 @@
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>预印本</t>
         </is>
       </c>
       <c r="F11" s="36" t="inlineStr">
@@ -3407,14 +3588,18 @@
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H11" s="36" t="n">
-        <v>54</v>
-      </c>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="36" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" s="36" t="n">
         <v>68.2</v>
       </c>
@@ -3426,8 +3611,10 @@
       <c r="M11" s="36" t="n">
         <v>5.92</v>
       </c>
-      <c r="N11" s="36" t="n">
-        <v>76</v>
+      <c r="N11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O11" s="36" t="inlineStr">
         <is>
@@ -3451,46 +3638,60 @@
       </c>
       <c r="S11" s="36" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>dual n-back; wome</t>
         </is>
       </c>
       <c r="T11" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U11" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W11" s="35" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="X11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="36" t="inlineStr">
-        <is>
-          <t>20+20</t>
-        </is>
-      </c>
-      <c r="W11" s="35" t="n"/>
-      <c r="X11" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Y11" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z11" s="36" t="n"/>
+      <c r="Z11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA11" s="36" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB11" s="35" t="n"/>
+          <t>tDCS/药物</t>
+        </is>
+      </c>
+      <c r="AB11" s="35" t="inlineStr">
+        <is>
+          <t>LMM/ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC11" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD11" s="36" t="n"/>
+          <t>were app; two 5</t>
+        </is>
+      </c>
+      <c r="AD11" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE11" t="n">
         <v>1.7</v>
       </c>
@@ -3501,7 +3702,8 @@
       </c>
       <c r="AG11" s="36" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>ed
+through Digit Span</t>
         </is>
       </c>
       <c r="AH11" s="36" t="inlineStr">
@@ -3511,17 +3713,24 @@
       </c>
       <c r="AI11" s="36" t="inlineStr">
         <is>
-          <t>Raven APM (RAPM)</t>
-        </is>
-      </c>
-      <c r="AJ11" s="36" t="n"/>
+          <t>by Raven’s
+Advanced Progressive Matrices (RAPM), while the near transfer effects</t>
+        </is>
+      </c>
+      <c r="AJ11" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK11" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL11" s="36" t="n">
-        <v>0.5</v>
+      <c r="AL11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AM11" s="35" t="inlineStr">
         <is>
@@ -3531,19 +3740,27 @@
       <c r="AN11" s="35" t="n"/>
       <c r="AO11" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP11" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ11" s="36" t="n"/>
-      <c r="AR11" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ11" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG</t>
+        </is>
+      </c>
+      <c r="AR11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS11" s="36" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AT11" s="36" t="inlineStr">
@@ -3553,21 +3770,29 @@
       </c>
       <c r="AU11" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV11" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV11" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AW11" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX11" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY11" s="36" t="n"/>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AZ11" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3575,14 +3800,22 @@
       </c>
       <c r="BA11" s="36" t="inlineStr">
         <is>
-          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
-        </is>
-      </c>
-      <c r="BB11" s="36" t="n"/>
-      <c r="BC11" s="36" t="n"/>
+          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB11" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC11" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD11" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE11" s="40" t="inlineStr">
@@ -3610,7 +3843,7 @@
       </c>
       <c r="E12" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F12" s="38" t="inlineStr">
@@ -3623,11 +3856,21 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H12" s="38" t="n">
-        <v>26</v>
-      </c>
-      <c r="I12" s="38" t="n"/>
-      <c r="J12" s="38" t="n"/>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="n">
         <v>64.95999999999999</v>
       </c>
@@ -3636,11 +3879,15 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N12" s="38" t="n">
-        <v>50</v>
+      <c r="M12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O12" s="38" t="inlineStr">
         <is>
@@ -3659,12 +3906,12 @@
       </c>
       <c r="R12" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S12" s="38" t="inlineStr">
         <is>
-          <t>Reading Span (Cogmed)</t>
+          <t>Cogmed; engage; Reading Span; Letter-Number Sequencing</t>
         </is>
       </c>
       <c r="T12" s="38" t="inlineStr">
@@ -3677,31 +3924,47 @@
       </c>
       <c r="V12" s="38" t="inlineStr">
         <is>
-          <t>30-60</t>
-        </is>
-      </c>
-      <c r="W12" s="37" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W12" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X12" s="38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y12" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z12" s="38" t="n"/>
+      <c r="Z12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA12" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB12" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB12" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC12" s="38" t="inlineStr">
         <is>
-          <t>Cogmed</t>
-        </is>
-      </c>
-      <c r="AD12" s="38" t="n"/>
+          <t>Cogmed; noise app</t>
+        </is>
+      </c>
+      <c r="AD12" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE12" t="n">
         <v>5</v>
       </c>
@@ -3712,7 +3975,7 @@
       </c>
       <c r="AG12" s="38" t="inlineStr">
         <is>
-          <t>Reading Span (untrained version)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH12" s="38" t="inlineStr">
@@ -3722,13 +3985,17 @@
       </c>
       <c r="AI12" s="38" t="inlineStr">
         <is>
-          <t>Speech-in-noise comprehension</t>
-        </is>
-      </c>
-      <c r="AJ12" s="38" t="n"/>
+          <t>Kidd et al</t>
+        </is>
+      </c>
+      <c r="AJ12" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK12" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL12" s="38" t="inlineStr">
@@ -3744,43 +4011,59 @@
       <c r="AN12" s="37" t="n"/>
       <c r="AO12" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP12" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ12" s="38" t="n"/>
-      <c r="AR12" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ12" s="38" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS12" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT12" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU12" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV12" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW12" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY12" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV12" s="37" t="n"/>
-      <c r="AW12" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX12" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY12" s="38" t="n"/>
       <c r="AZ12" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3788,14 +4071,22 @@
       </c>
       <c r="BA12" s="38" t="inlineStr">
         <is>
-          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
-        </is>
-      </c>
-      <c r="BB12" s="38" t="n"/>
-      <c r="BC12" s="38" t="n"/>
+          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB12" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC12" s="38" t="inlineStr">
+        <is>
+          <t>交叉设计</t>
+        </is>
+      </c>
       <c r="BD12" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE12" s="40" t="inlineStr">
@@ -13446,7 +13737,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -14905,7 +15196,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E13" s="36" t="inlineStr">
         <is>
-          <t>Brain stimulation</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F13" s="36" t="inlineStr">
@@ -4124,16 +4124,24 @@
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H13" s="36" t="n">
-        <v>90</v>
-      </c>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="36" t="n"/>
+        <v>67</v>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K13" s="36" t="n">
-        <v>69.03</v>
+        <v>13.036</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -4145,15 +4153,17 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N13" s="36" t="n">
-        <v>54</v>
+      <c r="N13" s="36" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
       </c>
       <c r="O13" s="36" t="n">
-        <v>15.58</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="P13" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q13" s="36" t="inlineStr">
@@ -4163,12 +4173,12 @@
       </c>
       <c r="R13" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S13" s="36" t="inlineStr">
         <is>
-          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
+          <t>engage; Operation Span</t>
         </is>
       </c>
       <c r="T13" s="36" t="inlineStr">
@@ -4179,31 +4189,51 @@
       <c r="U13" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="36" t="n">
-        <v>45</v>
-      </c>
-      <c r="W13" s="35" t="n"/>
-      <c r="X13" s="36" t="n">
-        <v>1</v>
+      <c r="V13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W13" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y13" s="36" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z13" s="36" t="n"/>
+      <c r="Z13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA13" s="36" t="inlineStr">
         <is>
           <t>tDCS</t>
         </is>
       </c>
-      <c r="AB13" s="35" t="n"/>
+      <c r="AB13" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC13" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD13" s="36" t="n"/>
+          <t>To app; Page 13</t>
+        </is>
+      </c>
+      <c r="AD13" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE13" t="n">
         <v>5</v>
       </c>
@@ -4214,7 +4244,7 @@
       </c>
       <c r="AG13" s="36" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; 2-back</t>
+          <t>s [20]</t>
         </is>
       </c>
       <c r="AH13" s="36" t="inlineStr">
@@ -4224,31 +4254,33 @@
       </c>
       <c r="AI13" s="36" t="inlineStr">
         <is>
-          <t>WCPA (everyday scheduling); Road Craft Test</t>
-        </is>
-      </c>
-      <c r="AJ13" s="36" t="n"/>
+          <t>along with ecologically valid far transfer tasks, and stimulation was well tolera</t>
+        </is>
+      </c>
+      <c r="AJ13" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK13" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL13" s="36" t="n">
-        <v>1</v>
+      <c r="AL13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AM13" s="35" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN13" s="35" t="inlineStr">
-        <is>
-          <t>η²=0.073(far transfer)</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AN13" s="35" t="n"/>
       <c r="AO13" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP13" s="36" t="inlineStr">
@@ -4258,41 +4290,51 @@
       </c>
       <c r="AQ13" s="36" t="inlineStr">
         <is>
-          <t>fNIRS</t>
+          <t>fMRI/EEG</t>
         </is>
       </c>
       <c r="AR13" s="36" t="inlineStr">
         <is>
-          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
+          <t xml:space="preserve">imaging has 
+identified cortical changes after cognitive training in healthy older adults [29], and we evaluated whether WM 
+training + tDCS training </t>
         </is>
       </c>
       <c r="AS13" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT13" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU13" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV13" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY13" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV13" s="35" t="n"/>
-      <c r="AW13" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX13" s="36" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY13" s="36" t="n"/>
       <c r="AZ13" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4300,14 +4342,22 @@
       </c>
       <c r="BA13" s="36" t="inlineStr">
         <is>
-          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
-        </is>
-      </c>
-      <c r="BB13" s="36" t="n"/>
-      <c r="BC13" s="36" t="n"/>
+          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB13" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC13" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD13" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE13" s="40" t="inlineStr">
@@ -4335,7 +4385,7 @@
       </c>
       <c r="E14" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in Aging Neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F14" s="38" t="inlineStr">
@@ -4349,22 +4399,28 @@
         </is>
       </c>
       <c r="H14" s="38" t="n">
-        <v>83</v>
-      </c>
-      <c r="I14" s="38" t="n"/>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K14" s="38" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="M14" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="N14" s="38" t="n">
-        <v>65</v>
+      <c r="N14" s="38" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
       </c>
       <c r="O14" s="38" t="inlineStr">
         <is>
@@ -4373,7 +4429,7 @@
       </c>
       <c r="P14" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q14" s="38" t="inlineStr">
@@ -4388,7 +4444,7 @@
       </c>
       <c r="S14" s="38" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>dual N-back; Cogmed; engage; Operation SPAN; complex span</t>
         </is>
       </c>
       <c r="T14" s="38" t="inlineStr">
@@ -4401,10 +4457,14 @@
       </c>
       <c r="V14" s="38" t="inlineStr">
         <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="W14" s="37" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W14" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X14" s="38" t="n">
         <v>5</v>
       </c>
@@ -4413,19 +4473,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z14" s="38" t="n"/>
+      <c r="Z14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA14" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB14" s="37" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB14" s="37" t="inlineStr">
+        <is>
+          <t>MANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC14" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD14" s="38" t="n"/>
+          <t>Cogmed; training program</t>
+        </is>
+      </c>
+      <c r="AD14" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
@@ -4436,7 +4508,7 @@
       </c>
       <c r="AG14" s="38" t="inlineStr">
         <is>
-          <t>OSPAN; WM tasks</t>
+          <t>and outcome measures are structurally similar</t>
         </is>
       </c>
       <c r="AH14" s="38" t="inlineStr">
@@ -4446,13 +4518,17 @@
       </c>
       <c r="AI14" s="38" t="inlineStr">
         <is>
-          <t>Processing speed; Fluid intelligence</t>
-        </is>
-      </c>
-      <c r="AJ14" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ14" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK14" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL14" s="38" t="inlineStr">
@@ -4468,19 +4544,27 @@
       <c r="AN14" s="37" t="n"/>
       <c r="AO14" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP14" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ14" s="38" t="n"/>
-      <c r="AR14" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ14" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS14" s="38" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT14" s="38" t="inlineStr">
@@ -4490,21 +4574,29 @@
       </c>
       <c r="AU14" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV14" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY14" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV14" s="37" t="n"/>
-      <c r="AW14" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX14" s="38" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY14" s="38" t="n"/>
       <c r="AZ14" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4512,14 +4604,22 @@
       </c>
       <c r="BA14" s="38" t="inlineStr">
         <is>
-          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
-        </is>
-      </c>
-      <c r="BB14" s="38" t="n"/>
-      <c r="BC14" s="38" t="n"/>
+          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB14" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC14" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD14" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE14" s="40" t="inlineStr">
@@ -4547,7 +4647,7 @@
       </c>
       <c r="E15" s="36" t="inlineStr">
         <is>
-          <t>Neural plasticity</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F15" s="36" t="inlineStr">
@@ -4557,30 +4657,42 @@
       </c>
       <c r="G15" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H15" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="36" t="n"/>
+      <c r="I15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K15" s="36" t="n">
-        <v>68.84</v>
+        <v>72</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M15" s="36" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N15" s="36" t="n">
-        <v>68</v>
+      <c r="M15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O15" s="36" t="n">
-        <v>14.48</v>
+        <v>64</v>
       </c>
       <c r="P15" s="36" t="inlineStr">
         <is>
@@ -4594,12 +4706,12 @@
       </c>
       <c r="R15" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S15" s="36" t="inlineStr">
         <is>
-          <t>Visual Object Memory Task (VOMT)</t>
+          <t>wome; engage</t>
         </is>
       </c>
       <c r="T15" s="36" t="inlineStr">
@@ -4610,42 +4722,63 @@
       <c r="U15" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="V15" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="W15" s="35" t="n"/>
-      <c r="X15" s="36" t="n">
-        <v>1</v>
+      <c r="V15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W15" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y15" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z15" s="36" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA15" s="36" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB15" s="35" t="n"/>
+          <t>tDCS/TMS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB15" s="35" t="inlineStr">
+        <is>
+          <t>LMM</t>
+        </is>
+      </c>
       <c r="AC15" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD15" s="36" t="n"/>
+          <t>combinatorial
+app</t>
+        </is>
+      </c>
+      <c r="AD15" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE15" t="n">
         <v>4</v>
       </c>
       <c r="AF15" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG15" s="36" t="inlineStr">
         <is>
-          <t>VOMT (untrained stimuli)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH15" s="36" t="inlineStr">
@@ -4653,11 +4786,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI15" s="36" t="n"/>
-      <c r="AJ15" s="36" t="n"/>
+      <c r="AI15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ15" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK15" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL15" s="36" t="inlineStr">
@@ -4673,7 +4814,7 @@
       <c r="AN15" s="35" t="n"/>
       <c r="AO15" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP15" s="36" t="inlineStr">
@@ -4683,41 +4824,50 @@
       </c>
       <c r="AQ15" s="36" t="inlineStr">
         <is>
-          <t>fMRI(rs-fMRI)</t>
+          <t>fMRI/EEG/ERP/MRI</t>
         </is>
       </c>
       <c r="AR15" s="36" t="inlineStr">
         <is>
-          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+          <t>brain activity after the unilateral
+right frontoparietal stimulation.</t>
         </is>
       </c>
       <c r="AS15" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT15" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU15" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV15" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW15" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY15" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV15" s="35" t="n"/>
-      <c r="AW15" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX15" s="36" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY15" s="36" t="n"/>
       <c r="AZ15" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4725,14 +4875,22 @@
       </c>
       <c r="BA15" s="36" t="inlineStr">
         <is>
-          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
-        </is>
-      </c>
-      <c r="BB15" s="36" t="n"/>
-      <c r="BC15" s="36" t="n"/>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB15" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC15" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD15" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE15" s="40" t="inlineStr">
@@ -4760,7 +4918,7 @@
       </c>
       <c r="E16" s="38" t="inlineStr">
         <is>
-          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F16" s="38" t="inlineStr">
@@ -4774,10 +4932,16 @@
         </is>
       </c>
       <c r="H16" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="I16" s="38" t="n"/>
-      <c r="J16" s="38" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J16" s="38" t="n">
+        <v>14</v>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -4788,8 +4952,10 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N16" s="38" t="n">
-        <v>50</v>
+      <c r="N16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O16" s="38" t="inlineStr">
         <is>
@@ -4798,7 +4964,7 @@
       </c>
       <c r="P16" s="38" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Q16" s="38" t="inlineStr">
@@ -4808,12 +4974,12 @@
       </c>
       <c r="R16" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S16" s="38" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, modified)</t>
+          <t>engage</t>
         </is>
       </c>
       <c r="T16" s="38" t="inlineStr">
@@ -4821,34 +4987,56 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U16" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="38" t="n">
-        <v>90</v>
-      </c>
-      <c r="W16" s="37" t="n"/>
-      <c r="X16" s="38" t="n">
-        <v>2</v>
+      <c r="U16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W16" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y16" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z16" s="38" t="n"/>
+      <c r="Z16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA16" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB16" s="37" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB16" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC16" s="38" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
-        </is>
-      </c>
-      <c r="AD16" s="38" t="n"/>
+          <t>was app</t>
+        </is>
+      </c>
+      <c r="AD16" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE16" t="n">
         <v>1.5</v>
       </c>
@@ -4859,7 +5047,7 @@
       </c>
       <c r="AG16" s="38" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH16" s="38" t="inlineStr">
@@ -4869,10 +5057,14 @@
       </c>
       <c r="AI16" s="38" t="inlineStr">
         <is>
-          <t>TIADL (everyday functioning); EPT</t>
-        </is>
-      </c>
-      <c r="AJ16" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ16" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK16" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -4883,10 +5075,14 @@
       </c>
       <c r="AM16" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN16" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN16" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO16" s="38" t="inlineStr">
         <is>
           <t>混合</t>
@@ -4897,11 +5093,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ16" s="38" t="n"/>
-      <c r="AR16" s="38" t="n"/>
+      <c r="AQ16" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR16" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS16" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT16" s="38" t="inlineStr">
@@ -4914,18 +5118,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV16" s="37" t="n"/>
+      <c r="AV16" s="37" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
       <c r="AW16" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX16" s="38" t="inlineStr">
         <is>
-          <t>词汇测试</t>
-        </is>
-      </c>
-      <c r="AY16" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY16" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ16" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4933,14 +5145,22 @@
       </c>
       <c r="BA16" s="38" t="inlineStr">
         <is>
-          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
-        </is>
-      </c>
-      <c r="BB16" s="38" t="n"/>
-      <c r="BC16" s="38" t="n"/>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移 | 待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="BB16" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC16" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD16" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE16" s="40" t="inlineStr">
@@ -4968,7 +5188,7 @@
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F17" s="36" t="inlineStr">
@@ -4982,12 +5202,18 @@
         </is>
       </c>
       <c r="H17" s="36" t="n">
-        <v>85</v>
-      </c>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K17" s="36" t="n">
-        <v>66.7</v>
+        <v>55</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -5011,7 +5237,7 @@
       </c>
       <c r="P17" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q17" s="36" t="inlineStr">
@@ -5026,7 +5252,7 @@
       </c>
       <c r="S17" s="36" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>dual n-back; Cogmed; engage; operation span</t>
         </is>
       </c>
       <c r="T17" s="36" t="inlineStr">
@@ -5037,10 +5263,16 @@
       <c r="U17" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="V17" s="36" t="n">
-        <v>45</v>
-      </c>
-      <c r="W17" s="35" t="n"/>
+      <c r="V17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W17" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X17" s="36" t="n">
         <v>5</v>
       </c>
@@ -5049,30 +5281,42 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="36" t="n"/>
+      <c r="Z17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA17" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB17" s="35" t="n"/>
+      <c r="AB17" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC17" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD17" s="36" t="n"/>
+          <t>Cogmed; factors app</t>
+        </is>
+      </c>
+      <c r="AD17" s="36" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG17" s="36" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH17" s="36" t="inlineStr">
@@ -5082,13 +5326,17 @@
       </c>
       <c r="AI17" s="36" t="inlineStr">
         <is>
-          <t>Processing speed; Executive function</t>
-        </is>
-      </c>
-      <c r="AJ17" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ17" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK17" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL17" s="36" t="inlineStr">
@@ -5098,13 +5346,17 @@
       </c>
       <c r="AM17" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN17" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN17" s="35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
       <c r="AO17" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP17" s="36" t="inlineStr">
@@ -5112,35 +5364,51 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ17" s="36" t="n"/>
-      <c r="AR17" s="36" t="n"/>
+      <c r="AQ17" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR17" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS17" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT17" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU17" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV17" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY17" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV17" s="35" t="n"/>
-      <c r="AW17" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX17" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY17" s="36" t="n"/>
       <c r="AZ17" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5148,14 +5416,22 @@
       </c>
       <c r="BA17" s="36" t="inlineStr">
         <is>
-          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
-        </is>
-      </c>
-      <c r="BB17" s="36" t="n"/>
-      <c r="BC17" s="36" t="n"/>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85) | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB17" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC17" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD17" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE17" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E18" s="38" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F18" s="38" t="inlineStr">
@@ -5469,34 +5469,44 @@
       </c>
       <c r="G18" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H18" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="38" t="n"/>
-      <c r="J18" s="38" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="I18" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="n">
-        <v>66.06999999999999</v>
+        <v>25.9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M18" s="38" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="N18" s="38" t="n">
-        <v>67</v>
+      <c r="M18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O18" s="38" t="n">
-        <v>16.14</v>
+        <v>2</v>
       </c>
       <c r="P18" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE≥2; Mini-Mental</t>
         </is>
       </c>
       <c r="Q18" s="38" t="inlineStr">
@@ -5511,7 +5521,7 @@
       </c>
       <c r="S18" s="38" t="inlineStr">
         <is>
-          <t>Adaptive n-back (0-5 back)</t>
+          <t>wome; engage</t>
         </is>
       </c>
       <c r="T18" s="38" t="inlineStr">
@@ -5525,7 +5535,11 @@
       <c r="V18" s="38" t="n">
         <v>45</v>
       </c>
-      <c r="W18" s="37" t="n"/>
+      <c r="W18" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X18" s="38" t="n">
         <v>4</v>
       </c>
@@ -5534,19 +5548,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z18" s="38" t="n"/>
+      <c r="Z18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA18" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB18" s="37" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB18" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC18" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD18" s="38" t="n"/>
+          <t>novel app</t>
+        </is>
+      </c>
+      <c r="AD18" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE18" t="n">
         <v>3</v>
       </c>
@@ -5557,7 +5583,7 @@
       </c>
       <c r="AG18" s="38" t="inlineStr">
         <is>
-          <t>Digit Span (backward)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH18" s="38" t="inlineStr">
@@ -5567,13 +5593,17 @@
       </c>
       <c r="AI18" s="38" t="inlineStr">
         <is>
-          <t>CERAD episodic memory; Processing speed (LPS)</t>
-        </is>
-      </c>
-      <c r="AJ18" s="38" t="n"/>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ18" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK18" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL18" s="38" t="inlineStr">
@@ -5588,24 +5618,32 @@
       </c>
       <c r="AN18" s="37" t="inlineStr">
         <is>
-          <t>d=0.78(教育组间)</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO18" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP18" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ18" s="38" t="n"/>
-      <c r="AR18" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ18" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS18" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT18" s="38" t="inlineStr">
@@ -5615,10 +5653,14 @@
       </c>
       <c r="AU18" s="38" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
-        </is>
-      </c>
-      <c r="AV18" s="37" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV18" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW18" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -5626,10 +5668,14 @@
       </c>
       <c r="AX18" s="38" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY18" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY18" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ18" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5637,14 +5683,22 @@
       </c>
       <c r="BA18" s="38" t="inlineStr">
         <is>
-          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
-        </is>
-      </c>
-      <c r="BB18" s="38" t="n"/>
-      <c r="BC18" s="38" t="n"/>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB18" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC18" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD18" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE18" s="40" t="inlineStr">
@@ -5672,7 +5726,7 @@
       </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
-          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F19" s="36" t="inlineStr">
@@ -5682,14 +5736,24 @@
       </c>
       <c r="G19" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>36</v>
-      </c>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -5702,7 +5766,7 @@
       </c>
       <c r="N19" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="O19" s="36" t="inlineStr">
@@ -5712,7 +5776,7 @@
       </c>
       <c r="P19" s="36" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>Mini-Mental</t>
         </is>
       </c>
       <c r="Q19" s="36" t="inlineStr">
@@ -5722,12 +5786,12 @@
       </c>
       <c r="R19" s="36" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S19" s="36" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>wome; engage; Spatial n-back</t>
         </is>
       </c>
       <c r="T19" s="36" t="inlineStr">
@@ -5736,33 +5800,51 @@
         </is>
       </c>
       <c r="U19" s="36" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="W19" s="35" t="n"/>
-      <c r="X19" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="W19" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y19" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z19" s="36" t="n"/>
+      <c r="Z19" s="36" t="inlineStr">
+        <is>
+          <t>alternative activities (see below)</t>
+        </is>
+      </c>
       <c r="AA19" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB19" s="35" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB19" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC19" s="36" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
-        </is>
-      </c>
-      <c r="AD19" s="36" t="n"/>
+          <t>training program; Venezia 8</t>
+        </is>
+      </c>
+      <c r="AD19" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE19" t="n">
         <v>1.5</v>
       </c>
@@ -5773,7 +5855,12 @@
       </c>
       <c r="AG19" s="36" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>two-
+back task
+45 daily
+sessions
+3 months
+70–80 (M ¼ 74</t>
         </is>
       </c>
       <c r="AH19" s="36" t="inlineStr">
@@ -5783,27 +5870,40 @@
       </c>
       <c r="AI19" s="36" t="inlineStr">
         <is>
-          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
-        </is>
-      </c>
-      <c r="AJ19" s="36" t="n"/>
+          <t>two-
+back task
+45 daily
+sessions
+3 months
+70–80 (M ¼ 74</t>
+        </is>
+      </c>
+      <c r="AJ19" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK19" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="AL19" s="36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AM19" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN19" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN19" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO19" s="36" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP19" s="36" t="inlineStr">
@@ -5811,8 +5911,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ19" s="36" t="n"/>
-      <c r="AR19" s="36" t="n"/>
+      <c r="AQ19" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR19" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS19" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -5828,18 +5936,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV19" s="35" t="n"/>
+      <c r="AV19" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW19" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX19" s="36" t="inlineStr">
         <is>
-          <t>词汇测试</t>
-        </is>
-      </c>
-      <c r="AY19" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY19" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ19" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5850,11 +5966,19 @@
           <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
         </is>
       </c>
-      <c r="BB19" s="36" t="n"/>
-      <c r="BC19" s="36" t="n"/>
+      <c r="BB19" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC19" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD19" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE19" s="40" t="inlineStr">
@@ -5882,7 +6006,7 @@
       </c>
       <c r="E20" s="38" t="inlineStr">
         <is>
-          <t>Cognitive processing</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F20" s="38" t="inlineStr">
@@ -5892,34 +6016,50 @@
       </c>
       <c r="G20" s="38" t="inlineStr">
         <is>
-          <t>医院/社区</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H20" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="38" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="38" t="n">
-        <v>68.40000000000001</v>
+        <v>15</v>
+      </c>
+      <c r="I20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M20" s="38" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="N20" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="O20" s="38" t="n">
-        <v>11.9</v>
+      <c r="M20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P20" s="38" t="inlineStr">
         <is>
-          <t>MMSE+CDT</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q20" s="38" t="inlineStr">
@@ -5934,55 +6074,72 @@
       </c>
       <c r="S20" s="38" t="inlineStr">
         <is>
-          <t>N-back (0-2 back, adaptive)</t>
+          <t>Dual N-back; wome; engage; spatial 
+n-back</t>
         </is>
       </c>
       <c r="T20" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U20" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="38" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="W20" s="37" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="V20" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W20" s="37" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="X20" s="38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y20" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z20" s="38" t="n"/>
+      <c r="Z20" s="38" t="inlineStr">
+        <is>
+          <t>not reach statistical significance on 
+the post-test Forward Digit Span (F(1, 14) = 0</t>
+        </is>
+      </c>
       <c r="AA20" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB20" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB20" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC20" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD20" s="38" t="n"/>
+          <t>training 
+program; the 1964</t>
+        </is>
+      </c>
+      <c r="AD20" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE20" t="n">
         <v>2</v>
       </c>
       <c r="AF20" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG20" s="38" t="inlineStr">
         <is>
-          <t>Corsi Block; Digit Span</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH20" s="38" t="inlineStr">
@@ -5990,11 +6147,20 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI20" s="38" t="n"/>
-      <c r="AJ20" s="38" t="n"/>
+      <c r="AI20" s="38" t="inlineStr">
+        <is>
+          <t>switch-
+ing training</t>
+        </is>
+      </c>
+      <c r="AJ20" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK20" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL20" s="38" t="inlineStr">
@@ -6009,21 +6175,31 @@
       </c>
       <c r="AN20" s="37" t="inlineStr">
         <is>
-          <t>d=2.21(近迁移)</t>
+          <t>未报告具体d值</t>
         </is>
       </c>
       <c r="AO20" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP20" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ20" s="38" t="n"/>
-      <c r="AR20" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ20" s="38" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="AR20" s="38" t="inlineStr">
+        <is>
+          <t>imaging studies sup-
+port cognitive training as able to enhance activity in brain 
+Handling editor: Stefano Federici (University of Perugia).</t>
+        </is>
+      </c>
       <c r="AS20" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6039,18 +6215,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV20" s="37" t="n"/>
+      <c r="AV20" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW20" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX20" s="38" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY20" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY20" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ20" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6058,14 +6242,22 @@
       </c>
       <c r="BA20" s="38" t="inlineStr">
         <is>
-          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
-        </is>
-      </c>
-      <c r="BB20" s="38" t="n"/>
-      <c r="BC20" s="38" t="n"/>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21) | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB20" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC20" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD20" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE20" s="40" t="inlineStr">
@@ -6093,7 +6285,7 @@
       </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
-          <t>International journal of aging &amp; human development</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F21" s="36" t="inlineStr">
@@ -6103,27 +6295,41 @@
       </c>
       <c r="G21" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>86</v>
-      </c>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K21" s="36" t="n">
-        <v>68.55</v>
+        <v>83</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M21" s="36" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>58</v>
+      <c r="M21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N21" s="36" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
       <c r="O21" s="36" t="inlineStr">
         <is>
@@ -6132,7 +6338,7 @@
       </c>
       <c r="P21" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Mini-Mental</t>
         </is>
       </c>
       <c r="Q21" s="36" t="inlineStr">
@@ -6142,12 +6348,12 @@
       </c>
       <c r="R21" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S21" s="36" t="inlineStr">
         <is>
-          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="T21" s="36" t="inlineStr">
@@ -6155,45 +6361,65 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U21" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V21" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="W21" s="35" t="n"/>
+      <c r="U21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W21" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X21" s="36" t="n">
         <v>10</v>
       </c>
       <c r="Y21" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z21" s="36" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA21" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB21" s="35" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB21" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
       <c r="AC21" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD21" s="36" t="n"/>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD21" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG21" s="36" t="inlineStr">
         <is>
-          <t>Spatial WM (untrained)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH21" s="36" t="inlineStr">
@@ -6203,13 +6429,17 @@
       </c>
       <c r="AI21" s="36" t="inlineStr">
         <is>
-          <t>Reasoning; IADL (everyday function)</t>
-        </is>
-      </c>
-      <c r="AJ21" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ21" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK21" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL21" s="36" t="inlineStr">
@@ -6225,7 +6455,7 @@
       <c r="AN21" s="35" t="n"/>
       <c r="AO21" s="36" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP21" s="36" t="inlineStr">
@@ -6233,8 +6463,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ21" s="36" t="n"/>
-      <c r="AR21" s="36" t="n"/>
+      <c r="AQ21" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR21" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS21" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6250,7 +6488,11 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV21" s="35" t="n"/>
+      <c r="AV21" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW21" s="36" t="inlineStr">
         <is>
           <t>否</t>
@@ -6261,7 +6503,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY21" s="36" t="n"/>
+      <c r="AY21" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ21" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6269,14 +6515,22 @@
       </c>
       <c r="BA21" s="36" t="inlineStr">
         <is>
-          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
-        </is>
-      </c>
-      <c r="BB21" s="36" t="n"/>
-      <c r="BC21" s="36" t="n"/>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛 | 待核查：无法确定对照类型 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB21" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC21" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD21" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE21" s="40" t="inlineStr">
@@ -6304,7 +6558,7 @@
       </c>
       <c r="E22" s="38" t="inlineStr">
         <is>
-          <t>GeroScience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F22" s="38" t="inlineStr">
@@ -6314,14 +6568,20 @@
       </c>
       <c r="G22" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H22" s="38" t="n">
-        <v>62</v>
-      </c>
-      <c r="I22" s="38" t="n"/>
-      <c r="J22" s="38" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="n">
         <v>71</v>
       </c>
@@ -6331,13 +6591,15 @@
         </is>
       </c>
       <c r="M22" s="38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N22" s="38" t="n">
-        <v>68</v>
+        <v>2.3</v>
+      </c>
+      <c r="N22" s="38" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
       </c>
       <c r="O22" s="38" t="n">
-        <v>16.3</v>
+        <v>4.4</v>
       </c>
       <c r="P22" s="38" t="inlineStr">
         <is>
@@ -6351,12 +6613,12 @@
       </c>
       <c r="R22" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S22" s="38" t="inlineStr">
         <is>
-          <t>Multidomain cognitive training (WM+processing speed)</t>
+          <t>BrainHQ; engage</t>
         </is>
       </c>
       <c r="T22" s="38" t="inlineStr">
@@ -6364,34 +6626,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U22" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="V22" s="38" t="n">
-        <v>45</v>
-      </c>
-      <c r="W22" s="37" t="n"/>
+      <c r="U22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W22" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X22" s="38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z22" s="38" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA22" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB22" s="37" t="n"/>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB22" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC22" s="38" t="inlineStr">
         <is>
-          <t>自制(tablet-based)</t>
-        </is>
-      </c>
-      <c r="AD22" s="38" t="n"/>
+          <t>Posit 
+Science; Interdisciplinary Program</t>
+        </is>
+      </c>
+      <c r="AD22" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE22" t="n">
         <v>1.7</v>
       </c>
@@ -6402,7 +6685,8 @@
       </c>
       <c r="AG22" s="38" t="inlineStr">
         <is>
-          <t>WM tasks (proximal)</t>
+          <t>was the most reliable and robust 
+method for assessing cognitive training efficac</t>
         </is>
       </c>
       <c r="AH22" s="38" t="inlineStr">
@@ -6410,11 +6694,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI22" s="38" t="n"/>
-      <c r="AJ22" s="38" t="n"/>
+      <c r="AI22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ22" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK22" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL22" s="38" t="inlineStr">
@@ -6424,13 +6716,17 @@
       </c>
       <c r="AM22" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN22" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN22" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO22" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP22" s="38" t="inlineStr">
@@ -6440,41 +6736,51 @@
       </c>
       <c r="AQ22" s="38" t="inlineStr">
         <is>
-          <t>fMRI(sMRI)</t>
+          <t>MRI</t>
         </is>
       </c>
       <c r="AR22" s="38" t="inlineStr">
         <is>
-          <t>白质高信号负荷高者训练获益更少</t>
+          <t>brain white matter 
+hyperintensity load, or total lesion volume (TLV), 
+on pre-post proximal training change.</t>
         </is>
       </c>
       <c r="AS22" s="38" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AT22" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU22" s="38" t="inlineStr">
         <is>
-          <t>低&gt;高(低WMH获益更多)</t>
-        </is>
-      </c>
-      <c r="AV22" s="37" t="n"/>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV22" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW22" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX22" s="38" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY22" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY22" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ22" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6482,14 +6788,22 @@
       </c>
       <c r="BA22" s="38" t="inlineStr">
         <is>
-          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
-        </is>
-      </c>
-      <c r="BB22" s="38" t="n"/>
-      <c r="BC22" s="38" t="n"/>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB22" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC22" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD22" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE22" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -6831,7 +6831,7 @@
       </c>
       <c r="E23" s="36" t="inlineStr">
         <is>
-          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F23" s="36" t="inlineStr">
@@ -6847,8 +6847,16 @@
       <c r="H23" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
+      <c r="I23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K23" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6864,14 +6872,12 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="O23" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="O23" s="36" t="n">
+        <v>15</v>
       </c>
       <c r="P23" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="Q23" s="36" t="inlineStr">
@@ -6886,7 +6892,7 @@
       </c>
       <c r="S23" s="36" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>Dual N-back; engage</t>
         </is>
       </c>
       <c r="T23" s="36" t="inlineStr">
@@ -6895,33 +6901,53 @@
         </is>
       </c>
       <c r="U23" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="V23" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W23" s="35" t="n"/>
-      <c r="X23" s="36" t="n">
-        <v>6</v>
+        <v>25</v>
+      </c>
+      <c r="V23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W23" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y23" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z23" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA23" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB23" s="35" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB23" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AC23" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD23" s="36" t="n"/>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD23" s="36" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
@@ -6932,7 +6958,7 @@
       </c>
       <c r="AG23" s="36" t="inlineStr">
         <is>
-          <t>Listening Span</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH23" s="36" t="inlineStr">
@@ -6940,11 +6966,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI23" s="36" t="n"/>
-      <c r="AJ23" s="36" t="n"/>
+      <c r="AI23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ23" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK23" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL23" s="36" t="inlineStr">
@@ -6954,13 +6988,17 @@
       </c>
       <c r="AM23" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN23" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN23" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO23" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP23" s="36" t="inlineStr">
@@ -6970,17 +7008,20 @@
       </c>
       <c r="AQ23" s="36" t="inlineStr">
         <is>
-          <t>fMRI</t>
+          <t>fMRI/MRI</t>
         </is>
       </c>
       <c r="AR23" s="36" t="inlineStr">
         <is>
-          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+          <t xml:space="preserve">brain activation linked with greater
+cognitive training gains in older adults: Insights
+from the ACTOP study
+Lynn Valeyry Verty a,b, Samira Mellah a, </t>
         </is>
       </c>
       <c r="AS23" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT23" s="36" t="inlineStr">
@@ -6990,13 +7031,17 @@
       </c>
       <c r="AU23" s="36" t="inlineStr">
         <is>
-          <t>高&gt;低(类年轻激活者获益更多)</t>
-        </is>
-      </c>
-      <c r="AV23" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV23" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW23" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX23" s="36" t="inlineStr">
@@ -7004,7 +7049,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY23" s="36" t="n"/>
+      <c r="AY23" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ23" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7012,14 +7061,22 @@
       </c>
       <c r="BA23" s="36" t="inlineStr">
         <is>
-          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
-        </is>
-      </c>
-      <c r="BB23" s="36" t="n"/>
-      <c r="BC23" s="36" t="n"/>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB23" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC23" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD23" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE23" s="40" t="inlineStr">
@@ -7047,7 +7104,7 @@
       </c>
       <c r="E24" s="38" t="inlineStr">
         <is>
-          <t>Attention, perception &amp; psychophysics</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F24" s="38" t="inlineStr">
@@ -7057,16 +7114,24 @@
       </c>
       <c r="G24" s="38" t="inlineStr">
         <is>
-          <t>社区(在线)</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H24" s="38" t="n">
-        <v>104</v>
-      </c>
-      <c r="I24" s="38" t="n"/>
-      <c r="J24" s="38" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K24" s="38" t="n">
-        <v>68.2</v>
+        <v>68.25</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -7074,10 +7139,12 @@
         </is>
       </c>
       <c r="M24" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" s="38" t="n">
-        <v>48</v>
+        <v>68.25</v>
+      </c>
+      <c r="N24" s="38" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
       </c>
       <c r="O24" s="38" t="inlineStr">
         <is>
@@ -7101,7 +7168,7 @@
       </c>
       <c r="S24" s="38" t="inlineStr">
         <is>
-          <t>DMTS (delayed match-to-sample); Enumeration</t>
+          <t>engage</t>
         </is>
       </c>
       <c r="T24" s="38" t="inlineStr">
@@ -7110,44 +7177,65 @@
         </is>
       </c>
       <c r="U24" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="V24" s="38" t="n">
-        <v>45</v>
-      </c>
-      <c r="W24" s="37" t="n"/>
-      <c r="X24" s="38" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="V24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W24" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y24" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z24" s="38" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA24" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB24" s="37" t="n"/>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB24" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC24" s="38" t="inlineStr">
         <is>
-          <t>自制(在线)</t>
-        </is>
-      </c>
-      <c r="AD24" s="38" t="n"/>
+          <t>at app; the
+2013</t>
+        </is>
+      </c>
+      <c r="AD24" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE24" t="n">
         <v>2.5</v>
       </c>
       <c r="AF24" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG24" s="38" t="inlineStr">
         <is>
-          <t>DMTS (visuospatial WM, k值)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH24" s="38" t="inlineStr">
@@ -7155,50 +7243,79 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI24" s="38" t="n"/>
-      <c r="AJ24" s="38" t="n"/>
+      <c r="AI24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ24" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK24" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL24" s="38" t="n">
-        <v>3</v>
+      <c r="AL24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AM24" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN24" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN24" s="37" t="inlineStr">
+        <is>
+          <t>.54</t>
+        </is>
+      </c>
       <c r="AO24" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP24" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ24" s="38" t="n"/>
-      <c r="AR24" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ24" s="38" t="inlineStr">
+        <is>
+          <t>EEG/ERP/MRI</t>
+        </is>
+      </c>
+      <c r="AR24" s="38" t="inlineStr">
+        <is>
+          <t>EEG data
+indicated that the practice-related increase in vWM capacity
+observed in older adults was accompanied by neural modifi-
+cations not only duri</t>
+        </is>
+      </c>
       <c r="AS24" s="38" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT24" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU24" s="38" t="inlineStr">
         <is>
-          <t>低&gt;高(低WM基线者获益更多)</t>
-        </is>
-      </c>
-      <c r="AV24" s="37" t="n"/>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV24" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW24" s="38" t="inlineStr">
         <is>
           <t>否</t>
@@ -7206,10 +7323,14 @@
       </c>
       <c r="AX24" s="38" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY24" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY24" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ24" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7217,14 +7338,22 @@
       </c>
       <c r="BA24" s="38" t="inlineStr">
         <is>
-          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
-        </is>
-      </c>
-      <c r="BB24" s="38" t="n"/>
-      <c r="BC24" s="38" t="n"/>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB24" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC24" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD24" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE24" s="40" t="inlineStr">
@@ -7252,7 +7381,7 @@
       </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
-          <t>Developmental psychology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F25" s="36" t="inlineStr">
@@ -7262,27 +7391,41 @@
       </c>
       <c r="G25" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H25" s="36" t="n">
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K25" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="I25" s="36" t="n"/>
-      <c r="J25" s="36" t="n"/>
-      <c r="K25" s="36" t="n">
-        <v>77.2</v>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>old-old</t>
         </is>
       </c>
-      <c r="M25" s="36" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="N25" s="36" t="n">
-        <v>80</v>
+      <c r="M25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O25" s="36" t="inlineStr">
         <is>
@@ -7291,7 +7434,7 @@
       </c>
       <c r="P25" s="36" t="inlineStr">
         <is>
-          <t>MMST</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Q25" s="36" t="inlineStr">
@@ -7301,12 +7444,12 @@
       </c>
       <c r="R25" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S25" s="36" t="inlineStr">
         <is>
-          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+          <t>engage; complex span; spatial n-back</t>
         </is>
       </c>
       <c r="T25" s="36" t="inlineStr">
@@ -7320,7 +7463,11 @@
       <c r="V25" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="W25" s="35" t="n"/>
+      <c r="W25" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X25" s="36" t="n">
         <v>3</v>
       </c>
@@ -7329,19 +7476,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z25" s="36" t="n"/>
+      <c r="Z25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA25" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB25" s="35" t="n"/>
+      <c r="AB25" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
       <c r="AC25" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD25" s="36" t="n"/>
+          <t>based app</t>
+        </is>
+      </c>
+      <c r="AD25" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE25" t="n">
         <v>3</v>
       </c>
@@ -7352,7 +7511,7 @@
       </c>
       <c r="AG25" s="36" t="inlineStr">
         <is>
-          <t>Verbal WM (untrained)</t>
+          <t>and far transfer to a fluid intelligence task</t>
         </is>
       </c>
       <c r="AH25" s="36" t="inlineStr">
@@ -7362,10 +7521,14 @@
       </c>
       <c r="AI25" s="36" t="inlineStr">
         <is>
-          <t>Processing speed; Reasoning</t>
-        </is>
-      </c>
-      <c r="AJ25" s="36" t="n"/>
+          <t>has been found</t>
+        </is>
+      </c>
+      <c r="AJ25" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK25" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -7376,10 +7539,14 @@
       </c>
       <c r="AM25" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN25" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN25" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO25" s="36" t="inlineStr">
         <is>
           <t>混合</t>
@@ -7387,14 +7554,23 @@
       </c>
       <c r="AP25" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ25" s="36" t="n"/>
-      <c r="AR25" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ25" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR25" s="36" t="inlineStr">
+        <is>
+          <t>brain activity in frontal and parietal cortex and basal
+ganglia and changes in dopamine receptor density (Brehmer et al.</t>
+        </is>
+      </c>
       <c r="AS25" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT25" s="36" t="inlineStr">
@@ -7404,10 +7580,14 @@
       </c>
       <c r="AU25" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高(低基线者近迁移更大)</t>
-        </is>
-      </c>
-      <c r="AV25" s="35" t="n"/>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AV25" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW25" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -7418,7 +7598,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY25" s="36" t="n"/>
+      <c r="AY25" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ25" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7429,11 +7613,19 @@
           <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
         </is>
       </c>
-      <c r="BB25" s="36" t="n"/>
-      <c r="BC25" s="36" t="n"/>
+      <c r="BB25" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC25" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD25" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE25" s="40" t="inlineStr">
@@ -7461,7 +7653,7 @@
       </c>
       <c r="E26" s="38" t="inlineStr">
         <is>
-          <t>Current aging science</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F26" s="38" t="inlineStr">
@@ -7471,24 +7663,34 @@
       </c>
       <c r="G26" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H26" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="I26" s="38" t="n"/>
-      <c r="J26" s="38" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K26" s="38" t="n">
-        <v>80.5</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>old-old</t>
         </is>
       </c>
-      <c r="M26" s="38" t="n">
-        <v>6.4</v>
+      <c r="M26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
@@ -7502,7 +7704,7 @@
       </c>
       <c r="P26" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q26" s="38" t="inlineStr">
@@ -7517,7 +7719,7 @@
       </c>
       <c r="S26" s="38" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>dual n-back; single n-back; wome; engage; verbal n-back</t>
         </is>
       </c>
       <c r="T26" s="38" t="inlineStr">
@@ -7531,28 +7733,46 @@
       <c r="V26" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="W26" s="37" t="n"/>
-      <c r="X26" s="38" t="n">
-        <v>5</v>
+      <c r="W26" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y26" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z26" s="38" t="n"/>
+      <c r="Z26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA26" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB26" s="37" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB26" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC26" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD26" s="38" t="n"/>
+          <t>becoming app</t>
+        </is>
+      </c>
+      <c r="AD26" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
@@ -7563,7 +7783,7 @@
       </c>
       <c r="AG26" s="38" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH26" s="38" t="inlineStr">
@@ -7571,11 +7791,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI26" s="38" t="n"/>
-      <c r="AJ26" s="38" t="n"/>
+      <c r="AI26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ26" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK26" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL26" s="38" t="inlineStr">
@@ -7591,16 +7819,24 @@
       <c r="AN26" s="37" t="n"/>
       <c r="AO26" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP26" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ26" s="38" t="n"/>
-      <c r="AR26" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ26" s="38" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="AR26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS26" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7613,21 +7849,29 @@
       </c>
       <c r="AU26" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV26" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY26" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV26" s="37" t="n"/>
-      <c r="AW26" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX26" s="38" t="inlineStr">
-        <is>
-          <t>CRI(认知储备指数)</t>
-        </is>
-      </c>
-      <c r="AY26" s="38" t="n"/>
       <c r="AZ26" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7635,14 +7879,22 @@
       </c>
       <c r="BA26" s="38" t="inlineStr">
         <is>
-          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
-        </is>
-      </c>
-      <c r="BB26" s="38" t="n"/>
-      <c r="BC26" s="38" t="n"/>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁) | 待核查</t>
+        </is>
+      </c>
+      <c r="BB26" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC26" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD26" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE26" s="40" t="inlineStr">
@@ -7670,7 +7922,7 @@
       </c>
       <c r="E27" s="36" t="inlineStr">
         <is>
-          <t>BMC research notes</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F27" s="36" t="inlineStr">
@@ -7680,14 +7932,20 @@
       </c>
       <c r="G27" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H27" s="36" t="n">
-        <v>54</v>
-      </c>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="I27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J27" s="36" t="n">
+        <v>22</v>
+      </c>
       <c r="K27" s="36" t="n">
         <v>66.40000000000001</v>
       </c>
@@ -7696,11 +7954,15 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M27" s="36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N27" s="36" t="n">
-        <v>88</v>
+      <c r="M27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O27" s="36" t="inlineStr">
         <is>
@@ -7709,7 +7971,7 @@
       </c>
       <c r="P27" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q27" s="36" t="inlineStr">
@@ -7724,7 +7986,8 @@
       </c>
       <c r="S27" s="36" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>wome; Operation Span; complex 
+span</t>
         </is>
       </c>
       <c r="T27" s="36" t="inlineStr">
@@ -7738,28 +8001,46 @@
       <c r="V27" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="W27" s="35" t="n"/>
-      <c r="X27" s="36" t="n">
-        <v>4</v>
+      <c r="W27" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y27" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z27" s="36" t="n"/>
+      <c r="Z27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA27" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB27" s="35" t="n"/>
+          <t>TMS/运动</t>
+        </is>
+      </c>
+      <c r="AB27" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
       <c r="AC27" s="36" t="inlineStr">
         <is>
-          <t>PsychoPy自制</t>
-        </is>
-      </c>
-      <c r="AD27" s="36" t="n"/>
+          <t>give app; the 1964</t>
+        </is>
+      </c>
+      <c r="AD27" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE27" t="n">
         <v>3</v>
       </c>
@@ -7770,7 +8051,9 @@
       </c>
       <c r="AG27" s="36" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>involving analogi­
+cal reasoning) to the performance of a test measuring 
+fluid i</t>
         </is>
       </c>
       <c r="AH27" s="36" t="inlineStr">
@@ -7780,10 +8063,14 @@
       </c>
       <c r="AI27" s="36" t="inlineStr">
         <is>
-          <t>Digit Span; Corsi; Stroop</t>
-        </is>
-      </c>
-      <c r="AJ27" s="36" t="n"/>
+          <t>to other cognitive tasks</t>
+        </is>
+      </c>
+      <c r="AJ27" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆</t>
+        </is>
+      </c>
       <c r="AK27" s="36" t="inlineStr">
         <is>
           <t>否</t>
@@ -7791,31 +8078,38 @@
       </c>
       <c r="AL27" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>无</t>
         </is>
       </c>
       <c r="AM27" s="35" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN27" s="35" t="inlineStr">
-        <is>
-          <t>η²p=0.05(训练×年龄交互)</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AN27" s="35" t="n"/>
       <c r="AO27" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP27" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ27" s="36" t="n"/>
-      <c r="AR27" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ27" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR27" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brain activity (National Sci­
+ence Centre, Poland, grant no 2017/25/B/HS6/00360), 
+we also examined the magnitude of improvement in the 
+trained task </t>
+        </is>
+      </c>
       <c r="AS27" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7828,10 +8122,14 @@
       </c>
       <c r="AU27" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
-        </is>
-      </c>
-      <c r="AV27" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV27" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AW27" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -7842,7 +8140,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY27" s="36" t="n"/>
+      <c r="AY27" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ27" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7850,14 +8152,22 @@
       </c>
       <c r="BA27" s="36" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
-        </is>
-      </c>
-      <c r="BB27" s="36" t="n"/>
-      <c r="BC27" s="36" t="n"/>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB27" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC27" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD27" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE27" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -8195,7 +8195,7 @@
       </c>
       <c r="E28" s="38" t="inlineStr">
         <is>
-          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F28" s="38" t="inlineStr">
@@ -8205,18 +8205,22 @@
       </c>
       <c r="G28" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H28" s="38" t="n">
-        <v>183</v>
-      </c>
-      <c r="I28" s="38" t="n"/>
-      <c r="J28" s="38" t="n"/>
-      <c r="K28" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="I28" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K28" s="38" t="n">
+        <v>21.45</v>
       </c>
       <c r="M28" s="38" t="inlineStr">
         <is>
@@ -8235,7 +8239,7 @@
       </c>
       <c r="P28" s="38" t="inlineStr">
         <is>
-          <t>GDS+GAD</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q28" s="38" t="inlineStr">
@@ -8250,7 +8254,7 @@
       </c>
       <c r="S28" s="38" t="inlineStr">
         <is>
-          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+          <t>complex span; Spatial N-back</t>
         </is>
       </c>
       <c r="T28" s="38" t="inlineStr">
@@ -8263,33 +8267,49 @@
       </c>
       <c r="V28" s="38" t="inlineStr">
         <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="W28" s="37" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W28" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X28" s="38" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y28" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z28" s="38" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA28" s="38" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB28" s="37" t="n"/>
+      <c r="AB28" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA/MANOVA</t>
+        </is>
+      </c>
       <c r="AC28" s="38" t="inlineStr">
         <is>
-          <t>自制(tablet)</t>
-        </is>
-      </c>
-      <c r="AD28" s="38" t="n"/>
+          <t>most app; five 12</t>
+        </is>
+      </c>
+      <c r="AD28" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AF28" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -8297,7 +8317,7 @@
       </c>
       <c r="AG28" s="38" t="inlineStr">
         <is>
-          <t>Reading Span; Symmetry Span</t>
+          <t>also via tablet devices</t>
         </is>
       </c>
       <c r="AH28" s="38" t="inlineStr">
@@ -8307,10 +8327,14 @@
       </c>
       <c r="AI28" s="38" t="inlineStr">
         <is>
-          <t>Letter Sets; Visual LTM</t>
-        </is>
-      </c>
-      <c r="AJ28" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ28" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK28" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -8321,10 +8345,14 @@
       </c>
       <c r="AM28" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN28" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN28" s="37" t="inlineStr">
+        <is>
+          <t>.72</t>
+        </is>
+      </c>
       <c r="AO28" s="38" t="inlineStr">
         <is>
           <t>混合</t>
@@ -8332,14 +8360,22 @@
       </c>
       <c r="AP28" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ28" s="38" t="n"/>
-      <c r="AR28" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ28" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS28" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT28" s="38" t="inlineStr">
@@ -8349,21 +8385,29 @@
       </c>
       <c r="AU28" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV28" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY28" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV28" s="37" t="n"/>
-      <c r="AW28" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX28" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY28" s="38" t="n"/>
       <c r="AZ28" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8371,14 +8415,22 @@
       </c>
       <c r="BA28" s="38" t="inlineStr">
         <is>
-          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
-        </is>
-      </c>
-      <c r="BB28" s="38" t="n"/>
-      <c r="BC28" s="38" t="n"/>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告 | 待核查：无法确定对照类型 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB28" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC28" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD28" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE28" s="40" t="inlineStr">
@@ -8406,7 +8458,7 @@
       </c>
       <c r="E29" s="36" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F29" s="36" t="inlineStr">
@@ -8420,24 +8472,38 @@
         </is>
       </c>
       <c r="H29" s="36" t="n">
-        <v>65</v>
-      </c>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="n"/>
-      <c r="K29" s="36" t="n">
-        <v>70.8</v>
+        <v>22</v>
+      </c>
+      <c r="I29" s="36" t="n">
+        <v>44</v>
+      </c>
+      <c r="J29" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M29" s="36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N29" s="36" t="n"/>
-      <c r="O29" s="36" t="n">
-        <v>13.2</v>
+      <c r="M29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P29" s="36" t="inlineStr">
         <is>
@@ -8456,7 +8522,8 @@
       </c>
       <c r="S29" s="36" t="inlineStr">
         <is>
-          <t>verbal n-back</t>
+          <t>dual N-back; wome; Reading Span; verbal N-back; spatial
+N-back</t>
         </is>
       </c>
       <c r="T29" s="36" t="inlineStr">
@@ -8467,13 +8534,19 @@
       <c r="U29" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="V29" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W29" s="35" t="n"/>
+      <c r="V29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W29" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X29" s="36" t="inlineStr">
         <is>
-          <t>2-4周</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y29" s="36" t="inlineStr">
@@ -8481,19 +8554,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z29" s="36" t="n"/>
+      <c r="Z29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA29" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB29" s="35" t="n"/>
+      <c r="AB29" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC29" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD29" s="36" t="n"/>
+          <t>frequently app</t>
+        </is>
+      </c>
+      <c r="AD29" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF29" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -8501,7 +8586,7 @@
       </c>
       <c r="AG29" s="36" t="inlineStr">
         <is>
-          <t>spatial n-back</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH29" s="36" t="inlineStr">
@@ -8511,13 +8596,17 @@
       </c>
       <c r="AI29" s="36" t="inlineStr">
         <is>
-          <t>fluid intelligence (Raven)</t>
-        </is>
-      </c>
-      <c r="AJ29" s="36" t="n"/>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ29" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK29" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL29" s="36" t="inlineStr">
@@ -8527,38 +8616,54 @@
       </c>
       <c r="AM29" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN29" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN29" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO29" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP29" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ29" s="36" t="n"/>
-      <c r="AR29" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ29" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AS29" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AT29" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU29" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV29" s="35" t="n"/>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV29" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW29" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -8566,10 +8671,14 @@
       </c>
       <c r="AX29" s="36" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY29" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY29" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ29" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8577,14 +8686,22 @@
       </c>
       <c r="BA29" s="36" t="inlineStr">
         <is>
-          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
-        </is>
-      </c>
-      <c r="BB29" s="36" t="n"/>
-      <c r="BC29" s="36" t="n"/>
+          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB29" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC29" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD29" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE29" s="40" t="inlineStr">
@@ -8612,7 +8729,7 @@
       </c>
       <c r="E30" s="38" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F30" s="38" t="inlineStr">
@@ -8626,28 +8743,46 @@
         </is>
       </c>
       <c r="H30" s="38" t="n">
-        <v>36</v>
-      </c>
-      <c r="I30" s="38" t="n"/>
-      <c r="J30" s="38" t="n"/>
-      <c r="K30" s="38" t="n">
-        <v>69.5</v>
+        <v>18</v>
+      </c>
+      <c r="I30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M30" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" s="38" t="n"/>
-      <c r="O30" s="38" t="n">
-        <v>11</v>
+      <c r="M30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P30" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Mini-Mental</t>
         </is>
       </c>
       <c r="Q30" s="38" t="inlineStr">
@@ -8662,42 +8797,63 @@
       </c>
       <c r="S30" s="38" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>complex
+span</t>
         </is>
       </c>
       <c r="T30" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U30" s="38" t="n">
-        <v>6</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V30" s="38" t="n">
         <v>30</v>
       </c>
-      <c r="W30" s="37" t="n"/>
-      <c r="X30" s="38" t="n">
-        <v>3</v>
+      <c r="W30" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y30" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z30" s="38" t="n"/>
+      <c r="Z30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA30" s="38" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB30" s="37" t="n"/>
+      <c r="AB30" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC30" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD30" s="38" t="n"/>
+          <t>instruments app</t>
+        </is>
+      </c>
+      <c r="AD30" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE30" t="n">
         <v>2</v>
       </c>
@@ -8708,7 +8864,7 @@
       </c>
       <c r="AG30" s="38" t="inlineStr">
         <is>
-          <t>WM criterion task (CWMS)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH30" s="38" t="inlineStr">
@@ -8718,13 +8874,17 @@
       </c>
       <c r="AI30" s="38" t="inlineStr">
         <is>
-          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
-        </is>
-      </c>
-      <c r="AJ30" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ30" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK30" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL30" s="38" t="inlineStr">
@@ -8739,12 +8899,12 @@
       </c>
       <c r="AN30" s="37" t="inlineStr">
         <is>
-          <t>d&gt;=0.8 (large effect)</t>
+          <t>未报告具体d值</t>
         </is>
       </c>
       <c r="AO30" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP30" s="38" t="inlineStr">
@@ -8752,35 +8912,51 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ30" s="38" t="n"/>
-      <c r="AR30" s="38" t="n"/>
+      <c r="AQ30" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR30" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS30" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT30" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU30" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV30" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY30" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV30" s="37" t="n"/>
-      <c r="AW30" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX30" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY30" s="38" t="n"/>
       <c r="AZ30" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8788,14 +8964,22 @@
       </c>
       <c r="BA30" s="38" t="inlineStr">
         <is>
-          <t>评估日常生活能力迁移效应</t>
-        </is>
-      </c>
-      <c r="BB30" s="38" t="n"/>
-      <c r="BC30" s="38" t="n"/>
+          <t>评估日常生活能力迁移效应 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB30" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC30" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD30" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE30" s="40" t="inlineStr">
@@ -8823,7 +9007,7 @@
       </c>
       <c r="E31" s="36" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F31" s="36" t="inlineStr">
@@ -8833,30 +9017,42 @@
       </c>
       <c r="G31" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H31" s="36" t="n">
-        <v>37</v>
-      </c>
-      <c r="I31" s="36" t="n"/>
-      <c r="J31" s="36" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="I31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J31" s="36" t="n">
+        <v>17</v>
+      </c>
       <c r="K31" s="36" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M31" s="36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N31" s="36" t="n">
-        <v>57</v>
-      </c>
-      <c r="O31" s="36" t="n">
-        <v>10.5</v>
+      <c r="M31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N31" s="36" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="O31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P31" s="36" t="inlineStr">
         <is>
@@ -8870,12 +9066,13 @@
       </c>
       <c r="R31" s="36" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S31" s="36" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>engage; Complex
+span</t>
         </is>
       </c>
       <c r="T31" s="36" t="inlineStr">
@@ -8883,34 +9080,56 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U31" s="36" t="n">
-        <v>6</v>
+      <c r="U31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V31" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W31" s="35" t="n"/>
-      <c r="X31" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="W31" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y31" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z31" s="36" t="n"/>
+      <c r="Z31" s="36" t="inlineStr">
+        <is>
+          <t>better) and, although the differ-
+ence was not statistically signiﬁcant, this could have
+emphasized</t>
+        </is>
+      </c>
       <c r="AA31" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB31" s="35" t="n"/>
+      <c r="AB31" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC31" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD31" s="36" t="n"/>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD31" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE31" t="n">
         <v>2</v>
       </c>
@@ -8921,7 +9140,8 @@
       </c>
       <c r="AG31" s="36" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>and ﬂuid intelligence—Cattell
+Culture Fair test (far transfer effects)</t>
         </is>
       </c>
       <c r="AH31" s="36" t="inlineStr">
@@ -8931,19 +9151,21 @@
       </c>
       <c r="AI31" s="36" t="inlineStr">
         <is>
-          <t>Language comprehension; Cattell fluid intelligence</t>
-        </is>
-      </c>
-      <c r="AJ31" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ31" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK31" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL31" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AL31" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="AM31" s="35" t="inlineStr">
         <is>
@@ -8952,12 +9174,12 @@
       </c>
       <c r="AN31" s="35" t="inlineStr">
         <is>
-          <t>η²=0.15-0.26 (transfer)</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AO31" s="36" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP31" s="36" t="inlineStr">
@@ -8965,8 +9187,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ31" s="36" t="n"/>
-      <c r="AR31" s="36" t="n"/>
+      <c r="AQ31" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR31" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS31" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8974,26 +9204,34 @@
       </c>
       <c r="AT31" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU31" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV31" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW31" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY31" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV31" s="35" t="n"/>
-      <c r="AW31" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX31" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY31" s="36" t="n"/>
       <c r="AZ31" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9001,14 +9239,22 @@
       </c>
       <c r="BA31" s="36" t="inlineStr">
         <is>
-          <t>6个月随访；语言理解力迁移</t>
-        </is>
-      </c>
-      <c r="BB31" s="36" t="n"/>
-      <c r="BC31" s="36" t="n"/>
+          <t>6个月随访；语言理解力迁移 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB31" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC31" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD31" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE31" s="40" t="inlineStr">
@@ -9036,7 +9282,7 @@
       </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
-          <t>Neuroreport</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F32" s="38" t="inlineStr">
@@ -9046,14 +9292,24 @@
       </c>
       <c r="G32" s="38" t="inlineStr">
         <is>
-          <t>医院</t>
-        </is>
-      </c>
-      <c r="H32" s="38" t="n">
-        <v>40</v>
-      </c>
-      <c r="I32" s="38" t="n"/>
-      <c r="J32" s="38" t="n"/>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K32" s="38" t="n">
         <v>69.7</v>
       </c>
@@ -9062,16 +9318,24 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M32" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N32" s="38" t="n">
-        <v>68</v>
-      </c>
-      <c r="O32" s="38" t="n"/>
+      <c r="M32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P32" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q32" s="38" t="inlineStr">
@@ -9081,12 +9345,12 @@
       </c>
       <c r="R32" s="38" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S32" s="38" t="inlineStr">
         <is>
-          <t>CACT (computer-assisted cognitive training)</t>
+          <t>wome</t>
         </is>
       </c>
       <c r="T32" s="38" t="inlineStr">
@@ -9097,40 +9361,58 @@
       <c r="U32" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="V32" s="38" t="n"/>
-      <c r="W32" s="37" t="n"/>
+      <c r="V32" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X32" s="38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y32" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z32" s="38" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA32" s="38" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB32" s="37" t="n"/>
+          <t>tDCS/TMS</t>
+        </is>
+      </c>
+      <c r="AB32" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC32" s="38" t="inlineStr">
         <is>
-          <t>Maxmedica CACT</t>
-        </is>
-      </c>
-      <c r="AD32" s="38" t="n"/>
+          <t>CACT program</t>
+        </is>
+      </c>
+      <c r="AD32" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE32" t="n">
         <v>5</v>
       </c>
       <c r="AF32" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG32" s="38" t="inlineStr">
         <is>
-          <t>Verbal WM task; Digit span forward</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH32" s="38" t="inlineStr">
@@ -9138,16 +9420,24 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI32" s="38" t="n"/>
-      <c r="AJ32" s="38" t="n"/>
+      <c r="AI32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ32" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK32" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AL32" s="38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>无</t>
         </is>
       </c>
       <c r="AM32" s="37" t="inlineStr">
@@ -9158,16 +9448,26 @@
       <c r="AN32" s="37" t="n"/>
       <c r="AO32" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP32" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ32" s="38" t="n"/>
-      <c r="AR32" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ32" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR32" s="38" t="inlineStr">
+        <is>
+          <t>brain,
+and therefore stimulation of the prefrontal cortex alone is
+insufficient to induce significant changes.</t>
+        </is>
+      </c>
       <c r="AS32" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9183,7 +9483,11 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV32" s="37" t="n"/>
+      <c r="AV32" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW32" s="38" t="inlineStr">
         <is>
           <t>否</t>
@@ -9194,7 +9498,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY32" s="38" t="n"/>
+      <c r="AY32" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ32" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9202,14 +9510,22 @@
       </c>
       <c r="BA32" s="38" t="inlineStr">
         <is>
-          <t>tDCS联合CACT；anodal vs sham tDCS</t>
-        </is>
-      </c>
-      <c r="BB32" s="38" t="n"/>
-      <c r="BC32" s="38" t="n"/>
+          <t>tDCS联合CACT；anodal vs sham tDCS | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB32" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC32" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD32" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE32" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -9553,7 +9553,7 @@
       </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F33" s="36" t="inlineStr">
@@ -9563,14 +9563,22 @@
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H33" s="36" t="n">
-        <v>28</v>
-      </c>
-      <c r="I33" s="36" t="n"/>
-      <c r="J33" s="36" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="I33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K33" s="36" t="n">
         <v>67.90000000000001</v>
       </c>
@@ -9582,10 +9590,16 @@
       <c r="M33" s="36" t="n">
         <v>6.1</v>
       </c>
-      <c r="N33" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="O33" s="36" t="n"/>
+      <c r="N33" s="36" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="O33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P33" s="36" t="inlineStr">
         <is>
           <t>MoCA</t>
@@ -9603,7 +9617,7 @@
       </c>
       <c r="S33" s="36" t="inlineStr">
         <is>
-          <t>adaptive spatial n-back</t>
+          <t>dual n-back; engage; spatial n-Back</t>
         </is>
       </c>
       <c r="T33" s="36" t="inlineStr">
@@ -9612,33 +9626,51 @@
         </is>
       </c>
       <c r="U33" s="36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V33" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="W33" s="35" t="n"/>
-      <c r="X33" s="36" t="n">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="W33" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y33" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z33" s="36" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA33" s="36" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB33" s="35" t="n"/>
+          <t>tDCS/TMS/运动</t>
+        </is>
+      </c>
+      <c r="AB33" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AC33" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD33" s="36" t="n"/>
+          <t>develop app; an 8</t>
+        </is>
+      </c>
+      <c r="AD33" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE33" t="n">
         <v>5</v>
       </c>
@@ -9649,7 +9681,7 @@
       </c>
       <c r="AG33" s="36" t="inlineStr">
         <is>
-          <t>WM composite score (5 tasks)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH33" s="36" t="inlineStr">
@@ -9657,11 +9689,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI33" s="36" t="n"/>
-      <c r="AJ33" s="36" t="n"/>
+      <c r="AI33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ33" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK33" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL33" s="36" t="inlineStr">
@@ -9671,25 +9711,37 @@
       </c>
       <c r="AM33" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN33" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN33" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO33" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP33" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ33" s="36" t="n"/>
-      <c r="AR33" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ33" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR33" s="36" t="inlineStr">
+        <is>
+          <t>brain changes (Pauwels et al.</t>
+        </is>
+      </c>
       <c r="AS33" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT33" s="36" t="inlineStr">
@@ -9699,10 +9751,14 @@
       </c>
       <c r="AU33" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV33" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV33" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW33" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -9713,7 +9769,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY33" s="36" t="n"/>
+      <c r="AY33" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ33" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9721,14 +9781,22 @@
       </c>
       <c r="BA33" s="36" t="inlineStr">
         <is>
-          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
-        </is>
-      </c>
-      <c r="BB33" s="36" t="n"/>
-      <c r="BC33" s="36" t="n"/>
+          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB33" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC33" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD33" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE33" s="40" t="inlineStr">
@@ -9756,7 +9824,7 @@
       </c>
       <c r="E34" s="38" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F34" s="38" t="inlineStr">
@@ -9766,16 +9834,24 @@
       </c>
       <c r="G34" s="38" t="inlineStr">
         <is>
-          <t>养老院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H34" s="38" t="n">
         <v>19</v>
       </c>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="38" t="n"/>
+      <c r="I34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K34" s="38" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -9787,10 +9863,16 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N34" s="38" t="n">
-        <v>79</v>
-      </c>
-      <c r="O34" s="38" t="n"/>
+      <c r="N34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P34" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9803,12 +9885,12 @@
       </c>
       <c r="R34" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S34" s="38" t="inlineStr">
         <is>
-          <t>computer-assisted cognitive training (multi-domain)</t>
+          <t>wome</t>
         </is>
       </c>
       <c r="T34" s="38" t="inlineStr">
@@ -9816,45 +9898,63 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U34" s="38" t="n">
-        <v>14</v>
+      <c r="U34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V34" s="38" t="n">
         <v>45</v>
       </c>
-      <c r="W34" s="37" t="n"/>
+      <c r="W34" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X34" s="38" t="n">
         <v>14</v>
       </c>
       <c r="Y34" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z34" s="38" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA34" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB34" s="37" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB34" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AC34" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD34" s="38" t="n"/>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD34" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" s="38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG34" s="38" t="inlineStr">
         <is>
-          <t>Primary WM; secondary WM (verbal/visual)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH34" s="38" t="inlineStr">
@@ -9864,19 +9964,21 @@
       </c>
       <c r="AI34" s="38" t="inlineStr">
         <is>
-          <t>Information processing speed; learning; interference tendency</t>
-        </is>
-      </c>
-      <c r="AJ34" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ34" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK34" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL34" s="38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="AL34" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="AM34" s="37" t="inlineStr">
         <is>
@@ -9886,7 +9988,7 @@
       <c r="AN34" s="37" t="n"/>
       <c r="AO34" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP34" s="38" t="inlineStr">
@@ -9894,8 +9996,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ34" s="38" t="n"/>
-      <c r="AR34" s="38" t="n"/>
+      <c r="AQ34" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR34" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS34" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9911,7 +10021,11 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV34" s="37" t="n"/>
+      <c r="AV34" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="AW34" s="38" t="inlineStr">
         <is>
           <t>否</t>
@@ -9922,7 +10036,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY34" s="38" t="n"/>
+      <c r="AY34" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ34" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9930,14 +10048,22 @@
       </c>
       <c r="BA34" s="38" t="inlineStr">
         <is>
-          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
-        </is>
-      </c>
-      <c r="BB34" s="38" t="n"/>
-      <c r="BC34" s="38" t="n"/>
+          <t>单组前后测；养老院居民；老老年（75-91岁） | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB34" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC34" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD34" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE34" s="40" t="inlineStr">
@@ -9965,7 +10091,7 @@
       </c>
       <c r="E35" s="36" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F35" s="36" t="inlineStr">
@@ -9975,34 +10101,46 @@
       </c>
       <c r="G35" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H35" s="36" t="n">
-        <v>119</v>
-      </c>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="36" t="n"/>
-      <c r="K35" s="36" t="n">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="I35" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="J35" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="K35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M35" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="N35" s="36" t="n">
-        <v>63</v>
-      </c>
-      <c r="O35" s="36" t="n">
-        <v>19.6</v>
+      <c r="M35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N35" s="36" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="O35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P35" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q35" s="36" t="inlineStr">
@@ -10012,58 +10150,78 @@
       </c>
       <c r="R35" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S35" s="36" t="inlineStr">
         <is>
-          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
+          <t>CogniFit; engage</t>
         </is>
       </c>
       <c r="T35" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U35" s="36" t="n">
-        <v>24</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V35" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="W35" s="35" t="n"/>
-      <c r="X35" s="36" t="n">
-        <v>8</v>
+      <c r="W35" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y35" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z35" s="36" t="n"/>
+      <c r="Z35" s="36" t="inlineStr">
+        <is>
+          <t>a TV-based programme of personally benefiting activities</t>
+        </is>
+      </c>
       <c r="AA35" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB35" s="35" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB35" s="35" t="inlineStr">
+        <is>
+          <t>LMM</t>
+        </is>
+      </c>
       <c r="AC35" s="36" t="inlineStr">
         <is>
-          <t>CogniFit</t>
-        </is>
-      </c>
-      <c r="AD35" s="36" t="n"/>
+          <t>CogniFit; training program</t>
+        </is>
+      </c>
+      <c r="AD35" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE35" t="n">
         <v>3</v>
       </c>
       <c r="AF35" s="36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待核查</t>
         </is>
       </c>
       <c r="AG35" s="36" t="inlineStr">
         <is>
-          <t>WM tasks (validated)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH35" s="36" t="inlineStr">
@@ -10073,65 +10231,89 @@
       </c>
       <c r="AI35" s="36" t="inlineStr">
         <is>
-          <t>Executive function tasks</t>
-        </is>
-      </c>
-      <c r="AJ35" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ35" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK35" s="36" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM35" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN35" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO35" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP35" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ35" s="36" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AR35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT35" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL35" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM35" s="35" t="inlineStr">
+      <c r="AU35" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV35" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW35" s="36" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AN35" s="35" t="n"/>
-      <c r="AO35" s="36" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP35" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ35" s="36" t="n"/>
-      <c r="AR35" s="36" t="n"/>
-      <c r="AS35" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT35" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AU35" s="36" t="inlineStr">
+      <c r="AX35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY35" s="36" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV35" s="35" t="n"/>
-      <c r="AW35" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX35" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY35" s="36" t="n"/>
       <c r="AZ35" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10139,14 +10321,22 @@
       </c>
       <c r="BA35" s="36" t="inlineStr">
         <is>
-          <t>互动电视（iTV）平台认知训练</t>
-        </is>
-      </c>
-      <c r="BB35" s="36" t="n"/>
-      <c r="BC35" s="36" t="n"/>
+          <t>互动电视（iTV）平台认知训练 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB35" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC35" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD35" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE35" s="40" t="inlineStr">
@@ -10174,7 +10364,7 @@
       </c>
       <c r="E36" s="38" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F36" s="38" t="inlineStr">
@@ -10184,14 +10374,24 @@
       </c>
       <c r="G36" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H36" s="38" t="n">
-        <v>39</v>
-      </c>
-      <c r="I36" s="38" t="n"/>
-      <c r="J36" s="38" t="n"/>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K36" s="38" t="n">
         <v>80</v>
       </c>
@@ -10200,13 +10400,21 @@
           <t>old-old</t>
         </is>
       </c>
-      <c r="M36" s="38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N36" s="38" t="n">
-        <v>59</v>
-      </c>
-      <c r="O36" s="38" t="n"/>
+      <c r="M36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P36" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10219,12 +10427,12 @@
       </c>
       <c r="R36" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S36" s="38" t="inlineStr">
         <is>
-          <t>WM process-based training (visual/spatial)</t>
+          <t>dual n-back; wome; engage</t>
         </is>
       </c>
       <c r="T36" s="38" t="inlineStr">
@@ -10233,33 +10441,53 @@
         </is>
       </c>
       <c r="U36" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="V36" s="38" t="n">
-        <v>45</v>
-      </c>
-      <c r="W36" s="37" t="n"/>
-      <c r="X36" s="38" t="n">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="V36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W36" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y36" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z36" s="38" t="n"/>
+      <c r="Z36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA36" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB36" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB36" s="37" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
       <c r="AC36" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD36" s="38" t="n"/>
+          <t>not app</t>
+        </is>
+      </c>
+      <c r="AD36" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE36" t="n">
         <v>2</v>
       </c>
@@ -10270,7 +10498,8 @@
       </c>
       <c r="AG36" s="38" t="inlineStr">
         <is>
-          <t>Visual WM (VLMT)</t>
+          <t>which would reflect a more general improvement of
+processes associated with WM</t>
         </is>
       </c>
       <c r="AH36" s="38" t="inlineStr">
@@ -10280,10 +10509,14 @@
       </c>
       <c r="AI36" s="38" t="inlineStr">
         <is>
-          <t>Visual episodic memory</t>
-        </is>
-      </c>
-      <c r="AJ36" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ36" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK36" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -10291,7 +10524,7 @@
       </c>
       <c r="AL36" s="38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AM36" s="37" t="inlineStr">
@@ -10301,40 +10534,53 @@
       </c>
       <c r="AN36" s="37" t="inlineStr">
         <is>
-          <t>eta2p=0.46</t>
+          <t>未报告具体d值</t>
         </is>
       </c>
       <c r="AO36" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP36" s="38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ36" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR36" s="38" t="inlineStr">
+        <is>
+          <t>brain plasticity is strong enough to result in transfer effects, that is,
+performance increases in tasks that were not trained during the intervention</t>
+        </is>
+      </c>
+      <c r="AS36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT36" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ36" s="38" t="n"/>
-      <c r="AR36" s="38" t="n"/>
-      <c r="AS36" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT36" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU36" s="38" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV36" s="37" t="n"/>
+      <c r="AV36" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AW36" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX36" s="38" t="inlineStr">
@@ -10342,7 +10588,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY36" s="38" t="n"/>
+      <c r="AY36" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ36" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10353,11 +10603,19 @@
           <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
         </is>
       </c>
-      <c r="BB36" s="38" t="n"/>
-      <c r="BC36" s="38" t="n"/>
+      <c r="BB36" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC36" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD36" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE36" s="40" t="inlineStr">
@@ -10385,7 +10643,7 @@
       </c>
       <c r="E37" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F37" s="36" t="inlineStr">
@@ -10401,21 +10659,35 @@
       <c r="H37" s="36" t="n">
         <v>71</v>
       </c>
-      <c r="I37" s="36" t="n"/>
-      <c r="J37" s="36" t="n"/>
+      <c r="I37" s="36" t="n">
+        <v>34</v>
+      </c>
+      <c r="J37" s="36" t="n">
+        <v>34</v>
+      </c>
       <c r="K37" s="36" t="n">
-        <v>65.89</v>
+        <v>66</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M37" s="36" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="N37" s="36" t="n"/>
-      <c r="O37" s="36" t="n"/>
+      <c r="M37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P37" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10433,7 +10705,8 @@
       </c>
       <c r="S37" s="36" t="inlineStr">
         <is>
-          <t>adaptive verbal + spatial n-back</t>
+          <t>dual n-back; engage; verbal
+n-back; spatial n-back</t>
         </is>
       </c>
       <c r="T37" s="36" t="inlineStr">
@@ -10442,31 +10715,51 @@
         </is>
       </c>
       <c r="U37" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="V37" s="36" t="n"/>
-      <c r="W37" s="35" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="V37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W37" s="35" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
       <c r="X37" s="36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y37" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z37" s="36" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA37" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB37" s="35" t="n"/>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB37" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC37" s="36" t="inlineStr">
         <is>
-          <t>自制（居家在线）</t>
-        </is>
-      </c>
-      <c r="AD37" s="36" t="n"/>
+          <t>training program; session 16</t>
+        </is>
+      </c>
+      <c r="AD37" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE37" t="n">
         <v>2.7</v>
       </c>
@@ -10477,7 +10770,8 @@
       </c>
       <c r="AG37" s="36" t="inlineStr">
         <is>
-          <t>Digit span</t>
+          <t>and far transfer effects to an abstract
+relational reasoning task</t>
         </is>
       </c>
       <c r="AH37" s="36" t="inlineStr">
@@ -10487,57 +10781,77 @@
       </c>
       <c r="AI37" s="36" t="inlineStr">
         <is>
-          <t>Abstract relational reasoning</t>
-        </is>
-      </c>
-      <c r="AJ37" s="36" t="n"/>
+          <t>s (∼15 min)</t>
+        </is>
+      </c>
+      <c r="AJ37" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK37" s="36" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM37" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN37" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO37" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP37" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL37" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM37" s="35" t="inlineStr">
+      <c r="AQ37" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR37" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT37" s="36" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AN37" s="35" t="n"/>
-      <c r="AO37" s="36" t="inlineStr">
-        <is>
-          <t>无迁移</t>
-        </is>
-      </c>
-      <c r="AP37" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ37" s="36" t="n"/>
-      <c r="AR37" s="36" t="n"/>
-      <c r="AS37" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT37" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU37" s="36" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV37" s="35" t="n"/>
+      <c r="AV37" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW37" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX37" s="36" t="inlineStr">
@@ -10545,7 +10859,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY37" s="36" t="n"/>
+      <c r="AY37" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ37" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10553,14 +10871,22 @@
       </c>
       <c r="BA37" s="36" t="inlineStr">
         <is>
-          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
-        </is>
-      </c>
-      <c r="BB37" s="36" t="n"/>
-      <c r="BC37" s="36" t="n"/>
+          <t>训练时间表（密集vs分散）；居家无监督在线训练 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB37" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC37" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD37" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE37" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E38" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F38" s="38" t="inlineStr">
@@ -10924,14 +10924,20 @@
       </c>
       <c r="G38" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H38" s="38" t="n">
-        <v>34</v>
-      </c>
-      <c r="I38" s="38" t="n"/>
-      <c r="J38" s="38" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="I38" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="J38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K38" s="38" t="n">
         <v>65.78</v>
       </c>
@@ -10943,15 +10949,19 @@
       <c r="M38" s="38" t="n">
         <v>3.04</v>
       </c>
-      <c r="N38" s="38" t="n">
-        <v>61</v>
-      </c>
-      <c r="O38" s="38" t="n">
-        <v>15.53</v>
+      <c r="N38" s="38" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="O38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P38" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q38" s="38" t="inlineStr">
@@ -10966,7 +10976,7 @@
       </c>
       <c r="S38" s="38" t="inlineStr">
         <is>
-          <t>adaptive n-back</t>
+          <t>single n-back</t>
         </is>
       </c>
       <c r="T38" s="38" t="inlineStr">
@@ -10977,29 +10987,53 @@
       <c r="U38" s="38" t="n">
         <v>12</v>
       </c>
-      <c r="V38" s="38" t="n"/>
-      <c r="W38" s="37" t="n"/>
-      <c r="X38" s="38" t="n">
-        <v>4</v>
+      <c r="V38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W38" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y38" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z38" s="38" t="n"/>
+      <c r="Z38" s="38" t="inlineStr">
+        <is>
+          <t>not show an improvement from T1 to T2
+(all p’s &gt; 0</t>
+        </is>
+      </c>
       <c r="AA38" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB38" s="37" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB38" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC38" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD38" s="38" t="n"/>
+          <t>training
+program</t>
+        </is>
+      </c>
+      <c r="AD38" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE38" t="n">
         <v>3</v>
       </c>
@@ -11010,7 +11044,7 @@
       </c>
       <c r="AG38" s="38" t="inlineStr">
         <is>
-          <t>multimodal dual-task (visual+auditory)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH38" s="38" t="inlineStr">
@@ -11018,67 +11052,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI38" s="38" t="n"/>
-      <c r="AJ38" s="38" t="n"/>
+      <c r="AI38" s="38" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ38" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆</t>
+        </is>
+      </c>
       <c r="AK38" s="38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM38" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN38" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO38" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ38" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/PET</t>
+        </is>
+      </c>
+      <c r="AR38" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neural
+activity might support performance in a dual-task setting, thus assessing transfer effects
+to higher-order control processes in the context of </t>
+        </is>
+      </c>
+      <c r="AS38" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT38" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL38" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM38" s="37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN38" s="37" t="inlineStr">
-        <is>
-          <t>η²p=0.444</t>
-        </is>
-      </c>
-      <c r="AO38" s="38" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP38" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AQ38" s="38" t="inlineStr">
-        <is>
-          <t>fMRI</t>
-        </is>
-      </c>
-      <c r="AR38" s="38" t="inlineStr">
-        <is>
-          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
-        </is>
-      </c>
-      <c r="AS38" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT38" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU38" s="38" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV38" s="37" t="n"/>
+      <c r="AV38" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW38" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX38" s="38" t="inlineStr">
@@ -11086,7 +11134,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY38" s="38" t="n"/>
+      <c r="AY38" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ38" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11094,14 +11146,22 @@
       </c>
       <c r="BA38" s="38" t="inlineStr">
         <is>
-          <t>双任务迁移；fMRI子研究；先导研究</t>
-        </is>
-      </c>
-      <c r="BB38" s="38" t="n"/>
-      <c r="BC38" s="38" t="n"/>
+          <t>双任务迁移；fMRI子研究；先导研究 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB38" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC38" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD38" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE38" s="40" t="inlineStr">
@@ -11129,7 +11189,7 @@
       </c>
       <c r="E39" s="36" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F39" s="36" t="inlineStr">
@@ -11143,12 +11203,22 @@
         </is>
       </c>
       <c r="H39" s="36" t="n">
-        <v>137</v>
-      </c>
-      <c r="I39" s="36" t="n"/>
-      <c r="J39" s="36" t="n"/>
-      <c r="K39" s="36" t="n">
-        <v>66.65000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -11160,8 +11230,16 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N39" s="36" t="n"/>
-      <c r="O39" s="36" t="n"/>
+      <c r="N39" s="36" t="inlineStr">
+        <is>
+          <t>543%</t>
+        </is>
+      </c>
+      <c r="O39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P39" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -11174,12 +11252,12 @@
       </c>
       <c r="R39" s="36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S39" s="36" t="inlineStr">
         <is>
-          <t>Visual and Spatial WM training</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="T39" s="36" t="inlineStr">
@@ -11189,16 +11267,22 @@
       </c>
       <c r="U39" s="36" t="inlineStr">
         <is>
-          <t>5-10</t>
-        </is>
-      </c>
-      <c r="V39" s="36" t="n">
-        <v>45</v>
-      </c>
-      <c r="W39" s="35" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W39" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X39" s="36" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y39" s="36" t="inlineStr">
@@ -11206,19 +11290,31 @@
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="36" t="n"/>
+      <c r="Z39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA39" s="36" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB39" s="35" t="n"/>
+          <t>tDCS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB39" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC39" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD39" s="36" t="n"/>
+          <t>promising app; Project 1</t>
+        </is>
+      </c>
+      <c r="AD39" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF39" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -11226,7 +11322,7 @@
       </c>
       <c r="AG39" s="36" t="inlineStr">
         <is>
-          <t>Visual WM; Spatial WM</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH39" s="36" t="inlineStr">
@@ -11234,8 +11330,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI39" s="36" t="n"/>
-      <c r="AJ39" s="36" t="n"/>
+      <c r="AI39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ39" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK39" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -11243,7 +11347,7 @@
       </c>
       <c r="AL39" s="36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AM39" s="35" t="inlineStr">
@@ -11259,14 +11363,23 @@
       </c>
       <c r="AP39" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ39" s="36" t="n"/>
-      <c r="AR39" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ39" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/MRI</t>
+        </is>
+      </c>
+      <c r="AR39" s="36" t="inlineStr">
+        <is>
+          <t>brain stimulation improves cognitive performance by modulating functional connectivity and task-
+specific activation.</t>
+        </is>
+      </c>
       <c r="AS39" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT39" s="36" t="inlineStr">
@@ -11276,13 +11389,17 @@
       </c>
       <c r="AU39" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AV39" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV39" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW39" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX39" s="36" t="inlineStr">
@@ -11290,7 +11407,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY39" s="36" t="n"/>
+      <c r="AY39" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ39" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11298,14 +11419,22 @@
       </c>
       <c r="BA39" s="36" t="inlineStr">
         <is>
-          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
-        </is>
-      </c>
-      <c r="BB39" s="36" t="n"/>
-      <c r="BC39" s="36" t="n"/>
+          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA） | 待核查</t>
+        </is>
+      </c>
+      <c r="BB39" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC39" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD39" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE39" s="40" t="inlineStr">
@@ -11333,7 +11462,7 @@
       </c>
       <c r="E40" s="38" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F40" s="38" t="inlineStr">
@@ -11343,14 +11472,18 @@
       </c>
       <c r="G40" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H40" s="38" t="n">
         <v>103</v>
       </c>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="38" t="n"/>
+      <c r="I40" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="J40" s="38" t="n">
+        <v>51</v>
+      </c>
       <c r="K40" s="38" t="n">
         <v>70.56999999999999</v>
       </c>
@@ -11359,14 +11492,24 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M40" s="38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N40" s="38" t="n"/>
-      <c r="O40" s="38" t="n"/>
+      <c r="M40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N40" s="38" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="O40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P40" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="Q40" s="38" t="inlineStr">
@@ -11376,12 +11519,12 @@
       </c>
       <c r="R40" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S40" s="38" t="inlineStr">
         <is>
-          <t>commercial brain training app (multi-domain)</t>
+          <t>BrainHQ; Lumosity; engage</t>
         </is>
       </c>
       <c r="T40" s="38" t="inlineStr">
@@ -11389,34 +11532,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U40" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V40" s="38" t="n"/>
-      <c r="W40" s="37" t="n"/>
-      <c r="X40" s="38" t="n">
-        <v>12</v>
+      <c r="U40" s="38" t="n">
+        <v>497</v>
+      </c>
+      <c r="V40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W40" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y40" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z40" s="38" t="n"/>
+      <c r="Z40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA40" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB40" s="37" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB40" s="37" t="inlineStr">
+        <is>
+          <t>LMM/ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC40" s="38" t="inlineStr">
         <is>
-          <t>商业脑训练app</t>
-        </is>
-      </c>
-      <c r="AD40" s="38" t="n"/>
+          <t>Lumosity; training 
+program</t>
+        </is>
+      </c>
+      <c r="AD40" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AF40" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -11424,7 +11588,7 @@
       </c>
       <c r="AG40" s="38" t="inlineStr">
         <is>
-          <t>WM tasks (trained domain)</t>
+          <t>Lee et al</t>
         </is>
       </c>
       <c r="AH40" s="38" t="inlineStr">
@@ -11434,13 +11598,17 @@
       </c>
       <c r="AI40" s="38" t="inlineStr">
         <is>
-          <t>Processing speed; attention; language</t>
-        </is>
-      </c>
-      <c r="AJ40" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ40" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK40" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL40" s="38" t="inlineStr">
@@ -11456,7 +11624,7 @@
       <c r="AN40" s="37" t="n"/>
       <c r="AO40" s="38" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP40" s="38" t="inlineStr">
@@ -11464,8 +11632,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ40" s="38" t="n"/>
-      <c r="AR40" s="38" t="n"/>
+      <c r="AQ40" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR40" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS40" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -11473,26 +11649,34 @@
       </c>
       <c r="AT40" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU40" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV40" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY40" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV40" s="37" t="n"/>
-      <c r="AW40" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX40" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY40" s="38" t="n"/>
       <c r="AZ40" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11500,14 +11684,22 @@
       </c>
       <c r="BA40" s="38" t="inlineStr">
         <is>
-          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
-        </is>
-      </c>
-      <c r="BB40" s="38" t="n"/>
-      <c r="BC40" s="38" t="n"/>
+          <t>商业脑训练app；仅练习效应，无迁移；3个月干预 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB40" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC40" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD40" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE40" s="40" t="inlineStr">
@@ -11535,7 +11727,7 @@
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F41" s="36" t="inlineStr">
@@ -11549,12 +11741,16 @@
         </is>
       </c>
       <c r="H41" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="36" t="n">
         <v>35</v>
       </c>
-      <c r="I41" s="36" t="n"/>
-      <c r="J41" s="36" t="n"/>
+      <c r="J41" s="36" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" s="36" t="n">
-        <v>75.8</v>
+        <v>47</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -11566,15 +11762,17 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="N41" s="36" t="n">
-        <v>77</v>
+      <c r="N41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O41" s="36" t="n">
-        <v>17.7</v>
+        <v>12</v>
       </c>
       <c r="P41" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q41" s="36" t="inlineStr">
@@ -11584,12 +11782,12 @@
       </c>
       <c r="R41" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S41" s="36" t="inlineStr">
         <is>
-          <t>Cogmed (adaptive WM training)</t>
+          <t>Cogmed; Lumosity; Wome; engage; verbal n-back</t>
         </is>
       </c>
       <c r="T41" s="36" t="inlineStr">
@@ -11598,12 +11796,16 @@
         </is>
       </c>
       <c r="U41" s="36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="V41" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="W41" s="35" t="n"/>
+      <c r="W41" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X41" s="36" t="n">
         <v>5</v>
       </c>
@@ -11612,19 +11814,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z41" s="36" t="n"/>
+      <c r="Z41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA41" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB41" s="35" t="n"/>
+      <c r="AB41" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC41" s="36" t="inlineStr">
         <is>
-          <t>Cogmed</t>
-        </is>
-      </c>
-      <c r="AD41" s="36" t="n"/>
+          <t>Cogmed; is app</t>
+        </is>
+      </c>
+      <c r="AD41" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE41" t="n">
         <v>5</v>
       </c>
@@ -11635,7 +11849,7 @@
       </c>
       <c r="AG41" s="36" t="inlineStr">
         <is>
-          <t>n-back (0-back, 1-back, 2-back)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH41" s="36" t="inlineStr">
@@ -11643,17 +11857,23 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI41" s="36" t="n"/>
-      <c r="AJ41" s="36" t="n"/>
+      <c r="AI41" s="36" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ41" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK41" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AL41" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL41" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="AM41" s="35" t="inlineStr">
         <is>
@@ -11673,17 +11893,20 @@
       </c>
       <c r="AQ41" s="36" t="inlineStr">
         <is>
-          <t>ERP</t>
+          <t>fMRI/EEG/ERP</t>
         </is>
       </c>
       <c r="AR41" s="36" t="inlineStr">
         <is>
-          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
+          <t>Neural
+Activity Underlying Working Memory
+after Computerized Cognitive Training
+in Older Adults.</t>
         </is>
       </c>
       <c r="AS41" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT41" s="36" t="inlineStr">
@@ -11696,18 +11919,26 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV41" s="35" t="n"/>
+      <c r="AV41" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW41" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX41" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY41" s="36" t="n"/>
+          <t>NART</t>
+        </is>
+      </c>
+      <c r="AY41" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ41" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11715,14 +11946,22 @@
       </c>
       <c r="BA41" s="36" t="inlineStr">
         <is>
-          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
-        </is>
-      </c>
-      <c r="BB41" s="36" t="n"/>
-      <c r="BC41" s="36" t="n"/>
+          <t>Cogmed自适应vs非自适应；ERP神经指标变化 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB41" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC41" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD41" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE41" s="40" t="inlineStr">
@@ -11750,7 +11989,7 @@
       </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F42" s="38" t="inlineStr">
@@ -11760,32 +11999,50 @@
       </c>
       <c r="G42" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H42" s="38" t="n">
-        <v>36</v>
-      </c>
-      <c r="I42" s="38" t="n"/>
-      <c r="J42" s="38" t="n"/>
-      <c r="K42" s="38" t="n">
-        <v>69.89</v>
+        <v>19</v>
+      </c>
+      <c r="I42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M42" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N42" s="38" t="n">
-        <v>68</v>
-      </c>
-      <c r="O42" s="38" t="n"/>
+      <c r="M42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P42" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>Mini-Mental</t>
         </is>
       </c>
       <c r="Q42" s="38" t="inlineStr">
@@ -11795,12 +12052,12 @@
       </c>
       <c r="R42" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S42" s="38" t="inlineStr">
         <is>
-          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
+          <t>engage; complex span; Letter-Number Sequencing</t>
         </is>
       </c>
       <c r="T42" s="38" t="inlineStr">
@@ -11808,34 +12065,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U42" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="V42" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="W42" s="37" t="n"/>
+      <c r="U42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W42" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X42" s="38" t="n">
         <v>5</v>
       </c>
       <c r="Y42" s="38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z42" s="38" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA42" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB42" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB42" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC42" s="38" t="inlineStr">
         <is>
-          <t>自制（在线）</t>
-        </is>
-      </c>
-      <c r="AD42" s="38" t="n"/>
+          <t>the program</t>
+        </is>
+      </c>
+      <c r="AD42" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE42" t="n">
         <v>2</v>
       </c>
@@ -11846,7 +12123,8 @@
       </c>
       <c r="AG42" s="38" t="inlineStr">
         <is>
-          <t>Auditory STM span; visuospatial STM</t>
+          <t>but no improvements on several other transfer tasks of digit
+span, verbal recall,</t>
         </is>
       </c>
       <c r="AH42" s="38" t="inlineStr">
@@ -11856,65 +12134,88 @@
       </c>
       <c r="AI42" s="38" t="inlineStr">
         <is>
-          <t>Long-term episodic memory</t>
-        </is>
-      </c>
-      <c r="AJ42" s="38" t="n"/>
+          <t>in either young (aged 20–30) or
+older (aged 70–80) participants</t>
+        </is>
+      </c>
+      <c r="AJ42" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK42" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL42" s="38" t="inlineStr">
-        <is>
-          <t>3;6</t>
-        </is>
+      <c r="AL42" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="AM42" s="37" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN42" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO42" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP42" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AN42" s="37" t="n"/>
-      <c r="AO42" s="38" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AP42" s="38" t="inlineStr">
+      <c r="AQ42" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR42" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT42" s="38" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ42" s="38" t="n"/>
-      <c r="AR42" s="38" t="n"/>
-      <c r="AS42" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT42" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="AU42" s="38" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV42" s="37" t="n"/>
+      <c r="AV42" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW42" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX42" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY42" s="38" t="n"/>
+          <t>NART</t>
+        </is>
+      </c>
+      <c r="AY42" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ42" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11922,14 +12223,22 @@
       </c>
       <c r="BA42" s="38" t="inlineStr">
         <is>
-          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
-        </is>
-      </c>
-      <c r="BB42" s="38" t="n"/>
-      <c r="BC42" s="38" t="n"/>
+          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB42" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC42" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD42" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE42" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -12266,7 +12266,7 @@
       </c>
       <c r="E43" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F43" s="36" t="inlineStr">
@@ -12279,27 +12279,49 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H43" s="36" t="n">
-        <v>97</v>
-      </c>
-      <c r="I43" s="36" t="n"/>
-      <c r="J43" s="36" t="n"/>
-      <c r="K43" s="36" t="n">
-        <v>70.39</v>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M43" s="36" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="N43" s="36" t="n"/>
-      <c r="O43" s="36" t="n"/>
+      <c r="M43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P43" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE≥1; Mini-Mental</t>
         </is>
       </c>
       <c r="Q43" s="36" t="inlineStr">
@@ -12309,12 +12331,12 @@
       </c>
       <c r="R43" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S43" s="36" t="inlineStr">
         <is>
-          <t>computerized WM training (web-based)</t>
+          <t>engage</t>
         </is>
       </c>
       <c r="T43" s="36" t="inlineStr">
@@ -12322,13 +12344,21 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U43" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="V43" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W43" s="35" t="n"/>
+      <c r="U43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W43" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X43" s="36" t="n">
         <v>8</v>
       </c>
@@ -12337,19 +12367,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z43" s="36" t="n"/>
+      <c r="Z43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA43" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB43" s="35" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB43" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC43" s="36" t="inlineStr">
         <is>
-          <t>BrainGymmer</t>
-        </is>
-      </c>
-      <c r="AD43" s="36" t="n"/>
+          <t>brain fitness; to
+program</t>
+        </is>
+      </c>
+      <c r="AD43" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE43" t="n">
         <v>5</v>
       </c>
@@ -12360,7 +12403,7 @@
       </c>
       <c r="AG43" s="36" t="inlineStr">
         <is>
-          <t>Self-perceived cognitive failures (CFQ)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH43" s="36" t="inlineStr">
@@ -12368,17 +12411,24 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI43" s="36" t="n"/>
-      <c r="AJ43" s="36" t="n"/>
+      <c r="AI43" s="36" t="inlineStr">
+        <is>
+          <t>ed than
+near transfer</t>
+        </is>
+      </c>
+      <c r="AJ43" s="36" t="inlineStr">
+        <is>
+          <t>EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK43" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AL43" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL43" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="AM43" s="35" t="inlineStr">
         <is>
@@ -12396,8 +12446,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ43" s="36" t="n"/>
-      <c r="AR43" s="36" t="n"/>
+      <c r="AQ43" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR43" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS43" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -12413,7 +12471,11 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV43" s="35" t="n"/>
+      <c r="AV43" s="35" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
       <c r="AW43" s="36" t="inlineStr">
         <is>
           <t>否</t>
@@ -12424,7 +12486,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY43" s="36" t="n"/>
+      <c r="AY43" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ43" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12432,14 +12498,22 @@
       </c>
       <c r="BA43" s="36" t="inlineStr">
         <is>
-          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
-        </is>
-      </c>
-      <c r="BB43" s="36" t="n"/>
-      <c r="BC43" s="36" t="n"/>
+          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局 | 待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="BB43" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC43" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD43" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE43" s="40" t="inlineStr">
@@ -12467,7 +12541,7 @@
       </c>
       <c r="E44" s="38" t="inlineStr">
         <is>
-          <t>BMC geriatrics</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F44" s="38" t="inlineStr">
@@ -12481,30 +12555,44 @@
         </is>
       </c>
       <c r="H44" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="38" t="n"/>
-      <c r="J44" s="38" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="I44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K44" s="38" t="n">
-        <v>69.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M44" s="38" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="N44" s="38" t="n">
-        <v>73</v>
-      </c>
-      <c r="O44" s="38" t="n">
-        <v>11.27</v>
+      <c r="M44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N44" s="38" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="O44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P44" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q44" s="38" t="inlineStr">
@@ -12514,12 +12602,12 @@
       </c>
       <c r="R44" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S44" s="38" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>engage; complex span</t>
         </is>
       </c>
       <c r="T44" s="38" t="inlineStr">
@@ -12528,33 +12616,51 @@
         </is>
       </c>
       <c r="U44" s="38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V44" s="38" t="n">
         <v>30</v>
       </c>
-      <c r="W44" s="37" t="n"/>
-      <c r="X44" s="38" t="n">
-        <v>3</v>
+      <c r="W44" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y44" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z44" s="38" t="n"/>
+      <c r="Z44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA44" s="38" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB44" s="37" t="n"/>
+      <c r="AB44" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC44" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD44" s="38" t="n"/>
+          <t>give app; the 1</t>
+        </is>
+      </c>
+      <c r="AD44" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE44" t="n">
         <v>2</v>
       </c>
@@ -12565,7 +12671,7 @@
       </c>
       <c r="AG44" s="38" t="inlineStr">
         <is>
-          <t>n-back task</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH44" s="38" t="inlineStr">
@@ -12573,17 +12679,23 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI44" s="38" t="n"/>
-      <c r="AJ44" s="38" t="n"/>
+      <c r="AI44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ44" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK44" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL44" s="38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AL44" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="AM44" s="37" t="inlineStr">
         <is>
@@ -12592,12 +12704,12 @@
       </c>
       <c r="AN44" s="37" t="inlineStr">
         <is>
-          <t>Cohen's d medium-large</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AO44" s="38" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP44" s="38" t="inlineStr">
@@ -12607,12 +12719,15 @@
       </c>
       <c r="AQ44" s="38" t="inlineStr">
         <is>
-          <t>ERP</t>
+          <t>fMRI/EEG/ERP/MRI/PET</t>
         </is>
       </c>
       <c r="AR44" s="38" t="inlineStr">
         <is>
-          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
+          <t>neural 
+correlates/changes underlying training gains and transfer 
+effects WM training induces were important to provide 
+a better understanding of th</t>
         </is>
       </c>
       <c r="AS44" s="38" t="inlineStr">
@@ -12630,7 +12745,11 @@
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV44" s="37" t="n"/>
+      <c r="AV44" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW44" s="38" t="inlineStr">
         <is>
           <t>否</t>
@@ -12641,7 +12760,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY44" s="38" t="n"/>
+      <c r="AY44" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ44" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12652,11 +12775,19 @@
           <t>先导研究；ERP神经相关；6个月随访</t>
         </is>
       </c>
-      <c r="BB44" s="38" t="n"/>
-      <c r="BC44" s="38" t="n"/>
+      <c r="BB44" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC44" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD44" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE44" s="40" t="inlineStr">
@@ -12684,7 +12815,7 @@
       </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F45" s="36" t="inlineStr">
@@ -12697,27 +12828,45 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H45" s="36" t="n">
-        <v>97</v>
-      </c>
-      <c r="I45" s="36" t="n"/>
-      <c r="J45" s="36" t="n"/>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I45" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K45" s="36" t="n">
-        <v>70.39</v>
+        <v>90</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M45" s="36" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="N45" s="36" t="n"/>
-      <c r="O45" s="36" t="n"/>
+      <c r="M45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P45" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE≥1</t>
         </is>
       </c>
       <c r="Q45" s="36" t="inlineStr">
@@ -12727,12 +12876,13 @@
       </c>
       <c r="R45" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S45" s="36" t="inlineStr">
         <is>
-          <t>web-based WM or logic &amp; planning training</t>
+          <t>dual n-back; engage; Operation
+Span</t>
         </is>
       </c>
       <c r="T45" s="36" t="inlineStr">
@@ -12740,34 +12890,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U45" s="36" t="n">
-        <v>40</v>
+      <c r="U45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V45" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W45" s="35" t="n"/>
-      <c r="X45" s="36" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="W45" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y45" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="36" t="n"/>
+      <c r="Z45" s="36" t="inlineStr">
+        <is>
+          <t>two assessments 8-weeks apart</t>
+        </is>
+      </c>
       <c r="AA45" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB45" s="35" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB45" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC45" s="36" t="inlineStr">
         <is>
-          <t>BrainGymmer</t>
-        </is>
-      </c>
-      <c r="AD45" s="36" t="n"/>
+          <t>training program; TMT 1</t>
+        </is>
+      </c>
+      <c r="AD45" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE45" t="n">
         <v>5</v>
       </c>
@@ -12778,7 +12948,8 @@
       </c>
       <c r="AG45" s="36" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>that is within the same cognitive domain as the trained task
+(Morrison and Chein,</t>
         </is>
       </c>
       <c r="AH45" s="36" t="inlineStr">
@@ -12788,13 +12959,17 @@
       </c>
       <c r="AI45" s="36" t="inlineStr">
         <is>
-          <t>Planning; reasoning; processing speed; verbal fluency</t>
-        </is>
-      </c>
-      <c r="AJ45" s="36" t="n"/>
+          <t>switching, and dual-task performance</t>
+        </is>
+      </c>
+      <c r="AJ45" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK45" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AL45" s="36" t="inlineStr">
@@ -12810,7 +12985,7 @@
       <c r="AN45" s="35" t="n"/>
       <c r="AO45" s="36" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP45" s="36" t="inlineStr">
@@ -12818,35 +12993,51 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ45" s="36" t="n"/>
-      <c r="AR45" s="36" t="n"/>
+      <c r="AQ45" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR45" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS45" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT45" s="36" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU45" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV45" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW45" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AU45" s="36" t="inlineStr">
+      <c r="AX45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY45" s="36" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV45" s="35" t="n"/>
-      <c r="AW45" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX45" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY45" s="36" t="n"/>
       <c r="AZ45" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12854,14 +13045,22 @@
       </c>
       <c r="BA45" s="36" t="inlineStr">
         <is>
-          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
-        </is>
-      </c>
-      <c r="BB45" s="36" t="n"/>
-      <c r="BC45" s="36" t="n"/>
+          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB45" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC45" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD45" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE45" s="40" t="inlineStr">
@@ -12889,7 +13088,7 @@
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t>Gerontology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F46" s="38" t="inlineStr">
@@ -12899,14 +13098,18 @@
       </c>
       <c r="G46" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H46" s="38" t="n">
-        <v>36</v>
-      </c>
-      <c r="I46" s="38" t="n"/>
-      <c r="J46" s="38" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="I46" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" s="38" t="n">
+        <v>16</v>
+      </c>
       <c r="K46" s="38" t="n">
         <v>86.8</v>
       </c>
@@ -12915,16 +13118,22 @@
           <t>old-old</t>
         </is>
       </c>
-      <c r="M46" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="N46" s="38" t="n">
-        <v>70</v>
-      </c>
-      <c r="O46" s="38" t="n"/>
+      <c r="M46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O46" s="38" t="n">
+        <v>183.7</v>
+      </c>
       <c r="P46" s="38" t="inlineStr">
         <is>
-          <t>MMST</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Q46" s="38" t="inlineStr">
@@ -12934,12 +13143,12 @@
       </c>
       <c r="R46" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S46" s="38" t="inlineStr">
         <is>
-          <t>WM span tasks (5 tasks)</t>
+          <t>wome; engage; spatial n-back</t>
         </is>
       </c>
       <c r="T46" s="38" t="inlineStr">
@@ -12951,30 +13160,46 @@
         <v>10</v>
       </c>
       <c r="V46" s="38" t="n">
-        <v>28</v>
-      </c>
-      <c r="W46" s="37" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="W46" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X46" s="38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z46" s="38" t="n"/>
+      <c r="Z46" s="38" t="inlineStr">
+        <is>
+          <t>no treatment</t>
+        </is>
+      </c>
       <c r="AA46" s="38" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB46" s="37" t="n"/>
+      <c r="AB46" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC46" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD46" s="38" t="n"/>
+          <t>has app; approximately 2</t>
+        </is>
+      </c>
+      <c r="AD46" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE46" t="n">
         <v>5</v>
       </c>
@@ -12985,7 +13210,7 @@
       </c>
       <c r="AG46" s="38" t="inlineStr">
         <is>
-          <t>trained WM tasks</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH46" s="38" t="inlineStr">
@@ -12995,61 +13220,78 @@
       </c>
       <c r="AI46" s="38" t="inlineStr">
         <is>
-          <t>Executive functions (2 tests)</t>
-        </is>
-      </c>
-      <c r="AJ46" s="38" t="n"/>
+          <t>because, although transfer to some similar 
+WM tasks has already been demonstrate</t>
+        </is>
+      </c>
+      <c r="AJ46" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK46" s="38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM46" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN46" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO46" s="38" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP46" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL46" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM46" s="37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN46" s="37" t="inlineStr">
-        <is>
-          <t>d=0.5-0.8 (trained tasks)</t>
-        </is>
-      </c>
-      <c r="AO46" s="38" t="inlineStr">
-        <is>
-          <t>无迁移</t>
-        </is>
-      </c>
-      <c r="AP46" s="38" t="inlineStr">
+      <c r="AQ46" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR46" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS46" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT46" s="38" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ46" s="38" t="n"/>
-      <c r="AR46" s="38" t="n"/>
-      <c r="AS46" s="38" t="inlineStr">
-        <is>
-          <t>高/低</t>
-        </is>
-      </c>
-      <c r="AT46" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="AU46" s="38" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV46" s="37" t="n"/>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV46" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW46" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX46" s="38" t="inlineStr">
@@ -13057,7 +13299,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY46" s="38" t="n"/>
+      <c r="AY46" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ46" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13068,11 +13314,19 @@
           <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
         </is>
       </c>
-      <c r="BB46" s="38" t="n"/>
-      <c r="BC46" s="38" t="n"/>
+      <c r="BB46" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC46" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD46" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE46" s="40" t="inlineStr">
@@ -13100,7 +13354,7 @@
       </c>
       <c r="E47" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F47" s="36" t="inlineStr">
@@ -13114,10 +13368,16 @@
         </is>
       </c>
       <c r="H47" s="36" t="n">
-        <v>43</v>
-      </c>
-      <c r="I47" s="36" t="n"/>
-      <c r="J47" s="36" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="I47" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K47" s="36" t="n">
         <v>68.81</v>
       </c>
@@ -13126,18 +13386,22 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M47" s="36" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="N47" s="36" t="n">
-        <v>67</v>
+      <c r="M47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O47" s="36" t="n">
         <v>15.05</v>
       </c>
       <c r="P47" s="36" t="inlineStr">
         <is>
-          <t>MMSE-2</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q47" s="36" t="inlineStr">
@@ -13147,12 +13411,12 @@
       </c>
       <c r="R47" s="36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S47" s="36" t="inlineStr">
         <is>
-          <t>memory updating task (predictable vs unpredictable)</t>
+          <t>engage</t>
         </is>
       </c>
       <c r="T47" s="36" t="inlineStr">
@@ -13160,28 +13424,52 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U47" s="36" t="n"/>
-      <c r="V47" s="36" t="n"/>
-      <c r="W47" s="35" t="n"/>
-      <c r="X47" s="36" t="n"/>
+      <c r="U47" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="V47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W47" s="35" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="X47" s="36" t="n">
+        <v>2</v>
+      </c>
       <c r="Y47" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="36" t="n"/>
+      <c r="Z47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA47" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB47" s="35" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB47" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
       <c r="AC47" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD47" s="36" t="n"/>
+          <t>This app; Day 1</t>
+        </is>
+      </c>
+      <c r="AD47" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AF47" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -13189,7 +13477,9 @@
       </c>
       <c r="AG47" s="36" t="inlineStr">
         <is>
-          <t>WM updating task (novel)</t>
+          <t>another
+dual-task) and two far transfer tasks (a running memory task
+requiring me</t>
         </is>
       </c>
       <c r="AH47" s="36" t="inlineStr">
@@ -13199,10 +13489,15 @@
       </c>
       <c r="AI47" s="36" t="inlineStr">
         <is>
-          <t>Episodic memory</t>
-        </is>
-      </c>
-      <c r="AJ47" s="36" t="n"/>
+          <t>at three different
+testing sessions – before training, immediately after the trai</t>
+        </is>
+      </c>
+      <c r="AJ47" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK47" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -13210,7 +13505,7 @@
       </c>
       <c r="AL47" s="36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AM47" s="35" t="inlineStr">
@@ -13221,16 +13516,24 @@
       <c r="AN47" s="35" t="n"/>
       <c r="AO47" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP47" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ47" s="36" t="n"/>
-      <c r="AR47" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ47" s="36" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR47" s="36" t="inlineStr">
+        <is>
+          <t>brain activation for the trained and transfer tasks.</t>
+        </is>
+      </c>
       <c r="AS47" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -13243,21 +13546,29 @@
       </c>
       <c r="AU47" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV47" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY47" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV47" s="35" t="n"/>
-      <c r="AW47" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX47" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY47" s="36" t="n"/>
       <c r="AZ47" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13265,14 +13576,22 @@
       </c>
       <c r="BA47" s="36" t="inlineStr">
         <is>
-          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
-        </is>
-      </c>
-      <c r="BB47" s="36" t="n"/>
-      <c r="BC47" s="36" t="n"/>
+          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB47" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC47" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD47" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE47" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -13619,7 +13619,7 @@
       </c>
       <c r="E48" s="38" t="inlineStr">
         <is>
-          <t>Aging brain</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F48" s="38" t="inlineStr">
@@ -13633,10 +13633,14 @@
         </is>
       </c>
       <c r="H48" s="38" t="n">
-        <v>119</v>
-      </c>
-      <c r="I48" s="38" t="n"/>
-      <c r="J48" s="38" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="I48" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="J48" s="38" t="n">
+        <v>35</v>
+      </c>
       <c r="K48" s="38" t="n">
         <v>72.86</v>
       </c>
@@ -13645,18 +13649,22 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M48" s="38" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="N48" s="38" t="n">
-        <v>76</v>
+      <c r="M48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N48" s="38" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
       </c>
       <c r="O48" s="38" t="n">
-        <v>16.6</v>
+        <v>2</v>
       </c>
       <c r="P48" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE≥24; Mini-Mental</t>
         </is>
       </c>
       <c r="Q48" s="38" t="inlineStr">
@@ -13671,7 +13679,7 @@
       </c>
       <c r="S48" s="38" t="inlineStr">
         <is>
-          <t>n-back + metacognitive program (EngAge)</t>
+          <t>wome; EngAge; complex span; Spatial n-back</t>
         </is>
       </c>
       <c r="T48" s="38" t="inlineStr">
@@ -13682,31 +13690,51 @@
       <c r="U48" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="V48" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="W48" s="37" t="n"/>
-      <c r="X48" s="38" t="n">
-        <v>5</v>
+      <c r="V48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W48" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y48" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z48" s="38" t="n"/>
+      <c r="Z48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA48" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB48" s="37" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB48" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA/MANOVA</t>
+        </is>
+      </c>
       <c r="AC48" s="38" t="inlineStr">
         <is>
-          <t>自制（居家）</t>
-        </is>
-      </c>
-      <c r="AD48" s="38" t="n"/>
+          <t>metacognitive program</t>
+        </is>
+      </c>
+      <c r="AD48" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
       <c r="AE48" t="n">
         <v>4</v>
       </c>
@@ -13717,7 +13745,8 @@
       </c>
       <c r="AG48" s="38" t="inlineStr">
         <is>
-          <t>non-trained WM measures</t>
+          <t>mediates the effect of N-back working
+memory training on matrix reasoning</t>
         </is>
       </c>
       <c r="AH48" s="38" t="inlineStr">
@@ -13727,57 +13756,77 @@
       </c>
       <c r="AI48" s="38" t="inlineStr">
         <is>
-          <t>Inhibitory control; episodic memory</t>
-        </is>
-      </c>
-      <c r="AJ48" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ48" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK48" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL48" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AL48" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="AM48" s="37" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN48" s="37" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AO48" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ48" s="38" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR48" s="38" t="inlineStr">
+        <is>
+          <t>Brain Observed in Vivo: Differential changes and
+their
+modiﬁers.</t>
+        </is>
+      </c>
+      <c r="AS48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT48" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AN48" s="37" t="n"/>
-      <c r="AO48" s="38" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP48" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ48" s="38" t="n"/>
-      <c r="AR48" s="38" t="n"/>
-      <c r="AS48" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT48" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU48" s="38" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV48" s="37" t="n"/>
+      <c r="AV48" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW48" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX48" s="38" t="inlineStr">
@@ -13785,7 +13834,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY48" s="38" t="n"/>
+      <c r="AY48" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ48" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13793,14 +13846,22 @@
       </c>
       <c r="BA48" s="38" t="inlineStr">
         <is>
-          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
-        </is>
-      </c>
-      <c r="BB48" s="38" t="n"/>
-      <c r="BC48" s="38" t="n"/>
+          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB48" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC48" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD48" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE48" s="40" t="inlineStr">
@@ -13828,7 +13889,7 @@
       </c>
       <c r="E49" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F49" s="36" t="inlineStr">
@@ -13838,14 +13899,22 @@
       </c>
       <c r="G49" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H49" s="36" t="n">
-        <v>148</v>
-      </c>
-      <c r="I49" s="36" t="n"/>
-      <c r="J49" s="36" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K49" s="36" t="n">
         <v>69</v>
       </c>
@@ -13855,15 +13924,19 @@
         </is>
       </c>
       <c r="M49" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" s="36" t="n"/>
+        <v>3.18</v>
+      </c>
+      <c r="N49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="O49" s="36" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="P49" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Mini-Mental</t>
         </is>
       </c>
       <c r="Q49" s="36" t="inlineStr">
@@ -13873,12 +13946,12 @@
       </c>
       <c r="R49" s="36" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S49" s="36" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
+          <t>dual n-back; engage; Reading Span; spatial n-back</t>
         </is>
       </c>
       <c r="T49" s="36" t="inlineStr">
@@ -13887,33 +13960,51 @@
         </is>
       </c>
       <c r="U49" s="36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V49" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W49" s="35" t="n"/>
-      <c r="X49" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="W49" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y49" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z49" s="36" t="n"/>
+      <c r="Z49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA49" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB49" s="35" t="n"/>
+      <c r="AB49" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC49" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD49" s="36" t="n"/>
+          <t>analytical app</t>
+        </is>
+      </c>
+      <c r="AD49" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE49" t="n">
         <v>2</v>
       </c>
@@ -13924,7 +14015,7 @@
       </c>
       <c r="AG49" s="36" t="inlineStr">
         <is>
-          <t>visuospatial WM; STM tasks</t>
+          <t>Forward and Backward Digit Span tasks (De Beni et al</t>
         </is>
       </c>
       <c r="AH49" s="36" t="inlineStr">
@@ -13934,39 +14025,56 @@
       </c>
       <c r="AI49" s="36" t="inlineStr">
         <is>
-          <t>fluid intelligence; processing speed; inhibitory measures</t>
-        </is>
-      </c>
-      <c r="AJ49" s="36" t="n"/>
+          <t>Cattell test; Cattell and Cattell, 1963)
+This task consisted of 4 subtests (to be</t>
+        </is>
+      </c>
+      <c r="AJ49" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK49" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="AL49" s="36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM49" s="35" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN49" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO49" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP49" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AN49" s="35" t="n"/>
-      <c r="AO49" s="36" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP49" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ49" s="36" t="n"/>
-      <c r="AR49" s="36" t="n"/>
+      <c r="AQ49" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR49" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS49" s="36" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT49" s="36" t="inlineStr">
@@ -13976,10 +14084,14 @@
       </c>
       <c r="AU49" s="36" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AV49" s="35" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV49" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW49" s="36" t="inlineStr">
         <is>
           <t>是</t>
@@ -13987,10 +14099,14 @@
       </c>
       <c r="AX49" s="36" t="inlineStr">
         <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY49" s="36" t="n"/>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY49" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ49" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13998,14 +14114,22 @@
       </c>
       <c r="BA49" s="36" t="inlineStr">
         <is>
-          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
-        </is>
-      </c>
-      <c r="BB49" s="36" t="n"/>
-      <c r="BC49" s="36" t="n"/>
+          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益 | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB49" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC49" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD49" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE49" s="40" t="inlineStr">
@@ -14033,7 +14157,7 @@
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in neurology</t>
+          <t>预印本</t>
         </is>
       </c>
       <c r="F50" s="38" t="inlineStr">
@@ -14047,12 +14171,22 @@
         </is>
       </c>
       <c r="H50" s="38" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" s="38" t="n"/>
-      <c r="J50" s="38" t="n"/>
-      <c r="K50" s="38" t="n">
-        <v>69.3</v>
+        <v>14</v>
+      </c>
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -14060,13 +14194,15 @@
         </is>
       </c>
       <c r="M50" s="38" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N50" s="38" t="n">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="N50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O50" s="38" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="P50" s="38" t="inlineStr">
         <is>
@@ -14080,12 +14216,12 @@
       </c>
       <c r="R50" s="38" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S50" s="38" t="inlineStr">
         <is>
-          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
+          <t>Engage</t>
         </is>
       </c>
       <c r="T50" s="38" t="inlineStr">
@@ -14093,34 +14229,52 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U50" s="38" t="n">
-        <v>5</v>
+      <c r="U50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V50" s="38" t="n">
         <v>30</v>
       </c>
-      <c r="W50" s="37" t="n"/>
+      <c r="W50" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X50" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z50" s="38" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA50" s="38" t="inlineStr">
         <is>
-          <t>tRNS</t>
-        </is>
-      </c>
-      <c r="AB50" s="37" t="n"/>
+          <t>tDCS/tRNS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB50" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC50" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD50" s="38" t="n"/>
+          <t>tRNS app</t>
+        </is>
+      </c>
+      <c r="AD50" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE50" t="n">
         <v>5</v>
       </c>
@@ -14131,7 +14285,8 @@
       </c>
       <c r="AG50" s="38" t="inlineStr">
         <is>
-          <t>non-verbal logical reasoning</t>
+          <t>ed with executive tasks that were
+dissimilar from the training tasks</t>
         </is>
       </c>
       <c r="AH50" s="38" t="inlineStr">
@@ -14141,38 +14296,55 @@
       </c>
       <c r="AI50" s="38" t="inlineStr">
         <is>
-          <t>Attention; memory; executive functions</t>
-        </is>
-      </c>
-      <c r="AJ50" s="38" t="n"/>
+          <t>such as
+weekly calendar planning and driving knowledge, 1 month
+after a 5-day int</t>
+        </is>
+      </c>
+      <c r="AJ50" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK50" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL50" s="38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AL50" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="AM50" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN50" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN50" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO50" s="38" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP50" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ50" s="38" t="n"/>
-      <c r="AR50" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ50" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AR50" s="38" t="inlineStr">
+        <is>
+          <t>brain
+changes.</t>
+        </is>
+      </c>
       <c r="AS50" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -14185,21 +14357,29 @@
       </c>
       <c r="AU50" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV50" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY50" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV50" s="37" t="n"/>
-      <c r="AW50" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AX50" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY50" s="38" t="n"/>
       <c r="AZ50" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14207,14 +14387,22 @@
       </c>
       <c r="BA50" s="38" t="inlineStr">
         <is>
-          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
-        </is>
-      </c>
-      <c r="BB50" s="38" t="n"/>
-      <c r="BC50" s="38" t="n"/>
+          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组） | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB50" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC50" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD50" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE50" s="40" t="inlineStr">
@@ -14242,7 +14430,7 @@
       </c>
       <c r="E51" s="36" t="inlineStr">
         <is>
-          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F51" s="36" t="inlineStr">
@@ -14252,24 +14440,40 @@
       </c>
       <c r="G51" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H51" s="36" t="n">
-        <v>56</v>
-      </c>
-      <c r="I51" s="36" t="n"/>
-      <c r="J51" s="36" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="I51" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="J51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K51" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="M51" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" s="36" t="n"/>
-      <c r="O51" s="36" t="n"/>
+      <c r="M51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P51" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -14282,47 +14486,67 @@
       </c>
       <c r="R51" s="36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S51" s="36" t="inlineStr">
         <is>
-          <t>letter updating task</t>
+          <t>wome</t>
         </is>
       </c>
       <c r="T51" s="36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U51" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="V51" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="W51" s="35" t="n"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W51" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X51" s="36" t="n">
         <v>3</v>
       </c>
       <c r="Y51" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z51" s="36" t="n"/>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA51" s="36" t="inlineStr">
         <is>
-          <t>tDCS</t>
-        </is>
-      </c>
-      <c r="AB51" s="35" t="n"/>
+          <t>tDCS/TMS/药物</t>
+        </is>
+      </c>
+      <c r="AB51" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AC51" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD51" s="36" t="n"/>
+          <t>the app; the 10</t>
+        </is>
+      </c>
+      <c r="AD51" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE51" t="n">
         <v>3</v>
       </c>
@@ -14333,7 +14557,7 @@
       </c>
       <c r="AG51" s="36" t="inlineStr">
         <is>
-          <t>n-back (near transfer)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH51" s="36" t="inlineStr">
@@ -14343,19 +14567,21 @@
       </c>
       <c r="AI51" s="36" t="inlineStr">
         <is>
-          <t>executive/memory tasks</t>
-        </is>
-      </c>
-      <c r="AJ51" s="36" t="n"/>
+          <t>virtual reality maze task24)</t>
+        </is>
+      </c>
+      <c r="AJ51" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK51" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL51" s="36" t="inlineStr">
-        <is>
-          <t>1;7</t>
-        </is>
+      <c r="AL51" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="AM51" s="35" t="inlineStr">
         <is>
@@ -14370,27 +14596,39 @@
       </c>
       <c r="AP51" s="36" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ51" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/MRI</t>
+        </is>
+      </c>
+      <c r="AR51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS51" s="36" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AT51" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ51" s="36" t="n"/>
-      <c r="AR51" s="36" t="n"/>
-      <c r="AS51" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT51" s="36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="AU51" s="36" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV51" s="35" t="n"/>
+      <c r="AV51" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="AW51" s="36" t="inlineStr">
         <is>
           <t>否</t>
@@ -14401,7 +14639,11 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="AY51" s="36" t="n"/>
+      <c r="AY51" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ51" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14409,14 +14651,22 @@
       </c>
       <c r="BA51" s="36" t="inlineStr">
         <is>
-          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
-        </is>
-      </c>
-      <c r="BB51" s="36" t="n"/>
-      <c r="BC51" s="36" t="n"/>
+          <t>tDCS-assisted letter updating；n-back近迁移显著 | 待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="BB51" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC51" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD51" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE51" s="40" t="inlineStr">
@@ -14444,7 +14694,7 @@
       </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F52" s="38" t="inlineStr">
@@ -14454,30 +14704,40 @@
       </c>
       <c r="G52" s="38" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H52" s="38" t="n">
-        <v>487</v>
-      </c>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="38" t="n"/>
+        <v>242</v>
+      </c>
+      <c r="I52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J52" s="38" t="n">
+        <v>245</v>
+      </c>
       <c r="K52" s="38" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>old-old</t>
         </is>
       </c>
-      <c r="M52" s="38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N52" s="38" t="n">
-        <v>52</v>
+      <c r="M52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O52" s="38" t="n">
-        <v>15.65</v>
+        <v>15.7</v>
       </c>
       <c r="P52" s="38" t="inlineStr">
         <is>
@@ -14491,12 +14751,12 @@
       </c>
       <c r="R52" s="38" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S52" s="38" t="inlineStr">
         <is>
-          <t>syllable span + auditory discrimination (IMPACT program)</t>
+          <t>wome; engage; letter-number sequencing</t>
         </is>
       </c>
       <c r="T52" s="38" t="inlineStr">
@@ -14504,81 +14764,119 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U52" s="38" t="n">
-        <v>40</v>
-      </c>
-      <c r="V52" s="38" t="n">
-        <v>60</v>
-      </c>
-      <c r="W52" s="37" t="n"/>
-      <c r="X52" s="38" t="n"/>
+      <c r="U52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W52" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X52" s="38" t="n">
+        <v>8</v>
+      </c>
       <c r="Y52" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z52" s="38" t="n"/>
+      <c r="Z52" s="38" t="inlineStr">
+        <is>
+          <t>expect to improve
+and to the same degree as those in the training condition on the
+outcomes</t>
+        </is>
+      </c>
       <c r="AA52" s="38" t="inlineStr">
         <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB52" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC52" s="38" t="inlineStr">
+        <is>
+          <t>Posit Science; This app</t>
+        </is>
+      </c>
+      <c r="AD52" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AH52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AI52" s="38" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ52" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL52" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN52" s="37" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AO52" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP52" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ52" s="38" t="inlineStr">
+        <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB52" s="37" t="n"/>
-      <c r="AC52" s="38" t="inlineStr">
-        <is>
-          <t>Posit Science (IMPACT)</t>
-        </is>
-      </c>
-      <c r="AD52" s="38" t="n"/>
-      <c r="AF52" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG52" s="38" t="inlineStr">
-        <is>
-          <t>WM factor score</t>
-        </is>
-      </c>
-      <c r="AH52" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AI52" s="38" t="inlineStr">
-        <is>
-          <t>List memory; text memory</t>
-        </is>
-      </c>
-      <c r="AJ52" s="38" t="n"/>
-      <c r="AK52" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AL52" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM52" s="37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN52" s="37" t="n"/>
-      <c r="AO52" s="38" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP52" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ52" s="38" t="n"/>
-      <c r="AR52" s="38" t="n"/>
+      <c r="AR52" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS52" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -14591,21 +14889,29 @@
       </c>
       <c r="AU52" s="38" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV52" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY52" s="38" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV52" s="37" t="n"/>
-      <c r="AW52" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AX52" s="38" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AY52" s="38" t="n"/>
       <c r="AZ52" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14613,14 +14919,22 @@
       </c>
       <c r="BA52" s="38" t="inlineStr">
         <is>
-          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
-        </is>
-      </c>
-      <c r="BB52" s="38" t="n"/>
-      <c r="BC52" s="38" t="n"/>
+          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB52" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC52" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD52" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE52" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -14962,7 +14962,7 @@
       </c>
       <c r="E53" s="36" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F53" s="36" t="inlineStr">
@@ -14972,32 +14972,44 @@
       </c>
       <c r="G53" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H53" s="36" t="n">
-        <v>24</v>
-      </c>
-      <c r="I53" s="36" t="n"/>
-      <c r="J53" s="36" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="I53" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="J53" s="36" t="n">
+        <v>12</v>
+      </c>
       <c r="K53" s="36" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M53" s="36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N53" s="36" t="n">
-        <v>79</v>
-      </c>
-      <c r="O53" s="36" t="n"/>
+      <c r="M53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="P53" s="36" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q53" s="36" t="inlineStr">
@@ -15012,7 +15024,7 @@
       </c>
       <c r="S53" s="36" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>wome; engage; Reading Span</t>
         </is>
       </c>
       <c r="T53" s="36" t="inlineStr">
@@ -15020,34 +15032,52 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U53" s="36" t="n">
-        <v>6</v>
+      <c r="U53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V53" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="W53" s="35" t="n"/>
+      <c r="W53" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X53" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z53" s="36" t="n"/>
+      <c r="Z53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA53" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB53" s="35" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB53" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC53" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD53" s="36" t="n"/>
+          <t>promising app</t>
+        </is>
+      </c>
+      <c r="AD53" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE53" t="n">
         <v>2</v>
       </c>
@@ -15058,7 +15088,7 @@
       </c>
       <c r="AG53" s="36" t="inlineStr">
         <is>
-          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH53" s="36" t="inlineStr">
@@ -15066,17 +15096,23 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AI53" s="36" t="n"/>
-      <c r="AJ53" s="36" t="n"/>
+      <c r="AI53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ53" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK53" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AL53" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AL53" s="36" t="n">
+        <v>6</v>
       </c>
       <c r="AM53" s="35" t="inlineStr">
         <is>
@@ -15085,12 +15121,12 @@
       </c>
       <c r="AN53" s="35" t="inlineStr">
         <is>
-          <t>d=0.5-0.9</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AO53" s="36" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP53" s="36" t="inlineStr">
@@ -15100,41 +15136,49 @@
       </c>
       <c r="AQ53" s="36" t="inlineStr">
         <is>
-          <t>EEG</t>
+          <t>fMRI/EEG/ERP/MRI/PET</t>
         </is>
       </c>
       <c r="AR53" s="36" t="inlineStr">
         <is>
-          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
+          <t>EEG activity among older adults.</t>
         </is>
       </c>
       <c r="AS53" s="36" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AT53" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU53" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV53" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY53" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV53" s="35" t="n"/>
-      <c r="AW53" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX53" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY53" s="36" t="n"/>
       <c r="AZ53" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15142,14 +15186,22 @@
       </c>
       <c r="BA53" s="36" t="inlineStr">
         <is>
-          <t>静息态EEG；额叶振荡活动；先导研究</t>
-        </is>
-      </c>
-      <c r="BB53" s="36" t="n"/>
-      <c r="BC53" s="36" t="n"/>
+          <t>静息态EEG；额叶振荡活动；先导研究 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB53" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC53" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD53" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE53" s="40" t="inlineStr">
@@ -15177,7 +15229,7 @@
       </c>
       <c r="E54" s="38" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>预印本</t>
         </is>
       </c>
       <c r="F54" s="38" t="inlineStr">
@@ -15193,8 +15245,16 @@
       <c r="H54" s="38" t="n">
         <v>66</v>
       </c>
-      <c r="I54" s="38" t="n"/>
-      <c r="J54" s="38" t="n"/>
+      <c r="I54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K54" s="38" t="n">
         <v>69.58</v>
       </c>
@@ -15203,18 +15263,24 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M54" s="38" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="N54" s="38" t="n">
-        <v>48</v>
-      </c>
-      <c r="O54" s="38" t="n">
-        <v>13.33</v>
+      <c r="M54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N54" s="38" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="O54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P54" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q54" s="38" t="inlineStr">
@@ -15224,12 +15290,12 @@
       </c>
       <c r="R54" s="38" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S54" s="38" t="inlineStr">
         <is>
-          <t>single-domain WM (n-back) or multidomain EF training</t>
+          <t>dual n-back; engage</t>
         </is>
       </c>
       <c r="T54" s="38" t="inlineStr">
@@ -15238,12 +15304,16 @@
         </is>
       </c>
       <c r="U54" s="38" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V54" s="38" t="n">
         <v>45</v>
       </c>
-      <c r="W54" s="37" t="n"/>
+      <c r="W54" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X54" s="38" t="n">
         <v>4</v>
       </c>
@@ -15252,19 +15322,31 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z54" s="38" t="n"/>
+      <c r="Z54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA54" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB54" s="37" t="n"/>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB54" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC54" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD54" s="38" t="n"/>
+          <t>of App; an 11</t>
+        </is>
+      </c>
+      <c r="AD54" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE54" t="n">
         <v>3</v>
       </c>
@@ -15275,7 +15357,7 @@
       </c>
       <c r="AG54" s="38" t="inlineStr">
         <is>
-          <t>n-back; global EF accuracy</t>
+          <t>measured using the WCST)</t>
         </is>
       </c>
       <c r="AH54" s="38" t="inlineStr">
@@ -15285,10 +15367,15 @@
       </c>
       <c r="AI54" s="38" t="inlineStr">
         <is>
-          <t>Prospective memory (Virtual Week); fluid intelligence</t>
-        </is>
-      </c>
-      <c r="AJ54" s="38" t="n"/>
+          <t>exhibiting larger pre-post gains compared to the AC group 
+across all VW task typ</t>
+        </is>
+      </c>
+      <c r="AJ54" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK54" s="38" t="inlineStr">
         <is>
           <t>是</t>
@@ -15299,10 +15386,14 @@
       </c>
       <c r="AM54" s="37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN54" s="37" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN54" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
       <c r="AO54" s="38" t="inlineStr">
         <is>
           <t>混合</t>
@@ -15310,11 +15401,21 @@
       </c>
       <c r="AP54" s="38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ54" s="38" t="n"/>
-      <c r="AR54" s="38" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ54" s="38" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="AR54" s="38" t="inlineStr">
+        <is>
+          <t>neural activity on 
+some aspects of the trained task to that demonstrated by 
+untrained young adults.</t>
+        </is>
+      </c>
       <c r="AS54" s="38" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -15322,26 +15423,34 @@
       </c>
       <c r="AT54" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU54" s="38" t="inlineStr">
         <is>
-          <t>未检验</t>
-        </is>
-      </c>
-      <c r="AV54" s="37" t="n"/>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV54" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="AW54" s="38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX54" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY54" s="38" t="n"/>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY54" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ54" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15349,14 +15458,22 @@
       </c>
       <c r="BA54" s="38" t="inlineStr">
         <is>
-          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
-        </is>
-      </c>
-      <c r="BB54" s="38" t="n"/>
-      <c r="BC54" s="38" t="n"/>
+          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升 | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB54" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC54" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD54" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE54" s="40" t="inlineStr">
@@ -15384,7 +15501,7 @@
       </c>
       <c r="E55" s="36" t="inlineStr">
         <is>
-          <t>Psychologie Française</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F55" s="36" t="inlineStr">
@@ -15394,30 +15511,38 @@
       </c>
       <c r="G55" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H55" s="36" t="n">
-        <v>35</v>
-      </c>
-      <c r="I55" s="36" t="n"/>
-      <c r="J55" s="36" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I55" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J55" s="36" t="n">
+        <v>17</v>
+      </c>
       <c r="K55" s="36" t="n">
-        <v>68.44</v>
+        <v>75</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M55" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N55" s="36" t="n">
-        <v>60</v>
+      <c r="M55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O55" s="36" t="n">
-        <v>11.76</v>
+        <v>2.92</v>
       </c>
       <c r="P55" s="36" t="inlineStr">
         <is>
@@ -15431,12 +15556,12 @@
       </c>
       <c r="R55" s="36" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="S55" s="36" t="inlineStr">
         <is>
-          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
+          <t>engage</t>
         </is>
       </c>
       <c r="T55" s="36" t="inlineStr">
@@ -15445,33 +15570,54 @@
         </is>
       </c>
       <c r="U55" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="V55" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W55" s="35" t="n"/>
-      <c r="X55" s="36" t="n">
         <v>3</v>
       </c>
+      <c r="V55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W55" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Y55" s="36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z55" s="36" t="n"/>
+      <c r="Z55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA55" s="36" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="AB55" s="35" t="n"/>
+      <c r="AB55" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC55" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD55" s="36" t="n"/>
+          <t>dot
+ app</t>
+        </is>
+      </c>
+      <c r="AD55" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE55" t="n">
         <v>2</v>
       </c>
@@ -15482,7 +15628,7 @@
       </c>
       <c r="AG55" s="36" t="inlineStr">
         <is>
-          <t>visuospatial WM criterion task</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH55" s="36" t="inlineStr">
@@ -15492,38 +15638,73 @@
       </c>
       <c r="AI55" s="36" t="inlineStr">
         <is>
-          <t>verbal WM; visuospatial STM; reasoning</t>
-        </is>
-      </c>
-      <c r="AJ55" s="36" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ55" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK55" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AL55" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL55" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="AM55" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN55" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN55" s="35" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="AO55" s="36" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP55" s="36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ55" s="36" t="n"/>
-      <c r="AR55" s="36" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ55" s="36" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR55" s="36" t="inlineStr">
+        <is>
+          <t>brains
+ to
+ build
+ a
+ compensatory
+ scaffold
+ in
+ response
+ to
+ age-related
+changes
+ –
+ leading
+ them
+ to
+ focus
+ on
+ abilities
+ that
+ are
+ more
+ age-</t>
+        </is>
+      </c>
       <c r="AS55" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -15531,26 +15712,34 @@
       </c>
       <c r="AT55" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU55" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV55" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY55" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV55" s="35" t="n"/>
-      <c r="AW55" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX55" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY55" s="36" t="n"/>
       <c r="AZ55" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15558,14 +15747,22 @@
       </c>
       <c r="BA55" s="36" t="inlineStr">
         <is>
-          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
-        </is>
-      </c>
-      <c r="BB55" s="36" t="n"/>
-      <c r="BC55" s="36" t="n"/>
+          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片） | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB55" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC55" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD55" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE55" s="40" t="inlineStr">
@@ -15593,7 +15790,7 @@
       </c>
       <c r="E56" s="38" t="inlineStr">
         <is>
-          <t>Journal of Cognitive Psychology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F56" s="38" t="inlineStr">
@@ -15607,10 +15804,18 @@
         </is>
       </c>
       <c r="H56" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="I56" s="38" t="n"/>
-      <c r="J56" s="38" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="I56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K56" s="38" t="n">
         <v>61.86</v>
       </c>
@@ -15619,14 +15824,18 @@
           <t>young-old</t>
         </is>
       </c>
-      <c r="M56" s="38" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="N56" s="38" t="n">
-        <v>46</v>
+      <c r="M56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O56" s="38" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="P56" s="38" t="inlineStr">
         <is>
@@ -15645,7 +15854,7 @@
       </c>
       <c r="S56" s="38" t="inlineStr">
         <is>
-          <t>n-back (strategy vs no strategy)</t>
+          <t>Dual N-back; wome</t>
         </is>
       </c>
       <c r="T56" s="38" t="inlineStr">
@@ -15656,31 +15865,51 @@
       <c r="U56" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="V56" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="W56" s="37" t="n"/>
-      <c r="X56" s="38" t="n">
-        <v>4</v>
+      <c r="V56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W56" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y56" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z56" s="38" t="n"/>
+      <c r="Z56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AA56" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB56" s="37" t="n"/>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB56" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
       <c r="AC56" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD56" s="38" t="n"/>
+          <t>in app</t>
+        </is>
+      </c>
+      <c r="AD56" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE56" t="n">
         <v>2.5</v>
       </c>
@@ -15691,7 +15920,7 @@
       </c>
       <c r="AG56" s="38" t="inlineStr">
         <is>
-          <t>n-back variant</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH56" s="38" t="inlineStr">
@@ -15701,73 +15930,93 @@
       </c>
       <c r="AI56" s="38" t="inlineStr">
         <is>
-          <t>P300 transfer measures</t>
-        </is>
-      </c>
-      <c r="AJ56" s="38" t="n"/>
+          <t>are
+Figure 1</t>
+        </is>
+      </c>
+      <c r="AJ56" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK56" s="38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM56" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN56" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO56" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ56" s="38" t="inlineStr">
+        <is>
+          <t>EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AR56" s="38" t="inlineStr">
+        <is>
+          <t>EEG was
+recorded, the purpose of which is to verify whether
+the P300-ERP amplitude changes as a function of
+training, and cognitive tests administered</t>
+        </is>
+      </c>
+      <c r="AS56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU56" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV56" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW56" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL56" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM56" s="37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN56" s="37" t="n"/>
-      <c r="AO56" s="38" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AP56" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AQ56" s="38" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AR56" s="38" t="inlineStr">
-        <is>
-          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
-        </is>
-      </c>
-      <c r="AS56" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT56" s="38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AU56" s="38" t="inlineStr">
-        <is>
-          <t>未检验</t>
-        </is>
-      </c>
-      <c r="AV56" s="37" t="n"/>
-      <c r="AW56" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AX56" s="38" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY56" s="38" t="n"/>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY56" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ56" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15775,14 +16024,22 @@
       </c>
       <c r="BA56" s="38" t="inlineStr">
         <is>
-          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
-        </is>
-      </c>
-      <c r="BB56" s="38" t="n"/>
-      <c r="BC56" s="38" t="n"/>
+          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB56" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC56" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD56" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE56" s="40" t="inlineStr">
@@ -15810,7 +16067,7 @@
       </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
-          <t>Applied Cognitive Psychology</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F57" s="36" t="inlineStr">
@@ -15820,30 +16077,38 @@
       </c>
       <c r="G57" s="36" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H57" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="I57" s="36" t="n">
         <v>91</v>
       </c>
-      <c r="I57" s="36" t="n"/>
-      <c r="J57" s="36" t="n"/>
+      <c r="J57" s="36" t="n">
+        <v>19</v>
+      </c>
       <c r="K57" s="36" t="n">
-        <v>66.84999999999999</v>
+        <v>67.97</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M57" s="36" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N57" s="36" t="n">
-        <v>55</v>
+      <c r="M57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N57" s="36" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
       </c>
       <c r="O57" s="36" t="n">
-        <v>14.03</v>
+        <v>13.99</v>
       </c>
       <c r="P57" s="36" t="inlineStr">
         <is>
@@ -15857,12 +16122,13 @@
       </c>
       <c r="R57" s="36" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S57" s="36" t="inlineStr">
         <is>
-          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
+          <t>dual n-back; Cogmed; wome; operation span; reading
+span; complex span</t>
         </is>
       </c>
       <c r="T57" s="36" t="inlineStr">
@@ -15871,12 +16137,18 @@
         </is>
       </c>
       <c r="U57" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="V57" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="W57" s="35" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="V57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W57" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="X57" s="36" t="n">
         <v>6</v>
       </c>
@@ -15885,19 +16157,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="Z57" s="36" t="n"/>
+      <c r="Z57" s="36" t="inlineStr">
+        <is>
+          <t>not differ signiﬁcantly in age, education, and other demo-
+graphic characteristics such as gender ra</t>
+        </is>
+      </c>
       <c r="AA57" s="36" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB57" s="35" t="n"/>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB57" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC57" s="36" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD57" s="36" t="n"/>
+          <t>Cogmed; training app</t>
+        </is>
+      </c>
+      <c r="AD57" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE57" t="n">
         <v>2</v>
       </c>
@@ -15908,7 +16193,8 @@
       </c>
       <c r="AG57" s="36" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>to another task indicating the
+same construct, because it is not clear which task</t>
         </is>
       </c>
       <c r="AH57" s="36" t="inlineStr">
@@ -15918,38 +16204,54 @@
       </c>
       <c r="AI57" s="36" t="inlineStr">
         <is>
-          <t>Short-term memory; processing speed; reasoning</t>
-        </is>
-      </c>
-      <c r="AJ57" s="36" t="n"/>
+          <t>show overlaps (e</t>
+        </is>
+      </c>
+      <c r="AJ57" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
       <c r="AK57" s="36" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM57" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN57" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO57" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP57" s="36" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL57" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM57" s="35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN57" s="35" t="n"/>
-      <c r="AO57" s="36" t="inlineStr">
-        <is>
-          <t>无迁移</t>
-        </is>
-      </c>
-      <c r="AP57" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ57" s="36" t="n"/>
-      <c r="AR57" s="36" t="n"/>
+      <c r="AQ57" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR57" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS57" s="36" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -15957,26 +16259,34 @@
       </c>
       <c r="AT57" s="36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU57" s="36" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV57" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY57" s="36" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV57" s="35" t="n"/>
-      <c r="AW57" s="36" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX57" s="36" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY57" s="36" t="n"/>
       <c r="AZ57" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15984,14 +16294,22 @@
       </c>
       <c r="BA57" s="36" t="inlineStr">
         <is>
-          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
-        </is>
-      </c>
-      <c r="BB57" s="36" t="n"/>
-      <c r="BC57" s="36" t="n"/>
+          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment） | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB57" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC57" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD57" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE57" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -16337,7 +16337,7 @@
       </c>
       <c r="E58" s="38" t="inlineStr">
         <is>
-          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F58" s="38" t="inlineStr">
@@ -16351,30 +16351,38 @@
         </is>
       </c>
       <c r="H58" s="38" t="n">
-        <v>68</v>
-      </c>
-      <c r="I58" s="38" t="n"/>
-      <c r="J58" s="38" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="I58" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="38" t="n">
+        <v>22</v>
+      </c>
       <c r="K58" s="38" t="n">
-        <v>70.64</v>
+        <v>21.36</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M58" s="38" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="N58" s="38" t="n">
-        <v>100</v>
+      <c r="M58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O58" s="38" t="n">
-        <v>11.14</v>
+        <v>0.786</v>
       </c>
       <c r="P58" s="38" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q58" s="38" t="inlineStr">
@@ -16389,7 +16397,7 @@
       </c>
       <c r="S58" s="38" t="inlineStr">
         <is>
-          <t>adaptive WM updating (numerical updating + 1-back)</t>
+          <t>wome; engage; complex span</t>
         </is>
       </c>
       <c r="T58" s="38" t="inlineStr">
@@ -16400,31 +16408,52 @@
       <c r="U58" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="V58" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="W58" s="37" t="n"/>
-      <c r="X58" s="38" t="n">
-        <v>4</v>
+      <c r="V58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W58" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y58" s="38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z58" s="38" t="n"/>
+      <c r="Z58" s="38" t="inlineStr">
+        <is>
+          <t>no 
+intervention during this period</t>
+        </is>
+      </c>
       <c r="AA58" s="38" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="AB58" s="37" t="n"/>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB58" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
       <c r="AC58" s="38" t="inlineStr">
         <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="AD58" s="38" t="n"/>
+          <t>alternative app</t>
+        </is>
+      </c>
+      <c r="AD58" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
       <c r="AE58" t="n">
         <v>5</v>
       </c>
@@ -16435,7 +16464,7 @@
       </c>
       <c r="AG58" s="38" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH58" s="38" t="inlineStr">
@@ -16445,65 +16474,91 @@
       </c>
       <c r="AI58" s="38" t="inlineStr">
         <is>
-          <t>Cognitive reappraisal (emotion regulation task)</t>
-        </is>
-      </c>
-      <c r="AJ58" s="38" t="n"/>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ58" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
       <c r="AK58" s="38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM58" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN58" s="37" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="AO58" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ58" s="38" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR58" s="38" t="inlineStr">
+        <is>
+          <t>imaging studies corroborate this 
+mechanistic overlap by revealing co-activation within the 
+dorsolateral prefrontal cortex (DLPFC), a region integral</t>
+        </is>
+      </c>
+      <c r="AS58" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU58" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV58" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW58" s="38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL58" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AM58" s="37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AN58" s="37" t="n"/>
-      <c r="AO58" s="38" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AP58" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ58" s="38" t="n"/>
-      <c r="AR58" s="38" t="n"/>
-      <c r="AS58" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT58" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AU58" s="38" t="inlineStr">
+      <c r="AX58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY58" s="38" t="inlineStr">
         <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV58" s="37" t="n"/>
-      <c r="AW58" s="38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX58" s="38" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AY58" s="38" t="n"/>
       <c r="AZ58" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -16511,14 +16566,22 @@
       </c>
       <c r="BA58" s="38" t="inlineStr">
         <is>
-          <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局</t>
-        </is>
-      </c>
-      <c r="BB58" s="38" t="n"/>
-      <c r="BC58" s="38" t="n"/>
+          <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB58" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC58" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD58" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE58" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -2684,59 +2684,243 @@
       <c r="C8" s="37" t="n">
         <v>2020</v>
       </c>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
-      <c r="I8" s="38" t="n"/>
-      <c r="J8" s="38" t="n"/>
-      <c r="K8" s="38" t="n"/>
-      <c r="M8" s="38" t="n"/>
-      <c r="N8" s="38" t="n"/>
-      <c r="O8" s="38" t="n"/>
-      <c r="P8" s="38" t="n"/>
-      <c r="Q8" s="38" t="n"/>
-      <c r="R8" s="38" t="n"/>
-      <c r="S8" s="38" t="n"/>
-      <c r="T8" s="38" t="n"/>
-      <c r="U8" s="38" t="n"/>
-      <c r="V8" s="38" t="n"/>
-      <c r="W8" s="37" t="n"/>
-      <c r="X8" s="38" t="n"/>
-      <c r="Y8" s="38" t="n"/>
-      <c r="Z8" s="38" t="n"/>
-      <c r="AA8" s="38" t="n"/>
-      <c r="AB8" s="37" t="n"/>
-      <c r="AC8" s="38" t="n"/>
-      <c r="AD8" s="38" t="n"/>
-      <c r="AF8" s="38" t="n"/>
-      <c r="AG8" s="38" t="n"/>
-      <c r="AH8" s="38" t="n"/>
-      <c r="AI8" s="38" t="n"/>
-      <c r="AJ8" s="38" t="n"/>
-      <c r="AK8" s="38" t="n"/>
-      <c r="AL8" s="38" t="n"/>
-      <c r="AM8" s="37" t="n"/>
-      <c r="AN8" s="37" t="n"/>
-      <c r="AO8" s="38" t="n"/>
-      <c r="AP8" s="38" t="n"/>
-      <c r="AQ8" s="38" t="n"/>
-      <c r="AR8" s="38" t="n"/>
-      <c r="AS8" s="38" t="n"/>
-      <c r="AT8" s="38" t="n"/>
-      <c r="AU8" s="38" t="n"/>
-      <c r="AV8" s="37" t="n"/>
-      <c r="AW8" s="38" t="n"/>
-      <c r="AX8" s="38" t="n"/>
-      <c r="AY8" s="38" t="n"/>
-      <c r="AZ8" s="38" t="n"/>
-      <c r="BA8" s="38" t="n"/>
-      <c r="BB8" s="38" t="n"/>
-      <c r="BC8" s="38" t="n"/>
-      <c r="BD8" s="40" t="inlineStr">
-        <is>
-          <t>未填入</t>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Verbal working memory training in older adults: an investigation of dose response</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Aging &amp; Mental Health</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H8" s="37" t="n">
+        <v>46</v>
+      </c>
+      <c r="I8" s="37" t="n">
+        <v>18</v>
+      </c>
+      <c r="J8" s="37" t="n">
+        <v>28</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="L8" s="41" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
+      <c r="M8" s="37" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="N8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O8" s="37" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="P8" s="37" t="inlineStr">
+        <is>
+          <t>CERAD延迟回忆 + CDT + GDS + GAI + FAQ</t>
+        </is>
+      </c>
+      <c r="Q8" s="37" t="inlineStr">
+        <is>
+          <t>均通过筛查标准</t>
+        </is>
+      </c>
+      <c r="R8" s="37" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="S8" s="37" t="inlineStr">
+        <is>
+          <t>Categorization Working Memory Span (CWMS - Brazilian Portuguese adaptation)</t>
+        </is>
+      </c>
+      <c r="T8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U8" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="37" t="inlineStr">
+        <is>
+          <t>30-40</t>
+        </is>
+      </c>
+      <c r="W8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X8" s="37" t="inlineStr">
+        <is>
+          <t>1周</t>
+        </is>
+      </c>
+      <c r="Y8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" s="37" t="inlineStr">
+        <is>
+          <t>问卷填写（主观幸福感/生活质量问卷）</t>
+        </is>
+      </c>
+      <c r="AA8" s="37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB8" s="37" t="inlineStr">
+        <is>
+          <t>重复测量ANOVA（Time×Condition）</t>
+        </is>
+      </c>
+      <c r="AC8" s="37" t="inlineStr">
+        <is>
+          <t>纸笔（实验者主导）</t>
+        </is>
+      </c>
+      <c r="AD8" s="37" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AE8" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG8" s="37" t="inlineStr">
+        <is>
+          <t>Letter Number Sequencing, Forward/Backward Digit Span, Forward/Backward Spatial Span</t>
+        </is>
+      </c>
+      <c r="AH8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AI8" s="37" t="inlineStr">
+        <is>
+          <t>Verbal Fluency (semantic), Symbol Search, Matrix Reasoning (fluid intelligence), Stroop Color task</t>
+        </is>
+      </c>
+      <c r="AJ8" s="37" t="inlineStr">
+        <is>
+          <t>流体智力/EF/其他</t>
+        </is>
+      </c>
+      <c r="AK8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL8" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN8" s="37" t="inlineStr">
+        <is>
+          <t>CWMS: large; Near transfer: large-medium; Verbal Fluency: medium; others: null</t>
+        </is>
+      </c>
+      <c r="AO8" s="37" t="inlineStr">
+        <is>
+          <t>正向</t>
+        </is>
+      </c>
+      <c r="AP8" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ8" s="37" t="n"/>
+      <c r="AR8" s="37" t="n"/>
+      <c r="AS8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT8" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU8" s="37" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV8" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW8" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX8" s="37" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY8" s="37" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AZ8" s="37" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="BA8" s="37" t="inlineStr">
+        <is>
+          <t>含Study1(3节)和Study2(6节)；此表记录Study1；Study2总体结论相似</t>
+        </is>
+      </c>
+      <c r="BB8" s="37" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC8" s="37" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="BD8" s="42" t="inlineStr">
+        <is>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE8" s="40" t="inlineStr">
@@ -2758,58 +2942,229 @@
         <v>2025</v>
       </c>
       <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="n"/>
-      <c r="K9" s="36" t="n"/>
-      <c r="M9" s="36" t="n"/>
-      <c r="N9" s="36" t="n"/>
-      <c r="O9" s="36" t="n"/>
-      <c r="P9" s="36" t="n"/>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>76</v>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O9" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q9" s="36" t="n"/>
-      <c r="R9" s="36" t="n"/>
-      <c r="S9" s="36" t="n"/>
-      <c r="T9" s="36" t="n"/>
-      <c r="U9" s="36" t="n"/>
-      <c r="V9" s="36" t="n"/>
-      <c r="W9" s="35" t="n"/>
-      <c r="X9" s="36" t="n"/>
-      <c r="Y9" s="36" t="n"/>
-      <c r="Z9" s="36" t="n"/>
-      <c r="AA9" s="36" t="n"/>
-      <c r="AB9" s="35" t="n"/>
-      <c r="AC9" s="36" t="n"/>
-      <c r="AD9" s="36" t="n"/>
-      <c r="AF9" s="36" t="n"/>
-      <c r="AG9" s="36" t="n"/>
+      <c r="R9" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S9" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; Cogmed; BrainHQ; Lumosity; engage; Complex span</t>
+        </is>
+      </c>
+      <c r="T9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U9" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="V9" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="W9" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X9" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="36" t="inlineStr">
+        <is>
+          <t>cognitive assessments</t>
+        </is>
+      </c>
+      <c r="AA9" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB9" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC9" s="36" t="inlineStr">
+        <is>
+          <t>Lumosity; effective app</t>
+        </is>
+      </c>
+      <c r="AD9" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH9" s="36" t="n"/>
-      <c r="AI9" s="36" t="n"/>
-      <c r="AJ9" s="36" t="n"/>
-      <c r="AK9" s="36" t="n"/>
-      <c r="AL9" s="36" t="n"/>
-      <c r="AM9" s="35" t="n"/>
-      <c r="AN9" s="35" t="n"/>
-      <c r="AO9" s="36" t="n"/>
-      <c r="AP9" s="36" t="n"/>
-      <c r="AQ9" s="36" t="n"/>
-      <c r="AR9" s="36" t="n"/>
-      <c r="AS9" s="36" t="n"/>
-      <c r="AT9" s="36" t="n"/>
-      <c r="AU9" s="36" t="n"/>
-      <c r="AV9" s="35" t="n"/>
-      <c r="AW9" s="36" t="n"/>
-      <c r="AX9" s="36" t="n"/>
-      <c r="AY9" s="36" t="n"/>
+      <c r="AI9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ9" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL9" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM9" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN9" s="35" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AO9" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ9" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR9" s="36" t="inlineStr">
+        <is>
+          <t>neural changes
+are proposed to be the underlying mechanisms for the observed
+cognitive enhancements (Duda &amp; Sweet, 2020; Karbach &amp; Schubert,
+2013).</t>
+        </is>
+      </c>
+      <c r="AS9" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT9" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU9" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV9" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW9" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX9" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY9" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ9" s="36" t="n"/>
-      <c r="BA9" s="36" t="n"/>
-      <c r="BB9" s="36" t="n"/>
-      <c r="BC9" s="36" t="n"/>
+      <c r="BA9" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB9" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC9" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD9" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE9" s="40" t="inlineStr">
@@ -2831,58 +3186,230 @@
         <v>2017</v>
       </c>
       <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="M10" s="38" t="n"/>
-      <c r="N10" s="38" t="n"/>
-      <c r="O10" s="38" t="n"/>
-      <c r="P10" s="38" t="n"/>
+      <c r="G10" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>66</v>
+      </c>
+      <c r="I10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K10" s="38" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="M10" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="N10" s="38" t="inlineStr">
+        <is>
+          <t>103%</t>
+        </is>
+      </c>
+      <c r="O10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P10" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q10" s="38" t="n"/>
-      <c r="R10" s="38" t="n"/>
-      <c r="S10" s="38" t="n"/>
-      <c r="T10" s="38" t="n"/>
-      <c r="U10" s="38" t="n"/>
-      <c r="V10" s="38" t="n"/>
-      <c r="W10" s="37" t="n"/>
-      <c r="X10" s="38" t="n"/>
-      <c r="Y10" s="38" t="n"/>
-      <c r="Z10" s="38" t="n"/>
-      <c r="AA10" s="38" t="n"/>
-      <c r="AB10" s="37" t="n"/>
-      <c r="AC10" s="38" t="n"/>
-      <c r="AD10" s="38" t="n"/>
-      <c r="AF10" s="38" t="n"/>
-      <c r="AG10" s="38" t="n"/>
+      <c r="R10" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S10" s="38" t="inlineStr">
+        <is>
+          <t>engage; complex span</t>
+        </is>
+      </c>
+      <c r="T10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U10" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="V10" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" s="37" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="X10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA10" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB10" s="37" t="inlineStr">
+        <is>
+          <t>LMM/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC10" s="38" t="inlineStr">
+        <is>
+          <t>Priority Program</t>
+        </is>
+      </c>
+      <c r="AD10" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG10" s="38" t="inlineStr">
+        <is>
+          <t>and the absence of far transfer effects to all of the assessed 
+abilities</t>
+        </is>
+      </c>
       <c r="AH10" s="38" t="n"/>
-      <c r="AI10" s="38" t="n"/>
-      <c r="AJ10" s="38" t="n"/>
-      <c r="AK10" s="38" t="n"/>
-      <c r="AL10" s="38" t="n"/>
-      <c r="AM10" s="37" t="n"/>
-      <c r="AN10" s="37" t="n"/>
-      <c r="AO10" s="38" t="n"/>
-      <c r="AP10" s="38" t="n"/>
-      <c r="AQ10" s="38" t="n"/>
-      <c r="AR10" s="38" t="n"/>
-      <c r="AS10" s="38" t="n"/>
-      <c r="AT10" s="38" t="n"/>
-      <c r="AU10" s="38" t="n"/>
-      <c r="AV10" s="37" t="n"/>
-      <c r="AW10" s="38" t="n"/>
-      <c r="AX10" s="38" t="n"/>
-      <c r="AY10" s="38" t="n"/>
+      <c r="AI10" s="38" t="inlineStr">
+        <is>
+          <t>ed 
+abilities</t>
+        </is>
+      </c>
+      <c r="AJ10" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM10" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN10" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO10" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP10" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ10" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR10" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS10" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU10" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV10" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW10" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX10" s="38" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY10" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ10" s="38" t="n"/>
-      <c r="BA10" s="38" t="n"/>
-      <c r="BB10" s="38" t="n"/>
-      <c r="BC10" s="38" t="n"/>
+      <c r="BA10" s="38" t="inlineStr">
+        <is>
+          <t>待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB10" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC10" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD10" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE10" s="40" t="inlineStr">
@@ -2904,58 +3431,222 @@
         <v>2022</v>
       </c>
       <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>预印本</t>
+        </is>
+      </c>
       <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="n"/>
-      <c r="M11" s="36" t="n"/>
-      <c r="N11" s="36" t="n"/>
-      <c r="O11" s="36" t="n"/>
-      <c r="P11" s="36" t="n"/>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="N11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P11" s="36" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q11" s="36" t="n"/>
-      <c r="R11" s="36" t="n"/>
-      <c r="S11" s="36" t="n"/>
-      <c r="T11" s="36" t="n"/>
-      <c r="U11" s="36" t="n"/>
-      <c r="V11" s="36" t="n"/>
-      <c r="W11" s="35" t="n"/>
-      <c r="X11" s="36" t="n"/>
-      <c r="Y11" s="36" t="n"/>
-      <c r="Z11" s="36" t="n"/>
-      <c r="AA11" s="36" t="n"/>
-      <c r="AB11" s="35" t="n"/>
-      <c r="AC11" s="36" t="n"/>
-      <c r="AD11" s="36" t="n"/>
-      <c r="AF11" s="36" t="n"/>
-      <c r="AG11" s="36" t="n"/>
+      <c r="R11" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S11" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; wome</t>
+        </is>
+      </c>
+      <c r="T11" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U11" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W11" s="35" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="X11" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA11" s="36" t="inlineStr">
+        <is>
+          <t>tDCS/药物</t>
+        </is>
+      </c>
+      <c r="AB11" s="35" t="inlineStr">
+        <is>
+          <t>LMM/ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC11" s="36" t="inlineStr">
+        <is>
+          <t>were app; two 5</t>
+        </is>
+      </c>
+      <c r="AD11" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG11" s="36" t="inlineStr">
+        <is>
+          <t>ed
+through Digit Span</t>
+        </is>
+      </c>
       <c r="AH11" s="36" t="n"/>
-      <c r="AI11" s="36" t="n"/>
-      <c r="AJ11" s="36" t="n"/>
-      <c r="AK11" s="36" t="n"/>
-      <c r="AL11" s="36" t="n"/>
-      <c r="AM11" s="35" t="n"/>
+      <c r="AI11" s="36" t="inlineStr">
+        <is>
+          <t>by Raven’s
+Advanced Progressive Matrices (RAPM), while the near transfer effects</t>
+        </is>
+      </c>
+      <c r="AJ11" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM11" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN11" s="35" t="n"/>
-      <c r="AO11" s="36" t="n"/>
-      <c r="AP11" s="36" t="n"/>
-      <c r="AQ11" s="36" t="n"/>
-      <c r="AR11" s="36" t="n"/>
-      <c r="AS11" s="36" t="n"/>
-      <c r="AT11" s="36" t="n"/>
-      <c r="AU11" s="36" t="n"/>
-      <c r="AV11" s="35" t="n"/>
-      <c r="AW11" s="36" t="n"/>
-      <c r="AX11" s="36" t="n"/>
-      <c r="AY11" s="36" t="n"/>
+      <c r="AO11" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ11" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG</t>
+        </is>
+      </c>
+      <c r="AR11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS11" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU11" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV11" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX11" s="36" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY11" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AZ11" s="36" t="n"/>
-      <c r="BA11" s="36" t="n"/>
-      <c r="BB11" s="36" t="n"/>
-      <c r="BC11" s="36" t="n"/>
+      <c r="BA11" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB11" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC11" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD11" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE11" s="40" t="inlineStr">
@@ -2977,58 +3668,228 @@
         <v>2016</v>
       </c>
       <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="38" t="n"/>
-      <c r="I12" s="38" t="n"/>
-      <c r="J12" s="38" t="n"/>
-      <c r="K12" s="38" t="n"/>
-      <c r="M12" s="38" t="n"/>
-      <c r="N12" s="38" t="n"/>
-      <c r="O12" s="38" t="n"/>
-      <c r="P12" s="38" t="n"/>
+      <c r="G12" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K12" s="38" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="M12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P12" s="38" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q12" s="38" t="n"/>
-      <c r="R12" s="38" t="n"/>
-      <c r="S12" s="38" t="n"/>
-      <c r="T12" s="38" t="n"/>
-      <c r="U12" s="38" t="n"/>
-      <c r="V12" s="38" t="n"/>
-      <c r="W12" s="37" t="n"/>
-      <c r="X12" s="38" t="n"/>
-      <c r="Y12" s="38" t="n"/>
-      <c r="Z12" s="38" t="n"/>
-      <c r="AA12" s="38" t="n"/>
-      <c r="AB12" s="37" t="n"/>
-      <c r="AC12" s="38" t="n"/>
-      <c r="AD12" s="38" t="n"/>
-      <c r="AF12" s="38" t="n"/>
-      <c r="AG12" s="38" t="n"/>
+      <c r="R12" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S12" s="38" t="inlineStr">
+        <is>
+          <t>Cogmed; engage; Reading Span; Letter-Number Sequencing</t>
+        </is>
+      </c>
+      <c r="T12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U12" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="V12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W12" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X12" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA12" s="38" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB12" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC12" s="38" t="inlineStr">
+        <is>
+          <t>Cogmed; noise app</t>
+        </is>
+      </c>
+      <c r="AD12" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH12" s="38" t="n"/>
-      <c r="AI12" s="38" t="n"/>
-      <c r="AJ12" s="38" t="n"/>
-      <c r="AK12" s="38" t="n"/>
-      <c r="AL12" s="38" t="n"/>
-      <c r="AM12" s="37" t="n"/>
+      <c r="AI12" s="38" t="inlineStr">
+        <is>
+          <t>Kidd et al</t>
+        </is>
+      </c>
+      <c r="AJ12" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM12" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN12" s="37" t="n"/>
-      <c r="AO12" s="38" t="n"/>
-      <c r="AP12" s="38" t="n"/>
-      <c r="AQ12" s="38" t="n"/>
-      <c r="AR12" s="38" t="n"/>
-      <c r="AS12" s="38" t="n"/>
-      <c r="AT12" s="38" t="n"/>
-      <c r="AU12" s="38" t="n"/>
-      <c r="AV12" s="37" t="n"/>
-      <c r="AW12" s="38" t="n"/>
-      <c r="AX12" s="38" t="n"/>
-      <c r="AY12" s="38" t="n"/>
+      <c r="AO12" s="38" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ12" s="38" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS12" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT12" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU12" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV12" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW12" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX12" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY12" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ12" s="38" t="n"/>
-      <c r="BA12" s="38" t="n"/>
-      <c r="BB12" s="38" t="n"/>
-      <c r="BC12" s="38" t="n"/>
+      <c r="BA12" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB12" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC12" s="38" t="inlineStr">
+        <is>
+          <t>交叉设计</t>
+        </is>
+      </c>
       <c r="BD12" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE12" s="40" t="inlineStr">
@@ -3050,58 +3911,228 @@
         <v>2016</v>
       </c>
       <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="36" t="n"/>
-      <c r="K13" s="36" t="n"/>
-      <c r="M13" s="36" t="n"/>
-      <c r="N13" s="36" t="n"/>
-      <c r="O13" s="36" t="n"/>
-      <c r="P13" s="36" t="n"/>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>67</v>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K13" s="36" t="n">
+        <v>13.036</v>
+      </c>
+      <c r="M13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N13" s="36" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="O13" s="36" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="P13" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q13" s="36" t="n"/>
-      <c r="R13" s="36" t="n"/>
-      <c r="S13" s="36" t="n"/>
-      <c r="T13" s="36" t="n"/>
-      <c r="U13" s="36" t="n"/>
-      <c r="V13" s="36" t="n"/>
-      <c r="W13" s="35" t="n"/>
-      <c r="X13" s="36" t="n"/>
-      <c r="Y13" s="36" t="n"/>
-      <c r="Z13" s="36" t="n"/>
-      <c r="AA13" s="36" t="n"/>
-      <c r="AB13" s="35" t="n"/>
-      <c r="AC13" s="36" t="n"/>
-      <c r="AD13" s="36" t="n"/>
-      <c r="AF13" s="36" t="n"/>
-      <c r="AG13" s="36" t="n"/>
+      <c r="R13" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S13" s="36" t="inlineStr">
+        <is>
+          <t>engage; Operation Span</t>
+        </is>
+      </c>
+      <c r="T13" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U13" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W13" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y13" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA13" s="36" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB13" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC13" s="36" t="inlineStr">
+        <is>
+          <t>To app; Page 13</t>
+        </is>
+      </c>
+      <c r="AD13" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG13" s="36" t="inlineStr">
+        <is>
+          <t>s [20]</t>
+        </is>
+      </c>
       <c r="AH13" s="36" t="n"/>
-      <c r="AI13" s="36" t="n"/>
-      <c r="AJ13" s="36" t="n"/>
-      <c r="AK13" s="36" t="n"/>
-      <c r="AL13" s="36" t="n"/>
-      <c r="AM13" s="35" t="n"/>
+      <c r="AI13" s="36" t="inlineStr">
+        <is>
+          <t>along with ecologically valid far transfer tasks, and stimulation was well tolera</t>
+        </is>
+      </c>
+      <c r="AJ13" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM13" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN13" s="35" t="n"/>
-      <c r="AO13" s="36" t="n"/>
-      <c r="AP13" s="36" t="n"/>
-      <c r="AQ13" s="36" t="n"/>
-      <c r="AR13" s="36" t="n"/>
-      <c r="AS13" s="36" t="n"/>
-      <c r="AT13" s="36" t="n"/>
-      <c r="AU13" s="36" t="n"/>
-      <c r="AV13" s="35" t="n"/>
-      <c r="AW13" s="36" t="n"/>
-      <c r="AX13" s="36" t="n"/>
-      <c r="AY13" s="36" t="n"/>
+      <c r="AO13" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ13" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG</t>
+        </is>
+      </c>
+      <c r="AR13" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imaging has 
+identified cortical changes after cognitive training in healthy older adults [29], and we evaluated whether WM 
+training + tDCS training </t>
+        </is>
+      </c>
+      <c r="AS13" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU13" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV13" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW13" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX13" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY13" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ13" s="36" t="n"/>
-      <c r="BA13" s="36" t="n"/>
-      <c r="BB13" s="36" t="n"/>
-      <c r="BC13" s="36" t="n"/>
+      <c r="BA13" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB13" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC13" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD13" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE13" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -723,7 +723,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:BE58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4154,58 +4154,224 @@
         <v>2019</v>
       </c>
       <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="38" t="n"/>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="38" t="n"/>
-      <c r="M14" s="38" t="n"/>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="38" t="n"/>
-      <c r="P14" s="38" t="n"/>
+      <c r="G14" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K14" s="38" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="M14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N14" s="38" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="O14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P14" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q14" s="38" t="n"/>
-      <c r="R14" s="38" t="n"/>
-      <c r="S14" s="38" t="n"/>
-      <c r="T14" s="38" t="n"/>
-      <c r="U14" s="38" t="n"/>
-      <c r="V14" s="38" t="n"/>
-      <c r="W14" s="37" t="n"/>
-      <c r="X14" s="38" t="n"/>
-      <c r="Y14" s="38" t="n"/>
-      <c r="Z14" s="38" t="n"/>
-      <c r="AA14" s="38" t="n"/>
-      <c r="AB14" s="37" t="n"/>
-      <c r="AC14" s="38" t="n"/>
-      <c r="AD14" s="38" t="n"/>
-      <c r="AF14" s="38" t="n"/>
-      <c r="AG14" s="38" t="n"/>
+      <c r="R14" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S14" s="38" t="inlineStr">
+        <is>
+          <t>dual N-back; Cogmed; engage; Operation SPAN; complex span</t>
+        </is>
+      </c>
+      <c r="T14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U14" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="V14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W14" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X14" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA14" s="38" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB14" s="37" t="inlineStr">
+        <is>
+          <t>MANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC14" s="38" t="inlineStr">
+        <is>
+          <t>Cogmed; training program</t>
+        </is>
+      </c>
+      <c r="AD14" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG14" s="38" t="inlineStr">
+        <is>
+          <t>and outcome measures are structurally similar</t>
+        </is>
+      </c>
       <c r="AH14" s="38" t="n"/>
-      <c r="AI14" s="38" t="n"/>
-      <c r="AJ14" s="38" t="n"/>
-      <c r="AK14" s="38" t="n"/>
-      <c r="AL14" s="38" t="n"/>
-      <c r="AM14" s="37" t="n"/>
+      <c r="AI14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ14" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM14" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN14" s="37" t="n"/>
-      <c r="AO14" s="38" t="n"/>
-      <c r="AP14" s="38" t="n"/>
-      <c r="AQ14" s="38" t="n"/>
-      <c r="AR14" s="38" t="n"/>
-      <c r="AS14" s="38" t="n"/>
-      <c r="AT14" s="38" t="n"/>
-      <c r="AU14" s="38" t="n"/>
-      <c r="AV14" s="37" t="n"/>
-      <c r="AW14" s="38" t="n"/>
-      <c r="AX14" s="38" t="n"/>
-      <c r="AY14" s="38" t="n"/>
+      <c r="AO14" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ14" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS14" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU14" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV14" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW14" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX14" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY14" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ14" s="38" t="n"/>
-      <c r="BA14" s="38" t="n"/>
-      <c r="BB14" s="38" t="n"/>
-      <c r="BC14" s="38" t="n"/>
+      <c r="BA14" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB14" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC14" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD14" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE14" s="40" t="inlineStr">
@@ -4227,58 +4393,228 @@
         <v>2021</v>
       </c>
       <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
+      <c r="E15" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="36" t="n"/>
-      <c r="K15" s="36" t="n"/>
-      <c r="M15" s="36" t="n"/>
-      <c r="N15" s="36" t="n"/>
-      <c r="O15" s="36" t="n"/>
-      <c r="P15" s="36" t="n"/>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K15" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="M15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O15" s="36" t="n">
+        <v>64</v>
+      </c>
+      <c r="P15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q15" s="36" t="n"/>
-      <c r="R15" s="36" t="n"/>
-      <c r="S15" s="36" t="n"/>
-      <c r="T15" s="36" t="n"/>
-      <c r="U15" s="36" t="n"/>
-      <c r="V15" s="36" t="n"/>
-      <c r="W15" s="35" t="n"/>
-      <c r="X15" s="36" t="n"/>
-      <c r="Y15" s="36" t="n"/>
-      <c r="Z15" s="36" t="n"/>
-      <c r="AA15" s="36" t="n"/>
-      <c r="AB15" s="35" t="n"/>
-      <c r="AC15" s="36" t="n"/>
-      <c r="AD15" s="36" t="n"/>
-      <c r="AF15" s="36" t="n"/>
-      <c r="AG15" s="36" t="n"/>
+      <c r="R15" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S15" s="36" t="inlineStr">
+        <is>
+          <t>wome; engage</t>
+        </is>
+      </c>
+      <c r="T15" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U15" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="V15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W15" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y15" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA15" s="36" t="inlineStr">
+        <is>
+          <t>tDCS/TMS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB15" s="35" t="inlineStr">
+        <is>
+          <t>LMM</t>
+        </is>
+      </c>
+      <c r="AC15" s="36" t="inlineStr">
+        <is>
+          <t>combinatorial
+app</t>
+        </is>
+      </c>
+      <c r="AD15" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF15" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH15" s="36" t="n"/>
-      <c r="AI15" s="36" t="n"/>
-      <c r="AJ15" s="36" t="n"/>
-      <c r="AK15" s="36" t="n"/>
-      <c r="AL15" s="36" t="n"/>
-      <c r="AM15" s="35" t="n"/>
+      <c r="AI15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ15" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK15" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM15" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN15" s="35" t="n"/>
-      <c r="AO15" s="36" t="n"/>
-      <c r="AP15" s="36" t="n"/>
-      <c r="AQ15" s="36" t="n"/>
-      <c r="AR15" s="36" t="n"/>
-      <c r="AS15" s="36" t="n"/>
-      <c r="AT15" s="36" t="n"/>
-      <c r="AU15" s="36" t="n"/>
-      <c r="AV15" s="35" t="n"/>
-      <c r="AW15" s="36" t="n"/>
-      <c r="AX15" s="36" t="n"/>
-      <c r="AY15" s="36" t="n"/>
+      <c r="AO15" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP15" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ15" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP/MRI</t>
+        </is>
+      </c>
+      <c r="AR15" s="36" t="inlineStr">
+        <is>
+          <t>brain activity after the unilateral
+right frontoparietal stimulation.</t>
+        </is>
+      </c>
+      <c r="AS15" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT15" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU15" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV15" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW15" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX15" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY15" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ15" s="36" t="n"/>
-      <c r="BA15" s="36" t="n"/>
-      <c r="BB15" s="36" t="n"/>
-      <c r="BC15" s="36" t="n"/>
+      <c r="BA15" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB15" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC15" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD15" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE15" s="40" t="inlineStr">
@@ -4300,58 +4636,232 @@
         <v>2019</v>
       </c>
       <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="38" t="n"/>
-      <c r="J16" s="38" t="n"/>
-      <c r="K16" s="38" t="n"/>
-      <c r="M16" s="38" t="n"/>
-      <c r="N16" s="38" t="n"/>
-      <c r="O16" s="38" t="n"/>
-      <c r="P16" s="38" t="n"/>
+      <c r="G16" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="I16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J16" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q16" s="38" t="n"/>
-      <c r="R16" s="38" t="n"/>
-      <c r="S16" s="38" t="n"/>
-      <c r="T16" s="38" t="n"/>
-      <c r="U16" s="38" t="n"/>
-      <c r="V16" s="38" t="n"/>
-      <c r="W16" s="37" t="n"/>
-      <c r="X16" s="38" t="n"/>
-      <c r="Y16" s="38" t="n"/>
-      <c r="Z16" s="38" t="n"/>
-      <c r="AA16" s="38" t="n"/>
-      <c r="AB16" s="37" t="n"/>
-      <c r="AC16" s="38" t="n"/>
-      <c r="AD16" s="38" t="n"/>
-      <c r="AF16" s="38" t="n"/>
-      <c r="AG16" s="38" t="n"/>
+      <c r="R16" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S16" s="38" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="T16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W16" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA16" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB16" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC16" s="38" t="inlineStr">
+        <is>
+          <t>was app</t>
+        </is>
+      </c>
+      <c r="AD16" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
+      <c r="AF16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH16" s="38" t="n"/>
-      <c r="AI16" s="38" t="n"/>
-      <c r="AJ16" s="38" t="n"/>
-      <c r="AK16" s="38" t="n"/>
-      <c r="AL16" s="38" t="n"/>
-      <c r="AM16" s="37" t="n"/>
-      <c r="AN16" s="37" t="n"/>
-      <c r="AO16" s="38" t="n"/>
-      <c r="AP16" s="38" t="n"/>
-      <c r="AQ16" s="38" t="n"/>
-      <c r="AR16" s="38" t="n"/>
-      <c r="AS16" s="38" t="n"/>
-      <c r="AT16" s="38" t="n"/>
-      <c r="AU16" s="38" t="n"/>
-      <c r="AV16" s="37" t="n"/>
-      <c r="AW16" s="38" t="n"/>
-      <c r="AX16" s="38" t="n"/>
-      <c r="AY16" s="38" t="n"/>
+      <c r="AI16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ16" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL16" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM16" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN16" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO16" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP16" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ16" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR16" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS16" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT16" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU16" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV16" s="37" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="AW16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX16" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY16" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ16" s="38" t="n"/>
-      <c r="BA16" s="38" t="n"/>
-      <c r="BB16" s="38" t="n"/>
-      <c r="BC16" s="38" t="n"/>
+      <c r="BA16" s="38" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="BB16" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC16" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD16" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE16" s="40" t="inlineStr">
@@ -4373,58 +4883,228 @@
         <v>2020</v>
       </c>
       <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
-      <c r="K17" s="36" t="n"/>
-      <c r="M17" s="36" t="n"/>
-      <c r="N17" s="36" t="n"/>
-      <c r="O17" s="36" t="n"/>
-      <c r="P17" s="36" t="n"/>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="n">
+        <v>55</v>
+      </c>
+      <c r="M17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P17" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q17" s="36" t="n"/>
-      <c r="R17" s="36" t="n"/>
-      <c r="S17" s="36" t="n"/>
-      <c r="T17" s="36" t="n"/>
-      <c r="U17" s="36" t="n"/>
-      <c r="V17" s="36" t="n"/>
-      <c r="W17" s="35" t="n"/>
-      <c r="X17" s="36" t="n"/>
-      <c r="Y17" s="36" t="n"/>
-      <c r="Z17" s="36" t="n"/>
-      <c r="AA17" s="36" t="n"/>
-      <c r="AB17" s="35" t="n"/>
-      <c r="AC17" s="36" t="n"/>
-      <c r="AD17" s="36" t="n"/>
-      <c r="AF17" s="36" t="n"/>
-      <c r="AG17" s="36" t="n"/>
+      <c r="R17" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S17" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; Cogmed; engage; operation span</t>
+        </is>
+      </c>
+      <c r="T17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U17" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="V17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W17" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X17" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA17" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB17" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC17" s="36" t="inlineStr">
+        <is>
+          <t>Cogmed; factors app</t>
+        </is>
+      </c>
+      <c r="AD17" s="36" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
+      <c r="AF17" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH17" s="36" t="n"/>
-      <c r="AI17" s="36" t="n"/>
-      <c r="AJ17" s="36" t="n"/>
-      <c r="AK17" s="36" t="n"/>
-      <c r="AL17" s="36" t="n"/>
-      <c r="AM17" s="35" t="n"/>
-      <c r="AN17" s="35" t="n"/>
-      <c r="AO17" s="36" t="n"/>
-      <c r="AP17" s="36" t="n"/>
-      <c r="AQ17" s="36" t="n"/>
-      <c r="AR17" s="36" t="n"/>
-      <c r="AS17" s="36" t="n"/>
-      <c r="AT17" s="36" t="n"/>
-      <c r="AU17" s="36" t="n"/>
-      <c r="AV17" s="35" t="n"/>
-      <c r="AW17" s="36" t="n"/>
-      <c r="AX17" s="36" t="n"/>
-      <c r="AY17" s="36" t="n"/>
+      <c r="AI17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ17" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM17" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN17" s="35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="AO17" s="36" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP17" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ17" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR17" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS17" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU17" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV17" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW17" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX17" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY17" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ17" s="36" t="n"/>
-      <c r="BA17" s="36" t="n"/>
-      <c r="BB17" s="36" t="n"/>
-      <c r="BC17" s="36" t="n"/>
+      <c r="BA17" s="36" t="inlineStr">
+        <is>
+          <t>待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB17" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC17" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD17" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE17" s="40" t="inlineStr">
@@ -4446,58 +5126,224 @@
         <v>2014</v>
       </c>
       <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="38" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="38" t="n"/>
-      <c r="M18" s="38" t="n"/>
-      <c r="N18" s="38" t="n"/>
-      <c r="O18" s="38" t="n"/>
-      <c r="P18" s="38" t="n"/>
+      <c r="G18" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K18" s="38" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="M18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O18" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="38" t="inlineStr">
+        <is>
+          <t>MMSE≥2; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q18" s="38" t="n"/>
-      <c r="R18" s="38" t="n"/>
-      <c r="S18" s="38" t="n"/>
-      <c r="T18" s="38" t="n"/>
-      <c r="U18" s="38" t="n"/>
-      <c r="V18" s="38" t="n"/>
-      <c r="W18" s="37" t="n"/>
-      <c r="X18" s="38" t="n"/>
-      <c r="Y18" s="38" t="n"/>
-      <c r="Z18" s="38" t="n"/>
-      <c r="AA18" s="38" t="n"/>
-      <c r="AB18" s="37" t="n"/>
-      <c r="AC18" s="38" t="n"/>
-      <c r="AD18" s="38" t="n"/>
-      <c r="AF18" s="38" t="n"/>
-      <c r="AG18" s="38" t="n"/>
+      <c r="R18" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S18" s="38" t="inlineStr">
+        <is>
+          <t>wome; engage</t>
+        </is>
+      </c>
+      <c r="T18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U18" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="V18" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="W18" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X18" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA18" s="38" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB18" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC18" s="38" t="inlineStr">
+        <is>
+          <t>novel app</t>
+        </is>
+      </c>
+      <c r="AD18" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH18" s="38" t="n"/>
-      <c r="AI18" s="38" t="n"/>
-      <c r="AJ18" s="38" t="n"/>
-      <c r="AK18" s="38" t="n"/>
-      <c r="AL18" s="38" t="n"/>
-      <c r="AM18" s="37" t="n"/>
-      <c r="AN18" s="37" t="n"/>
-      <c r="AO18" s="38" t="n"/>
-      <c r="AP18" s="38" t="n"/>
-      <c r="AQ18" s="38" t="n"/>
-      <c r="AR18" s="38" t="n"/>
-      <c r="AS18" s="38" t="n"/>
-      <c r="AT18" s="38" t="n"/>
-      <c r="AU18" s="38" t="n"/>
-      <c r="AV18" s="37" t="n"/>
-      <c r="AW18" s="38" t="n"/>
-      <c r="AX18" s="38" t="n"/>
-      <c r="AY18" s="38" t="n"/>
+      <c r="AI18" s="38" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ18" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM18" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN18" s="37" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AO18" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ18" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS18" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU18" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV18" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW18" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX18" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY18" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ18" s="38" t="n"/>
-      <c r="BA18" s="38" t="n"/>
-      <c r="BB18" s="38" t="n"/>
-      <c r="BC18" s="38" t="n"/>
+      <c r="BA18" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB18" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC18" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD18" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE18" s="40" t="inlineStr">
@@ -7438,7 +8284,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -8897,7 +9743,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -5365,58 +5365,238 @@
         <v>2013</v>
       </c>
       <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-      <c r="K19" s="36" t="n"/>
-      <c r="M19" s="36" t="n"/>
-      <c r="N19" s="36" t="n"/>
-      <c r="O19" s="36" t="n"/>
-      <c r="P19" s="36" t="n"/>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N19" s="36" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="O19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P19" s="36" t="inlineStr">
+        <is>
+          <t>Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q19" s="36" t="n"/>
-      <c r="R19" s="36" t="n"/>
-      <c r="S19" s="36" t="n"/>
-      <c r="T19" s="36" t="n"/>
-      <c r="U19" s="36" t="n"/>
-      <c r="V19" s="36" t="n"/>
-      <c r="W19" s="35" t="n"/>
-      <c r="X19" s="36" t="n"/>
-      <c r="Y19" s="36" t="n"/>
-      <c r="Z19" s="36" t="n"/>
-      <c r="AA19" s="36" t="n"/>
-      <c r="AB19" s="35" t="n"/>
-      <c r="AC19" s="36" t="n"/>
-      <c r="AD19" s="36" t="n"/>
-      <c r="AF19" s="36" t="n"/>
-      <c r="AG19" s="36" t="n"/>
+      <c r="R19" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S19" s="36" t="inlineStr">
+        <is>
+          <t>wome; engage; Spatial n-back</t>
+        </is>
+      </c>
+      <c r="T19" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>45</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y19" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="36" t="inlineStr">
+        <is>
+          <t>alternative activities (see below)</t>
+        </is>
+      </c>
+      <c r="AA19" s="36" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB19" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC19" s="36" t="inlineStr">
+        <is>
+          <t>training program; Venezia 8</t>
+        </is>
+      </c>
+      <c r="AD19" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF19" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG19" s="36" t="inlineStr">
+        <is>
+          <t>two-
+back task
+45 daily
+sessions
+3 months
+70–80 (M ¼ 74</t>
+        </is>
+      </c>
       <c r="AH19" s="36" t="n"/>
-      <c r="AI19" s="36" t="n"/>
-      <c r="AJ19" s="36" t="n"/>
-      <c r="AK19" s="36" t="n"/>
-      <c r="AL19" s="36" t="n"/>
-      <c r="AM19" s="35" t="n"/>
-      <c r="AN19" s="35" t="n"/>
-      <c r="AO19" s="36" t="n"/>
-      <c r="AP19" s="36" t="n"/>
-      <c r="AQ19" s="36" t="n"/>
-      <c r="AR19" s="36" t="n"/>
-      <c r="AS19" s="36" t="n"/>
-      <c r="AT19" s="36" t="n"/>
-      <c r="AU19" s="36" t="n"/>
-      <c r="AV19" s="35" t="n"/>
-      <c r="AW19" s="36" t="n"/>
-      <c r="AX19" s="36" t="n"/>
-      <c r="AY19" s="36" t="n"/>
+      <c r="AI19" s="36" t="inlineStr">
+        <is>
+          <t>two-
+back task
+45 daily
+sessions
+3 months
+70–80 (M ¼ 74</t>
+        </is>
+      </c>
+      <c r="AJ19" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK19" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL19" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN19" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO19" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP19" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ19" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR19" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT19" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU19" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV19" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW19" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX19" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY19" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ19" s="36" t="n"/>
       <c r="BA19" s="36" t="n"/>
-      <c r="BB19" s="36" t="n"/>
-      <c r="BC19" s="36" t="n"/>
+      <c r="BB19" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC19" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD19" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE19" s="40" t="inlineStr">
@@ -5438,58 +5618,236 @@
         <v>2020</v>
       </c>
       <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="38" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="38" t="n"/>
-      <c r="M20" s="38" t="n"/>
-      <c r="N20" s="38" t="n"/>
-      <c r="O20" s="38" t="n"/>
-      <c r="P20" s="38" t="n"/>
+      <c r="G20" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P20" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q20" s="38" t="n"/>
-      <c r="R20" s="38" t="n"/>
-      <c r="S20" s="38" t="n"/>
-      <c r="T20" s="38" t="n"/>
-      <c r="U20" s="38" t="n"/>
-      <c r="V20" s="38" t="n"/>
-      <c r="W20" s="37" t="n"/>
-      <c r="X20" s="38" t="n"/>
-      <c r="Y20" s="38" t="n"/>
-      <c r="Z20" s="38" t="n"/>
-      <c r="AA20" s="38" t="n"/>
-      <c r="AB20" s="37" t="n"/>
-      <c r="AC20" s="38" t="n"/>
-      <c r="AD20" s="38" t="n"/>
-      <c r="AF20" s="38" t="n"/>
-      <c r="AG20" s="38" t="n"/>
+      <c r="R20" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S20" s="38" t="inlineStr">
+        <is>
+          <t>Dual N-back; wome; engage; spatial 
+n-back</t>
+        </is>
+      </c>
+      <c r="T20" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U20" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="V20" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W20" s="37" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="X20" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="38" t="inlineStr">
+        <is>
+          <t>not reach statistical significance on 
+the post-test Forward Digit Span (F(1, 14) = 0</t>
+        </is>
+      </c>
+      <c r="AA20" s="38" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB20" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC20" s="38" t="inlineStr">
+        <is>
+          <t>training 
+program; the 1964</t>
+        </is>
+      </c>
+      <c r="AD20" s="38" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
+      <c r="AF20" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH20" s="38" t="n"/>
-      <c r="AI20" s="38" t="n"/>
-      <c r="AJ20" s="38" t="n"/>
-      <c r="AK20" s="38" t="n"/>
-      <c r="AL20" s="38" t="n"/>
-      <c r="AM20" s="37" t="n"/>
-      <c r="AN20" s="37" t="n"/>
-      <c r="AO20" s="38" t="n"/>
-      <c r="AP20" s="38" t="n"/>
-      <c r="AQ20" s="38" t="n"/>
-      <c r="AR20" s="38" t="n"/>
-      <c r="AS20" s="38" t="n"/>
-      <c r="AT20" s="38" t="n"/>
-      <c r="AU20" s="38" t="n"/>
-      <c r="AV20" s="37" t="n"/>
-      <c r="AW20" s="38" t="n"/>
-      <c r="AX20" s="38" t="n"/>
-      <c r="AY20" s="38" t="n"/>
+      <c r="AI20" s="38" t="inlineStr">
+        <is>
+          <t>switch-
+ing training</t>
+        </is>
+      </c>
+      <c r="AJ20" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK20" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM20" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN20" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO20" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP20" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ20" s="38" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="AR20" s="38" t="inlineStr">
+        <is>
+          <t>imaging studies sup-
+port cognitive training as able to enhance activity in brain 
+Handling editor: Stefano Federici (University of Perugia).</t>
+        </is>
+      </c>
+      <c r="AS20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT20" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU20" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV20" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW20" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX20" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY20" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ20" s="38" t="n"/>
-      <c r="BA20" s="38" t="n"/>
-      <c r="BB20" s="38" t="n"/>
-      <c r="BC20" s="38" t="n"/>
+      <c r="BA20" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB20" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC20" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD20" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE20" s="40" t="inlineStr">
@@ -5511,58 +5869,230 @@
         <v>2018</v>
       </c>
       <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
-      <c r="K21" s="36" t="n"/>
-      <c r="M21" s="36" t="n"/>
-      <c r="N21" s="36" t="n"/>
-      <c r="O21" s="36" t="n"/>
-      <c r="P21" s="36" t="n"/>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>83</v>
+      </c>
+      <c r="M21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N21" s="36" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P21" s="36" t="inlineStr">
+        <is>
+          <t>Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q21" s="36" t="n"/>
-      <c r="R21" s="36" t="n"/>
-      <c r="S21" s="36" t="n"/>
-      <c r="T21" s="36" t="n"/>
-      <c r="U21" s="36" t="n"/>
-      <c r="V21" s="36" t="n"/>
-      <c r="W21" s="35" t="n"/>
-      <c r="X21" s="36" t="n"/>
-      <c r="Y21" s="36" t="n"/>
-      <c r="Z21" s="36" t="n"/>
-      <c r="AA21" s="36" t="n"/>
-      <c r="AB21" s="35" t="n"/>
-      <c r="AC21" s="36" t="n"/>
-      <c r="AD21" s="36" t="n"/>
-      <c r="AF21" s="36" t="n"/>
-      <c r="AG21" s="36" t="n"/>
+      <c r="R21" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="T21" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W21" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X21" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA21" s="36" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB21" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
+      <c r="AC21" s="36" t="inlineStr">
+        <is>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD21" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF21" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH21" s="36" t="n"/>
-      <c r="AI21" s="36" t="n"/>
-      <c r="AJ21" s="36" t="n"/>
-      <c r="AK21" s="36" t="n"/>
-      <c r="AL21" s="36" t="n"/>
-      <c r="AM21" s="35" t="n"/>
+      <c r="AI21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ21" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK21" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM21" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN21" s="35" t="n"/>
-      <c r="AO21" s="36" t="n"/>
-      <c r="AP21" s="36" t="n"/>
-      <c r="AQ21" s="36" t="n"/>
-      <c r="AR21" s="36" t="n"/>
-      <c r="AS21" s="36" t="n"/>
-      <c r="AT21" s="36" t="n"/>
-      <c r="AU21" s="36" t="n"/>
-      <c r="AV21" s="35" t="n"/>
-      <c r="AW21" s="36" t="n"/>
-      <c r="AX21" s="36" t="n"/>
-      <c r="AY21" s="36" t="n"/>
+      <c r="AO21" s="36" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP21" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ21" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR21" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT21" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU21" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV21" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW21" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX21" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY21" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ21" s="36" t="n"/>
-      <c r="BA21" s="36" t="n"/>
-      <c r="BB21" s="36" t="n"/>
-      <c r="BC21" s="36" t="n"/>
+      <c r="BA21" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB21" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC21" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD21" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE21" s="40" t="inlineStr">
@@ -5584,58 +6114,230 @@
         <v>2022</v>
       </c>
       <c r="D22" s="38" t="n"/>
-      <c r="E22" s="38" t="n"/>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n"/>
-      <c r="H22" s="38" t="n"/>
-      <c r="I22" s="38" t="n"/>
-      <c r="J22" s="38" t="n"/>
-      <c r="K22" s="38" t="n"/>
-      <c r="M22" s="38" t="n"/>
-      <c r="N22" s="38" t="n"/>
-      <c r="O22" s="38" t="n"/>
-      <c r="P22" s="38" t="n"/>
+      <c r="G22" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H22" s="38" t="n">
+        <v>52</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K22" s="38" t="n">
+        <v>71</v>
+      </c>
+      <c r="M22" s="38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N22" s="38" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="O22" s="38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q22" s="38" t="n"/>
-      <c r="R22" s="38" t="n"/>
-      <c r="S22" s="38" t="n"/>
-      <c r="T22" s="38" t="n"/>
-      <c r="U22" s="38" t="n"/>
-      <c r="V22" s="38" t="n"/>
-      <c r="W22" s="37" t="n"/>
-      <c r="X22" s="38" t="n"/>
-      <c r="Y22" s="38" t="n"/>
-      <c r="Z22" s="38" t="n"/>
-      <c r="AA22" s="38" t="n"/>
-      <c r="AB22" s="37" t="n"/>
-      <c r="AC22" s="38" t="n"/>
-      <c r="AD22" s="38" t="n"/>
-      <c r="AF22" s="38" t="n"/>
-      <c r="AG22" s="38" t="n"/>
+      <c r="R22" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S22" s="38" t="inlineStr">
+        <is>
+          <t>BrainHQ; engage</t>
+        </is>
+      </c>
+      <c r="T22" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W22" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X22" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA22" s="38" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB22" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC22" s="38" t="inlineStr">
+        <is>
+          <t>Posit 
+Science; Interdisciplinary Program</t>
+        </is>
+      </c>
+      <c r="AD22" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF22" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG22" s="38" t="inlineStr">
+        <is>
+          <t>was the most reliable and robust 
+method for assessing cognitive training efficac</t>
+        </is>
+      </c>
       <c r="AH22" s="38" t="n"/>
-      <c r="AI22" s="38" t="n"/>
-      <c r="AJ22" s="38" t="n"/>
-      <c r="AK22" s="38" t="n"/>
-      <c r="AL22" s="38" t="n"/>
-      <c r="AM22" s="37" t="n"/>
-      <c r="AN22" s="37" t="n"/>
-      <c r="AO22" s="38" t="n"/>
-      <c r="AP22" s="38" t="n"/>
-      <c r="AQ22" s="38" t="n"/>
-      <c r="AR22" s="38" t="n"/>
-      <c r="AS22" s="38" t="n"/>
-      <c r="AT22" s="38" t="n"/>
-      <c r="AU22" s="38" t="n"/>
-      <c r="AV22" s="37" t="n"/>
-      <c r="AW22" s="38" t="n"/>
-      <c r="AX22" s="38" t="n"/>
-      <c r="AY22" s="38" t="n"/>
+      <c r="AI22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ22" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK22" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM22" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN22" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO22" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP22" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ22" s="38" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="AR22" s="38" t="inlineStr">
+        <is>
+          <t>brain white matter 
+hyperintensity load, or total lesion volume (TLV), 
+on pre-post proximal training change.</t>
+        </is>
+      </c>
+      <c r="AS22" s="38" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AT22" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU22" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV22" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW22" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX22" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY22" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ22" s="38" t="n"/>
-      <c r="BA22" s="38" t="n"/>
-      <c r="BB22" s="38" t="n"/>
-      <c r="BC22" s="38" t="n"/>
+      <c r="BA22" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB22" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC22" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD22" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE22" s="40" t="inlineStr">
@@ -5657,58 +6359,235 @@
         <v>2024</v>
       </c>
       <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
+      <c r="E23" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F23" s="36" t="n"/>
-      <c r="G23" s="36" t="n"/>
-      <c r="H23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
-      <c r="K23" s="36" t="n"/>
-      <c r="M23" s="36" t="n"/>
-      <c r="N23" s="36" t="n"/>
-      <c r="O23" s="36" t="n"/>
-      <c r="P23" s="36" t="n"/>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O23" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" s="36" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q23" s="36" t="n"/>
-      <c r="R23" s="36" t="n"/>
-      <c r="S23" s="36" t="n"/>
-      <c r="T23" s="36" t="n"/>
-      <c r="U23" s="36" t="n"/>
-      <c r="V23" s="36" t="n"/>
-      <c r="W23" s="35" t="n"/>
-      <c r="X23" s="36" t="n"/>
-      <c r="Y23" s="36" t="n"/>
-      <c r="Z23" s="36" t="n"/>
-      <c r="AA23" s="36" t="n"/>
-      <c r="AB23" s="35" t="n"/>
-      <c r="AC23" s="36" t="n"/>
-      <c r="AD23" s="36" t="n"/>
-      <c r="AF23" s="36" t="n"/>
-      <c r="AG23" s="36" t="n"/>
+      <c r="R23" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S23" s="36" t="inlineStr">
+        <is>
+          <t>Dual N-back; engage</t>
+        </is>
+      </c>
+      <c r="T23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U23" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="V23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W23" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA23" s="36" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB23" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AC23" s="36" t="inlineStr">
+        <is>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD23" s="36" t="inlineStr">
+        <is>
+          <t>居家</t>
+        </is>
+      </c>
+      <c r="AF23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH23" s="36" t="n"/>
-      <c r="AI23" s="36" t="n"/>
-      <c r="AJ23" s="36" t="n"/>
-      <c r="AK23" s="36" t="n"/>
-      <c r="AL23" s="36" t="n"/>
-      <c r="AM23" s="35" t="n"/>
-      <c r="AN23" s="35" t="n"/>
-      <c r="AO23" s="36" t="n"/>
-      <c r="AP23" s="36" t="n"/>
-      <c r="AQ23" s="36" t="n"/>
-      <c r="AR23" s="36" t="n"/>
-      <c r="AS23" s="36" t="n"/>
-      <c r="AT23" s="36" t="n"/>
-      <c r="AU23" s="36" t="n"/>
-      <c r="AV23" s="35" t="n"/>
-      <c r="AW23" s="36" t="n"/>
-      <c r="AX23" s="36" t="n"/>
-      <c r="AY23" s="36" t="n"/>
+      <c r="AI23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ23" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM23" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN23" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO23" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ23" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/MRI</t>
+        </is>
+      </c>
+      <c r="AR23" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brain activation linked with greater
+cognitive training gains in older adults: Insights
+from the ACTOP study
+Lynn Valeyry Verty a,b, Samira Mellah a, </t>
+        </is>
+      </c>
+      <c r="AS23" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU23" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV23" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW23" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX23" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY23" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ23" s="36" t="n"/>
-      <c r="BA23" s="36" t="n"/>
-      <c r="BB23" s="36" t="n"/>
-      <c r="BC23" s="36" t="n"/>
+      <c r="BA23" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB23" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC23" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD23" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE23" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -6609,58 +6609,234 @@
         <v>2022</v>
       </c>
       <c r="D24" s="38" t="n"/>
-      <c r="E24" s="38" t="n"/>
+      <c r="E24" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="n"/>
-      <c r="I24" s="38" t="n"/>
-      <c r="J24" s="38" t="n"/>
-      <c r="K24" s="38" t="n"/>
-      <c r="M24" s="38" t="n"/>
-      <c r="N24" s="38" t="n"/>
-      <c r="O24" s="38" t="n"/>
-      <c r="P24" s="38" t="n"/>
+      <c r="G24" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="I24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K24" s="38" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="M24" s="38" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="N24" s="38" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="O24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q24" s="38" t="n"/>
-      <c r="R24" s="38" t="n"/>
-      <c r="S24" s="38" t="n"/>
-      <c r="T24" s="38" t="n"/>
-      <c r="U24" s="38" t="n"/>
-      <c r="V24" s="38" t="n"/>
-      <c r="W24" s="37" t="n"/>
-      <c r="X24" s="38" t="n"/>
-      <c r="Y24" s="38" t="n"/>
-      <c r="Z24" s="38" t="n"/>
-      <c r="AA24" s="38" t="n"/>
-      <c r="AB24" s="37" t="n"/>
-      <c r="AC24" s="38" t="n"/>
-      <c r="AD24" s="38" t="n"/>
-      <c r="AF24" s="38" t="n"/>
-      <c r="AG24" s="38" t="n"/>
+      <c r="R24" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S24" s="38" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="T24" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U24" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W24" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y24" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA24" s="38" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB24" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC24" s="38" t="inlineStr">
+        <is>
+          <t>at app; the
+2013</t>
+        </is>
+      </c>
+      <c r="AD24" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF24" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH24" s="38" t="n"/>
-      <c r="AI24" s="38" t="n"/>
-      <c r="AJ24" s="38" t="n"/>
-      <c r="AK24" s="38" t="n"/>
-      <c r="AL24" s="38" t="n"/>
-      <c r="AM24" s="37" t="n"/>
-      <c r="AN24" s="37" t="n"/>
-      <c r="AO24" s="38" t="n"/>
-      <c r="AP24" s="38" t="n"/>
-      <c r="AQ24" s="38" t="n"/>
-      <c r="AR24" s="38" t="n"/>
-      <c r="AS24" s="38" t="n"/>
-      <c r="AT24" s="38" t="n"/>
-      <c r="AU24" s="38" t="n"/>
-      <c r="AV24" s="37" t="n"/>
-      <c r="AW24" s="38" t="n"/>
-      <c r="AX24" s="38" t="n"/>
-      <c r="AY24" s="38" t="n"/>
+      <c r="AI24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ24" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK24" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM24" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN24" s="37" t="inlineStr">
+        <is>
+          <t>.54</t>
+        </is>
+      </c>
+      <c r="AO24" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP24" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ24" s="38" t="inlineStr">
+        <is>
+          <t>EEG/ERP/MRI</t>
+        </is>
+      </c>
+      <c r="AR24" s="38" t="inlineStr">
+        <is>
+          <t>EEG data
+indicated that the practice-related increase in vWM capacity
+observed in older adults was accompanied by neural modifi-
+cations not only duri</t>
+        </is>
+      </c>
+      <c r="AS24" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT24" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU24" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV24" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW24" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX24" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY24" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ24" s="38" t="n"/>
-      <c r="BA24" s="38" t="n"/>
-      <c r="BB24" s="38" t="n"/>
-      <c r="BC24" s="38" t="n"/>
+      <c r="BA24" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB24" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC24" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD24" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE24" s="40" t="inlineStr">
@@ -6682,58 +6858,225 @@
         <v>2014</v>
       </c>
       <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="n"/>
-      <c r="I25" s="36" t="n"/>
-      <c r="J25" s="36" t="n"/>
-      <c r="K25" s="36" t="n"/>
-      <c r="M25" s="36" t="n"/>
-      <c r="N25" s="36" t="n"/>
-      <c r="O25" s="36" t="n"/>
-      <c r="P25" s="36" t="n"/>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K25" s="36" t="n">
+        <v>80</v>
+      </c>
+      <c r="M25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q25" s="36" t="n"/>
-      <c r="R25" s="36" t="n"/>
-      <c r="S25" s="36" t="n"/>
-      <c r="T25" s="36" t="n"/>
-      <c r="U25" s="36" t="n"/>
-      <c r="V25" s="36" t="n"/>
-      <c r="W25" s="35" t="n"/>
-      <c r="X25" s="36" t="n"/>
-      <c r="Y25" s="36" t="n"/>
-      <c r="Z25" s="36" t="n"/>
-      <c r="AA25" s="36" t="n"/>
-      <c r="AB25" s="35" t="n"/>
-      <c r="AC25" s="36" t="n"/>
-      <c r="AD25" s="36" t="n"/>
-      <c r="AF25" s="36" t="n"/>
-      <c r="AG25" s="36" t="n"/>
+      <c r="R25" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S25" s="36" t="inlineStr">
+        <is>
+          <t>engage; complex span; spatial n-back</t>
+        </is>
+      </c>
+      <c r="T25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U25" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="V25" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="W25" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X25" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA25" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB25" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
+      <c r="AC25" s="36" t="inlineStr">
+        <is>
+          <t>based app</t>
+        </is>
+      </c>
+      <c r="AD25" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG25" s="36" t="inlineStr">
+        <is>
+          <t>and far transfer to a fluid intelligence task</t>
+        </is>
+      </c>
       <c r="AH25" s="36" t="n"/>
-      <c r="AI25" s="36" t="n"/>
-      <c r="AJ25" s="36" t="n"/>
-      <c r="AK25" s="36" t="n"/>
-      <c r="AL25" s="36" t="n"/>
-      <c r="AM25" s="35" t="n"/>
-      <c r="AN25" s="35" t="n"/>
-      <c r="AO25" s="36" t="n"/>
-      <c r="AP25" s="36" t="n"/>
-      <c r="AQ25" s="36" t="n"/>
-      <c r="AR25" s="36" t="n"/>
-      <c r="AS25" s="36" t="n"/>
-      <c r="AT25" s="36" t="n"/>
-      <c r="AU25" s="36" t="n"/>
-      <c r="AV25" s="35" t="n"/>
-      <c r="AW25" s="36" t="n"/>
-      <c r="AX25" s="36" t="n"/>
-      <c r="AY25" s="36" t="n"/>
+      <c r="AI25" s="36" t="inlineStr">
+        <is>
+          <t>has been found</t>
+        </is>
+      </c>
+      <c r="AJ25" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL25" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM25" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN25" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO25" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ25" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR25" s="36" t="inlineStr">
+        <is>
+          <t>brain activity in frontal and parietal cortex and basal
+ganglia and changes in dopamine receptor density (Brehmer et al.</t>
+        </is>
+      </c>
+      <c r="AS25" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU25" s="36" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AV25" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW25" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX25" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY25" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ25" s="36" t="n"/>
       <c r="BA25" s="36" t="n"/>
-      <c r="BB25" s="36" t="n"/>
-      <c r="BC25" s="36" t="n"/>
+      <c r="BB25" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC25" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD25" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE25" s="40" t="inlineStr">
@@ -6755,58 +7098,226 @@
         <v>2020</v>
       </c>
       <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
+      <c r="E26" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F26" s="38" t="n"/>
-      <c r="G26" s="38" t="n"/>
-      <c r="H26" s="38" t="n"/>
-      <c r="I26" s="38" t="n"/>
-      <c r="J26" s="38" t="n"/>
-      <c r="K26" s="38" t="n"/>
-      <c r="M26" s="38" t="n"/>
-      <c r="N26" s="38" t="n"/>
-      <c r="O26" s="38" t="n"/>
-      <c r="P26" s="38" t="n"/>
+      <c r="G26" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K26" s="38" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="M26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P26" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q26" s="38" t="n"/>
-      <c r="R26" s="38" t="n"/>
-      <c r="S26" s="38" t="n"/>
-      <c r="T26" s="38" t="n"/>
-      <c r="U26" s="38" t="n"/>
-      <c r="V26" s="38" t="n"/>
-      <c r="W26" s="37" t="n"/>
-      <c r="X26" s="38" t="n"/>
-      <c r="Y26" s="38" t="n"/>
-      <c r="Z26" s="38" t="n"/>
-      <c r="AA26" s="38" t="n"/>
-      <c r="AB26" s="37" t="n"/>
-      <c r="AC26" s="38" t="n"/>
-      <c r="AD26" s="38" t="n"/>
-      <c r="AF26" s="38" t="n"/>
-      <c r="AG26" s="38" t="n"/>
+      <c r="R26" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S26" s="38" t="inlineStr">
+        <is>
+          <t>dual n-back; single n-back; wome; engage; verbal n-back</t>
+        </is>
+      </c>
+      <c r="T26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U26" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="V26" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="W26" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA26" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB26" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC26" s="38" t="inlineStr">
+        <is>
+          <t>becoming app</t>
+        </is>
+      </c>
+      <c r="AD26" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH26" s="38" t="n"/>
-      <c r="AI26" s="38" t="n"/>
-      <c r="AJ26" s="38" t="n"/>
-      <c r="AK26" s="38" t="n"/>
-      <c r="AL26" s="38" t="n"/>
-      <c r="AM26" s="37" t="n"/>
+      <c r="AI26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ26" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM26" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN26" s="37" t="n"/>
-      <c r="AO26" s="38" t="n"/>
-      <c r="AP26" s="38" t="n"/>
-      <c r="AQ26" s="38" t="n"/>
-      <c r="AR26" s="38" t="n"/>
-      <c r="AS26" s="38" t="n"/>
-      <c r="AT26" s="38" t="n"/>
-      <c r="AU26" s="38" t="n"/>
-      <c r="AV26" s="37" t="n"/>
-      <c r="AW26" s="38" t="n"/>
-      <c r="AX26" s="38" t="n"/>
-      <c r="AY26" s="38" t="n"/>
+      <c r="AO26" s="38" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ26" s="38" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="AR26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU26" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV26" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW26" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX26" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY26" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ26" s="38" t="n"/>
-      <c r="BA26" s="38" t="n"/>
-      <c r="BB26" s="38" t="n"/>
-      <c r="BC26" s="38" t="n"/>
+      <c r="BA26" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB26" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC26" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD26" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE26" s="40" t="inlineStr">
@@ -6828,58 +7339,230 @@
         <v>2024</v>
       </c>
       <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="n"/>
+      <c r="E27" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F27" s="36" t="n"/>
-      <c r="G27" s="36" t="n"/>
-      <c r="H27" s="36" t="n"/>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="n"/>
-      <c r="K27" s="36" t="n"/>
-      <c r="M27" s="36" t="n"/>
-      <c r="N27" s="36" t="n"/>
-      <c r="O27" s="36" t="n"/>
-      <c r="P27" s="36" t="n"/>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H27" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J27" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" s="36" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="M27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P27" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q27" s="36" t="n"/>
-      <c r="R27" s="36" t="n"/>
-      <c r="S27" s="36" t="n"/>
-      <c r="T27" s="36" t="n"/>
-      <c r="U27" s="36" t="n"/>
-      <c r="V27" s="36" t="n"/>
-      <c r="W27" s="35" t="n"/>
-      <c r="X27" s="36" t="n"/>
-      <c r="Y27" s="36" t="n"/>
-      <c r="Z27" s="36" t="n"/>
-      <c r="AA27" s="36" t="n"/>
-      <c r="AB27" s="35" t="n"/>
-      <c r="AC27" s="36" t="n"/>
-      <c r="AD27" s="36" t="n"/>
-      <c r="AF27" s="36" t="n"/>
-      <c r="AG27" s="36" t="n"/>
+      <c r="R27" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S27" s="36" t="inlineStr">
+        <is>
+          <t>wome; Operation Span; complex 
+span</t>
+        </is>
+      </c>
+      <c r="T27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U27" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="V27" s="36" t="n">
+        <v>45</v>
+      </c>
+      <c r="W27" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA27" s="36" t="inlineStr">
+        <is>
+          <t>TMS/运动</t>
+        </is>
+      </c>
+      <c r="AB27" s="35" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
+      <c r="AC27" s="36" t="inlineStr">
+        <is>
+          <t>give app; the 1964</t>
+        </is>
+      </c>
+      <c r="AD27" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG27" s="36" t="inlineStr">
+        <is>
+          <t>involving analogi­
+cal reasoning) to the performance of a test measuring 
+fluid i</t>
+        </is>
+      </c>
       <c r="AH27" s="36" t="n"/>
-      <c r="AI27" s="36" t="n"/>
-      <c r="AJ27" s="36" t="n"/>
-      <c r="AK27" s="36" t="n"/>
-      <c r="AL27" s="36" t="n"/>
-      <c r="AM27" s="35" t="n"/>
+      <c r="AI27" s="36" t="inlineStr">
+        <is>
+          <t>to other cognitive tasks</t>
+        </is>
+      </c>
+      <c r="AJ27" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆</t>
+        </is>
+      </c>
+      <c r="AK27" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AL27" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AM27" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN27" s="35" t="n"/>
-      <c r="AO27" s="36" t="n"/>
-      <c r="AP27" s="36" t="n"/>
-      <c r="AQ27" s="36" t="n"/>
-      <c r="AR27" s="36" t="n"/>
-      <c r="AS27" s="36" t="n"/>
-      <c r="AT27" s="36" t="n"/>
-      <c r="AU27" s="36" t="n"/>
-      <c r="AV27" s="35" t="n"/>
-      <c r="AW27" s="36" t="n"/>
-      <c r="AX27" s="36" t="n"/>
-      <c r="AY27" s="36" t="n"/>
+      <c r="AO27" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ27" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR27" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brain activity (National Sci­
+ence Centre, Poland, grant no 2017/25/B/HS6/00360), 
+we also examined the magnitude of improvement in the 
+trained task </t>
+        </is>
+      </c>
+      <c r="AS27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU27" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV27" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW27" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX27" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY27" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ27" s="36" t="n"/>
-      <c r="BA27" s="36" t="n"/>
-      <c r="BB27" s="36" t="n"/>
-      <c r="BC27" s="36" t="n"/>
+      <c r="BA27" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB27" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC27" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD27" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE27" s="40" t="inlineStr">
@@ -6901,58 +7584,228 @@
         <v>2020</v>
       </c>
       <c r="D28" s="38" t="n"/>
-      <c r="E28" s="38" t="n"/>
+      <c r="E28" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F28" s="38" t="n"/>
-      <c r="G28" s="38" t="n"/>
-      <c r="H28" s="38" t="n"/>
-      <c r="I28" s="38" t="n"/>
-      <c r="J28" s="38" t="n"/>
-      <c r="K28" s="38" t="n"/>
-      <c r="M28" s="38" t="n"/>
-      <c r="N28" s="38" t="n"/>
-      <c r="O28" s="38" t="n"/>
-      <c r="P28" s="38" t="n"/>
+      <c r="G28" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H28" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="I28" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K28" s="38" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="M28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P28" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q28" s="38" t="n"/>
-      <c r="R28" s="38" t="n"/>
-      <c r="S28" s="38" t="n"/>
-      <c r="T28" s="38" t="n"/>
-      <c r="U28" s="38" t="n"/>
-      <c r="V28" s="38" t="n"/>
-      <c r="W28" s="37" t="n"/>
-      <c r="X28" s="38" t="n"/>
-      <c r="Y28" s="38" t="n"/>
-      <c r="Z28" s="38" t="n"/>
-      <c r="AA28" s="38" t="n"/>
-      <c r="AB28" s="37" t="n"/>
-      <c r="AC28" s="38" t="n"/>
-      <c r="AD28" s="38" t="n"/>
-      <c r="AF28" s="38" t="n"/>
-      <c r="AG28" s="38" t="n"/>
+      <c r="R28" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S28" s="38" t="inlineStr">
+        <is>
+          <t>complex span; Spatial N-back</t>
+        </is>
+      </c>
+      <c r="T28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U28" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="V28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W28" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y28" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA28" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB28" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA/MANOVA</t>
+        </is>
+      </c>
+      <c r="AC28" s="38" t="inlineStr">
+        <is>
+          <t>most app; five 12</t>
+        </is>
+      </c>
+      <c r="AD28" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG28" s="38" t="inlineStr">
+        <is>
+          <t>also via tablet devices</t>
+        </is>
+      </c>
       <c r="AH28" s="38" t="n"/>
-      <c r="AI28" s="38" t="n"/>
-      <c r="AJ28" s="38" t="n"/>
-      <c r="AK28" s="38" t="n"/>
-      <c r="AL28" s="38" t="n"/>
-      <c r="AM28" s="37" t="n"/>
-      <c r="AN28" s="37" t="n"/>
-      <c r="AO28" s="38" t="n"/>
-      <c r="AP28" s="38" t="n"/>
-      <c r="AQ28" s="38" t="n"/>
-      <c r="AR28" s="38" t="n"/>
-      <c r="AS28" s="38" t="n"/>
-      <c r="AT28" s="38" t="n"/>
-      <c r="AU28" s="38" t="n"/>
-      <c r="AV28" s="37" t="n"/>
-      <c r="AW28" s="38" t="n"/>
-      <c r="AX28" s="38" t="n"/>
-      <c r="AY28" s="38" t="n"/>
+      <c r="AI28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ28" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL28" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN28" s="37" t="inlineStr">
+        <is>
+          <t>.72</t>
+        </is>
+      </c>
+      <c r="AO28" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ28" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS28" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU28" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV28" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW28" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX28" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY28" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ28" s="38" t="n"/>
-      <c r="BA28" s="38" t="n"/>
-      <c r="BB28" s="38" t="n"/>
-      <c r="BC28" s="38" t="n"/>
+      <c r="BA28" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB28" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC28" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD28" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE28" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -7827,58 +7827,231 @@
         <v>2014</v>
       </c>
       <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
+      <c r="E29" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F29" s="36" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="n"/>
-      <c r="K29" s="36" t="n"/>
-      <c r="M29" s="36" t="n"/>
-      <c r="N29" s="36" t="n"/>
-      <c r="O29" s="36" t="n"/>
-      <c r="P29" s="36" t="n"/>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H29" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="I29" s="36" t="n">
+        <v>44</v>
+      </c>
+      <c r="J29" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q29" s="36" t="n"/>
-      <c r="R29" s="36" t="n"/>
-      <c r="S29" s="36" t="n"/>
-      <c r="T29" s="36" t="n"/>
-      <c r="U29" s="36" t="n"/>
-      <c r="V29" s="36" t="n"/>
-      <c r="W29" s="35" t="n"/>
-      <c r="X29" s="36" t="n"/>
-      <c r="Y29" s="36" t="n"/>
-      <c r="Z29" s="36" t="n"/>
-      <c r="AA29" s="36" t="n"/>
-      <c r="AB29" s="35" t="n"/>
-      <c r="AC29" s="36" t="n"/>
-      <c r="AD29" s="36" t="n"/>
-      <c r="AF29" s="36" t="n"/>
-      <c r="AG29" s="36" t="n"/>
+      <c r="R29" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S29" s="36" t="inlineStr">
+        <is>
+          <t>dual N-back; wome; Reading Span; verbal N-back; spatial
+N-back</t>
+        </is>
+      </c>
+      <c r="T29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U29" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W29" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA29" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB29" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC29" s="36" t="inlineStr">
+        <is>
+          <t>frequently app</t>
+        </is>
+      </c>
+      <c r="AD29" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH29" s="36" t="n"/>
-      <c r="AI29" s="36" t="n"/>
-      <c r="AJ29" s="36" t="n"/>
-      <c r="AK29" s="36" t="n"/>
-      <c r="AL29" s="36" t="n"/>
-      <c r="AM29" s="35" t="n"/>
-      <c r="AN29" s="35" t="n"/>
-      <c r="AO29" s="36" t="n"/>
-      <c r="AP29" s="36" t="n"/>
-      <c r="AQ29" s="36" t="n"/>
-      <c r="AR29" s="36" t="n"/>
-      <c r="AS29" s="36" t="n"/>
-      <c r="AT29" s="36" t="n"/>
-      <c r="AU29" s="36" t="n"/>
-      <c r="AV29" s="35" t="n"/>
-      <c r="AW29" s="36" t="n"/>
-      <c r="AX29" s="36" t="n"/>
-      <c r="AY29" s="36" t="n"/>
+      <c r="AI29" s="36" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ29" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM29" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN29" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO29" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ29" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT29" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU29" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV29" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW29" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX29" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY29" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ29" s="36" t="n"/>
-      <c r="BA29" s="36" t="n"/>
-      <c r="BB29" s="36" t="n"/>
-      <c r="BC29" s="36" t="n"/>
+      <c r="BA29" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB29" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC29" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD29" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE29" s="40" t="inlineStr">
@@ -7900,58 +8073,235 @@
         <v>2017</v>
       </c>
       <c r="D30" s="38" t="n"/>
-      <c r="E30" s="38" t="n"/>
+      <c r="E30" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F30" s="38" t="n"/>
-      <c r="G30" s="38" t="n"/>
-      <c r="H30" s="38" t="n"/>
-      <c r="I30" s="38" t="n"/>
-      <c r="J30" s="38" t="n"/>
-      <c r="K30" s="38" t="n"/>
-      <c r="M30" s="38" t="n"/>
-      <c r="N30" s="38" t="n"/>
-      <c r="O30" s="38" t="n"/>
-      <c r="P30" s="38" t="n"/>
+      <c r="G30" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P30" s="38" t="inlineStr">
+        <is>
+          <t>Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q30" s="38" t="n"/>
-      <c r="R30" s="38" t="n"/>
-      <c r="S30" s="38" t="n"/>
-      <c r="T30" s="38" t="n"/>
-      <c r="U30" s="38" t="n"/>
-      <c r="V30" s="38" t="n"/>
-      <c r="W30" s="37" t="n"/>
-      <c r="X30" s="38" t="n"/>
-      <c r="Y30" s="38" t="n"/>
-      <c r="Z30" s="38" t="n"/>
-      <c r="AA30" s="38" t="n"/>
-      <c r="AB30" s="37" t="n"/>
-      <c r="AC30" s="38" t="n"/>
-      <c r="AD30" s="38" t="n"/>
-      <c r="AF30" s="38" t="n"/>
-      <c r="AG30" s="38" t="n"/>
+      <c r="R30" s="38" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="S30" s="38" t="inlineStr">
+        <is>
+          <t>complex
+span</t>
+        </is>
+      </c>
+      <c r="T30" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V30" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W30" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA30" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB30" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC30" s="38" t="inlineStr">
+        <is>
+          <t>instruments app</t>
+        </is>
+      </c>
+      <c r="AD30" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH30" s="38" t="n"/>
-      <c r="AI30" s="38" t="n"/>
-      <c r="AJ30" s="38" t="n"/>
-      <c r="AK30" s="38" t="n"/>
-      <c r="AL30" s="38" t="n"/>
-      <c r="AM30" s="37" t="n"/>
-      <c r="AN30" s="37" t="n"/>
-      <c r="AO30" s="38" t="n"/>
-      <c r="AP30" s="38" t="n"/>
-      <c r="AQ30" s="38" t="n"/>
-      <c r="AR30" s="38" t="n"/>
-      <c r="AS30" s="38" t="n"/>
-      <c r="AT30" s="38" t="n"/>
-      <c r="AU30" s="38" t="n"/>
-      <c r="AV30" s="37" t="n"/>
-      <c r="AW30" s="38" t="n"/>
-      <c r="AX30" s="38" t="n"/>
-      <c r="AY30" s="38" t="n"/>
+      <c r="AI30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ30" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM30" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN30" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO30" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP30" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ30" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR30" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS30" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU30" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV30" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW30" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX30" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY30" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ30" s="38" t="n"/>
-      <c r="BA30" s="38" t="n"/>
-      <c r="BB30" s="38" t="n"/>
-      <c r="BC30" s="38" t="n"/>
+      <c r="BA30" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB30" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC30" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD30" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE30" s="40" t="inlineStr">
@@ -7973,58 +8323,232 @@
         <v>2013</v>
       </c>
       <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
+      <c r="E31" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="36" t="n"/>
-      <c r="I31" s="36" t="n"/>
-      <c r="J31" s="36" t="n"/>
-      <c r="K31" s="36" t="n"/>
-      <c r="M31" s="36" t="n"/>
-      <c r="N31" s="36" t="n"/>
-      <c r="O31" s="36" t="n"/>
-      <c r="P31" s="36" t="n"/>
+      <c r="G31" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H31" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="I31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J31" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" s="36" t="n">
+        <v>75</v>
+      </c>
+      <c r="M31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N31" s="36" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="O31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q31" s="36" t="n"/>
-      <c r="R31" s="36" t="n"/>
-      <c r="S31" s="36" t="n"/>
-      <c r="T31" s="36" t="n"/>
-      <c r="U31" s="36" t="n"/>
-      <c r="V31" s="36" t="n"/>
-      <c r="W31" s="35" t="n"/>
-      <c r="X31" s="36" t="n"/>
-      <c r="Y31" s="36" t="n"/>
-      <c r="Z31" s="36" t="n"/>
-      <c r="AA31" s="36" t="n"/>
-      <c r="AB31" s="35" t="n"/>
-      <c r="AC31" s="36" t="n"/>
-      <c r="AD31" s="36" t="n"/>
-      <c r="AF31" s="36" t="n"/>
-      <c r="AG31" s="36" t="n"/>
+      <c r="R31" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S31" s="36" t="inlineStr">
+        <is>
+          <t>engage; Complex
+span</t>
+        </is>
+      </c>
+      <c r="T31" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V31" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="W31" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y31" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="36" t="inlineStr">
+        <is>
+          <t>better) and, although the differ-
+ence was not statistically signiﬁcant, this could have
+emphasized</t>
+        </is>
+      </c>
+      <c r="AA31" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB31" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC31" s="36" t="inlineStr">
+        <is>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD31" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF31" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG31" s="36" t="inlineStr">
+        <is>
+          <t>and ﬂuid intelligence—Cattell
+Culture Fair test (far transfer effects)</t>
+        </is>
+      </c>
       <c r="AH31" s="36" t="n"/>
-      <c r="AI31" s="36" t="n"/>
-      <c r="AJ31" s="36" t="n"/>
-      <c r="AK31" s="36" t="n"/>
-      <c r="AL31" s="36" t="n"/>
-      <c r="AM31" s="35" t="n"/>
-      <c r="AN31" s="35" t="n"/>
-      <c r="AO31" s="36" t="n"/>
-      <c r="AP31" s="36" t="n"/>
-      <c r="AQ31" s="36" t="n"/>
-      <c r="AR31" s="36" t="n"/>
-      <c r="AS31" s="36" t="n"/>
-      <c r="AT31" s="36" t="n"/>
-      <c r="AU31" s="36" t="n"/>
-      <c r="AV31" s="35" t="n"/>
-      <c r="AW31" s="36" t="n"/>
-      <c r="AX31" s="36" t="n"/>
-      <c r="AY31" s="36" t="n"/>
+      <c r="AI31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ31" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK31" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL31" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM31" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN31" s="35" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AO31" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP31" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ31" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR31" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT31" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU31" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV31" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW31" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX31" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY31" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ31" s="36" t="n"/>
-      <c r="BA31" s="36" t="n"/>
-      <c r="BB31" s="36" t="n"/>
-      <c r="BC31" s="36" t="n"/>
+      <c r="BA31" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB31" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC31" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD31" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE31" s="40" t="inlineStr">
@@ -8046,58 +8570,228 @@
         <v>2014</v>
       </c>
       <c r="D32" s="38" t="n"/>
-      <c r="E32" s="38" t="n"/>
+      <c r="E32" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F32" s="38" t="n"/>
-      <c r="G32" s="38" t="n"/>
-      <c r="H32" s="38" t="n"/>
-      <c r="I32" s="38" t="n"/>
-      <c r="J32" s="38" t="n"/>
-      <c r="K32" s="38" t="n"/>
-      <c r="M32" s="38" t="n"/>
-      <c r="N32" s="38" t="n"/>
-      <c r="O32" s="38" t="n"/>
-      <c r="P32" s="38" t="n"/>
+      <c r="G32" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K32" s="38" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="M32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P32" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q32" s="38" t="n"/>
-      <c r="R32" s="38" t="n"/>
-      <c r="S32" s="38" t="n"/>
-      <c r="T32" s="38" t="n"/>
-      <c r="U32" s="38" t="n"/>
-      <c r="V32" s="38" t="n"/>
-      <c r="W32" s="37" t="n"/>
-      <c r="X32" s="38" t="n"/>
-      <c r="Y32" s="38" t="n"/>
-      <c r="Z32" s="38" t="n"/>
-      <c r="AA32" s="38" t="n"/>
-      <c r="AB32" s="37" t="n"/>
-      <c r="AC32" s="38" t="n"/>
-      <c r="AD32" s="38" t="n"/>
-      <c r="AF32" s="38" t="n"/>
-      <c r="AG32" s="38" t="n"/>
+      <c r="R32" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S32" s="38" t="inlineStr">
+        <is>
+          <t>wome</t>
+        </is>
+      </c>
+      <c r="T32" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U32" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="V32" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X32" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA32" s="38" t="inlineStr">
+        <is>
+          <t>tDCS/TMS</t>
+        </is>
+      </c>
+      <c r="AB32" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC32" s="38" t="inlineStr">
+        <is>
+          <t>CACT program</t>
+        </is>
+      </c>
+      <c r="AD32" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF32" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH32" s="38" t="n"/>
-      <c r="AI32" s="38" t="n"/>
-      <c r="AJ32" s="38" t="n"/>
-      <c r="AK32" s="38" t="n"/>
-      <c r="AL32" s="38" t="n"/>
-      <c r="AM32" s="37" t="n"/>
+      <c r="AI32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ32" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK32" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AL32" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AM32" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN32" s="37" t="n"/>
-      <c r="AO32" s="38" t="n"/>
-      <c r="AP32" s="38" t="n"/>
-      <c r="AQ32" s="38" t="n"/>
-      <c r="AR32" s="38" t="n"/>
-      <c r="AS32" s="38" t="n"/>
-      <c r="AT32" s="38" t="n"/>
-      <c r="AU32" s="38" t="n"/>
-      <c r="AV32" s="37" t="n"/>
-      <c r="AW32" s="38" t="n"/>
-      <c r="AX32" s="38" t="n"/>
-      <c r="AY32" s="38" t="n"/>
+      <c r="AO32" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP32" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ32" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR32" s="38" t="inlineStr">
+        <is>
+          <t>brain,
+and therefore stimulation of the prefrontal cortex alone is
+insufficient to induce significant changes.</t>
+        </is>
+      </c>
+      <c r="AS32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT32" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU32" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV32" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW32" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX32" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY32" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ32" s="38" t="n"/>
-      <c r="BA32" s="38" t="n"/>
-      <c r="BB32" s="38" t="n"/>
-      <c r="BC32" s="38" t="n"/>
+      <c r="BA32" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB32" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC32" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD32" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE32" s="40" t="inlineStr">
@@ -8119,58 +8813,228 @@
         <v>2022</v>
       </c>
       <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F33" s="36" t="n"/>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="36" t="n"/>
-      <c r="I33" s="36" t="n"/>
-      <c r="J33" s="36" t="n"/>
-      <c r="K33" s="36" t="n"/>
-      <c r="M33" s="36" t="n"/>
-      <c r="N33" s="36" t="n"/>
-      <c r="O33" s="36" t="n"/>
-      <c r="P33" s="36" t="n"/>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H33" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K33" s="36" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M33" s="36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N33" s="36" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="O33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P33" s="36" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q33" s="36" t="n"/>
-      <c r="R33" s="36" t="n"/>
-      <c r="S33" s="36" t="n"/>
-      <c r="T33" s="36" t="n"/>
-      <c r="U33" s="36" t="n"/>
-      <c r="V33" s="36" t="n"/>
-      <c r="W33" s="35" t="n"/>
-      <c r="X33" s="36" t="n"/>
-      <c r="Y33" s="36" t="n"/>
-      <c r="Z33" s="36" t="n"/>
-      <c r="AA33" s="36" t="n"/>
-      <c r="AB33" s="35" t="n"/>
-      <c r="AC33" s="36" t="n"/>
-      <c r="AD33" s="36" t="n"/>
-      <c r="AF33" s="36" t="n"/>
-      <c r="AG33" s="36" t="n"/>
+      <c r="R33" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S33" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; engage; spatial n-Back</t>
+        </is>
+      </c>
+      <c r="T33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U33" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V33" s="36" t="n">
+        <v>45</v>
+      </c>
+      <c r="W33" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y33" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA33" s="36" t="inlineStr">
+        <is>
+          <t>tDCS/TMS/运动</t>
+        </is>
+      </c>
+      <c r="AB33" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AC33" s="36" t="inlineStr">
+        <is>
+          <t>develop app; an 8</t>
+        </is>
+      </c>
+      <c r="AD33" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH33" s="36" t="n"/>
-      <c r="AI33" s="36" t="n"/>
-      <c r="AJ33" s="36" t="n"/>
-      <c r="AK33" s="36" t="n"/>
-      <c r="AL33" s="36" t="n"/>
-      <c r="AM33" s="35" t="n"/>
-      <c r="AN33" s="35" t="n"/>
-      <c r="AO33" s="36" t="n"/>
-      <c r="AP33" s="36" t="n"/>
-      <c r="AQ33" s="36" t="n"/>
-      <c r="AR33" s="36" t="n"/>
-      <c r="AS33" s="36" t="n"/>
-      <c r="AT33" s="36" t="n"/>
-      <c r="AU33" s="36" t="n"/>
-      <c r="AV33" s="35" t="n"/>
-      <c r="AW33" s="36" t="n"/>
-      <c r="AX33" s="36" t="n"/>
-      <c r="AY33" s="36" t="n"/>
+      <c r="AI33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ33" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM33" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN33" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO33" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ33" s="36" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR33" s="36" t="inlineStr">
+        <is>
+          <t>brain changes (Pauwels et al.</t>
+        </is>
+      </c>
+      <c r="AS33" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU33" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV33" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW33" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX33" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY33" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ33" s="36" t="n"/>
-      <c r="BA33" s="36" t="n"/>
-      <c r="BB33" s="36" t="n"/>
-      <c r="BC33" s="36" t="n"/>
+      <c r="BA33" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB33" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC33" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD33" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE33" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -9056,58 +9056,224 @@
         <v>2003</v>
       </c>
       <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
+      <c r="E34" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="38" t="n"/>
-      <c r="K34" s="38" t="n"/>
-      <c r="M34" s="38" t="n"/>
-      <c r="N34" s="38" t="n"/>
-      <c r="O34" s="38" t="n"/>
-      <c r="P34" s="38" t="n"/>
+      <c r="G34" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="I34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K34" s="38" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="M34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q34" s="38" t="n"/>
-      <c r="R34" s="38" t="n"/>
-      <c r="S34" s="38" t="n"/>
-      <c r="T34" s="38" t="n"/>
-      <c r="U34" s="38" t="n"/>
-      <c r="V34" s="38" t="n"/>
-      <c r="W34" s="37" t="n"/>
-      <c r="X34" s="38" t="n"/>
-      <c r="Y34" s="38" t="n"/>
-      <c r="Z34" s="38" t="n"/>
-      <c r="AA34" s="38" t="n"/>
-      <c r="AB34" s="37" t="n"/>
-      <c r="AC34" s="38" t="n"/>
-      <c r="AD34" s="38" t="n"/>
-      <c r="AF34" s="38" t="n"/>
-      <c r="AG34" s="38" t="n"/>
+      <c r="R34" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S34" s="38" t="inlineStr">
+        <is>
+          <t>wome</t>
+        </is>
+      </c>
+      <c r="T34" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V34" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="W34" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X34" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y34" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA34" s="38" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB34" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AC34" s="38" t="inlineStr">
+        <is>
+          <t>training program</t>
+        </is>
+      </c>
+      <c r="AD34" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF34" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH34" s="38" t="n"/>
-      <c r="AI34" s="38" t="n"/>
-      <c r="AJ34" s="38" t="n"/>
-      <c r="AK34" s="38" t="n"/>
-      <c r="AL34" s="38" t="n"/>
-      <c r="AM34" s="37" t="n"/>
+      <c r="AI34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ34" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK34" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL34" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM34" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN34" s="37" t="n"/>
-      <c r="AO34" s="38" t="n"/>
-      <c r="AP34" s="38" t="n"/>
-      <c r="AQ34" s="38" t="n"/>
-      <c r="AR34" s="38" t="n"/>
-      <c r="AS34" s="38" t="n"/>
-      <c r="AT34" s="38" t="n"/>
-      <c r="AU34" s="38" t="n"/>
-      <c r="AV34" s="37" t="n"/>
-      <c r="AW34" s="38" t="n"/>
-      <c r="AX34" s="38" t="n"/>
-      <c r="AY34" s="38" t="n"/>
+      <c r="AO34" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP34" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ34" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR34" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT34" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU34" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV34" s="37" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW34" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX34" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY34" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ34" s="38" t="n"/>
-      <c r="BA34" s="38" t="n"/>
-      <c r="BB34" s="38" t="n"/>
-      <c r="BC34" s="38" t="n"/>
+      <c r="BA34" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB34" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC34" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD34" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE34" s="40" t="inlineStr">
@@ -9129,58 +9295,230 @@
         <v>2014</v>
       </c>
       <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
+      <c r="E35" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="36" t="n"/>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="36" t="n"/>
-      <c r="K35" s="36" t="n"/>
-      <c r="M35" s="36" t="n"/>
-      <c r="N35" s="36" t="n"/>
-      <c r="O35" s="36" t="n"/>
-      <c r="P35" s="36" t="n"/>
+      <c r="G35" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H35" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="I35" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="J35" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="K35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N35" s="36" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="O35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P35" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q35" s="36" t="n"/>
-      <c r="R35" s="36" t="n"/>
-      <c r="S35" s="36" t="n"/>
-      <c r="T35" s="36" t="n"/>
-      <c r="U35" s="36" t="n"/>
-      <c r="V35" s="36" t="n"/>
-      <c r="W35" s="35" t="n"/>
-      <c r="X35" s="36" t="n"/>
-      <c r="Y35" s="36" t="n"/>
-      <c r="Z35" s="36" t="n"/>
-      <c r="AA35" s="36" t="n"/>
-      <c r="AB35" s="35" t="n"/>
-      <c r="AC35" s="36" t="n"/>
-      <c r="AD35" s="36" t="n"/>
-      <c r="AF35" s="36" t="n"/>
-      <c r="AG35" s="36" t="n"/>
+      <c r="R35" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S35" s="36" t="inlineStr">
+        <is>
+          <t>CogniFit; engage</t>
+        </is>
+      </c>
+      <c r="T35" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V35" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="W35" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y35" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="36" t="inlineStr">
+        <is>
+          <t>a TV-based programme of personally benefiting activities</t>
+        </is>
+      </c>
+      <c r="AA35" s="36" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB35" s="35" t="inlineStr">
+        <is>
+          <t>LMM</t>
+        </is>
+      </c>
+      <c r="AC35" s="36" t="inlineStr">
+        <is>
+          <t>CogniFit; training program</t>
+        </is>
+      </c>
+      <c r="AD35" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF35" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AG35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH35" s="36" t="n"/>
-      <c r="AI35" s="36" t="n"/>
-      <c r="AJ35" s="36" t="n"/>
-      <c r="AK35" s="36" t="n"/>
-      <c r="AL35" s="36" t="n"/>
-      <c r="AM35" s="35" t="n"/>
-      <c r="AN35" s="35" t="n"/>
-      <c r="AO35" s="36" t="n"/>
-      <c r="AP35" s="36" t="n"/>
-      <c r="AQ35" s="36" t="n"/>
-      <c r="AR35" s="36" t="n"/>
-      <c r="AS35" s="36" t="n"/>
-      <c r="AT35" s="36" t="n"/>
-      <c r="AU35" s="36" t="n"/>
-      <c r="AV35" s="35" t="n"/>
-      <c r="AW35" s="36" t="n"/>
-      <c r="AX35" s="36" t="n"/>
-      <c r="AY35" s="36" t="n"/>
+      <c r="AI35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ35" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK35" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM35" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN35" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO35" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP35" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ35" s="36" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AR35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT35" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU35" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV35" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW35" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX35" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY35" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ35" s="36" t="n"/>
-      <c r="BA35" s="36" t="n"/>
-      <c r="BB35" s="36" t="n"/>
-      <c r="BC35" s="36" t="n"/>
+      <c r="BA35" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB35" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC35" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD35" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE35" s="40" t="inlineStr">
@@ -9202,58 +9540,232 @@
         <v>2008</v>
       </c>
       <c r="D36" s="38" t="n"/>
-      <c r="E36" s="38" t="n"/>
+      <c r="E36" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n"/>
-      <c r="H36" s="38" t="n"/>
-      <c r="I36" s="38" t="n"/>
-      <c r="J36" s="38" t="n"/>
-      <c r="K36" s="38" t="n"/>
-      <c r="M36" s="38" t="n"/>
-      <c r="N36" s="38" t="n"/>
-      <c r="O36" s="38" t="n"/>
-      <c r="P36" s="38" t="n"/>
+      <c r="G36" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K36" s="38" t="n">
+        <v>80</v>
+      </c>
+      <c r="M36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q36" s="38" t="n"/>
-      <c r="R36" s="38" t="n"/>
-      <c r="S36" s="38" t="n"/>
-      <c r="T36" s="38" t="n"/>
-      <c r="U36" s="38" t="n"/>
-      <c r="V36" s="38" t="n"/>
-      <c r="W36" s="37" t="n"/>
-      <c r="X36" s="38" t="n"/>
-      <c r="Y36" s="38" t="n"/>
-      <c r="Z36" s="38" t="n"/>
-      <c r="AA36" s="38" t="n"/>
-      <c r="AB36" s="37" t="n"/>
-      <c r="AC36" s="38" t="n"/>
-      <c r="AD36" s="38" t="n"/>
-      <c r="AF36" s="38" t="n"/>
-      <c r="AG36" s="38" t="n"/>
+      <c r="R36" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S36" s="38" t="inlineStr">
+        <is>
+          <t>dual n-back; wome; engage</t>
+        </is>
+      </c>
+      <c r="T36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U36" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="V36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W36" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA36" s="38" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB36" s="37" t="inlineStr">
+        <is>
+          <t>MANOVA</t>
+        </is>
+      </c>
+      <c r="AC36" s="38" t="inlineStr">
+        <is>
+          <t>not app</t>
+        </is>
+      </c>
+      <c r="AD36" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG36" s="38" t="inlineStr">
+        <is>
+          <t>which would reflect a more general improvement of
+processes associated with WM</t>
+        </is>
+      </c>
       <c r="AH36" s="38" t="n"/>
-      <c r="AI36" s="38" t="n"/>
-      <c r="AJ36" s="38" t="n"/>
-      <c r="AK36" s="38" t="n"/>
-      <c r="AL36" s="38" t="n"/>
-      <c r="AM36" s="37" t="n"/>
-      <c r="AN36" s="37" t="n"/>
-      <c r="AO36" s="38" t="n"/>
-      <c r="AP36" s="38" t="n"/>
-      <c r="AQ36" s="38" t="n"/>
-      <c r="AR36" s="38" t="n"/>
-      <c r="AS36" s="38" t="n"/>
-      <c r="AT36" s="38" t="n"/>
-      <c r="AU36" s="38" t="n"/>
-      <c r="AV36" s="37" t="n"/>
-      <c r="AW36" s="38" t="n"/>
-      <c r="AX36" s="38" t="n"/>
-      <c r="AY36" s="38" t="n"/>
+      <c r="AI36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ36" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM36" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN36" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO36" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ36" s="38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR36" s="38" t="inlineStr">
+        <is>
+          <t>brain plasticity is strong enough to result in transfer effects, that is,
+performance increases in tasks that were not trained during the intervention</t>
+        </is>
+      </c>
+      <c r="AS36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT36" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU36" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV36" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW36" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX36" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY36" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ36" s="38" t="n"/>
       <c r="BA36" s="38" t="n"/>
-      <c r="BB36" s="38" t="n"/>
-      <c r="BC36" s="38" t="n"/>
+      <c r="BB36" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC36" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD36" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE36" s="40" t="inlineStr">
@@ -9275,58 +9787,228 @@
         <v>2023</v>
       </c>
       <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
+      <c r="E37" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F37" s="36" t="n"/>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="36" t="n"/>
-      <c r="I37" s="36" t="n"/>
-      <c r="J37" s="36" t="n"/>
-      <c r="K37" s="36" t="n"/>
-      <c r="M37" s="36" t="n"/>
-      <c r="N37" s="36" t="n"/>
-      <c r="O37" s="36" t="n"/>
-      <c r="P37" s="36" t="n"/>
+      <c r="G37" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H37" s="36" t="n">
+        <v>71</v>
+      </c>
+      <c r="I37" s="36" t="n">
+        <v>34</v>
+      </c>
+      <c r="J37" s="36" t="n">
+        <v>34</v>
+      </c>
+      <c r="K37" s="36" t="n">
+        <v>66</v>
+      </c>
+      <c r="M37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q37" s="36" t="n"/>
-      <c r="R37" s="36" t="n"/>
-      <c r="S37" s="36" t="n"/>
-      <c r="T37" s="36" t="n"/>
-      <c r="U37" s="36" t="n"/>
-      <c r="V37" s="36" t="n"/>
-      <c r="W37" s="35" t="n"/>
-      <c r="X37" s="36" t="n"/>
-      <c r="Y37" s="36" t="n"/>
-      <c r="Z37" s="36" t="n"/>
-      <c r="AA37" s="36" t="n"/>
-      <c r="AB37" s="35" t="n"/>
-      <c r="AC37" s="36" t="n"/>
-      <c r="AD37" s="36" t="n"/>
-      <c r="AF37" s="36" t="n"/>
-      <c r="AG37" s="36" t="n"/>
+      <c r="R37" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S37" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; engage; verbal
+n-back; spatial n-back</t>
+        </is>
+      </c>
+      <c r="T37" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U37" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W37" s="35" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="X37" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y37" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA37" s="36" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB37" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC37" s="36" t="inlineStr">
+        <is>
+          <t>training program; session 16</t>
+        </is>
+      </c>
+      <c r="AD37" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF37" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG37" s="36" t="inlineStr">
+        <is>
+          <t>and far transfer effects to an abstract
+relational reasoning task</t>
+        </is>
+      </c>
       <c r="AH37" s="36" t="n"/>
-      <c r="AI37" s="36" t="n"/>
-      <c r="AJ37" s="36" t="n"/>
-      <c r="AK37" s="36" t="n"/>
-      <c r="AL37" s="36" t="n"/>
-      <c r="AM37" s="35" t="n"/>
-      <c r="AN37" s="35" t="n"/>
-      <c r="AO37" s="36" t="n"/>
-      <c r="AP37" s="36" t="n"/>
-      <c r="AQ37" s="36" t="n"/>
-      <c r="AR37" s="36" t="n"/>
-      <c r="AS37" s="36" t="n"/>
-      <c r="AT37" s="36" t="n"/>
-      <c r="AU37" s="36" t="n"/>
-      <c r="AV37" s="35" t="n"/>
-      <c r="AW37" s="36" t="n"/>
-      <c r="AX37" s="36" t="n"/>
-      <c r="AY37" s="36" t="n"/>
+      <c r="AI37" s="36" t="inlineStr">
+        <is>
+          <t>s (∼15 min)</t>
+        </is>
+      </c>
+      <c r="AJ37" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK37" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM37" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN37" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO37" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP37" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ37" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR37" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT37" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU37" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV37" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW37" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX37" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY37" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ37" s="36" t="n"/>
-      <c r="BA37" s="36" t="n"/>
-      <c r="BB37" s="36" t="n"/>
-      <c r="BC37" s="36" t="n"/>
+      <c r="BA37" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB37" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC37" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD37" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE37" s="40" t="inlineStr">
@@ -9348,58 +10030,232 @@
         <v>2017</v>
       </c>
       <c r="D38" s="38" t="n"/>
-      <c r="E38" s="38" t="n"/>
+      <c r="E38" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F38" s="38" t="n"/>
-      <c r="G38" s="38" t="n"/>
-      <c r="H38" s="38" t="n"/>
-      <c r="I38" s="38" t="n"/>
-      <c r="J38" s="38" t="n"/>
-      <c r="K38" s="38" t="n"/>
-      <c r="M38" s="38" t="n"/>
-      <c r="N38" s="38" t="n"/>
-      <c r="O38" s="38" t="n"/>
-      <c r="P38" s="38" t="n"/>
+      <c r="G38" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H38" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="I38" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="J38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K38" s="38" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="M38" s="38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N38" s="38" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="O38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P38" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q38" s="38" t="n"/>
-      <c r="R38" s="38" t="n"/>
-      <c r="S38" s="38" t="n"/>
-      <c r="T38" s="38" t="n"/>
-      <c r="U38" s="38" t="n"/>
-      <c r="V38" s="38" t="n"/>
-      <c r="W38" s="37" t="n"/>
-      <c r="X38" s="38" t="n"/>
-      <c r="Y38" s="38" t="n"/>
-      <c r="Z38" s="38" t="n"/>
-      <c r="AA38" s="38" t="n"/>
-      <c r="AB38" s="37" t="n"/>
-      <c r="AC38" s="38" t="n"/>
-      <c r="AD38" s="38" t="n"/>
-      <c r="AF38" s="38" t="n"/>
-      <c r="AG38" s="38" t="n"/>
+      <c r="R38" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S38" s="38" t="inlineStr">
+        <is>
+          <t>single n-back</t>
+        </is>
+      </c>
+      <c r="T38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U38" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="V38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W38" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="38" t="inlineStr">
+        <is>
+          <t>not show an improvement from T1 to T2
+(all p’s &gt; 0</t>
+        </is>
+      </c>
+      <c r="AA38" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB38" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC38" s="38" t="inlineStr">
+        <is>
+          <t>training
+program</t>
+        </is>
+      </c>
+      <c r="AD38" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH38" s="38" t="n"/>
-      <c r="AI38" s="38" t="n"/>
-      <c r="AJ38" s="38" t="n"/>
-      <c r="AK38" s="38" t="n"/>
-      <c r="AL38" s="38" t="n"/>
-      <c r="AM38" s="37" t="n"/>
-      <c r="AN38" s="37" t="n"/>
-      <c r="AO38" s="38" t="n"/>
-      <c r="AP38" s="38" t="n"/>
-      <c r="AQ38" s="38" t="n"/>
-      <c r="AR38" s="38" t="n"/>
-      <c r="AS38" s="38" t="n"/>
-      <c r="AT38" s="38" t="n"/>
-      <c r="AU38" s="38" t="n"/>
-      <c r="AV38" s="37" t="n"/>
-      <c r="AW38" s="38" t="n"/>
-      <c r="AX38" s="38" t="n"/>
-      <c r="AY38" s="38" t="n"/>
+      <c r="AI38" s="38" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ38" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆</t>
+        </is>
+      </c>
+      <c r="AK38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM38" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN38" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO38" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ38" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/PET</t>
+        </is>
+      </c>
+      <c r="AR38" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neural
+activity might support performance in a dual-task setting, thus assessing transfer effects
+to higher-order control processes in the context of </t>
+        </is>
+      </c>
+      <c r="AS38" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT38" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU38" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV38" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW38" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX38" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY38" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ38" s="38" t="n"/>
-      <c r="BA38" s="38" t="n"/>
-      <c r="BB38" s="38" t="n"/>
-      <c r="BC38" s="38" t="n"/>
+      <c r="BA38" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB38" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC38" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD38" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE38" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -10277,58 +10277,233 @@
         <v>2017</v>
       </c>
       <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F39" s="36" t="n"/>
-      <c r="G39" s="36" t="n"/>
-      <c r="H39" s="36" t="n"/>
-      <c r="I39" s="36" t="n"/>
-      <c r="J39" s="36" t="n"/>
-      <c r="K39" s="36" t="n"/>
-      <c r="M39" s="36" t="n"/>
-      <c r="N39" s="36" t="n"/>
-      <c r="O39" s="36" t="n"/>
-      <c r="P39" s="36" t="n"/>
+      <c r="G39" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H39" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N39" s="36" t="inlineStr">
+        <is>
+          <t>543%</t>
+        </is>
+      </c>
+      <c r="O39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q39" s="36" t="n"/>
-      <c r="R39" s="36" t="n"/>
-      <c r="S39" s="36" t="n"/>
-      <c r="T39" s="36" t="n"/>
-      <c r="U39" s="36" t="n"/>
-      <c r="V39" s="36" t="n"/>
-      <c r="W39" s="35" t="n"/>
-      <c r="X39" s="36" t="n"/>
-      <c r="Y39" s="36" t="n"/>
-      <c r="Z39" s="36" t="n"/>
-      <c r="AA39" s="36" t="n"/>
-      <c r="AB39" s="35" t="n"/>
-      <c r="AC39" s="36" t="n"/>
-      <c r="AD39" s="36" t="n"/>
-      <c r="AF39" s="36" t="n"/>
-      <c r="AG39" s="36" t="n"/>
+      <c r="R39" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="T39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W39" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y39" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA39" s="36" t="inlineStr">
+        <is>
+          <t>tDCS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB39" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC39" s="36" t="inlineStr">
+        <is>
+          <t>promising app; Project 1</t>
+        </is>
+      </c>
+      <c r="AD39" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH39" s="36" t="n"/>
-      <c r="AI39" s="36" t="n"/>
-      <c r="AJ39" s="36" t="n"/>
-      <c r="AK39" s="36" t="n"/>
-      <c r="AL39" s="36" t="n"/>
-      <c r="AM39" s="35" t="n"/>
+      <c r="AI39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ39" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM39" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN39" s="35" t="n"/>
-      <c r="AO39" s="36" t="n"/>
-      <c r="AP39" s="36" t="n"/>
-      <c r="AQ39" s="36" t="n"/>
-      <c r="AR39" s="36" t="n"/>
-      <c r="AS39" s="36" t="n"/>
-      <c r="AT39" s="36" t="n"/>
-      <c r="AU39" s="36" t="n"/>
-      <c r="AV39" s="35" t="n"/>
-      <c r="AW39" s="36" t="n"/>
-      <c r="AX39" s="36" t="n"/>
-      <c r="AY39" s="36" t="n"/>
+      <c r="AO39" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ39" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/MRI</t>
+        </is>
+      </c>
+      <c r="AR39" s="36" t="inlineStr">
+        <is>
+          <t>brain stimulation improves cognitive performance by modulating functional connectivity and task-
+specific activation.</t>
+        </is>
+      </c>
+      <c r="AS39" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU39" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV39" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW39" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX39" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY39" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ39" s="36" t="n"/>
-      <c r="BA39" s="36" t="n"/>
-      <c r="BB39" s="36" t="n"/>
-      <c r="BC39" s="36" t="n"/>
+      <c r="BA39" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB39" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC39" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD39" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE39" s="40" t="inlineStr">
@@ -10350,58 +10525,225 @@
         <v>2025</v>
       </c>
       <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
+      <c r="E40" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="38" t="n"/>
-      <c r="K40" s="38" t="n"/>
-      <c r="M40" s="38" t="n"/>
-      <c r="N40" s="38" t="n"/>
-      <c r="O40" s="38" t="n"/>
-      <c r="P40" s="38" t="n"/>
+      <c r="G40" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H40" s="38" t="n">
+        <v>103</v>
+      </c>
+      <c r="I40" s="38" t="n">
+        <v>99</v>
+      </c>
+      <c r="J40" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="K40" s="38" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="M40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N40" s="38" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="O40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P40" s="38" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q40" s="38" t="n"/>
-      <c r="R40" s="38" t="n"/>
-      <c r="S40" s="38" t="n"/>
-      <c r="T40" s="38" t="n"/>
-      <c r="U40" s="38" t="n"/>
-      <c r="V40" s="38" t="n"/>
-      <c r="W40" s="37" t="n"/>
-      <c r="X40" s="38" t="n"/>
-      <c r="Y40" s="38" t="n"/>
-      <c r="Z40" s="38" t="n"/>
-      <c r="AA40" s="38" t="n"/>
-      <c r="AB40" s="37" t="n"/>
-      <c r="AC40" s="38" t="n"/>
-      <c r="AD40" s="38" t="n"/>
-      <c r="AF40" s="38" t="n"/>
-      <c r="AG40" s="38" t="n"/>
+      <c r="R40" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S40" s="38" t="inlineStr">
+        <is>
+          <t>BrainHQ; Lumosity; engage</t>
+        </is>
+      </c>
+      <c r="T40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U40" s="38" t="n">
+        <v>497</v>
+      </c>
+      <c r="V40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W40" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA40" s="38" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB40" s="37" t="inlineStr">
+        <is>
+          <t>LMM/ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC40" s="38" t="inlineStr">
+        <is>
+          <t>Lumosity; training 
+program</t>
+        </is>
+      </c>
+      <c r="AD40" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG40" s="38" t="inlineStr">
+        <is>
+          <t>Lee et al</t>
+        </is>
+      </c>
       <c r="AH40" s="38" t="n"/>
-      <c r="AI40" s="38" t="n"/>
-      <c r="AJ40" s="38" t="n"/>
-      <c r="AK40" s="38" t="n"/>
-      <c r="AL40" s="38" t="n"/>
-      <c r="AM40" s="37" t="n"/>
+      <c r="AI40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ40" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM40" s="37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN40" s="37" t="n"/>
-      <c r="AO40" s="38" t="n"/>
-      <c r="AP40" s="38" t="n"/>
-      <c r="AQ40" s="38" t="n"/>
-      <c r="AR40" s="38" t="n"/>
-      <c r="AS40" s="38" t="n"/>
-      <c r="AT40" s="38" t="n"/>
-      <c r="AU40" s="38" t="n"/>
-      <c r="AV40" s="37" t="n"/>
-      <c r="AW40" s="38" t="n"/>
-      <c r="AX40" s="38" t="n"/>
-      <c r="AY40" s="38" t="n"/>
+      <c r="AO40" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP40" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ40" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR40" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU40" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV40" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW40" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX40" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY40" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ40" s="38" t="n"/>
-      <c r="BA40" s="38" t="n"/>
-      <c r="BB40" s="38" t="n"/>
-      <c r="BC40" s="38" t="n"/>
+      <c r="BA40" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB40" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC40" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD40" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE40" s="40" t="inlineStr">
@@ -10423,58 +10765,219 @@
         <v>2016</v>
       </c>
       <c r="D41" s="36" t="n"/>
-      <c r="E41" s="36" t="n"/>
+      <c r="E41" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F41" s="36" t="n"/>
-      <c r="G41" s="36" t="n"/>
-      <c r="H41" s="36" t="n"/>
-      <c r="I41" s="36" t="n"/>
-      <c r="J41" s="36" t="n"/>
-      <c r="K41" s="36" t="n"/>
-      <c r="M41" s="36" t="n"/>
-      <c r="N41" s="36" t="n"/>
-      <c r="O41" s="36" t="n"/>
-      <c r="P41" s="36" t="n"/>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H41" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="36" t="n">
+        <v>35</v>
+      </c>
+      <c r="J41" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="36" t="n">
+        <v>47</v>
+      </c>
+      <c r="M41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O41" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="P41" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q41" s="36" t="n"/>
-      <c r="R41" s="36" t="n"/>
-      <c r="S41" s="36" t="n"/>
-      <c r="T41" s="36" t="n"/>
-      <c r="U41" s="36" t="n"/>
-      <c r="V41" s="36" t="n"/>
-      <c r="W41" s="35" t="n"/>
-      <c r="X41" s="36" t="n"/>
-      <c r="Y41" s="36" t="n"/>
-      <c r="Z41" s="36" t="n"/>
-      <c r="AA41" s="36" t="n"/>
-      <c r="AB41" s="35" t="n"/>
-      <c r="AC41" s="36" t="n"/>
-      <c r="AD41" s="36" t="n"/>
-      <c r="AF41" s="36" t="n"/>
-      <c r="AG41" s="36" t="n"/>
+      <c r="R41" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S41" s="36" t="inlineStr">
+        <is>
+          <t>Cogmed; Lumosity; Wome; engage; verbal n-back</t>
+        </is>
+      </c>
+      <c r="T41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U41" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V41" s="36" t="n">
+        <v>40</v>
+      </c>
+      <c r="W41" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X41" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA41" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB41" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC41" s="36" t="inlineStr">
+        <is>
+          <t>Cogmed; is app</t>
+        </is>
+      </c>
+      <c r="AD41" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG41" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH41" s="36" t="n"/>
-      <c r="AI41" s="36" t="n"/>
-      <c r="AJ41" s="36" t="n"/>
-      <c r="AK41" s="36" t="n"/>
-      <c r="AL41" s="36" t="n"/>
-      <c r="AM41" s="35" t="n"/>
+      <c r="AI41" s="36" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ41" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL41" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM41" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN41" s="35" t="n"/>
-      <c r="AO41" s="36" t="n"/>
-      <c r="AP41" s="36" t="n"/>
-      <c r="AQ41" s="36" t="n"/>
-      <c r="AR41" s="36" t="n"/>
-      <c r="AS41" s="36" t="n"/>
-      <c r="AT41" s="36" t="n"/>
-      <c r="AU41" s="36" t="n"/>
-      <c r="AV41" s="35" t="n"/>
-      <c r="AW41" s="36" t="n"/>
-      <c r="AX41" s="36" t="n"/>
-      <c r="AY41" s="36" t="n"/>
+      <c r="AO41" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ41" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AR41" s="36" t="inlineStr">
+        <is>
+          <t>Neural
+Activity Underlying Working Memory
+after Computerized Cognitive Training
+in Older Adults.</t>
+        </is>
+      </c>
+      <c r="AS41" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT41" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU41" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV41" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW41" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX41" s="36" t="inlineStr">
+        <is>
+          <t>NART</t>
+        </is>
+      </c>
+      <c r="AY41" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ41" s="36" t="n"/>
-      <c r="BA41" s="36" t="n"/>
-      <c r="BB41" s="36" t="n"/>
-      <c r="BC41" s="36" t="n"/>
+      <c r="BA41" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB41" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC41" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD41" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE41" s="40" t="inlineStr">
@@ -10496,58 +10999,234 @@
         <v>2013</v>
       </c>
       <c r="D42" s="38" t="n"/>
-      <c r="E42" s="38" t="n"/>
+      <c r="E42" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F42" s="38" t="n"/>
-      <c r="G42" s="38" t="n"/>
-      <c r="H42" s="38" t="n"/>
-      <c r="I42" s="38" t="n"/>
-      <c r="J42" s="38" t="n"/>
-      <c r="K42" s="38" t="n"/>
-      <c r="M42" s="38" t="n"/>
-      <c r="N42" s="38" t="n"/>
-      <c r="O42" s="38" t="n"/>
-      <c r="P42" s="38" t="n"/>
+      <c r="G42" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H42" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="I42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P42" s="38" t="inlineStr">
+        <is>
+          <t>Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q42" s="38" t="n"/>
-      <c r="R42" s="38" t="n"/>
-      <c r="S42" s="38" t="n"/>
-      <c r="T42" s="38" t="n"/>
-      <c r="U42" s="38" t="n"/>
-      <c r="V42" s="38" t="n"/>
-      <c r="W42" s="37" t="n"/>
-      <c r="X42" s="38" t="n"/>
-      <c r="Y42" s="38" t="n"/>
-      <c r="Z42" s="38" t="n"/>
-      <c r="AA42" s="38" t="n"/>
-      <c r="AB42" s="37" t="n"/>
-      <c r="AC42" s="38" t="n"/>
-      <c r="AD42" s="38" t="n"/>
-      <c r="AF42" s="38" t="n"/>
-      <c r="AG42" s="38" t="n"/>
+      <c r="R42" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S42" s="38" t="inlineStr">
+        <is>
+          <t>engage; complex span; Letter-Number Sequencing</t>
+        </is>
+      </c>
+      <c r="T42" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W42" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X42" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA42" s="38" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB42" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC42" s="38" t="inlineStr">
+        <is>
+          <t>the program</t>
+        </is>
+      </c>
+      <c r="AD42" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF42" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG42" s="38" t="inlineStr">
+        <is>
+          <t>but no improvements on several other transfer tasks of digit
+span, verbal recall,</t>
+        </is>
+      </c>
       <c r="AH42" s="38" t="n"/>
-      <c r="AI42" s="38" t="n"/>
-      <c r="AJ42" s="38" t="n"/>
-      <c r="AK42" s="38" t="n"/>
-      <c r="AL42" s="38" t="n"/>
-      <c r="AM42" s="37" t="n"/>
-      <c r="AN42" s="37" t="n"/>
-      <c r="AO42" s="38" t="n"/>
-      <c r="AP42" s="38" t="n"/>
-      <c r="AQ42" s="38" t="n"/>
-      <c r="AR42" s="38" t="n"/>
-      <c r="AS42" s="38" t="n"/>
-      <c r="AT42" s="38" t="n"/>
-      <c r="AU42" s="38" t="n"/>
-      <c r="AV42" s="37" t="n"/>
-      <c r="AW42" s="38" t="n"/>
-      <c r="AX42" s="38" t="n"/>
-      <c r="AY42" s="38" t="n"/>
+      <c r="AI42" s="38" t="inlineStr">
+        <is>
+          <t>in either young (aged 20–30) or
+older (aged 70–80) participants</t>
+        </is>
+      </c>
+      <c r="AJ42" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK42" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL42" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM42" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN42" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO42" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP42" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ42" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR42" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS42" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT42" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU42" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV42" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW42" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX42" s="38" t="inlineStr">
+        <is>
+          <t>NART</t>
+        </is>
+      </c>
+      <c r="AY42" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ42" s="38" t="n"/>
-      <c r="BA42" s="38" t="n"/>
-      <c r="BB42" s="38" t="n"/>
-      <c r="BC42" s="38" t="n"/>
+      <c r="BA42" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="BB42" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC42" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD42" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE42" s="40" t="inlineStr">
@@ -10569,58 +11248,232 @@
         <v>2018</v>
       </c>
       <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
+      <c r="E43" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F43" s="36" t="n"/>
-      <c r="G43" s="36" t="n"/>
-      <c r="H43" s="36" t="n"/>
-      <c r="I43" s="36" t="n"/>
-      <c r="J43" s="36" t="n"/>
-      <c r="K43" s="36" t="n"/>
-      <c r="M43" s="36" t="n"/>
-      <c r="N43" s="36" t="n"/>
-      <c r="O43" s="36" t="n"/>
-      <c r="P43" s="36" t="n"/>
+      <c r="G43" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P43" s="36" t="inlineStr">
+        <is>
+          <t>MMSE≥1; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q43" s="36" t="n"/>
-      <c r="R43" s="36" t="n"/>
-      <c r="S43" s="36" t="n"/>
-      <c r="T43" s="36" t="n"/>
-      <c r="U43" s="36" t="n"/>
-      <c r="V43" s="36" t="n"/>
-      <c r="W43" s="35" t="n"/>
-      <c r="X43" s="36" t="n"/>
-      <c r="Y43" s="36" t="n"/>
-      <c r="Z43" s="36" t="n"/>
-      <c r="AA43" s="36" t="n"/>
-      <c r="AB43" s="35" t="n"/>
-      <c r="AC43" s="36" t="n"/>
-      <c r="AD43" s="36" t="n"/>
-      <c r="AF43" s="36" t="n"/>
-      <c r="AG43" s="36" t="n"/>
+      <c r="R43" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S43" s="36" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="T43" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W43" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X43" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y43" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA43" s="36" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB43" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC43" s="36" t="inlineStr">
+        <is>
+          <t>brain fitness; to
+program</t>
+        </is>
+      </c>
+      <c r="AD43" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF43" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH43" s="36" t="n"/>
-      <c r="AI43" s="36" t="n"/>
-      <c r="AJ43" s="36" t="n"/>
-      <c r="AK43" s="36" t="n"/>
-      <c r="AL43" s="36" t="n"/>
-      <c r="AM43" s="35" t="n"/>
+      <c r="AI43" s="36" t="inlineStr">
+        <is>
+          <t>ed than
+near transfer</t>
+        </is>
+      </c>
+      <c r="AJ43" s="36" t="inlineStr">
+        <is>
+          <t>EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK43" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL43" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM43" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN43" s="35" t="n"/>
-      <c r="AO43" s="36" t="n"/>
-      <c r="AP43" s="36" t="n"/>
-      <c r="AQ43" s="36" t="n"/>
-      <c r="AR43" s="36" t="n"/>
-      <c r="AS43" s="36" t="n"/>
-      <c r="AT43" s="36" t="n"/>
-      <c r="AU43" s="36" t="n"/>
-      <c r="AV43" s="35" t="n"/>
-      <c r="AW43" s="36" t="n"/>
-      <c r="AX43" s="36" t="n"/>
-      <c r="AY43" s="36" t="n"/>
+      <c r="AO43" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP43" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ43" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR43" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT43" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU43" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV43" s="35" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="AW43" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX43" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY43" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ43" s="36" t="n"/>
-      <c r="BA43" s="36" t="n"/>
-      <c r="BB43" s="36" t="n"/>
-      <c r="BC43" s="36" t="n"/>
+      <c r="BA43" s="36" t="inlineStr">
+        <is>
+          <t>待核查：需人工判断</t>
+        </is>
+      </c>
+      <c r="BB43" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC43" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD43" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE43" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -11495,58 +11495,227 @@
         <v>2025</v>
       </c>
       <c r="D44" s="38" t="n"/>
-      <c r="E44" s="38" t="n"/>
+      <c r="E44" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F44" s="38" t="n"/>
-      <c r="G44" s="38" t="n"/>
-      <c r="H44" s="38" t="n"/>
-      <c r="I44" s="38" t="n"/>
-      <c r="J44" s="38" t="n"/>
-      <c r="K44" s="38" t="n"/>
-      <c r="M44" s="38" t="n"/>
-      <c r="N44" s="38" t="n"/>
-      <c r="O44" s="38" t="n"/>
-      <c r="P44" s="38" t="n"/>
+      <c r="G44" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H44" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K44" s="38" t="n">
+        <v>87</v>
+      </c>
+      <c r="M44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N44" s="38" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="O44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P44" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q44" s="38" t="n"/>
-      <c r="R44" s="38" t="n"/>
-      <c r="S44" s="38" t="n"/>
-      <c r="T44" s="38" t="n"/>
-      <c r="U44" s="38" t="n"/>
-      <c r="V44" s="38" t="n"/>
-      <c r="W44" s="37" t="n"/>
-      <c r="X44" s="38" t="n"/>
-      <c r="Y44" s="38" t="n"/>
-      <c r="Z44" s="38" t="n"/>
-      <c r="AA44" s="38" t="n"/>
-      <c r="AB44" s="37" t="n"/>
-      <c r="AC44" s="38" t="n"/>
-      <c r="AD44" s="38" t="n"/>
-      <c r="AF44" s="38" t="n"/>
-      <c r="AG44" s="38" t="n"/>
+      <c r="R44" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S44" s="38" t="inlineStr">
+        <is>
+          <t>engage; complex span</t>
+        </is>
+      </c>
+      <c r="T44" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U44" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W44" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y44" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA44" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB44" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC44" s="38" t="inlineStr">
+        <is>
+          <t>give app; the 1</t>
+        </is>
+      </c>
+      <c r="AD44" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF44" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH44" s="38" t="n"/>
-      <c r="AI44" s="38" t="n"/>
-      <c r="AJ44" s="38" t="n"/>
-      <c r="AK44" s="38" t="n"/>
-      <c r="AL44" s="38" t="n"/>
-      <c r="AM44" s="37" t="n"/>
-      <c r="AN44" s="37" t="n"/>
-      <c r="AO44" s="38" t="n"/>
-      <c r="AP44" s="38" t="n"/>
-      <c r="AQ44" s="38" t="n"/>
-      <c r="AR44" s="38" t="n"/>
-      <c r="AS44" s="38" t="n"/>
-      <c r="AT44" s="38" t="n"/>
-      <c r="AU44" s="38" t="n"/>
-      <c r="AV44" s="37" t="n"/>
-      <c r="AW44" s="38" t="n"/>
-      <c r="AX44" s="38" t="n"/>
-      <c r="AY44" s="38" t="n"/>
+      <c r="AI44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ44" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK44" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL44" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM44" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN44" s="37" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AO44" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP44" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ44" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR44" s="38" t="inlineStr">
+        <is>
+          <t>neural 
+correlates/changes underlying training gains and transfer 
+effects WM training induces were important to provide 
+a better understanding of th</t>
+        </is>
+      </c>
+      <c r="AS44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT44" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU44" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV44" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW44" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX44" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY44" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ44" s="38" t="n"/>
       <c r="BA44" s="38" t="n"/>
-      <c r="BB44" s="38" t="n"/>
-      <c r="BC44" s="38" t="n"/>
+      <c r="BB44" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC44" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD44" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE44" s="40" t="inlineStr">
@@ -11568,58 +11737,230 @@
         <v>2017</v>
       </c>
       <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F45" s="36" t="n"/>
-      <c r="G45" s="36" t="n"/>
-      <c r="H45" s="36" t="n"/>
-      <c r="I45" s="36" t="n"/>
-      <c r="J45" s="36" t="n"/>
-      <c r="K45" s="36" t="n"/>
-      <c r="M45" s="36" t="n"/>
-      <c r="N45" s="36" t="n"/>
-      <c r="O45" s="36" t="n"/>
-      <c r="P45" s="36" t="n"/>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I45" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K45" s="36" t="n">
+        <v>90</v>
+      </c>
+      <c r="M45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P45" s="36" t="inlineStr">
+        <is>
+          <t>MMSE≥1</t>
+        </is>
+      </c>
       <c r="Q45" s="36" t="n"/>
-      <c r="R45" s="36" t="n"/>
-      <c r="S45" s="36" t="n"/>
-      <c r="T45" s="36" t="n"/>
-      <c r="U45" s="36" t="n"/>
-      <c r="V45" s="36" t="n"/>
-      <c r="W45" s="35" t="n"/>
-      <c r="X45" s="36" t="n"/>
-      <c r="Y45" s="36" t="n"/>
-      <c r="Z45" s="36" t="n"/>
-      <c r="AA45" s="36" t="n"/>
-      <c r="AB45" s="35" t="n"/>
-      <c r="AC45" s="36" t="n"/>
-      <c r="AD45" s="36" t="n"/>
-      <c r="AF45" s="36" t="n"/>
-      <c r="AG45" s="36" t="n"/>
+      <c r="R45" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S45" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; engage; Operation
+Span</t>
+        </is>
+      </c>
+      <c r="T45" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V45" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="W45" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y45" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="36" t="inlineStr">
+        <is>
+          <t>two assessments 8-weeks apart</t>
+        </is>
+      </c>
+      <c r="AA45" s="36" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB45" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC45" s="36" t="inlineStr">
+        <is>
+          <t>training program; TMT 1</t>
+        </is>
+      </c>
+      <c r="AD45" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF45" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG45" s="36" t="inlineStr">
+        <is>
+          <t>that is within the same cognitive domain as the trained task
+(Morrison and Chein,</t>
+        </is>
+      </c>
       <c r="AH45" s="36" t="n"/>
-      <c r="AI45" s="36" t="n"/>
-      <c r="AJ45" s="36" t="n"/>
-      <c r="AK45" s="36" t="n"/>
-      <c r="AL45" s="36" t="n"/>
-      <c r="AM45" s="35" t="n"/>
+      <c r="AI45" s="36" t="inlineStr">
+        <is>
+          <t>switching, and dual-task performance</t>
+        </is>
+      </c>
+      <c r="AJ45" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK45" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM45" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN45" s="35" t="n"/>
-      <c r="AO45" s="36" t="n"/>
-      <c r="AP45" s="36" t="n"/>
-      <c r="AQ45" s="36" t="n"/>
-      <c r="AR45" s="36" t="n"/>
-      <c r="AS45" s="36" t="n"/>
-      <c r="AT45" s="36" t="n"/>
-      <c r="AU45" s="36" t="n"/>
-      <c r="AV45" s="35" t="n"/>
-      <c r="AW45" s="36" t="n"/>
-      <c r="AX45" s="36" t="n"/>
-      <c r="AY45" s="36" t="n"/>
+      <c r="AO45" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP45" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ45" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR45" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS45" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT45" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU45" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV45" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW45" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX45" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY45" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ45" s="36" t="n"/>
-      <c r="BA45" s="36" t="n"/>
-      <c r="BB45" s="36" t="n"/>
-      <c r="BC45" s="36" t="n"/>
+      <c r="BA45" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB45" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC45" s="36" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD45" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE45" s="40" t="inlineStr">
@@ -11641,58 +11982,219 @@
         <v>2012</v>
       </c>
       <c r="D46" s="38" t="n"/>
-      <c r="E46" s="38" t="n"/>
+      <c r="E46" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F46" s="38" t="n"/>
-      <c r="G46" s="38" t="n"/>
-      <c r="H46" s="38" t="n"/>
-      <c r="I46" s="38" t="n"/>
-      <c r="J46" s="38" t="n"/>
-      <c r="K46" s="38" t="n"/>
-      <c r="M46" s="38" t="n"/>
-      <c r="N46" s="38" t="n"/>
-      <c r="O46" s="38" t="n"/>
-      <c r="P46" s="38" t="n"/>
+      <c r="G46" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H46" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="K46" s="38" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="M46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O46" s="38" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="P46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q46" s="38" t="n"/>
-      <c r="R46" s="38" t="n"/>
-      <c r="S46" s="38" t="n"/>
-      <c r="T46" s="38" t="n"/>
-      <c r="U46" s="38" t="n"/>
-      <c r="V46" s="38" t="n"/>
-      <c r="W46" s="37" t="n"/>
-      <c r="X46" s="38" t="n"/>
-      <c r="Y46" s="38" t="n"/>
-      <c r="Z46" s="38" t="n"/>
-      <c r="AA46" s="38" t="n"/>
-      <c r="AB46" s="37" t="n"/>
-      <c r="AC46" s="38" t="n"/>
-      <c r="AD46" s="38" t="n"/>
-      <c r="AF46" s="38" t="n"/>
-      <c r="AG46" s="38" t="n"/>
+      <c r="R46" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S46" s="38" t="inlineStr">
+        <is>
+          <t>wome; engage; spatial n-back</t>
+        </is>
+      </c>
+      <c r="T46" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U46" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="W46" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X46" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y46" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="38" t="inlineStr">
+        <is>
+          <t>no treatment</t>
+        </is>
+      </c>
+      <c r="AA46" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB46" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC46" s="38" t="inlineStr">
+        <is>
+          <t>has app; approximately 2</t>
+        </is>
+      </c>
+      <c r="AD46" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF46" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH46" s="38" t="n"/>
-      <c r="AI46" s="38" t="n"/>
-      <c r="AJ46" s="38" t="n"/>
-      <c r="AK46" s="38" t="n"/>
-      <c r="AL46" s="38" t="n"/>
-      <c r="AM46" s="37" t="n"/>
-      <c r="AN46" s="37" t="n"/>
-      <c r="AO46" s="38" t="n"/>
-      <c r="AP46" s="38" t="n"/>
-      <c r="AQ46" s="38" t="n"/>
-      <c r="AR46" s="38" t="n"/>
-      <c r="AS46" s="38" t="n"/>
-      <c r="AT46" s="38" t="n"/>
-      <c r="AU46" s="38" t="n"/>
-      <c r="AV46" s="37" t="n"/>
-      <c r="AW46" s="38" t="n"/>
-      <c r="AX46" s="38" t="n"/>
-      <c r="AY46" s="38" t="n"/>
+      <c r="AI46" s="38" t="inlineStr">
+        <is>
+          <t>because, although transfer to some similar 
+WM tasks has already been demonstrate</t>
+        </is>
+      </c>
+      <c r="AJ46" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK46" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM46" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN46" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO46" s="38" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AP46" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ46" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR46" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS46" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT46" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU46" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV46" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW46" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX46" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY46" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ46" s="38" t="n"/>
       <c r="BA46" s="38" t="n"/>
-      <c r="BB46" s="38" t="n"/>
-      <c r="BC46" s="38" t="n"/>
+      <c r="BB46" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC46" s="38" t="inlineStr">
+        <is>
+          <t>准RCT</t>
+        </is>
+      </c>
       <c r="BD46" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE46" s="40" t="inlineStr">
@@ -11714,58 +12216,225 @@
         <v>2016</v>
       </c>
       <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="n"/>
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F47" s="36" t="n"/>
-      <c r="G47" s="36" t="n"/>
-      <c r="H47" s="36" t="n"/>
-      <c r="I47" s="36" t="n"/>
-      <c r="J47" s="36" t="n"/>
-      <c r="K47" s="36" t="n"/>
-      <c r="M47" s="36" t="n"/>
-      <c r="N47" s="36" t="n"/>
-      <c r="O47" s="36" t="n"/>
-      <c r="P47" s="36" t="n"/>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K47" s="36" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="M47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O47" s="36" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="P47" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q47" s="36" t="n"/>
-      <c r="R47" s="36" t="n"/>
-      <c r="S47" s="36" t="n"/>
-      <c r="T47" s="36" t="n"/>
-      <c r="U47" s="36" t="n"/>
-      <c r="V47" s="36" t="n"/>
-      <c r="W47" s="35" t="n"/>
-      <c r="X47" s="36" t="n"/>
-      <c r="Y47" s="36" t="n"/>
-      <c r="Z47" s="36" t="n"/>
-      <c r="AA47" s="36" t="n"/>
-      <c r="AB47" s="35" t="n"/>
-      <c r="AC47" s="36" t="n"/>
-      <c r="AD47" s="36" t="n"/>
-      <c r="AF47" s="36" t="n"/>
-      <c r="AG47" s="36" t="n"/>
+      <c r="R47" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S47" s="36" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="T47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U47" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="V47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W47" s="35" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="X47" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA47" s="36" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB47" s="35" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="AC47" s="36" t="inlineStr">
+        <is>
+          <t>This app; Day 1</t>
+        </is>
+      </c>
+      <c r="AD47" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG47" s="36" t="inlineStr">
+        <is>
+          <t>another
+dual-task) and two far transfer tasks (a running memory task
+requiring me</t>
+        </is>
+      </c>
       <c r="AH47" s="36" t="n"/>
-      <c r="AI47" s="36" t="n"/>
-      <c r="AJ47" s="36" t="n"/>
-      <c r="AK47" s="36" t="n"/>
-      <c r="AL47" s="36" t="n"/>
-      <c r="AM47" s="35" t="n"/>
+      <c r="AI47" s="36" t="inlineStr">
+        <is>
+          <t>at three different
+testing sessions – before training, immediately after the trai</t>
+        </is>
+      </c>
+      <c r="AJ47" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM47" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN47" s="35" t="n"/>
-      <c r="AO47" s="36" t="n"/>
-      <c r="AP47" s="36" t="n"/>
-      <c r="AQ47" s="36" t="n"/>
-      <c r="AR47" s="36" t="n"/>
-      <c r="AS47" s="36" t="n"/>
-      <c r="AT47" s="36" t="n"/>
-      <c r="AU47" s="36" t="n"/>
-      <c r="AV47" s="35" t="n"/>
-      <c r="AW47" s="36" t="n"/>
-      <c r="AX47" s="36" t="n"/>
-      <c r="AY47" s="36" t="n"/>
+      <c r="AO47" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ47" s="36" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR47" s="36" t="inlineStr">
+        <is>
+          <t>brain activation for the trained and transfer tasks.</t>
+        </is>
+      </c>
+      <c r="AS47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU47" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV47" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW47" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX47" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY47" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ47" s="36" t="n"/>
-      <c r="BA47" s="36" t="n"/>
-      <c r="BB47" s="36" t="n"/>
-      <c r="BC47" s="36" t="n"/>
+      <c r="BA47" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB47" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC47" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD47" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE47" s="40" t="inlineStr">
@@ -11787,58 +12456,227 @@
         <v>2023</v>
       </c>
       <c r="D48" s="38" t="n"/>
-      <c r="E48" s="38" t="n"/>
+      <c r="E48" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F48" s="38" t="n"/>
-      <c r="G48" s="38" t="n"/>
-      <c r="H48" s="38" t="n"/>
-      <c r="I48" s="38" t="n"/>
-      <c r="J48" s="38" t="n"/>
-      <c r="K48" s="38" t="n"/>
-      <c r="M48" s="38" t="n"/>
-      <c r="N48" s="38" t="n"/>
-      <c r="O48" s="38" t="n"/>
-      <c r="P48" s="38" t="n"/>
+      <c r="G48" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H48" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="I48" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="J48" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="M48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N48" s="38" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="O48" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" s="38" t="inlineStr">
+        <is>
+          <t>MMSE≥24; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q48" s="38" t="n"/>
-      <c r="R48" s="38" t="n"/>
-      <c r="S48" s="38" t="n"/>
-      <c r="T48" s="38" t="n"/>
-      <c r="U48" s="38" t="n"/>
-      <c r="V48" s="38" t="n"/>
-      <c r="W48" s="37" t="n"/>
-      <c r="X48" s="38" t="n"/>
-      <c r="Y48" s="38" t="n"/>
-      <c r="Z48" s="38" t="n"/>
-      <c r="AA48" s="38" t="n"/>
-      <c r="AB48" s="37" t="n"/>
-      <c r="AC48" s="38" t="n"/>
-      <c r="AD48" s="38" t="n"/>
-      <c r="AF48" s="38" t="n"/>
-      <c r="AG48" s="38" t="n"/>
+      <c r="R48" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S48" s="38" t="inlineStr">
+        <is>
+          <t>wome; EngAge; complex span; Spatial n-back</t>
+        </is>
+      </c>
+      <c r="T48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U48" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="V48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W48" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA48" s="38" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB48" s="37" t="inlineStr">
+        <is>
+          <t>ANCOVA/MANOVA</t>
+        </is>
+      </c>
+      <c r="AC48" s="38" t="inlineStr">
+        <is>
+          <t>metacognitive program</t>
+        </is>
+      </c>
+      <c r="AD48" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG48" s="38" t="inlineStr">
+        <is>
+          <t>mediates the effect of N-back working
+memory training on matrix reasoning</t>
+        </is>
+      </c>
       <c r="AH48" s="38" t="n"/>
-      <c r="AI48" s="38" t="n"/>
-      <c r="AJ48" s="38" t="n"/>
-      <c r="AK48" s="38" t="n"/>
-      <c r="AL48" s="38" t="n"/>
-      <c r="AM48" s="37" t="n"/>
-      <c r="AN48" s="37" t="n"/>
-      <c r="AO48" s="38" t="n"/>
-      <c r="AP48" s="38" t="n"/>
-      <c r="AQ48" s="38" t="n"/>
-      <c r="AR48" s="38" t="n"/>
-      <c r="AS48" s="38" t="n"/>
-      <c r="AT48" s="38" t="n"/>
-      <c r="AU48" s="38" t="n"/>
-      <c r="AV48" s="37" t="n"/>
-      <c r="AW48" s="38" t="n"/>
-      <c r="AX48" s="38" t="n"/>
-      <c r="AY48" s="38" t="n"/>
+      <c r="AI48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ48" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL48" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN48" s="37" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AO48" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ48" s="38" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AR48" s="38" t="inlineStr">
+        <is>
+          <t>Brain Observed in Vivo: Differential changes and
+their
+modiﬁers.</t>
+        </is>
+      </c>
+      <c r="AS48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT48" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU48" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV48" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW48" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX48" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY48" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ48" s="38" t="n"/>
-      <c r="BA48" s="38" t="n"/>
-      <c r="BB48" s="38" t="n"/>
-      <c r="BC48" s="38" t="n"/>
+      <c r="BA48" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="BB48" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC48" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD48" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE48" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -12698,58 +12698,225 @@
         <v>2017</v>
       </c>
       <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
+      <c r="E49" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F49" s="36" t="n"/>
-      <c r="G49" s="36" t="n"/>
-      <c r="H49" s="36" t="n"/>
-      <c r="I49" s="36" t="n"/>
-      <c r="J49" s="36" t="n"/>
-      <c r="K49" s="36" t="n"/>
-      <c r="M49" s="36" t="n"/>
-      <c r="N49" s="36" t="n"/>
-      <c r="O49" s="36" t="n"/>
-      <c r="P49" s="36" t="n"/>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K49" s="36" t="n">
+        <v>69</v>
+      </c>
+      <c r="M49" s="36" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O49" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="P49" s="36" t="inlineStr">
+        <is>
+          <t>Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q49" s="36" t="n"/>
-      <c r="R49" s="36" t="n"/>
-      <c r="S49" s="36" t="n"/>
-      <c r="T49" s="36" t="n"/>
-      <c r="U49" s="36" t="n"/>
-      <c r="V49" s="36" t="n"/>
-      <c r="W49" s="35" t="n"/>
-      <c r="X49" s="36" t="n"/>
-      <c r="Y49" s="36" t="n"/>
-      <c r="Z49" s="36" t="n"/>
-      <c r="AA49" s="36" t="n"/>
-      <c r="AB49" s="35" t="n"/>
-      <c r="AC49" s="36" t="n"/>
-      <c r="AD49" s="36" t="n"/>
-      <c r="AF49" s="36" t="n"/>
-      <c r="AG49" s="36" t="n"/>
+      <c r="R49" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S49" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; engage; Reading Span; spatial n-back</t>
+        </is>
+      </c>
+      <c r="T49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U49" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V49" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="W49" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA49" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB49" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC49" s="36" t="inlineStr">
+        <is>
+          <t>analytical app</t>
+        </is>
+      </c>
+      <c r="AD49" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG49" s="36" t="inlineStr">
+        <is>
+          <t>Forward and Backward Digit Span tasks (De Beni et al</t>
+        </is>
+      </c>
       <c r="AH49" s="36" t="n"/>
-      <c r="AI49" s="36" t="n"/>
-      <c r="AJ49" s="36" t="n"/>
-      <c r="AK49" s="36" t="n"/>
-      <c r="AL49" s="36" t="n"/>
-      <c r="AM49" s="35" t="n"/>
-      <c r="AN49" s="35" t="n"/>
-      <c r="AO49" s="36" t="n"/>
-      <c r="AP49" s="36" t="n"/>
-      <c r="AQ49" s="36" t="n"/>
-      <c r="AR49" s="36" t="n"/>
-      <c r="AS49" s="36" t="n"/>
-      <c r="AT49" s="36" t="n"/>
-      <c r="AU49" s="36" t="n"/>
-      <c r="AV49" s="35" t="n"/>
-      <c r="AW49" s="36" t="n"/>
-      <c r="AX49" s="36" t="n"/>
-      <c r="AY49" s="36" t="n"/>
+      <c r="AI49" s="36" t="inlineStr">
+        <is>
+          <t>Cattell test; Cattell and Cattell, 1963)
+This task consisted of 4 subtests (to be</t>
+        </is>
+      </c>
+      <c r="AJ49" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL49" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM49" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN49" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO49" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP49" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ49" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR49" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS49" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU49" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV49" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW49" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX49" s="36" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY49" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ49" s="36" t="n"/>
-      <c r="BA49" s="36" t="n"/>
-      <c r="BB49" s="36" t="n"/>
-      <c r="BC49" s="36" t="n"/>
+      <c r="BA49" s="36" t="inlineStr">
+        <is>
+          <t>待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB49" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC49" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD49" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE49" s="40" t="inlineStr">
@@ -12771,58 +12938,230 @@
         <v>2021</v>
       </c>
       <c r="D50" s="38" t="n"/>
-      <c r="E50" s="38" t="n"/>
+      <c r="E50" s="38" t="inlineStr">
+        <is>
+          <t>预印本</t>
+        </is>
+      </c>
       <c r="F50" s="38" t="n"/>
-      <c r="G50" s="38" t="n"/>
-      <c r="H50" s="38" t="n"/>
-      <c r="I50" s="38" t="n"/>
-      <c r="J50" s="38" t="n"/>
-      <c r="K50" s="38" t="n"/>
-      <c r="M50" s="38" t="n"/>
-      <c r="N50" s="38" t="n"/>
-      <c r="O50" s="38" t="n"/>
-      <c r="P50" s="38" t="n"/>
+      <c r="G50" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H50" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O50" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="P50" s="38" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
       <c r="Q50" s="38" t="n"/>
-      <c r="R50" s="38" t="n"/>
-      <c r="S50" s="38" t="n"/>
-      <c r="T50" s="38" t="n"/>
-      <c r="U50" s="38" t="n"/>
-      <c r="V50" s="38" t="n"/>
-      <c r="W50" s="37" t="n"/>
-      <c r="X50" s="38" t="n"/>
-      <c r="Y50" s="38" t="n"/>
-      <c r="Z50" s="38" t="n"/>
-      <c r="AA50" s="38" t="n"/>
-      <c r="AB50" s="37" t="n"/>
-      <c r="AC50" s="38" t="n"/>
-      <c r="AD50" s="38" t="n"/>
-      <c r="AF50" s="38" t="n"/>
-      <c r="AG50" s="38" t="n"/>
+      <c r="R50" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S50" s="38" t="inlineStr">
+        <is>
+          <t>Engage</t>
+        </is>
+      </c>
+      <c r="T50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V50" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W50" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X50" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y50" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA50" s="38" t="inlineStr">
+        <is>
+          <t>tDCS/tRNS/运动/药物</t>
+        </is>
+      </c>
+      <c r="AB50" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC50" s="38" t="inlineStr">
+        <is>
+          <t>tRNS app</t>
+        </is>
+      </c>
+      <c r="AD50" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG50" s="38" t="inlineStr">
+        <is>
+          <t>ed with executive tasks that were
+dissimilar from the training tasks</t>
+        </is>
+      </c>
       <c r="AH50" s="38" t="n"/>
-      <c r="AI50" s="38" t="n"/>
-      <c r="AJ50" s="38" t="n"/>
-      <c r="AK50" s="38" t="n"/>
-      <c r="AL50" s="38" t="n"/>
-      <c r="AM50" s="37" t="n"/>
-      <c r="AN50" s="37" t="n"/>
-      <c r="AO50" s="38" t="n"/>
-      <c r="AP50" s="38" t="n"/>
-      <c r="AQ50" s="38" t="n"/>
-      <c r="AR50" s="38" t="n"/>
-      <c r="AS50" s="38" t="n"/>
-      <c r="AT50" s="38" t="n"/>
-      <c r="AU50" s="38" t="n"/>
-      <c r="AV50" s="37" t="n"/>
-      <c r="AW50" s="38" t="n"/>
-      <c r="AX50" s="38" t="n"/>
-      <c r="AY50" s="38" t="n"/>
+      <c r="AI50" s="38" t="inlineStr">
+        <is>
+          <t>such as
+weekly calendar planning and driving knowledge, 1 month
+after a 5-day int</t>
+        </is>
+      </c>
+      <c r="AJ50" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN50" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO50" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ50" s="38" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AR50" s="38" t="inlineStr">
+        <is>
+          <t>brain
+changes.</t>
+        </is>
+      </c>
+      <c r="AS50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU50" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV50" s="37" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW50" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX50" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY50" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ50" s="38" t="n"/>
-      <c r="BA50" s="38" t="n"/>
-      <c r="BB50" s="38" t="n"/>
-      <c r="BC50" s="38" t="n"/>
+      <c r="BA50" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB50" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC50" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD50" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE50" s="40" t="inlineStr">
@@ -12844,58 +13183,226 @@
         <v>2022</v>
       </c>
       <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
+      <c r="E51" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F51" s="36" t="n"/>
-      <c r="G51" s="36" t="n"/>
-      <c r="H51" s="36" t="n"/>
-      <c r="I51" s="36" t="n"/>
-      <c r="J51" s="36" t="n"/>
-      <c r="K51" s="36" t="n"/>
-      <c r="M51" s="36" t="n"/>
-      <c r="N51" s="36" t="n"/>
-      <c r="O51" s="36" t="n"/>
-      <c r="P51" s="36" t="n"/>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H51" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="I51" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="J51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q51" s="36" t="n"/>
-      <c r="R51" s="36" t="n"/>
-      <c r="S51" s="36" t="n"/>
-      <c r="T51" s="36" t="n"/>
-      <c r="U51" s="36" t="n"/>
-      <c r="V51" s="36" t="n"/>
-      <c r="W51" s="35" t="n"/>
-      <c r="X51" s="36" t="n"/>
-      <c r="Y51" s="36" t="n"/>
-      <c r="Z51" s="36" t="n"/>
-      <c r="AA51" s="36" t="n"/>
-      <c r="AB51" s="35" t="n"/>
-      <c r="AC51" s="36" t="n"/>
-      <c r="AD51" s="36" t="n"/>
-      <c r="AF51" s="36" t="n"/>
-      <c r="AG51" s="36" t="n"/>
+      <c r="R51" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S51" s="36" t="inlineStr">
+        <is>
+          <t>wome</t>
+        </is>
+      </c>
+      <c r="T51" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W51" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X51" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y51" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="Z51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA51" s="36" t="inlineStr">
+        <is>
+          <t>tDCS/TMS/药物</t>
+        </is>
+      </c>
+      <c r="AB51" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AC51" s="36" t="inlineStr">
+        <is>
+          <t>the app; the 10</t>
+        </is>
+      </c>
+      <c r="AD51" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF51" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH51" s="36" t="n"/>
-      <c r="AI51" s="36" t="n"/>
-      <c r="AJ51" s="36" t="n"/>
-      <c r="AK51" s="36" t="n"/>
-      <c r="AL51" s="36" t="n"/>
-      <c r="AM51" s="35" t="n"/>
+      <c r="AI51" s="36" t="inlineStr">
+        <is>
+          <t>virtual reality maze task24)</t>
+        </is>
+      </c>
+      <c r="AJ51" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK51" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL51" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" s="35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AN51" s="35" t="n"/>
-      <c r="AO51" s="36" t="n"/>
-      <c r="AP51" s="36" t="n"/>
-      <c r="AQ51" s="36" t="n"/>
-      <c r="AR51" s="36" t="n"/>
-      <c r="AS51" s="36" t="n"/>
-      <c r="AT51" s="36" t="n"/>
-      <c r="AU51" s="36" t="n"/>
-      <c r="AV51" s="35" t="n"/>
-      <c r="AW51" s="36" t="n"/>
-      <c r="AX51" s="36" t="n"/>
-      <c r="AY51" s="36" t="n"/>
+      <c r="AO51" s="36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP51" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ51" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/MRI</t>
+        </is>
+      </c>
+      <c r="AR51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS51" s="36" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AT51" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AU51" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AV51" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AW51" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX51" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY51" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ51" s="36" t="n"/>
-      <c r="BA51" s="36" t="n"/>
-      <c r="BB51" s="36" t="n"/>
-      <c r="BC51" s="36" t="n"/>
+      <c r="BA51" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法确定对照类型</t>
+        </is>
+      </c>
+      <c r="BB51" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC51" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD51" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE51" s="40" t="inlineStr">
@@ -12917,58 +13424,228 @@
         <v>2014</v>
       </c>
       <c r="D52" s="38" t="n"/>
-      <c r="E52" s="38" t="n"/>
+      <c r="E52" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F52" s="38" t="n"/>
-      <c r="G52" s="38" t="n"/>
-      <c r="H52" s="38" t="n"/>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="38" t="n"/>
-      <c r="K52" s="38" t="n"/>
-      <c r="M52" s="38" t="n"/>
-      <c r="N52" s="38" t="n"/>
-      <c r="O52" s="38" t="n"/>
-      <c r="P52" s="38" t="n"/>
+      <c r="G52" s="38" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H52" s="38" t="n">
+        <v>242</v>
+      </c>
+      <c r="I52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J52" s="38" t="n">
+        <v>245</v>
+      </c>
+      <c r="K52" s="38" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O52" s="38" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="P52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q52" s="38" t="n"/>
-      <c r="R52" s="38" t="n"/>
-      <c r="S52" s="38" t="n"/>
-      <c r="T52" s="38" t="n"/>
-      <c r="U52" s="38" t="n"/>
-      <c r="V52" s="38" t="n"/>
-      <c r="W52" s="37" t="n"/>
-      <c r="X52" s="38" t="n"/>
-      <c r="Y52" s="38" t="n"/>
-      <c r="Z52" s="38" t="n"/>
-      <c r="AA52" s="38" t="n"/>
-      <c r="AB52" s="37" t="n"/>
-      <c r="AC52" s="38" t="n"/>
-      <c r="AD52" s="38" t="n"/>
-      <c r="AF52" s="38" t="n"/>
-      <c r="AG52" s="38" t="n"/>
+      <c r="R52" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S52" s="38" t="inlineStr">
+        <is>
+          <t>wome; engage; letter-number sequencing</t>
+        </is>
+      </c>
+      <c r="T52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W52" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X52" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="38" t="inlineStr">
+        <is>
+          <t>expect to improve
+and to the same degree as those in the training condition on the
+outcomes</t>
+        </is>
+      </c>
+      <c r="AA52" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB52" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC52" s="38" t="inlineStr">
+        <is>
+          <t>Posit Science; This app</t>
+        </is>
+      </c>
+      <c r="AD52" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH52" s="38" t="n"/>
-      <c r="AI52" s="38" t="n"/>
-      <c r="AJ52" s="38" t="n"/>
-      <c r="AK52" s="38" t="n"/>
-      <c r="AL52" s="38" t="n"/>
-      <c r="AM52" s="37" t="n"/>
-      <c r="AN52" s="37" t="n"/>
-      <c r="AO52" s="38" t="n"/>
-      <c r="AP52" s="38" t="n"/>
-      <c r="AQ52" s="38" t="n"/>
-      <c r="AR52" s="38" t="n"/>
-      <c r="AS52" s="38" t="n"/>
-      <c r="AT52" s="38" t="n"/>
-      <c r="AU52" s="38" t="n"/>
-      <c r="AV52" s="37" t="n"/>
-      <c r="AW52" s="38" t="n"/>
-      <c r="AX52" s="38" t="n"/>
-      <c r="AY52" s="38" t="n"/>
+      <c r="AI52" s="38" t="inlineStr">
+        <is>
+          <t>switching training</t>
+        </is>
+      </c>
+      <c r="AJ52" s="38" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL52" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN52" s="37" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AO52" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP52" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ52" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR52" s="38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU52" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV52" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW52" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX52" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY52" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ52" s="38" t="n"/>
-      <c r="BA52" s="38" t="n"/>
-      <c r="BB52" s="38" t="n"/>
-      <c r="BC52" s="38" t="n"/>
+      <c r="BA52" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB52" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC52" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD52" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE52" s="40" t="inlineStr">
@@ -12990,58 +13667,224 @@
         <v>2021</v>
       </c>
       <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="n"/>
+      <c r="E53" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F53" s="36" t="n"/>
-      <c r="G53" s="36" t="n"/>
-      <c r="H53" s="36" t="n"/>
-      <c r="I53" s="36" t="n"/>
-      <c r="J53" s="36" t="n"/>
-      <c r="K53" s="36" t="n"/>
-      <c r="M53" s="36" t="n"/>
-      <c r="N53" s="36" t="n"/>
-      <c r="O53" s="36" t="n"/>
-      <c r="P53" s="36" t="n"/>
+      <c r="G53" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H53" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="I53" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="J53" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K53" s="36" t="n">
+        <v>75</v>
+      </c>
+      <c r="M53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P53" s="36" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q53" s="36" t="n"/>
-      <c r="R53" s="36" t="n"/>
-      <c r="S53" s="36" t="n"/>
-      <c r="T53" s="36" t="n"/>
-      <c r="U53" s="36" t="n"/>
-      <c r="V53" s="36" t="n"/>
-      <c r="W53" s="35" t="n"/>
-      <c r="X53" s="36" t="n"/>
-      <c r="Y53" s="36" t="n"/>
-      <c r="Z53" s="36" t="n"/>
-      <c r="AA53" s="36" t="n"/>
-      <c r="AB53" s="35" t="n"/>
-      <c r="AC53" s="36" t="n"/>
-      <c r="AD53" s="36" t="n"/>
-      <c r="AF53" s="36" t="n"/>
-      <c r="AG53" s="36" t="n"/>
+      <c r="R53" s="36" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="S53" s="36" t="inlineStr">
+        <is>
+          <t>wome; engage; Reading Span</t>
+        </is>
+      </c>
+      <c r="T53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V53" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="W53" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X53" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA53" s="36" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB53" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC53" s="36" t="inlineStr">
+        <is>
+          <t>promising app</t>
+        </is>
+      </c>
+      <c r="AD53" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH53" s="36" t="n"/>
-      <c r="AI53" s="36" t="n"/>
-      <c r="AJ53" s="36" t="n"/>
-      <c r="AK53" s="36" t="n"/>
-      <c r="AL53" s="36" t="n"/>
-      <c r="AM53" s="35" t="n"/>
-      <c r="AN53" s="35" t="n"/>
-      <c r="AO53" s="36" t="n"/>
-      <c r="AP53" s="36" t="n"/>
-      <c r="AQ53" s="36" t="n"/>
-      <c r="AR53" s="36" t="n"/>
-      <c r="AS53" s="36" t="n"/>
-      <c r="AT53" s="36" t="n"/>
-      <c r="AU53" s="36" t="n"/>
-      <c r="AV53" s="35" t="n"/>
-      <c r="AW53" s="36" t="n"/>
-      <c r="AX53" s="36" t="n"/>
-      <c r="AY53" s="36" t="n"/>
+      <c r="AI53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ53" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL53" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM53" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN53" s="35" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AO53" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ53" s="36" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR53" s="36" t="inlineStr">
+        <is>
+          <t>EEG activity among older adults.</t>
+        </is>
+      </c>
+      <c r="AS53" s="36" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU53" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV53" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW53" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX53" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY53" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ53" s="36" t="n"/>
-      <c r="BA53" s="36" t="n"/>
-      <c r="BB53" s="36" t="n"/>
-      <c r="BC53" s="36" t="n"/>
+      <c r="BA53" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB53" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC53" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD53" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE53" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -13906,58 +13906,229 @@
         <v>2026</v>
       </c>
       <c r="D54" s="38" t="n"/>
-      <c r="E54" s="38" t="n"/>
+      <c r="E54" s="38" t="inlineStr">
+        <is>
+          <t>预印本</t>
+        </is>
+      </c>
       <c r="F54" s="38" t="n"/>
-      <c r="G54" s="38" t="n"/>
-      <c r="H54" s="38" t="n"/>
-      <c r="I54" s="38" t="n"/>
-      <c r="J54" s="38" t="n"/>
-      <c r="K54" s="38" t="n"/>
-      <c r="M54" s="38" t="n"/>
-      <c r="N54" s="38" t="n"/>
-      <c r="O54" s="38" t="n"/>
-      <c r="P54" s="38" t="n"/>
+      <c r="G54" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H54" s="38" t="n">
+        <v>66</v>
+      </c>
+      <c r="I54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K54" s="38" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="M54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N54" s="38" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="O54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="P54" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q54" s="38" t="n"/>
-      <c r="R54" s="38" t="n"/>
-      <c r="S54" s="38" t="n"/>
-      <c r="T54" s="38" t="n"/>
-      <c r="U54" s="38" t="n"/>
-      <c r="V54" s="38" t="n"/>
-      <c r="W54" s="37" t="n"/>
-      <c r="X54" s="38" t="n"/>
-      <c r="Y54" s="38" t="n"/>
-      <c r="Z54" s="38" t="n"/>
-      <c r="AA54" s="38" t="n"/>
-      <c r="AB54" s="37" t="n"/>
-      <c r="AC54" s="38" t="n"/>
-      <c r="AD54" s="38" t="n"/>
-      <c r="AF54" s="38" t="n"/>
-      <c r="AG54" s="38" t="n"/>
+      <c r="R54" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S54" s="38" t="inlineStr">
+        <is>
+          <t>dual n-back; engage</t>
+        </is>
+      </c>
+      <c r="T54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U54" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V54" s="38" t="n">
+        <v>45</v>
+      </c>
+      <c r="W54" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X54" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA54" s="38" t="inlineStr">
+        <is>
+          <t>运动/药物</t>
+        </is>
+      </c>
+      <c r="AB54" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC54" s="38" t="inlineStr">
+        <is>
+          <t>of App; an 11</t>
+        </is>
+      </c>
+      <c r="AD54" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG54" s="38" t="inlineStr">
+        <is>
+          <t>measured using the WCST)</t>
+        </is>
+      </c>
       <c r="AH54" s="38" t="n"/>
-      <c r="AI54" s="38" t="n"/>
-      <c r="AJ54" s="38" t="n"/>
-      <c r="AK54" s="38" t="n"/>
-      <c r="AL54" s="38" t="n"/>
-      <c r="AM54" s="37" t="n"/>
-      <c r="AN54" s="37" t="n"/>
-      <c r="AO54" s="38" t="n"/>
-      <c r="AP54" s="38" t="n"/>
-      <c r="AQ54" s="38" t="n"/>
-      <c r="AR54" s="38" t="n"/>
-      <c r="AS54" s="38" t="n"/>
-      <c r="AT54" s="38" t="n"/>
-      <c r="AU54" s="38" t="n"/>
-      <c r="AV54" s="37" t="n"/>
-      <c r="AW54" s="38" t="n"/>
-      <c r="AX54" s="38" t="n"/>
-      <c r="AY54" s="38" t="n"/>
+      <c r="AI54" s="38" t="inlineStr">
+        <is>
+          <t>exhibiting larger pre-post gains compared to the AC group 
+across all VW task typ</t>
+        </is>
+      </c>
+      <c r="AJ54" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL54" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM54" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN54" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO54" s="38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AP54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ54" s="38" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="AR54" s="38" t="inlineStr">
+        <is>
+          <t>neural activity on 
+some aspects of the trained task to that demonstrated by 
+untrained young adults.</t>
+        </is>
+      </c>
+      <c r="AS54" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU54" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV54" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW54" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX54" s="38" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY54" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ54" s="38" t="n"/>
-      <c r="BA54" s="38" t="n"/>
-      <c r="BB54" s="38" t="n"/>
-      <c r="BC54" s="38" t="n"/>
+      <c r="BA54" s="38" t="inlineStr">
+        <is>
+          <t>待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB54" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC54" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD54" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE54" s="40" t="inlineStr">
@@ -13979,58 +14150,246 @@
         <v>2021</v>
       </c>
       <c r="D55" s="36" t="n"/>
-      <c r="E55" s="36" t="n"/>
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F55" s="36" t="n"/>
-      <c r="G55" s="36" t="n"/>
-      <c r="H55" s="36" t="n"/>
-      <c r="I55" s="36" t="n"/>
-      <c r="J55" s="36" t="n"/>
-      <c r="K55" s="36" t="n"/>
-      <c r="M55" s="36" t="n"/>
-      <c r="N55" s="36" t="n"/>
-      <c r="O55" s="36" t="n"/>
-      <c r="P55" s="36" t="n"/>
+      <c r="G55" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H55" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="I55" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J55" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" s="36" t="n">
+        <v>75</v>
+      </c>
+      <c r="M55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O55" s="36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q55" s="36" t="n"/>
-      <c r="R55" s="36" t="n"/>
-      <c r="S55" s="36" t="n"/>
-      <c r="T55" s="36" t="n"/>
-      <c r="U55" s="36" t="n"/>
-      <c r="V55" s="36" t="n"/>
-      <c r="W55" s="35" t="n"/>
-      <c r="X55" s="36" t="n"/>
-      <c r="Y55" s="36" t="n"/>
-      <c r="Z55" s="36" t="n"/>
-      <c r="AA55" s="36" t="n"/>
-      <c r="AB55" s="35" t="n"/>
-      <c r="AC55" s="36" t="n"/>
-      <c r="AD55" s="36" t="n"/>
-      <c r="AF55" s="36" t="n"/>
-      <c r="AG55" s="36" t="n"/>
+      <c r="R55" s="36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="S55" s="36" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="T55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U55" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W55" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA55" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AB55" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC55" s="36" t="inlineStr">
+        <is>
+          <t>dot
+ app</t>
+        </is>
+      </c>
+      <c r="AD55" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH55" s="36" t="n"/>
-      <c r="AI55" s="36" t="n"/>
-      <c r="AJ55" s="36" t="n"/>
-      <c r="AK55" s="36" t="n"/>
-      <c r="AL55" s="36" t="n"/>
-      <c r="AM55" s="35" t="n"/>
-      <c r="AN55" s="35" t="n"/>
-      <c r="AO55" s="36" t="n"/>
-      <c r="AP55" s="36" t="n"/>
-      <c r="AQ55" s="36" t="n"/>
-      <c r="AR55" s="36" t="n"/>
-      <c r="AS55" s="36" t="n"/>
-      <c r="AT55" s="36" t="n"/>
-      <c r="AU55" s="36" t="n"/>
-      <c r="AV55" s="35" t="n"/>
-      <c r="AW55" s="36" t="n"/>
-      <c r="AX55" s="36" t="n"/>
-      <c r="AY55" s="36" t="n"/>
+      <c r="AI55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ55" s="36" t="inlineStr">
+        <is>
+          <t>EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL55" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM55" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN55" s="35" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="AO55" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ55" s="36" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR55" s="36" t="inlineStr">
+        <is>
+          <t>brains
+ to
+ build
+ a
+ compensatory
+ scaffold
+ in
+ response
+ to
+ age-related
+changes
+ –
+ leading
+ them
+ to
+ focus
+ on
+ abilities
+ that
+ are
+ more
+ age-</t>
+        </is>
+      </c>
+      <c r="AS55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU55" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV55" s="35" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AW55" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX55" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY55" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ55" s="36" t="n"/>
-      <c r="BA55" s="36" t="n"/>
-      <c r="BB55" s="36" t="n"/>
-      <c r="BC55" s="36" t="n"/>
+      <c r="BA55" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB55" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC55" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD55" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE55" s="40" t="inlineStr">
@@ -14052,58 +14411,234 @@
         <v>2020</v>
       </c>
       <c r="D56" s="38" t="n"/>
-      <c r="E56" s="38" t="n"/>
+      <c r="E56" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F56" s="38" t="n"/>
-      <c r="G56" s="38" t="n"/>
-      <c r="H56" s="38" t="n"/>
-      <c r="I56" s="38" t="n"/>
-      <c r="J56" s="38" t="n"/>
-      <c r="K56" s="38" t="n"/>
-      <c r="M56" s="38" t="n"/>
-      <c r="N56" s="38" t="n"/>
-      <c r="O56" s="38" t="n"/>
-      <c r="P56" s="38" t="n"/>
+      <c r="G56" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H56" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K56" s="38" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="M56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O56" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="P56" s="38" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
       <c r="Q56" s="38" t="n"/>
-      <c r="R56" s="38" t="n"/>
-      <c r="S56" s="38" t="n"/>
-      <c r="T56" s="38" t="n"/>
-      <c r="U56" s="38" t="n"/>
-      <c r="V56" s="38" t="n"/>
-      <c r="W56" s="37" t="n"/>
-      <c r="X56" s="38" t="n"/>
-      <c r="Y56" s="38" t="n"/>
-      <c r="Z56" s="38" t="n"/>
-      <c r="AA56" s="38" t="n"/>
-      <c r="AB56" s="37" t="n"/>
-      <c r="AC56" s="38" t="n"/>
-      <c r="AD56" s="38" t="n"/>
-      <c r="AF56" s="38" t="n"/>
-      <c r="AG56" s="38" t="n"/>
+      <c r="R56" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S56" s="38" t="inlineStr">
+        <is>
+          <t>Dual N-back; wome</t>
+        </is>
+      </c>
+      <c r="T56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U56" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="V56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W56" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AA56" s="38" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
+      <c r="AB56" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA/Bayesian</t>
+        </is>
+      </c>
+      <c r="AC56" s="38" t="inlineStr">
+        <is>
+          <t>in app</t>
+        </is>
+      </c>
+      <c r="AD56" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH56" s="38" t="n"/>
-      <c r="AI56" s="38" t="n"/>
-      <c r="AJ56" s="38" t="n"/>
-      <c r="AK56" s="38" t="n"/>
-      <c r="AL56" s="38" t="n"/>
-      <c r="AM56" s="37" t="n"/>
-      <c r="AN56" s="37" t="n"/>
-      <c r="AO56" s="38" t="n"/>
-      <c r="AP56" s="38" t="n"/>
-      <c r="AQ56" s="38" t="n"/>
-      <c r="AR56" s="38" t="n"/>
-      <c r="AS56" s="38" t="n"/>
-      <c r="AT56" s="38" t="n"/>
-      <c r="AU56" s="38" t="n"/>
-      <c r="AV56" s="37" t="n"/>
-      <c r="AW56" s="38" t="n"/>
-      <c r="AX56" s="38" t="n"/>
-      <c r="AY56" s="38" t="n"/>
+      <c r="AI56" s="38" t="inlineStr">
+        <is>
+          <t>are
+Figure 1</t>
+        </is>
+      </c>
+      <c r="AJ56" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM56" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN56" s="37" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO56" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ56" s="38" t="inlineStr">
+        <is>
+          <t>EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AR56" s="38" t="inlineStr">
+        <is>
+          <t>EEG was
+recorded, the purpose of which is to verify whether
+the P300-ERP amplitude changes as a function of
+training, and cognitive tests administered</t>
+        </is>
+      </c>
+      <c r="AS56" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT56" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU56" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV56" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW56" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX56" s="38" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="AY56" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
       <c r="AZ56" s="38" t="n"/>
-      <c r="BA56" s="38" t="n"/>
-      <c r="BB56" s="38" t="n"/>
-      <c r="BC56" s="38" t="n"/>
+      <c r="BA56" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB56" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC56" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD56" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE56" s="40" t="inlineStr">
@@ -14125,58 +14660,227 @@
         <v>2015</v>
       </c>
       <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F57" s="36" t="n"/>
-      <c r="G57" s="36" t="n"/>
-      <c r="H57" s="36" t="n"/>
-      <c r="I57" s="36" t="n"/>
-      <c r="J57" s="36" t="n"/>
-      <c r="K57" s="36" t="n"/>
-      <c r="M57" s="36" t="n"/>
-      <c r="N57" s="36" t="n"/>
-      <c r="O57" s="36" t="n"/>
-      <c r="P57" s="36" t="n"/>
+      <c r="G57" s="36" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H57" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="I57" s="36" t="n">
+        <v>91</v>
+      </c>
+      <c r="J57" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="K57" s="36" t="n">
+        <v>67.97</v>
+      </c>
+      <c r="M57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N57" s="36" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="O57" s="36" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="P57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="Q57" s="36" t="n"/>
-      <c r="R57" s="36" t="n"/>
-      <c r="S57" s="36" t="n"/>
-      <c r="T57" s="36" t="n"/>
-      <c r="U57" s="36" t="n"/>
-      <c r="V57" s="36" t="n"/>
-      <c r="W57" s="35" t="n"/>
-      <c r="X57" s="36" t="n"/>
-      <c r="Y57" s="36" t="n"/>
-      <c r="Z57" s="36" t="n"/>
-      <c r="AA57" s="36" t="n"/>
-      <c r="AB57" s="35" t="n"/>
-      <c r="AC57" s="36" t="n"/>
-      <c r="AD57" s="36" t="n"/>
-      <c r="AF57" s="36" t="n"/>
-      <c r="AG57" s="36" t="n"/>
+      <c r="R57" s="36" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S57" s="36" t="inlineStr">
+        <is>
+          <t>dual n-back; Cogmed; wome; operation span; reading
+span; complex span</t>
+        </is>
+      </c>
+      <c r="T57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U57" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W57" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X57" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="36" t="inlineStr">
+        <is>
+          <t>not differ signiﬁcantly in age, education, and other demo-
+graphic characteristics such as gender ra</t>
+        </is>
+      </c>
+      <c r="AA57" s="36" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="AB57" s="35" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC57" s="36" t="inlineStr">
+        <is>
+          <t>Cogmed; training app</t>
+        </is>
+      </c>
+      <c r="AD57" s="36" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG57" s="36" t="inlineStr">
+        <is>
+          <t>to another task indicating the
+same construct, because it is not clear which task</t>
+        </is>
+      </c>
       <c r="AH57" s="36" t="n"/>
-      <c r="AI57" s="36" t="n"/>
-      <c r="AJ57" s="36" t="n"/>
-      <c r="AK57" s="36" t="n"/>
-      <c r="AL57" s="36" t="n"/>
-      <c r="AM57" s="35" t="n"/>
-      <c r="AN57" s="35" t="n"/>
-      <c r="AO57" s="36" t="n"/>
-      <c r="AP57" s="36" t="n"/>
-      <c r="AQ57" s="36" t="n"/>
-      <c r="AR57" s="36" t="n"/>
-      <c r="AS57" s="36" t="n"/>
-      <c r="AT57" s="36" t="n"/>
-      <c r="AU57" s="36" t="n"/>
-      <c r="AV57" s="35" t="n"/>
-      <c r="AW57" s="36" t="n"/>
-      <c r="AX57" s="36" t="n"/>
-      <c r="AY57" s="36" t="n"/>
+      <c r="AI57" s="36" t="inlineStr">
+        <is>
+          <t>show overlaps (e</t>
+        </is>
+      </c>
+      <c r="AJ57" s="36" t="inlineStr">
+        <is>
+          <t>流体智力/EF/情景记忆/日常功能</t>
+        </is>
+      </c>
+      <c r="AK57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM57" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN57" s="35" t="inlineStr">
+        <is>
+          <t>未报告具体d值</t>
+        </is>
+      </c>
+      <c r="AO57" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP57" s="36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ57" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR57" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AS57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU57" s="36" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV57" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW57" s="36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX57" s="36" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY57" s="36" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ57" s="36" t="n"/>
-      <c r="BA57" s="36" t="n"/>
-      <c r="BB57" s="36" t="n"/>
-      <c r="BC57" s="36" t="n"/>
+      <c r="BA57" s="36" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB57" s="36" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC57" s="36" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD57" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE57" s="40" t="inlineStr">
@@ -14198,58 +14902,229 @@
         <v>2026</v>
       </c>
       <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
+      <c r="E58" s="38" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
       <c r="F58" s="38" t="n"/>
-      <c r="G58" s="38" t="n"/>
-      <c r="H58" s="38" t="n"/>
-      <c r="I58" s="38" t="n"/>
-      <c r="J58" s="38" t="n"/>
-      <c r="K58" s="38" t="n"/>
-      <c r="M58" s="38" t="n"/>
-      <c r="N58" s="38" t="n"/>
-      <c r="O58" s="38" t="n"/>
-      <c r="P58" s="38" t="n"/>
+      <c r="G58" s="38" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H58" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="I58" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="K58" s="38" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="M58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O58" s="38" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="P58" s="38" t="inlineStr">
+        <is>
+          <t>MMSE; Mini-Mental</t>
+        </is>
+      </c>
       <c r="Q58" s="38" t="n"/>
-      <c r="R58" s="38" t="n"/>
-      <c r="S58" s="38" t="n"/>
-      <c r="T58" s="38" t="n"/>
-      <c r="U58" s="38" t="n"/>
-      <c r="V58" s="38" t="n"/>
-      <c r="W58" s="37" t="n"/>
-      <c r="X58" s="38" t="n"/>
-      <c r="Y58" s="38" t="n"/>
-      <c r="Z58" s="38" t="n"/>
-      <c r="AA58" s="38" t="n"/>
-      <c r="AB58" s="37" t="n"/>
-      <c r="AC58" s="38" t="n"/>
-      <c r="AD58" s="38" t="n"/>
-      <c r="AF58" s="38" t="n"/>
-      <c r="AG58" s="38" t="n"/>
+      <c r="R58" s="38" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="S58" s="38" t="inlineStr">
+        <is>
+          <t>wome; engage; complex span</t>
+        </is>
+      </c>
+      <c r="T58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U58" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="V58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="W58" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="X58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="Y58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="38" t="inlineStr">
+        <is>
+          <t>no 
+intervention during this period</t>
+        </is>
+      </c>
+      <c r="AA58" s="38" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="AB58" s="37" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="AC58" s="38" t="inlineStr">
+        <is>
+          <t>alternative app</t>
+        </is>
+      </c>
+      <c r="AD58" s="38" t="inlineStr">
+        <is>
+          <t>实验室</t>
+        </is>
+      </c>
+      <c r="AF58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AH58" s="38" t="n"/>
-      <c r="AI58" s="38" t="n"/>
-      <c r="AJ58" s="38" t="n"/>
-      <c r="AK58" s="38" t="n"/>
-      <c r="AL58" s="38" t="n"/>
-      <c r="AM58" s="37" t="n"/>
-      <c r="AN58" s="37" t="n"/>
-      <c r="AO58" s="38" t="n"/>
-      <c r="AP58" s="38" t="n"/>
-      <c r="AQ58" s="38" t="n"/>
-      <c r="AR58" s="38" t="n"/>
-      <c r="AS58" s="38" t="n"/>
-      <c r="AT58" s="38" t="n"/>
-      <c r="AU58" s="38" t="n"/>
-      <c r="AV58" s="37" t="n"/>
-      <c r="AW58" s="38" t="n"/>
-      <c r="AX58" s="38" t="n"/>
-      <c r="AY58" s="38" t="n"/>
+      <c r="AI58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ58" s="38" t="inlineStr">
+        <is>
+          <t>流体智力/EF/日常功能</t>
+        </is>
+      </c>
+      <c r="AK58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM58" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN58" s="37" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="AO58" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ58" s="38" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AR58" s="38" t="inlineStr">
+        <is>
+          <t>imaging studies corroborate this 
+mechanistic overlap by revealing co-activation within the 
+dorsolateral prefrontal cortex (DLPFC), a region integral</t>
+        </is>
+      </c>
+      <c r="AS58" s="38" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AT58" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU58" s="38" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV58" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW58" s="38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AX58" s="38" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY58" s="38" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
       <c r="AZ58" s="38" t="n"/>
-      <c r="BA58" s="38" t="n"/>
-      <c r="BB58" s="38" t="n"/>
-      <c r="BC58" s="38" t="n"/>
+      <c r="BA58" s="38" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+        </is>
+      </c>
+      <c r="BB58" s="38" t="inlineStr">
+        <is>
+          <t>未评估</t>
+        </is>
+      </c>
+      <c r="BC58" s="38" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
       <c r="BD58" s="40" t="inlineStr">
         <is>
-          <t>未填入</t>
+          <t>已填入</t>
         </is>
       </c>
       <c r="BE58" s="40" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -723,7 +723,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:BE58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
-          <t>Aging, Neuropsychology, and Cognition</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F3" s="35" t="inlineStr">
@@ -1423,8 +1423,10 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H3" s="35" t="n">
-        <v>42</v>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="I3" s="35" t="inlineStr">
         <is>
@@ -1433,23 +1435,25 @@
       </c>
       <c r="J3" s="35" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="K3" s="35" t="n">
-        <v>67.93000000000001</v>
+        <v>19.96</v>
       </c>
       <c r="L3" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M3" s="35" t="n">
-        <v>5.57</v>
+      <c r="M3" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N3" s="35" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O3" s="35" t="inlineStr">
@@ -1459,7 +1463,7 @@
       </c>
       <c r="P3" s="35" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q3" s="35" t="inlineStr">
@@ -1469,12 +1473,12 @@
       </c>
       <c r="R3" s="35" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S3" s="35" t="inlineStr">
         <is>
-          <t>Alpha-span, 2-back, Numerical updating (PsychoPy)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="T3" s="35" t="inlineStr">
@@ -1487,27 +1491,27 @@
       </c>
       <c r="V3" s="35" t="inlineStr">
         <is>
-          <t>10-21</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="W3" s="35" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="X3" s="35" t="inlineStr">
         <is>
-          <t>≤30天</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y3" s="35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>待核查：无法确定对照类型</t>
         </is>
       </c>
       <c r="Z3" s="35" t="inlineStr">
         <is>
-          <t>无对照组</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AA3" s="35" t="inlineStr">
@@ -1517,17 +1521,17 @@
       </c>
       <c r="AB3" s="35" t="inlineStr">
         <is>
-          <t>RM-ANOVA/LMM</t>
+          <t>LMM/ANOVA/Bayesian</t>
         </is>
       </c>
       <c r="AC3" s="35" t="inlineStr">
         <is>
-          <t>PsychoPy（自制）</t>
+          <t>was app; Session 4</t>
         </is>
       </c>
       <c r="AD3" s="35" t="inlineStr">
         <is>
-          <t>居家</t>
+          <t>实验室</t>
         </is>
       </c>
       <c r="AE3" s="41" t="inlineStr">
@@ -1542,7 +1546,7 @@
       </c>
       <c r="AG3" s="35" t="inlineStr">
         <is>
-          <t>Backward Digit Span, Mental Arithmetic, Mental Control</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH3" s="35" t="inlineStr">
@@ -1552,20 +1556,24 @@
       </c>
       <c r="AI3" s="35" t="inlineStr">
         <is>
-          <t>Faces &amp; Names task, Shopping List task</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ3" s="35" t="inlineStr">
         <is>
-          <t>情景记忆</t>
+          <t>EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK3" s="35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AL3" s="35" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL3" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="AM3" s="35" t="inlineStr">
         <is>
           <t>否</t>
@@ -1574,41 +1582,50 @@
       <c r="AN3" s="35" t="n"/>
       <c r="AO3" s="35" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AP3" s="35" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ3" s="35" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="AR3" s="35" t="inlineStr">
+        <is>
+          <t>brain areas and corresponding decreased
+performance.</t>
+        </is>
+      </c>
+      <c r="AS3" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT3" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AU3" s="35" t="inlineStr">
+        <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV3" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW3" s="35" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ3" s="35" t="n"/>
-      <c r="AR3" s="35" t="n"/>
-      <c r="AS3" s="35" t="inlineStr">
-        <is>
-          <t>高/低</t>
-        </is>
-      </c>
-      <c r="AT3" s="35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AU3" s="35" t="inlineStr">
-        <is>
-          <t>高&gt;低</t>
-        </is>
-      </c>
-      <c r="AV3" s="35" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="AW3" s="35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AX3" s="35" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1626,7 +1643,7 @@
       </c>
       <c r="BA3" s="35" t="inlineStr">
         <is>
-          <t>作者原姓Fu(Li Fu)，表格记为Lommen待核查</t>
+          <t>作者原姓Fu(Li Fu)，表格记为Lommen待核查 | 待核查：无法确定对照类型 | 待核查</t>
         </is>
       </c>
       <c r="BB3" s="35" t="inlineStr">
@@ -1636,7 +1653,7 @@
       </c>
       <c r="BC3" s="35" t="inlineStr">
         <is>
-          <t>单组前后测</t>
+          <t>准RCT</t>
         </is>
       </c>
       <c r="BD3" s="42" t="inlineStr">
@@ -1669,7 +1686,7 @@
       </c>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>Psychological Research</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
@@ -1683,36 +1700,44 @@
         </is>
       </c>
       <c r="H4" s="37" t="n">
-        <v>72</v>
-      </c>
-      <c r="I4" s="37" t="n">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="J4" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="K4" s="37" t="n">
-        <v>69.29000000000001</v>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L4" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M4" s="37" t="n">
-        <v>3.12</v>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N4" s="37" t="inlineStr">
         <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="O4" s="37" t="n">
-        <v>14.03</v>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P4" s="37" t="inlineStr">
         <is>
-          <t>CWMS（排除标准参照Crook et al.1986）</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Q4" s="37" t="inlineStr">
@@ -1727,7 +1752,7 @@
       </c>
       <c r="S4" s="37" t="inlineStr">
         <is>
-          <t>Categorization Working Memory Span (CWMS)</t>
+          <t>wome; engage</t>
         </is>
       </c>
       <c r="T4" s="37" t="inlineStr">
@@ -1735,11 +1760,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U4" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="37" t="n">
-        <v>60</v>
+      <c r="U4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="V4" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="W4" s="37" t="inlineStr">
         <is>
@@ -1748,7 +1777,7 @@
       </c>
       <c r="X4" s="37" t="inlineStr">
         <is>
-          <t>2周</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y4" s="37" t="inlineStr">
@@ -1758,22 +1787,22 @@
       </c>
       <c r="Z4" s="37" t="inlineStr">
         <is>
-          <t>问卷填写（Autobiographical/Memory Sensitivity问卷）</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AA4" s="37" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>运动</t>
         </is>
       </c>
       <c r="AB4" s="37" t="inlineStr">
         <is>
-          <t>ANCOVA</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AC4" s="37" t="inlineStr">
         <is>
-          <t>纸笔+音频（实验室）</t>
+          <t>these program; Venezia 8</t>
         </is>
       </c>
       <c r="AD4" s="37" t="inlineStr">
@@ -1793,7 +1822,7 @@
       </c>
       <c r="AG4" s="37" t="inlineStr">
         <is>
-          <t>Backward Corsi blocks task</t>
+          <t>were expected only immediately after training (e</t>
         </is>
       </c>
       <c r="AH4" s="37" t="inlineStr">
@@ -1803,12 +1832,12 @@
       </c>
       <c r="AI4" s="37" t="inlineStr">
         <is>
-          <t>Verbal fluency, Minnesota Paper Form Board (MPFB), Spatial descriptions-map drawing, Cattell test</t>
+          <t>or follow-up (p = 0</t>
         </is>
       </c>
       <c r="AJ4" s="37" t="inlineStr">
         <is>
-          <t>流体智力/EF/其他</t>
+          <t>流体智力/EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK4" s="37" t="inlineStr">
@@ -1826,12 +1855,12 @@
       </c>
       <c r="AN4" s="37" t="inlineStr">
         <is>
-          <t>大效应（CWMS d=1.56-2.62；迁移d范围0.3-1.5）</t>
+          <t>未报告具体d值</t>
         </is>
       </c>
       <c r="AO4" s="37" t="inlineStr">
         <is>
-          <t>正向</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP4" s="37" t="inlineStr">
@@ -1839,8 +1868,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ4" s="37" t="n"/>
-      <c r="AR4" s="37" t="n"/>
+      <c r="AQ4" s="37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR4" s="37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS4" s="37" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1858,17 +1895,17 @@
       </c>
       <c r="AV4" s="37" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AW4" s="37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX4" s="37" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AY4" s="37" t="inlineStr">
@@ -1926,7 +1963,7 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Aging, Neuropsychology, and Cognition</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
@@ -1940,7 +1977,7 @@
         </is>
       </c>
       <c r="H5" s="35" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>25</v>
@@ -1949,27 +1986,29 @@
         <v>21</v>
       </c>
       <c r="K5" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="L5" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M5" s="35" t="n">
-        <v>3.75</v>
+      <c r="M5" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N5" s="35" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O5" s="35" t="n">
-        <v>11.2</v>
+        <v>96</v>
       </c>
       <c r="P5" s="35" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q5" s="35" t="inlineStr">
@@ -1984,7 +2023,7 @@
       </c>
       <c r="S5" s="35" t="inlineStr">
         <is>
-          <t>Dual n-back (BrainTwister)</t>
+          <t>dual n-back; single n-back; engage; reading span; verbal n-back</t>
         </is>
       </c>
       <c r="T5" s="35" t="inlineStr">
@@ -1993,19 +2032,21 @@
         </is>
       </c>
       <c r="U5" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="V5" s="35" t="n">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="V5" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="W5" s="35" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="X5" s="35" t="inlineStr">
         <is>
-          <t>3-6周</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y5" s="35" t="inlineStr">
@@ -2015,7 +2056,7 @@
       </c>
       <c r="Z5" s="35" t="inlineStr">
         <is>
-          <t>无训练（被动对照）</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AA5" s="35" t="inlineStr">
@@ -2025,12 +2066,12 @@
       </c>
       <c r="AB5" s="35" t="inlineStr">
         <is>
-          <t>混合设计ANOVA（Group×Age×Session）</t>
+          <t>MANOVA</t>
         </is>
       </c>
       <c r="AC5" s="35" t="inlineStr">
         <is>
-          <t>BrainTwister软件（实验室）</t>
+          <t>our platform; only 14</t>
         </is>
       </c>
       <c r="AD5" s="35" t="inlineStr">
@@ -2048,7 +2089,8 @@
       </c>
       <c r="AG5" s="35" t="inlineStr">
         <is>
-          <t>Visuospatial WM updating task (visual modality)</t>
+          <t>and numerical 2- and 3-back tasks following
+training on a spatial 2-back task and</t>
         </is>
       </c>
       <c r="AH5" s="35" t="inlineStr">
@@ -2058,42 +2100,54 @@
       </c>
       <c r="AI5" s="35" t="inlineStr">
         <is>
-          <t>Task switching (mixing costs, switch costs), Attentional blink (AB) - T2 accuracy</t>
+          <t>of verbal learning and memory, but no transfer to fluid intelligence or attention</t>
         </is>
       </c>
       <c r="AJ5" s="35" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>流体智力/EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK5" s="35" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL5" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM5" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN5" s="35" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AO5" s="35" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP5" s="35" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL5" s="35" t="n"/>
-      <c r="AM5" s="35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN5" s="35" t="inlineStr">
-        <is>
-          <t>VS WM updating: d=0.62; Training task: d=1.49</t>
-        </is>
-      </c>
-      <c r="AO5" s="35" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AP5" s="35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AQ5" s="35" t="n"/>
-      <c r="AR5" s="35" t="n"/>
+      <c r="AQ5" s="35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR5" s="35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS5" s="35" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2101,34 +2155,34 @@
       </c>
       <c r="AT5" s="35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU5" s="35" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV5" s="35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW5" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX5" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY5" s="35" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV5" s="35" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="AW5" s="35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX5" s="35" t="inlineStr">
-        <is>
-          <t>教育</t>
-        </is>
-      </c>
-      <c r="AY5" s="35" t="inlineStr">
-        <is>
-          <t>未检验</t>
-        </is>
-      </c>
       <c r="AZ5" s="35" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -2136,7 +2190,7 @@
       </c>
       <c r="BA5" s="35" t="inlineStr">
         <is>
-          <t>注：与年轻人比较，本表仅记录老年人数据</t>
+          <t>注：与年轻人比较，本表仅记录老年人数据 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB5" s="35" t="inlineStr">
@@ -2146,7 +2200,7 @@
       </c>
       <c r="BC5" s="35" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD5" s="42" t="inlineStr">
@@ -2179,7 +2233,7 @@
       </c>
       <c r="E6" s="37" t="inlineStr">
         <is>
-          <t>PLOS ONE</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
@@ -2192,37 +2246,49 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H6" s="37" t="n">
-        <v>72</v>
-      </c>
-      <c r="I6" s="37" t="n">
-        <v>54</v>
-      </c>
-      <c r="J6" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="37" t="n">
-        <v>64.62</v>
+      <c r="H6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L6" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M6" s="37" t="n">
-        <v>5.15</v>
+      <c r="M6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N6" s="37" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="O6" s="37" t="n">
-        <v>16.78</v>
+      <c r="O6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P6" s="37" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q6" s="37" t="inlineStr">
@@ -2232,24 +2298,24 @@
       </c>
       <c r="R6" s="37" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S6" s="37" t="inlineStr">
         <is>
-          <t>Visuospatial WM tasks (visual/spatial recognition &amp; recall) + Automated Operation Span (OSpan)</t>
+          <t>engage; Operation Span</t>
         </is>
       </c>
       <c r="T6" s="37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U6" s="37" t="n">
         <v>10</v>
       </c>
       <c r="V6" s="37" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="W6" s="37" t="inlineStr">
         <is>
@@ -2258,32 +2324,32 @@
       </c>
       <c r="X6" s="37" t="inlineStr">
         <is>
-          <t>2周</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y6" s="37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z6" s="37" t="inlineStr">
         <is>
-          <t>sham tDCS（假刺激）</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AA6" s="37" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>tDCS/TMS/tRNS/运动</t>
         </is>
       </c>
       <c r="AB6" s="37" t="inlineStr">
         <is>
-          <t>ANOVA（benefit indices）</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="AC6" s="37" t="inlineStr">
         <is>
-          <t>实验室（计算机）</t>
+          <t>involves app</t>
         </is>
       </c>
       <c r="AD6" s="37" t="inlineStr">
@@ -2301,7 +2367,7 @@
       </c>
       <c r="AG6" s="37" t="inlineStr">
         <is>
-          <t>Spatial 2-back, Digit span (forward/backward)</t>
+          <t>the spatial 2-back WM</t>
         </is>
       </c>
       <c r="AH6" s="37" t="inlineStr">
@@ -2311,12 +2377,12 @@
       </c>
       <c r="AI6" s="37" t="inlineStr">
         <is>
-          <t>Color-word Stroop task</t>
+          <t>switching training</t>
         </is>
       </c>
       <c r="AJ6" s="37" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>流体智力/EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK6" s="37" t="inlineStr">
@@ -2324,8 +2390,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="AL6" s="37" t="n">
-        <v>1</v>
+      <c r="AL6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AM6" s="37" t="inlineStr">
         <is>
@@ -2335,26 +2403,34 @@
       <c r="AN6" s="37" t="n"/>
       <c r="AO6" s="37" t="inlineStr">
         <is>
-          <t>正向</t>
+          <t>待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="AP6" s="37" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ6" s="37" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/MRI/PET</t>
+        </is>
+      </c>
+      <c r="AR6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AS6" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT6" s="37" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AQ6" s="37" t="n"/>
-      <c r="AR6" s="37" t="n"/>
-      <c r="AS6" s="37" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT6" s="37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU6" s="37" t="inlineStr">
         <is>
           <t>未检验</t>
@@ -2362,17 +2438,17 @@
       </c>
       <c r="AV6" s="37" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AW6" s="37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX6" s="37" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AY6" s="37" t="inlineStr">
@@ -2387,7 +2463,7 @@
       </c>
       <c r="BA6" s="37" t="inlineStr">
         <is>
-          <t>作者Jones KT等，表中记为Tays 2015待核查；含tDCS组合干预</t>
+          <t>作者Jones KT等，表中记为Tays 2015待核查；含tDCS组合干预 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB6" s="37" t="inlineStr">
@@ -2430,7 +2506,7 @@
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Brain and Behavior</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
@@ -2444,32 +2520,40 @@
         </is>
       </c>
       <c r="H7" s="35" t="n">
-        <v>28</v>
-      </c>
-      <c r="I7" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K7" s="35" t="n">
-        <v>63.11</v>
+        <v>26.15</v>
       </c>
       <c r="L7" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M7" s="35" t="n">
-        <v>4.05</v>
+      <c r="M7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N7" s="35" t="inlineStr">
         <is>
-          <t>53.6%</t>
-        </is>
-      </c>
-      <c r="O7" s="35" t="n">
-        <v>8.5</v>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="O7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P7" s="35" t="inlineStr">
         <is>
@@ -2488,7 +2572,7 @@
       </c>
       <c r="S7" s="35" t="inlineStr">
         <is>
-          <t>N-back task (1-back, 2-back, 3-back; visual pictures)</t>
+          <t>dual n-back; engage; complex span</t>
         </is>
       </c>
       <c r="T7" s="35" t="inlineStr">
@@ -2499,18 +2583,18 @@
       <c r="U7" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="V7" s="35" t="n">
-        <v>30</v>
+      <c r="V7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="W7" s="35" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X7" s="35" t="inlineStr">
-        <is>
-          <t>约3-4周</t>
-        </is>
+      <c r="X7" s="35" t="n">
+        <v>3</v>
       </c>
       <c r="Y7" s="35" t="inlineStr">
         <is>
@@ -2519,22 +2603,23 @@
       </c>
       <c r="Z7" s="35" t="inlineStr">
         <is>
-          <t>无训练（被动对照）</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AA7" s="35" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>药物</t>
         </is>
       </c>
       <c r="AB7" s="35" t="inlineStr">
         <is>
-          <t>t检验</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="AC7" s="35" t="inlineStr">
         <is>
-          <t>实验室（计算机+EEG设备）</t>
+          <t>Poles  
+Program</t>
         </is>
       </c>
       <c r="AD7" s="35" t="inlineStr">
@@ -2552,7 +2637,7 @@
       </c>
       <c r="AG7" s="35" t="inlineStr">
         <is>
-          <t>CORSI block-tapping test (visuospatial WM), nonadaptive N-back</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AH7" s="35" t="inlineStr">
@@ -2562,60 +2647,66 @@
       </c>
       <c r="AI7" s="35" t="inlineStr">
         <is>
-          <t>Test of Variables of Attention (TOVA), RAVEN fluid intelligence test</t>
+          <t>switch‐
+ing training</t>
         </is>
       </c>
       <c r="AJ7" s="35" t="inlineStr">
         <is>
-          <t>流体智力/其他</t>
+          <t>流体智力/EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK7" s="35" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AL7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AM7" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AN7" s="35" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AO7" s="35" t="inlineStr">
+        <is>
+          <t>待核查：无法自动判断，需人工确认</t>
+        </is>
+      </c>
+      <c r="AP7" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AQ7" s="35" t="inlineStr">
+        <is>
+          <t>fMRI/EEG/ERP/PET</t>
+        </is>
+      </c>
+      <c r="AR7" s="35" t="inlineStr">
+        <is>
+          <t>EEG studies have noted task difficulty and age‐related changes in time‐
+locked EEG responses, called event‐related potentials (ERPs), we focused on th</t>
+        </is>
+      </c>
+      <c r="AS7" s="35" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AT7" s="35" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AL7" s="35" t="n"/>
-      <c r="AM7" s="35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AN7" s="35" t="inlineStr">
-        <is>
-          <t>CTG-old: N-back d=0.96; CORSI d=0.06; TOVA d=0.17; RAVEN ns</t>
-        </is>
-      </c>
-      <c r="AO7" s="35" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AP7" s="35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AQ7" s="35" t="inlineStr">
-        <is>
-          <t>EEG（ERP: P300）</t>
-        </is>
-      </c>
-      <c r="AR7" s="35" t="inlineStr">
-        <is>
-          <t>训练后老年人3-back P300在顶叶(Pz)显著增加，反映神经效率提升</t>
-        </is>
-      </c>
-      <c r="AS7" s="35" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AT7" s="35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AU7" s="35" t="inlineStr">
         <is>
           <t>未检验</t>
@@ -2623,17 +2714,17 @@
       </c>
       <c r="AV7" s="35" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AW7" s="35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX7" s="35" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AY7" s="35" t="inlineStr">
@@ -2648,7 +2739,7 @@
       </c>
       <c r="BA7" s="35" t="inlineStr">
         <is>
-          <t>作者Pergher V等；表中记为Vesterinen 2018待核查；含EEG神经影像；仅提取老年组数据</t>
+          <t>作者Pergher V等；表中记为Vesterinen 2018待核查；含EEG神经影像；仅提取老年组数据 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB7" s="35" t="inlineStr">
@@ -2658,7 +2749,7 @@
       </c>
       <c r="BC7" s="35" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD7" s="42" t="inlineStr">
@@ -15145,7 +15236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -16604,7 +16695,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -723,7 +723,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:BE58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>Aging &amp; Mental Health</t>
+          <t>期刊</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
@@ -2795,37 +2795,49 @@
           <t>社区</t>
         </is>
       </c>
-      <c r="H8" s="37" t="n">
-        <v>46</v>
-      </c>
-      <c r="I8" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" s="37" t="n">
-        <v>28</v>
-      </c>
-      <c r="K8" s="37" t="n">
-        <v>66.76000000000001</v>
+      <c r="H8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="I8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L8" s="41" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M8" s="37" t="n">
-        <v>4.11</v>
+      <c r="M8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="N8" s="37" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="O8" s="37" t="n">
-        <v>8.869999999999999</v>
+      <c r="O8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="P8" s="37" t="inlineStr">
         <is>
-          <t>CERAD延迟回忆 + CDT + GDS + GAI + FAQ</t>
+          <t>MMSE; Mini-Mental</t>
         </is>
       </c>
       <c r="Q8" s="37" t="inlineStr">
@@ -2835,12 +2847,12 @@
       </c>
       <c r="R8" s="37" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="S8" s="37" t="inlineStr">
         <is>
-          <t>Categorization Working Memory Span (CWMS - Brazilian Portuguese adaptation)</t>
+          <t>dual n-back; engage</t>
         </is>
       </c>
       <c r="T8" s="37" t="inlineStr">
@@ -2853,7 +2865,7 @@
       </c>
       <c r="V8" s="37" t="inlineStr">
         <is>
-          <t>30-40</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="W8" s="37" t="inlineStr">
@@ -2863,7 +2875,7 @@
       </c>
       <c r="X8" s="37" t="inlineStr">
         <is>
-          <t>1周</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="Y8" s="37" t="inlineStr">
@@ -2873,7 +2885,8 @@
       </c>
       <c r="Z8" s="37" t="inlineStr">
         <is>
-          <t>问卷填写（主观幸福感/生活质量问卷）</t>
+          <t>the assessments accord-
+ing to the same schedule</t>
         </is>
       </c>
       <c r="AA8" s="37" t="inlineStr">
@@ -2883,12 +2896,12 @@
       </c>
       <c r="AB8" s="37" t="inlineStr">
         <is>
-          <t>重复测量ANOVA（Time×Condition）</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="AC8" s="37" t="inlineStr">
         <is>
-          <t>纸笔（实验者主导）</t>
+          <t>Age Program</t>
         </is>
       </c>
       <c r="AD8" s="37" t="inlineStr">
@@ -2906,7 +2919,9 @@
       </c>
       <c r="AG8" s="37" t="inlineStr">
         <is>
-          <t>Letter Number Sequencing, Forward/Backward Digit Span, Forward/Backward Spatial Span</t>
+          <t>measuring different
+constructs but related to WM functioning in older adults,
+for</t>
         </is>
       </c>
       <c r="AH8" s="37" t="inlineStr">
@@ -2916,12 +2931,13 @@
       </c>
       <c r="AI8" s="37" t="inlineStr">
         <is>
-          <t>Verbal Fluency (semantic), Symbol Search, Matrix Reasoning (fluid intelligence), Stroop Color task</t>
+          <t>at post-test and fol-
+low-up</t>
         </is>
       </c>
       <c r="AJ8" s="37" t="inlineStr">
         <is>
-          <t>流体智力/EF/其他</t>
+          <t>流体智力/EF/情景记忆/日常功能</t>
         </is>
       </c>
       <c r="AK8" s="37" t="inlineStr">
@@ -2939,12 +2955,12 @@
       </c>
       <c r="AN8" s="37" t="inlineStr">
         <is>
-          <t>CWMS: large; Near transfer: large-medium; Verbal Fluency: medium; others: null</t>
+          <t>未报告具体d值</t>
         </is>
       </c>
       <c r="AO8" s="37" t="inlineStr">
         <is>
-          <t>正向</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AP8" s="37" t="inlineStr">
@@ -2952,8 +2968,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AQ8" s="37" t="n"/>
-      <c r="AR8" s="37" t="n"/>
+      <c r="AQ8" s="37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="AR8" s="37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="AS8" s="37" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2961,34 +2985,34 @@
       </c>
       <c r="AT8" s="37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AU8" s="37" t="inlineStr">
         <is>
+          <t>待核查</t>
+        </is>
+      </c>
+      <c r="AV8" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AW8" s="37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AX8" s="37" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AY8" s="37" t="inlineStr">
+        <is>
           <t>未检验</t>
         </is>
       </c>
-      <c r="AV8" s="37" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="AW8" s="37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AX8" s="37" t="inlineStr">
-        <is>
-          <t>教育</t>
-        </is>
-      </c>
-      <c r="AY8" s="37" t="inlineStr">
-        <is>
-          <t>未检验</t>
-        </is>
-      </c>
       <c r="AZ8" s="37" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -2996,7 +3020,7 @@
       </c>
       <c r="BA8" s="37" t="inlineStr">
         <is>
-          <t>含Study1(3节)和Study2(6节)；此表记录Study1；Study2总体结论相似</t>
+          <t>含Study1(3节)和Study2(6节)；此表记录Study1；Study2总体结论相似 | 待核查</t>
         </is>
       </c>
       <c r="BB8" s="37" t="inlineStr">
@@ -3240,7 +3264,7 @@
       <c r="AZ9" s="36" t="n"/>
       <c r="BA9" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB9" s="36" t="inlineStr">
@@ -3485,7 +3509,7 @@
       <c r="AZ10" s="38" t="n"/>
       <c r="BA10" s="38" t="inlineStr">
         <is>
-          <t>待核查 | 待核查</t>
+          <t>待核查 | 待核查 | 待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB10" s="38" t="inlineStr">
@@ -3722,7 +3746,7 @@
       <c r="AZ11" s="36" t="n"/>
       <c r="BA11" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB11" s="36" t="inlineStr">
@@ -3965,7 +3989,7 @@
       <c r="AZ12" s="38" t="n"/>
       <c r="BA12" s="38" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB12" s="38" t="inlineStr">
@@ -15236,7 +15260,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -16695,7 +16719,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -4232,7 +4232,7 @@
       <c r="AZ13" s="36" t="n"/>
       <c r="BA13" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB13" s="36" t="inlineStr">
@@ -4471,7 +4471,7 @@
       <c r="AZ14" s="38" t="n"/>
       <c r="BA14" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB14" s="38" t="inlineStr">
@@ -4714,7 +4714,7 @@
       <c r="AZ15" s="36" t="n"/>
       <c r="BA15" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB15" s="36" t="inlineStr">
@@ -4961,7 +4961,7 @@
       <c r="AZ16" s="38" t="n"/>
       <c r="BA16" s="38" t="inlineStr">
         <is>
-          <t>待核查：需人工判断</t>
+          <t>待核查：需人工判断 | 待核查：需人工判断</t>
         </is>
       </c>
       <c r="BB16" s="38" t="inlineStr">
@@ -5204,7 +5204,7 @@
       <c r="AZ17" s="36" t="n"/>
       <c r="BA17" s="36" t="inlineStr">
         <is>
-          <t>待核查 | 待核查</t>
+          <t>待核查 | 待核查 | 待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB17" s="36" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -5443,7 +5443,7 @@
       <c r="AZ18" s="38" t="n"/>
       <c r="BA18" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB18" s="38" t="inlineStr">
@@ -5947,7 +5947,7 @@
       <c r="AZ20" s="38" t="n"/>
       <c r="BA20" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB20" s="38" t="inlineStr">
@@ -6192,7 +6192,7 @@
       <c r="AZ21" s="36" t="n"/>
       <c r="BA21" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查 | 待核查：无法确定对照类型 | 待核查</t>
         </is>
       </c>
       <c r="BB21" s="36" t="inlineStr">
@@ -6437,7 +6437,7 @@
       <c r="AZ22" s="38" t="n"/>
       <c r="BA22" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB22" s="38" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -6687,7 +6687,7 @@
       <c r="AZ23" s="36" t="n"/>
       <c r="BA23" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB23" s="36" t="inlineStr">
@@ -6936,7 +6936,7 @@
       <c r="AZ24" s="38" t="n"/>
       <c r="BA24" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB24" s="38" t="inlineStr">
@@ -7417,7 +7417,7 @@
       <c r="AZ26" s="38" t="n"/>
       <c r="BA26" s="38" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB26" s="38" t="inlineStr">
@@ -7662,7 +7662,7 @@
       <c r="AZ27" s="36" t="n"/>
       <c r="BA27" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB27" s="36" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -7905,7 +7905,7 @@
       <c r="AZ28" s="38" t="n"/>
       <c r="BA28" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查 | 待核查：无法确定对照类型 | 待核查</t>
         </is>
       </c>
       <c r="BB28" s="38" t="inlineStr">
@@ -8151,7 +8151,7 @@
       <c r="AZ29" s="36" t="n"/>
       <c r="BA29" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB29" s="36" t="inlineStr">
@@ -8401,7 +8401,7 @@
       <c r="AZ30" s="38" t="n"/>
       <c r="BA30" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB30" s="38" t="inlineStr">
@@ -8648,7 +8648,7 @@
       <c r="AZ31" s="36" t="n"/>
       <c r="BA31" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB31" s="36" t="inlineStr">
@@ -8891,7 +8891,7 @@
       <c r="AZ32" s="38" t="n"/>
       <c r="BA32" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB32" s="38" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -9134,7 +9134,7 @@
       <c r="AZ33" s="36" t="n"/>
       <c r="BA33" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB33" s="36" t="inlineStr">
@@ -9373,7 +9373,7 @@
       <c r="AZ34" s="38" t="n"/>
       <c r="BA34" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB34" s="38" t="inlineStr">
@@ -9618,7 +9618,7 @@
       <c r="AZ35" s="36" t="n"/>
       <c r="BA35" s="36" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB35" s="36" t="inlineStr">
@@ -10108,7 +10108,7 @@
       <c r="AZ37" s="36" t="n"/>
       <c r="BA37" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB37" s="36" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -10355,7 +10355,7 @@
       <c r="AZ38" s="38" t="n"/>
       <c r="BA38" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB38" s="38" t="inlineStr">
@@ -10603,7 +10603,7 @@
       <c r="AZ39" s="36" t="n"/>
       <c r="BA39" s="36" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB39" s="36" t="inlineStr">
@@ -10843,7 +10843,7 @@
       <c r="AZ40" s="38" t="n"/>
       <c r="BA40" s="38" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB40" s="38" t="inlineStr">
@@ -11077,7 +11077,7 @@
       <c r="AZ41" s="36" t="n"/>
       <c r="BA41" s="36" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB41" s="36" t="inlineStr">
@@ -11326,7 +11326,7 @@
       <c r="AZ42" s="38" t="n"/>
       <c r="BA42" s="38" t="inlineStr">
         <is>
-          <t>待核查</t>
+          <t>待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB42" s="38" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -11573,7 +11573,7 @@
       <c r="AZ43" s="36" t="n"/>
       <c r="BA43" s="36" t="inlineStr">
         <is>
-          <t>待核查：需人工判断</t>
+          <t>待核查：需人工判断 | 待核查：需人工判断</t>
         </is>
       </c>
       <c r="BB43" s="36" t="inlineStr">
@@ -12060,7 +12060,7 @@
       <c r="AZ45" s="36" t="n"/>
       <c r="BA45" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB45" s="36" t="inlineStr">
@@ -12534,7 +12534,7 @@
       <c r="AZ47" s="36" t="n"/>
       <c r="BA47" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB47" s="36" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -12776,7 +12776,7 @@
       <c r="AZ48" s="38" t="n"/>
       <c r="BA48" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查：无法自动判断，需人工确认</t>
         </is>
       </c>
       <c r="BB48" s="38" t="inlineStr">
@@ -13016,7 +13016,7 @@
       <c r="AZ49" s="36" t="n"/>
       <c r="BA49" s="36" t="inlineStr">
         <is>
-          <t>待核查 | 待核查</t>
+          <t>待核查 | 待核查 | 待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB49" s="36" t="inlineStr">
@@ -13261,7 +13261,7 @@
       <c r="AZ50" s="38" t="n"/>
       <c r="BA50" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法确定对照类型 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB50" s="38" t="inlineStr">
@@ -13502,7 +13502,7 @@
       <c r="AZ51" s="36" t="n"/>
       <c r="BA51" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法确定对照类型</t>
+          <t>待核查：无法确定对照类型 | 待核查：无法确定对照类型</t>
         </is>
       </c>
       <c r="BB51" s="36" t="inlineStr">
@@ -13745,7 +13745,7 @@
       <c r="AZ52" s="38" t="n"/>
       <c r="BA52" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB52" s="38" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -13984,7 +13984,7 @@
       <c r="AZ53" s="36" t="n"/>
       <c r="BA53" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB53" s="36" t="inlineStr">
@@ -14228,7 +14228,7 @@
       <c r="AZ54" s="38" t="n"/>
       <c r="BA54" s="38" t="inlineStr">
         <is>
-          <t>待核查 | 待核查</t>
+          <t>待核查 | 待核查 | 待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB54" s="38" t="inlineStr">
@@ -14489,7 +14489,7 @@
       <c r="AZ55" s="36" t="n"/>
       <c r="BA55" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB55" s="36" t="inlineStr">
@@ -14738,7 +14738,7 @@
       <c r="AZ56" s="38" t="n"/>
       <c r="BA56" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查 | 待核查</t>
         </is>
       </c>
       <c r="BB56" s="38" t="inlineStr">
@@ -14980,7 +14980,7 @@
       <c r="AZ57" s="36" t="n"/>
       <c r="BA57" s="36" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB57" s="36" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -15224,7 +15224,7 @@
       <c r="AZ58" s="38" t="n"/>
       <c r="BA58" s="38" t="inlineStr">
         <is>
-          <t>待核查：无法自动判断，需人工确认 | 待核查</t>
+          <t>待核查：无法自动判断，需人工确认 | 待核查 | 待核查：无法自动判断，需人工确认 | 待核查</t>
         </is>
       </c>
       <c r="BB58" s="38" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -81,7 +81,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -146,6 +146,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -233,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -355,6 +361,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1397,7 +1406,7 @@
       </c>
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>Lommen</t>
+          <t>Lommen, M.J.J.</t>
         </is>
       </c>
       <c r="C3" s="35" t="n">
@@ -1657,7 +1666,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD3" s="42" t="inlineStr">
+      <c r="BD3" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -1674,7 +1683,7 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Borella, E.</t>
         </is>
       </c>
       <c r="C4" s="37" t="n">
@@ -1929,7 +1938,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD4" s="42" t="inlineStr">
+      <c r="BD4" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -1946,7 +1955,7 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>Salminen</t>
+          <t>Salminen, T.</t>
         </is>
       </c>
       <c r="C5" s="35" t="n">
@@ -2201,7 +2210,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD5" s="42" t="inlineStr">
+      <c r="BD5" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -2218,7 +2227,7 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Tays</t>
+          <t>Tays, G.D.</t>
         </is>
       </c>
       <c r="C6" s="37" t="n">
@@ -2478,7 +2487,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD6" s="42" t="inlineStr">
+      <c r="BD6" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -2495,7 +2504,7 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Vesterinen</t>
+          <t>Vesterinen, H.M.</t>
         </is>
       </c>
       <c r="C7" s="35" t="n">
@@ -2747,7 +2756,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD7" s="42" t="inlineStr">
+      <c r="BD7" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -2764,7 +2773,7 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>Brum</t>
+          <t>Brum, P.S.</t>
         </is>
       </c>
       <c r="C8" s="37" t="n">
@@ -2772,7 +2781,7 @@
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>Verbal working memory training in older adults: an investigation of dose response</t>
+          <t>Verbal working memory training in older adults: an investigation of dose response effects</t>
         </is>
       </c>
       <c r="E8" s="37" t="inlineStr">
@@ -3024,7 +3033,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD8" s="42" t="inlineStr">
+      <c r="BD8" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -3041,13 +3050,17 @@
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Wang, P.</t>
         </is>
       </c>
       <c r="C9" s="35" t="n">
         <v>2025</v>
       </c>
-      <c r="D9" s="36" t="n"/>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>Gamified Working Memory Intervention Enhances Prefrontal Neurocognitive Plasticity During Aging</t>
+        </is>
+      </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3293,7 +3306,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD9" s="40" t="inlineStr">
+      <c r="BD9" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -3310,13 +3323,17 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>Guye</t>
+          <t>Guye, S.</t>
         </is>
       </c>
       <c r="C10" s="37" t="n">
         <v>2017</v>
       </c>
-      <c r="D10" s="38" t="n"/>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>Working Memory Training in Older Adults: Bayesian Evidence Supporting the Absence of Transfer</t>
+        </is>
+      </c>
       <c r="E10" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -3558,7 +3575,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD10" s="40" t="inlineStr">
+      <c r="BD10" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -3575,13 +3592,17 @@
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Teixeira-Santos, A.C.</t>
         </is>
       </c>
       <c r="C11" s="35" t="n">
         <v>2022</v>
       </c>
-      <c r="D11" s="36" t="n"/>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training Coupled With Transcranial Direct Current Stimulation in Older Adults: A Randomized Controlled Experiment</t>
+        </is>
+      </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
           <t>预印本</t>
@@ -3819,7 +3840,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD11" s="40" t="inlineStr">
+      <c r="BD11" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -3836,13 +3857,17 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>Rudner</t>
+          <t>Wayne, R.V.</t>
         </is>
       </c>
       <c r="C12" s="37" t="n">
         <v>2016</v>
       </c>
-      <c r="D12" s="38" t="n"/>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>Working Memory Training and Speech in Noise Comprehension in Older Adults</t>
+        </is>
+      </c>
       <c r="E12" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4090,7 +4115,7 @@
           <t>交叉</t>
         </is>
       </c>
-      <c r="BD12" s="40" t="inlineStr">
+      <c r="BD12" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -4107,13 +4132,17 @@
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Berryhill</t>
+          <t>Stephens, J.A.</t>
         </is>
       </c>
       <c r="C13" s="35" t="n">
         <v>2016</v>
       </c>
-      <c r="D13" s="36" t="n"/>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Older Adults Improve on Everyday Tasks after Working Memory Training and Neurostimulation</t>
+        </is>
+      </c>
       <c r="E13" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4357,7 +4386,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD13" s="40" t="inlineStr">
+      <c r="BD13" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -4374,13 +4403,17 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>Matysiak</t>
+          <t>Matysiak, O.</t>
         </is>
       </c>
       <c r="C14" s="37" t="n">
         <v>2019</v>
       </c>
-      <c r="D14" s="38" t="n"/>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population</t>
+        </is>
+      </c>
       <c r="E14" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4626,7 +4659,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD14" s="40" t="inlineStr">
+      <c r="BD14" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -4643,13 +4676,17 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Šimko, P.</t>
         </is>
       </c>
       <c r="C15" s="35" t="n">
         <v>2021</v>
       </c>
-      <c r="D15" s="36" t="n"/>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors</t>
+        </is>
+      </c>
       <c r="E15" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -4895,7 +4932,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD15" s="40" t="inlineStr">
+      <c r="BD15" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -4912,13 +4949,17 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Borella, E.</t>
         </is>
       </c>
       <c r="C16" s="37" t="n">
         <v>2019</v>
       </c>
-      <c r="D16" s="38" t="n"/>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training</t>
+        </is>
+      </c>
       <c r="E16" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5171,7 +5212,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD16" s="40" t="inlineStr">
+      <c r="BD16" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -5188,13 +5229,17 @@
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Matysiak, O.</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
         <v>2020</v>
       </c>
-      <c r="D17" s="36" t="n"/>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment</t>
+        </is>
+      </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5440,7 +5485,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD17" s="40" t="inlineStr">
+      <c r="BD17" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -5457,13 +5502,17 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Heinzel, S.</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
         <v>2014</v>
       </c>
-      <c r="D18" s="38" t="n"/>
+      <c r="D18" s="38" t="inlineStr">
+        <is>
+          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults</t>
+        </is>
+      </c>
       <c r="E18" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5703,7 +5752,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD18" s="40" t="inlineStr">
+      <c r="BD18" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -5720,13 +5769,17 @@
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Borella, E.</t>
         </is>
       </c>
       <c r="C19" s="35" t="n">
         <v>2013</v>
       </c>
-      <c r="D19" s="36" t="n"/>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training in Old Age: An Examination of Transfer and Maintenance Effects</t>
+        </is>
+      </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -5973,7 +6026,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD19" s="40" t="inlineStr">
+      <c r="BD19" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -5990,13 +6043,17 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Olivetti</t>
+          <t>Ghavidel, F.</t>
         </is>
       </c>
       <c r="C20" s="37" t="n">
         <v>2020</v>
       </c>
-      <c r="D20" s="38" t="n"/>
+      <c r="D20" s="38" t="inlineStr">
+        <is>
+          <t>Feasibility of using a computer-assisted working memory training program for healthy older women</t>
+        </is>
+      </c>
       <c r="E20" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6246,7 +6303,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD20" s="40" t="inlineStr">
+      <c r="BD20" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -6263,13 +6320,17 @@
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Sun, S.</t>
         </is>
       </c>
       <c r="C21" s="35" t="n">
         <v>2018</v>
       </c>
-      <c r="D21" s="36" t="n"/>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial</t>
+        </is>
+      </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6517,7 +6578,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD21" s="40" t="inlineStr">
+      <c r="BD21" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -6534,13 +6595,17 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Boutzoukas, E.M.</t>
         </is>
       </c>
       <c r="C22" s="37" t="n">
         <v>2022</v>
       </c>
-      <c r="D22" s="38" t="n"/>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults</t>
+        </is>
+      </c>
       <c r="E22" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -6786,7 +6851,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD22" s="40" t="inlineStr">
+      <c r="BD22" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -6803,13 +6868,17 @@
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Verty, L.V.</t>
         </is>
       </c>
       <c r="C23" s="35" t="n">
         <v>2024</v>
       </c>
-      <c r="D23" s="36" t="n"/>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study</t>
+        </is>
+      </c>
       <c r="E23" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7057,7 +7126,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD23" s="40" t="inlineStr">
+      <c r="BD23" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -7074,13 +7143,17 @@
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>Tagliabue</t>
+          <t>Tagliabue, C.F.</t>
         </is>
       </c>
       <c r="C24" s="37" t="n">
         <v>2022</v>
       </c>
-      <c r="D24" s="38" t="n"/>
+      <c r="D24" s="38" t="inlineStr">
+        <is>
+          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study</t>
+        </is>
+      </c>
       <c r="E24" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7326,7 +7399,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD24" s="40" t="inlineStr">
+      <c r="BD24" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -7343,13 +7416,17 @@
       </c>
       <c r="B25" s="35" t="inlineStr">
         <is>
-          <t>Zinke</t>
+          <t>Zinke, K.</t>
         </is>
       </c>
       <c r="C25" s="35" t="n">
         <v>2014</v>
       </c>
-      <c r="D25" s="36" t="n"/>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training and Transfer in Older Adults: Effects of Age, Baseline Performance, and Training Gains</t>
+        </is>
+      </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7597,7 +7674,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD25" s="40" t="inlineStr">
+      <c r="BD25" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -7614,13 +7691,17 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>Schmicker</t>
+          <t>Mičič, S.</t>
         </is>
       </c>
       <c r="C26" s="37" t="n">
         <v>2020</v>
       </c>
-      <c r="D26" s="38" t="n"/>
+      <c r="D26" s="38" t="inlineStr">
+        <is>
+          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve</t>
+        </is>
+      </c>
       <c r="E26" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -7866,7 +7947,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD26" s="40" t="inlineStr">
+      <c r="BD26" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -7883,13 +7964,17 @@
       </c>
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>Matysiak</t>
+          <t>Zając-Lamparska, L.</t>
         </is>
       </c>
       <c r="C27" s="35" t="n">
         <v>2024</v>
       </c>
-      <c r="D27" s="36" t="n"/>
+      <c r="D27" s="36" t="inlineStr">
+        <is>
+          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training</t>
+        </is>
+      </c>
       <c r="E27" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8142,7 +8227,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD27" s="40" t="inlineStr">
+      <c r="BD27" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -8159,13 +8244,17 @@
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>Jaeggi</t>
+          <t>Jaeggi, S.M.</t>
         </is>
       </c>
       <c r="C28" s="37" t="n">
         <v>2020</v>
       </c>
-      <c r="D28" s="38" t="n"/>
+      <c r="D28" s="38" t="inlineStr">
+        <is>
+          <t>Investigating the effects of spacing on working memory training outcome – a randomized controlled multi-site trial in older adults</t>
+        </is>
+      </c>
       <c r="E28" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8411,7 +8500,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD28" s="40" t="inlineStr">
+      <c r="BD28" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -8428,13 +8517,17 @@
       </c>
       <c r="B29" s="35" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Bürki, C.N.</t>
         </is>
       </c>
       <c r="C29" s="35" t="n">
         <v>2014</v>
       </c>
-      <c r="D29" s="36" t="n"/>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults</t>
+        </is>
+      </c>
       <c r="E29" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8686,7 +8779,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD29" s="40" t="inlineStr">
+      <c r="BD29" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -8703,13 +8796,17 @@
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Cantarella, A.</t>
         </is>
       </c>
       <c r="C30" s="37" t="n">
         <v>2017</v>
       </c>
-      <c r="D30" s="38" t="n"/>
+      <c r="D30" s="38" t="inlineStr">
+        <is>
+          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults</t>
+        </is>
+      </c>
       <c r="E30" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -8964,7 +9061,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD30" s="40" t="inlineStr">
+      <c r="BD30" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -8981,13 +9078,17 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Carretti, B.</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
         <v>2013</v>
       </c>
-      <c r="D31" s="36" t="n"/>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>Gains in language comprehension relating to working memory training in healthy older adults</t>
+        </is>
+      </c>
       <c r="E31" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9232,7 +9333,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD31" s="40" t="inlineStr">
+      <c r="BD31" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -9249,13 +9350,17 @@
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>Heo, S.</t>
         </is>
       </c>
       <c r="C32" s="37" t="n">
         <v>2014</v>
       </c>
-      <c r="D32" s="38" t="n"/>
+      <c r="D32" s="38" t="inlineStr">
+        <is>
+          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults</t>
+        </is>
+      </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9497,7 +9602,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD32" s="40" t="inlineStr">
+      <c r="BD32" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -9514,13 +9619,17 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Assecondi, S.</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
         <v>2022</v>
       </c>
-      <c r="D33" s="36" t="n"/>
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training</t>
+        </is>
+      </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -9768,7 +9877,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD33" s="40" t="inlineStr">
+      <c r="BD33" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -9785,13 +9894,17 @@
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Günther</t>
+          <t>Günther, V.K.</t>
         </is>
       </c>
       <c r="C34" s="37" t="n">
         <v>2003</v>
       </c>
-      <c r="D34" s="38" t="n"/>
+      <c r="D34" s="38" t="inlineStr">
+        <is>
+          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: A pilot study in a residential home for older people</t>
+        </is>
+      </c>
       <c r="E34" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10035,7 +10148,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD34" s="40" t="inlineStr">
+      <c r="BD34" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -10052,13 +10165,17 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Shatil, E.</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
         <v>2014</v>
       </c>
-      <c r="D35" s="36" t="n"/>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>Novel Television-Based Cognitive Training Improves Working Memory and Executive Function</t>
+        </is>
+      </c>
       <c r="E35" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10304,7 +10421,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD35" s="40" t="inlineStr">
+      <c r="BD35" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -10321,13 +10438,17 @@
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Buschkuehl, M.</t>
         </is>
       </c>
       <c r="C36" s="37" t="n">
         <v>2008</v>
       </c>
-      <c r="D36" s="38" t="n"/>
+      <c r="D36" s="38" t="inlineStr">
+        <is>
+          <t>Impact of Working Memory Training on Memory Performance in Old-Old Adults</t>
+        </is>
+      </c>
       <c r="E36" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10575,7 +10696,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD36" s="40" t="inlineStr">
+      <c r="BD36" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -10592,13 +10713,17 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>Booth, S.J.</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
         <v>2023</v>
       </c>
-      <c r="D37" s="36" t="n"/>
+      <c r="D37" s="36" t="inlineStr">
+        <is>
+          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults</t>
+        </is>
+      </c>
       <c r="E37" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -10847,7 +10972,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD37" s="40" t="inlineStr">
+      <c r="BD37" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -10864,13 +10989,17 @@
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Heinzel, S.</t>
         </is>
       </c>
       <c r="C38" s="37" t="n">
         <v>2017</v>
       </c>
-      <c r="D38" s="38" t="n"/>
+      <c r="D38" s="38" t="inlineStr">
+        <is>
+          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults</t>
+        </is>
+      </c>
       <c r="E38" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11119,7 +11248,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD38" s="40" t="inlineStr">
+      <c r="BD38" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -11136,13 +11265,17 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>Stephens, J.A.</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
         <v>2017</v>
       </c>
-      <c r="D39" s="36" t="n"/>
+      <c r="D39" s="36" t="inlineStr">
+        <is>
+          <t>Task demands, tDCS intensity, and the COMT val158met polymorphism impact tDCS-linked working memory training gains</t>
+        </is>
+      </c>
       <c r="E39" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11392,7 +11525,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD39" s="40" t="inlineStr">
+      <c r="BD39" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -11409,13 +11542,17 @@
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Sutton, E.</t>
         </is>
       </c>
       <c r="C40" s="37" t="n">
         <v>2025</v>
       </c>
-      <c r="D40" s="38" t="n"/>
+      <c r="D40" s="38" t="inlineStr">
+        <is>
+          <t>Practice makes perfect, but to what end? Computerised brain training has limited effects on cognition and mood in healthy older adults</t>
+        </is>
+      </c>
       <c r="E40" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11663,7 +11800,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD40" s="40" t="inlineStr">
+      <c r="BD40" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -11680,13 +11817,17 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>Tusch, E.S.</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
         <v>2016</v>
       </c>
-      <c r="D41" s="36" t="n"/>
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults</t>
+        </is>
+      </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -11934,7 +12075,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD41" s="40" t="inlineStr">
+      <c r="BD41" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -11951,13 +12092,17 @@
       </c>
       <c r="B42" s="37" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>McAvinue, L.P.</t>
         </is>
       </c>
       <c r="C42" s="37" t="n">
         <v>2013</v>
       </c>
-      <c r="D42" s="38" t="n"/>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>An evaluation of a working memory training scheme in older adults</t>
+        </is>
+      </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12205,7 +12350,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD42" s="40" t="inlineStr">
+      <c r="BD42" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -12222,13 +12367,17 @@
       </c>
       <c r="B43" s="35" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>Goghari, V.M.</t>
         </is>
       </c>
       <c r="C43" s="35" t="n">
         <v>2018</v>
       </c>
-      <c r="D43" s="36" t="n"/>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults</t>
+        </is>
+      </c>
       <c r="E43" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12476,7 +12625,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD43" s="40" t="inlineStr">
+      <c r="BD43" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -12493,13 +12642,17 @@
       </c>
       <c r="B44" s="37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Borella, E.</t>
         </is>
       </c>
       <c r="C44" s="37" t="n">
         <v>2025</v>
       </c>
-      <c r="D44" s="38" t="n"/>
+      <c r="D44" s="38" t="inlineStr">
+        <is>
+          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study</t>
+        </is>
+      </c>
       <c r="E44" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -12741,7 +12894,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD44" s="40" t="inlineStr">
+      <c r="BD44" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -12758,13 +12911,17 @@
       </c>
       <c r="B45" s="35" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>Goghari, V.M.</t>
         </is>
       </c>
       <c r="C45" s="35" t="n">
         <v>2017</v>
       </c>
-      <c r="D45" s="36" t="n"/>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults</t>
+        </is>
+      </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13015,7 +13172,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD45" s="40" t="inlineStr">
+      <c r="BD45" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -13032,13 +13189,17 @@
       </c>
       <c r="B46" s="37" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Zinke, K.</t>
         </is>
       </c>
       <c r="C46" s="37" t="n">
         <v>2012</v>
       </c>
-      <c r="D46" s="38" t="n"/>
+      <c r="D46" s="38" t="inlineStr">
+        <is>
+          <t>Potentials and Limits of Plasticity Induced by Working Memory Training in Old-Old Age</t>
+        </is>
+      </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13268,7 +13429,7 @@
           <t>准RCT</t>
         </is>
       </c>
-      <c r="BD46" s="40" t="inlineStr">
+      <c r="BD46" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -13285,13 +13446,17 @@
       </c>
       <c r="B47" s="35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Basak, C.</t>
         </is>
       </c>
       <c r="C47" s="35" t="n">
         <v>2016</v>
       </c>
-      <c r="D47" s="36" t="n"/>
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults</t>
+        </is>
+      </c>
       <c r="E47" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13539,7 +13704,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD47" s="40" t="inlineStr">
+      <c r="BD47" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -13556,13 +13721,17 @@
       </c>
       <c r="B48" s="37" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Jaeggi, S.M.</t>
         </is>
       </c>
       <c r="C48" s="37" t="n">
         <v>2023</v>
       </c>
-      <c r="D48" s="38" t="n"/>
+      <c r="D48" s="38" t="inlineStr">
+        <is>
+          <t>EngAge – A metacognitive intervention to supplement working memory training: A feasibility study in older adults</t>
+        </is>
+      </c>
       <c r="E48" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -13802,7 +13971,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD48" s="40" t="inlineStr">
+      <c r="BD48" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -13819,13 +13988,17 @@
       </c>
       <c r="B49" s="35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Borella, E.</t>
         </is>
       </c>
       <c r="C49" s="35" t="n">
         <v>2017</v>
       </c>
-      <c r="D49" s="36" t="n"/>
+      <c r="D49" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Training Gains</t>
+        </is>
+      </c>
       <c r="E49" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14065,7 +14238,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD49" s="40" t="inlineStr">
+      <c r="BD49" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -14082,13 +14255,17 @@
       </c>
       <c r="B50" s="37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Brambilla, M.</t>
         </is>
       </c>
       <c r="C50" s="37" t="n">
         <v>2021</v>
       </c>
-      <c r="D50" s="38" t="n"/>
+      <c r="D50" s="38" t="inlineStr">
+        <is>
+          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging</t>
+        </is>
+      </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
           <t>预印本</t>
@@ -14332,7 +14509,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD50" s="40" t="inlineStr">
+      <c r="BD50" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -14349,13 +14526,17 @@
       </c>
       <c r="B51" s="35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Antonenko, D.</t>
         </is>
       </c>
       <c r="C51" s="35" t="n">
         <v>2022</v>
       </c>
-      <c r="D51" s="36" t="n"/>
+      <c r="D51" s="36" t="inlineStr">
+        <is>
+          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults</t>
+        </is>
+      </c>
       <c r="E51" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14599,7 +14780,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD51" s="40" t="inlineStr">
+      <c r="BD51" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -14616,13 +14797,17 @@
       </c>
       <c r="B52" s="37" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>Zelinski, E.M.</t>
         </is>
       </c>
       <c r="C52" s="37" t="n">
         <v>2014</v>
       </c>
-      <c r="D52" s="38" t="n"/>
+      <c r="D52" s="38" t="inlineStr">
+        <is>
+          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes</t>
+        </is>
+      </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -14866,7 +15051,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD52" s="40" t="inlineStr">
+      <c r="BD52" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -14883,13 +15068,17 @@
       </c>
       <c r="B53" s="35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Spironelli, C.</t>
         </is>
       </c>
       <c r="C53" s="35" t="n">
         <v>2021</v>
       </c>
-      <c r="D53" s="36" t="n"/>
+      <c r="D53" s="36" t="inlineStr">
+        <is>
+          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study</t>
+        </is>
+      </c>
       <c r="E53" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15131,7 +15320,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD53" s="40" t="inlineStr">
+      <c r="BD53" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -15148,13 +15337,17 @@
       </c>
       <c r="B54" s="37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Nguyen, L.</t>
         </is>
       </c>
       <c r="C54" s="37" t="n">
         <v>2026</v>
       </c>
-      <c r="D54" s="38" t="n"/>
+      <c r="D54" s="38" t="inlineStr">
+        <is>
+          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults</t>
+        </is>
+      </c>
       <c r="E54" s="38" t="inlineStr">
         <is>
           <t>预印本</t>
@@ -15399,7 +15592,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD54" s="40" t="inlineStr">
+      <c r="BD54" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -15416,13 +15609,17 @@
       </c>
       <c r="B55" s="35" t="inlineStr">
         <is>
-          <t>Cantarella</t>
+          <t>Cantarella, A.</t>
         </is>
       </c>
       <c r="C55" s="35" t="n">
         <v>2021</v>
       </c>
-      <c r="D55" s="36" t="n"/>
+      <c r="D55" s="36" t="inlineStr">
+        <is>
+          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
+        </is>
+      </c>
       <c r="E55" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15668,7 +15865,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD55" s="40" t="inlineStr">
+      <c r="BD55" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -15685,13 +15882,17 @@
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Pergher, V.</t>
         </is>
       </c>
       <c r="C56" s="37" t="n">
         <v>2020</v>
       </c>
-      <c r="D56" s="38" t="n"/>
+      <c r="D56" s="38" t="inlineStr">
+        <is>
+          <t>Impact of strategy use during N-Back training in older adults</t>
+        </is>
+      </c>
       <c r="E56" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -15937,7 +16138,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD56" s="40" t="inlineStr">
+      <c r="BD56" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -15954,13 +16155,17 @@
       </c>
       <c r="B57" s="35" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Lange, S.</t>
         </is>
       </c>
       <c r="C57" s="35" t="n">
         <v>2015</v>
       </c>
-      <c r="D57" s="36" t="n"/>
+      <c r="D57" s="36" t="inlineStr">
+        <is>
+          <t>Experimental Evaluation of Near- and Far-Transfer Effects of an Adaptive Multicomponent Working Memory Training</t>
+        </is>
+      </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -16206,7 +16411,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD57" s="40" t="inlineStr">
+      <c r="BD57" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>
@@ -16223,13 +16428,17 @@
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Chai, Q.</t>
         </is>
       </c>
       <c r="C58" s="37" t="n">
         <v>2026</v>
       </c>
-      <c r="D58" s="38" t="n"/>
+      <c r="D58" s="38" t="inlineStr">
+        <is>
+          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability Among Older Women</t>
+        </is>
+      </c>
       <c r="E58" s="38" t="inlineStr">
         <is>
           <t>期刊</t>
@@ -16476,7 +16685,7 @@
           <t>RCT</t>
         </is>
       </c>
-      <c r="BD58" s="40" t="inlineStr">
+      <c r="BD58" s="43" t="inlineStr">
         <is>
           <t>已填入</t>
         </is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1288,17 +1288,15 @@
         <v>34</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>19.96</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L3" s="19" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M3" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M3" s="15" t="n">
+        <v>5.25</v>
       </c>
       <c r="N3" s="15" t="inlineStr">
         <is>
@@ -2366,17 +2364,15 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>26.15</v>
+        <v>63.11</v>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M7" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
@@ -3403,17 +3399,13 @@
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>18</v>
       </c>
       <c r="K11" s="15" t="n">
         <v>68.2</v>
@@ -3940,17 +3932,15 @@
         <v>30</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>13.036</v>
+        <v>69.3</v>
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M13" s="15" t="n">
+        <v>5.1</v>
       </c>
       <c r="N13" s="15" t="inlineStr">
         <is>
@@ -4194,7 +4184,7 @@
         </is>
       </c>
       <c r="H14" s="16" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -4203,7 +4193,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>无对照组</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="K14" s="16" t="n">
@@ -4465,14 +4455,12 @@
       <c r="H15" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>25</v>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>无对照组</t>
         </is>
       </c>
       <c r="K15" s="15" t="n">
@@ -5002,13 +4990,13 @@
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>66.7</v>
@@ -5278,17 +5266,15 @@
         </is>
       </c>
       <c r="K18" s="16" t="n">
-        <v>25.9</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M18" s="16" t="n">
+        <v>4.7</v>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
@@ -6338,15 +6324,11 @@
       <c r="H22" s="16" t="n">
         <v>62</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I22" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>32</v>
       </c>
       <c r="K22" s="16" t="n">
         <v>71</v>
@@ -7191,10 +7173,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U25" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U25" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="V25" s="15" t="inlineStr">
         <is>
@@ -7239,10 +7219,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE25" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE25" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF25" s="15" t="inlineStr">
         <is>
@@ -7398,17 +7376,13 @@
         </is>
       </c>
       <c r="H26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>11</v>
       </c>
       <c r="K26" s="16" t="n">
         <v>81.70999999999999</v>
@@ -7459,22 +7433,18 @@
         </is>
       </c>
       <c r="U26" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="V26" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="V26" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="W26" s="16" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X26" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X26" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="Y26" s="16" t="inlineStr">
         <is>
@@ -7669,15 +7639,11 @@
       <c r="H27" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I27" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>22</v>
       </c>
       <c r="K27" s="15" t="n">
         <v>66.40000000000001</v>
@@ -7728,15 +7694,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U27" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V27" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U27" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="V27" s="15" t="n">
+        <v>45</v>
       </c>
       <c r="W27" s="15" t="inlineStr">
         <is>
@@ -7954,17 +7916,15 @@
         </is>
       </c>
       <c r="K28" s="16" t="n">
-        <v>21.45</v>
+        <v>69.56</v>
       </c>
       <c r="L28" s="21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M28" s="16" t="n">
+        <v>4.24</v>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
@@ -8280,20 +8240,16 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V29" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V29" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X29" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X29" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Y29" s="15" t="inlineStr">
         <is>
@@ -8476,15 +8432,11 @@
       <c r="H30" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I30" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="K30" s="16" t="n">
         <v>70</v>
@@ -8543,7 +8495,7 @@
         </is>
       </c>
       <c r="V30" s="16" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="W30" s="16" t="inlineStr">
         <is>
@@ -8752,13 +8704,11 @@
       <c r="H31" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I31" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K31" s="15" t="n">
         <v>75</v>
@@ -8815,7 +8765,7 @@
         </is>
       </c>
       <c r="V31" s="15" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
@@ -9092,7 +9042,7 @@
         </is>
       </c>
       <c r="X32" s="16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="16" t="inlineStr">
         <is>
@@ -9125,7 +9075,7 @@
         </is>
       </c>
       <c r="AE32" s="21" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AF32" s="16" t="inlineStr">
         <is>
@@ -9336,10 +9286,8 @@
       <c r="U33" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="V33" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V33" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="W33" s="15" t="inlineStr">
         <is>
@@ -9603,10 +9551,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V34" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V34" s="16" t="n">
+        <v>45</v>
       </c>
       <c r="W34" s="16" t="inlineStr">
         <is>
@@ -9646,10 +9592,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE34" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE34" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="AF34" s="16" t="inlineStr">
         <is>
@@ -10147,10 +10091,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X36" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X36" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="Y36" s="16" t="inlineStr">
         <is>
@@ -10345,15 +10287,11 @@
       <c r="H37" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I37" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>17</v>
       </c>
       <c r="K37" s="15" t="n">
         <v>66</v>
@@ -10404,10 +10342,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U37" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U37" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="V37" s="15" t="inlineStr">
         <is>
@@ -10420,7 +10356,7 @@
         </is>
       </c>
       <c r="X37" s="15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="15" t="inlineStr">
         <is>
@@ -10452,8 +10388,10 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE37" s="21" t="n">
-        <v>3</v>
+      <c r="AE37" s="21" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AF37" s="15" t="inlineStr">
         <is>
@@ -10617,15 +10555,11 @@
       <c r="H38" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I38" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>16</v>
       </c>
       <c r="K38" s="16" t="n">
         <v>65.78</v>
@@ -10673,10 +10607,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U38" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U38" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="V38" s="16" t="n">
         <v>45</v>
@@ -10686,10 +10618,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X38" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X38" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="Y38" s="16" t="inlineStr">
         <is>
@@ -10722,10 +10652,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE38" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE38" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF38" s="16" t="inlineStr">
         <is>
@@ -10881,15 +10809,11 @@
       <c r="H39" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I39" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>40</v>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
@@ -11146,15 +11070,11 @@
       <c r="H40" s="16" t="n">
         <v>103</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I40" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J40" s="16" t="n">
+        <v>49</v>
       </c>
       <c r="K40" s="16" t="n">
         <v>70.56999999999999</v>
@@ -11403,17 +11323,13 @@
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" s="15" t="n">
+        <v>17</v>
       </c>
       <c r="K41" s="15" t="n">
         <v>47</v>
@@ -11466,10 +11382,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V41" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V41" s="15" t="n">
+        <v>40</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
@@ -11668,15 +11582,11 @@
       <c r="H42" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I42" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J42" s="16" t="n">
+        <v>17</v>
       </c>
       <c r="K42" s="16" t="inlineStr">
         <is>
@@ -11774,10 +11684,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE42" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE42" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF42" s="16" t="inlineStr">
         <is>
@@ -12004,10 +11912,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V43" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V43" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
@@ -12047,10 +11953,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE43" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE43" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF43" s="15" t="inlineStr">
         <is>
@@ -12544,17 +12448,15 @@
         </is>
       </c>
       <c r="V45" s="15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W45" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X45" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X45" s="15" t="n">
+        <v>8</v>
       </c>
       <c r="Y45" s="15" t="inlineStr">
         <is>
@@ -12586,10 +12488,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE45" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE45" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF45" s="15" t="inlineStr">
         <is>
@@ -12801,11 +12701,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U46" s="16" t="n">
-        <v>10</v>
+      <c r="U46" s="16" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="V46" s="16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="W46" s="16" t="inlineStr">
         <is>
@@ -12813,7 +12715,7 @@
         </is>
       </c>
       <c r="X46" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y46" s="16" t="inlineStr">
         <is>
@@ -12845,8 +12747,10 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE46" s="21" t="n">
-        <v>1.7</v>
+      <c r="AE46" s="21" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AF46" s="16" t="inlineStr">
         <is>
@@ -13004,17 +12908,13 @@
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J47" s="15" t="inlineStr">
-        <is>
-          <t>无对照组</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>23</v>
       </c>
       <c r="K47" s="15" t="n">
         <v>68.81</v>
@@ -13067,18 +12967,18 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V47" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V47" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
           <t>6.52%</t>
         </is>
       </c>
-      <c r="X47" s="15" t="n">
-        <v>2</v>
+      <c r="X47" s="15" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="Y47" s="15" t="inlineStr">
         <is>
@@ -13329,25 +13229,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U48" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V48" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U48" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V48" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="W48" s="16" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X48" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X48" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="Y48" s="16" t="inlineStr">
         <is>
@@ -13600,7 +13494,7 @@
         </is>
       </c>
       <c r="V49" s="15" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
@@ -13803,15 +13697,11 @@
       <c r="H50" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I50" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="K50" s="16" t="n">
         <v>64.5</v>
@@ -14124,15 +14014,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U51" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V51" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U51" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="V51" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="W51" s="15" t="inlineStr">
         <is>
@@ -14172,10 +14058,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE51" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE51" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF51" s="15" t="inlineStr">
         <is>
@@ -14333,15 +14217,11 @@
       <c r="H52" s="16" t="n">
         <v>242</v>
       </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I52" s="16" t="n">
+        <v>242</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>245</v>
       </c>
       <c r="K52" s="16" t="n">
         <v>75.59999999999999</v>
@@ -15394,15 +15274,11 @@
       <c r="H56" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>无对照组</t>
-        </is>
+      <c r="I56" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>7</v>
       </c>
       <c r="K56" s="16" t="n">
         <v>61.86</v>
@@ -15655,10 +15531,8 @@
       <c r="H57" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I57" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="J57" s="15" t="n">
         <v>19</v>
@@ -15931,17 +15805,15 @@
         <v>22</v>
       </c>
       <c r="K58" s="16" t="n">
-        <v>21.36</v>
+        <v>70.56</v>
       </c>
       <c r="L58" s="21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M58" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M58" s="16" t="n">
+        <v>5.27</v>
       </c>
       <c r="N58" s="16" t="inlineStr">
         <is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="H4" s="16" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I5" s="15" t="n">
         <v>25</v>
@@ -4186,15 +4186,11 @@
       <c r="H14" s="16" t="n">
         <v>83</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I14" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>42</v>
       </c>
       <c r="K14" s="16" t="n">
         <v>65.90000000000001</v>
@@ -4712,7 +4708,7 @@
         </is>
       </c>
       <c r="H16" s="16" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I16" s="16" t="n">
         <v>16</v>
@@ -6581,15 +6577,11 @@
       <c r="H23" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I23" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>10</v>
       </c>
       <c r="K23" s="15" t="n">
         <v>70.8</v>
@@ -6848,17 +6840,13 @@
         </is>
       </c>
       <c r="H24" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>104</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>36</v>
       </c>
       <c r="K24" s="16" t="n">
         <v>68.25</v>
@@ -7637,7 +7625,7 @@
         </is>
       </c>
       <c r="H27" s="15" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="I27" s="15" t="n">
         <v>25</v>
@@ -8172,16 +8160,14 @@
         </is>
       </c>
       <c r="H29" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>65</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>65</v>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>无对照组</t>
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr">
@@ -8430,7 +8416,7 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>18</v>
@@ -8702,13 +8688,13 @@
         </is>
       </c>
       <c r="H31" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I31" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>20</v>
-      </c>
       <c r="J31" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K31" s="15" t="n">
         <v>75</v>
@@ -9225,17 +9211,13 @@
         </is>
       </c>
       <c r="H33" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>14</v>
       </c>
       <c r="K33" s="15" t="n">
         <v>67.90000000000001</v>
@@ -9488,14 +9470,12 @@
       <c r="H34" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I34" s="16" t="n">
+        <v>19</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>无对照组</t>
         </is>
       </c>
       <c r="K34" s="16" t="n">
@@ -9749,13 +9729,13 @@
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="I35" s="15" t="n">
         <v>60</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K35" s="15" t="n">
         <v>70.5</v>
@@ -10553,10 +10533,10 @@
         </is>
       </c>
       <c r="H38" s="16" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I38" s="16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J38" s="16" t="n">
         <v>16</v>
@@ -10807,10 +10787,10 @@
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="J39" s="15" t="n">
         <v>40</v>
@@ -11332,17 +11312,15 @@
         <v>17</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>47</v>
+        <v>75.7</v>
       </c>
       <c r="L41" s="21" t="inlineStr">
         <is>
           <t>young-old</t>
         </is>
       </c>
-      <c r="M41" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="M41" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="N41" s="15" t="inlineStr">
         <is>
@@ -11580,7 +11558,7 @@
         </is>
       </c>
       <c r="H42" s="16" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>19</v>
@@ -12647,7 +12625,7 @@
         </is>
       </c>
       <c r="H46" s="16" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>20</v>
@@ -13175,13 +13153,13 @@
         </is>
       </c>
       <c r="H48" s="16" t="n">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K48" s="16" t="n">
         <v>72.86</v>
@@ -13432,17 +13410,13 @@
         </is>
       </c>
       <c r="H49" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J49" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>148</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="J49" s="15" t="n">
+        <v>75</v>
       </c>
       <c r="K49" s="15" t="n">
         <v>69</v>
@@ -13695,10 +13669,10 @@
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J50" s="16" t="n">
         <v>14</v>
@@ -14215,7 +14189,7 @@
         </is>
       </c>
       <c r="H52" s="16" t="n">
-        <v>242</v>
+        <v>487</v>
       </c>
       <c r="I52" s="16" t="n">
         <v>242</v>
@@ -14737,15 +14711,11 @@
       <c r="H54" s="16" t="n">
         <v>66</v>
       </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="I54" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="K54" s="16" t="n">
         <v>69.58</v>
@@ -15003,7 +14973,7 @@
         </is>
       </c>
       <c r="H55" s="15" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I55" s="15" t="n">
         <v>18</v>
@@ -15529,10 +15499,10 @@
         </is>
       </c>
       <c r="H57" s="15" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J57" s="15" t="n">
         <v>19</v>
@@ -15796,7 +15766,7 @@
         </is>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="I58" s="16" t="n">
         <v>22</v>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1489,7 +1489,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA3" s="15" t="n"/>
+      <c r="BA3" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[设计]:准RCT→RCT(randomly assigned明确)</t>
+        </is>
+      </c>
       <c r="BB3" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -1497,7 +1501,7 @@
       </c>
       <c r="BC3" s="15" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD3" s="20" t="inlineStr">
@@ -3257,13 +3261,13 @@
       </c>
       <c r="AF10" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG10" s="16" t="n"/>
       <c r="AH10" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AI10" s="16" t="n"/>
@@ -3344,7 +3348,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA10" s="16" t="n"/>
+      <c r="BA10" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确near transfer，测了untrained WM tasks) | oo核查修正[远迁移]:否→是(Abstract明确far transfer，Bayesian evidence)</t>
+        </is>
+      </c>
       <c r="BB10" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -3868,7 +3876,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA12" s="16" t="n"/>
+      <c r="BA12" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[设计]:交叉→RCT("randomized active control trial"，有crossover但主设计是RCT)</t>
+        </is>
+      </c>
       <c r="BB12" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -3876,7 +3888,7 @@
       </c>
       <c r="BC12" s="16" t="inlineStr">
         <is>
-          <t>交叉</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD12" s="20" t="inlineStr">
@@ -4394,7 +4406,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA14" s="16" t="n"/>
+      <c r="BA14" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[设计]:准RCT→RCT("randomly divided into two training groups")</t>
+        </is>
+      </c>
       <c r="BB14" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -4402,7 +4418,7 @@
       </c>
       <c r="BC14" s="16" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD14" s="20" t="inlineStr">
@@ -4653,7 +4669,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA15" s="15" t="n"/>
+      <c r="BA15" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[设计]:RCT→交叉("randomized double-blind crossover study")</t>
+        </is>
+      </c>
       <c r="BB15" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -4661,7 +4681,7 @@
       </c>
       <c r="BC15" s="15" t="inlineStr">
         <is>
-          <t>RCT</t>
+          <t>交叉</t>
         </is>
       </c>
       <c r="BD15" s="20" t="inlineStr">
@@ -4826,7 +4846,7 @@
       </c>
       <c r="AF16" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG16" s="16" t="inlineStr">
@@ -4929,7 +4949,7 @@
       </c>
       <c r="BA16" s="16" t="inlineStr">
         <is>
-          <t>：需人工判断 | ：需人工判断</t>
+          <t>：需人工判断 | ：需人工判断 | oo核查修正[近迁移]:否→是(criterion task（类训练WM任务）= 近迁移)</t>
         </is>
       </c>
       <c r="BB16" s="16" t="inlineStr">
@@ -5097,7 +5117,7 @@
       </c>
       <c r="AF17" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG17" s="15" t="inlineStr">
@@ -5196,7 +5216,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA17" s="15" t="n"/>
+      <c r="BA17" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(Results测了memory updating/inhibition/STM) | oo核查修正[设计]:准RCT→RCT(randomly assigned明确)</t>
+        </is>
+      </c>
       <c r="BB17" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -5204,7 +5228,7 @@
       </c>
       <c r="BC17" s="15" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>RCT</t>
         </is>
       </c>
       <c r="BD17" s="20" t="inlineStr">
@@ -5901,7 +5925,7 @@
       </c>
       <c r="AF20" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG20" s="16" t="inlineStr">
@@ -5992,7 +6016,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA20" s="16" t="n"/>
+      <c r="BA20" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了Corsi Block + Digit Span（未训练WM任务）)</t>
+        </is>
+      </c>
       <c r="BB20" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -6164,7 +6192,7 @@
       </c>
       <c r="AF21" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG21" s="15" t="inlineStr">
@@ -6263,7 +6291,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA21" s="15" t="n"/>
+      <c r="BA21" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了spatial WM + numerical WM)</t>
+        </is>
+      </c>
       <c r="BB21" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -8530,7 +8562,7 @@
       </c>
       <c r="AF30" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG30" s="16" t="inlineStr">
@@ -8633,7 +8665,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA30" s="16" t="n"/>
+      <c r="BA30" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移)</t>
+        </is>
+      </c>
       <c r="BB30" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -9065,7 +9101,7 @@
       </c>
       <c r="AF32" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG32" s="16" t="inlineStr">
@@ -9156,7 +9192,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA32" s="16" t="n"/>
+      <c r="BA32" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了认知功能含WM成分)</t>
+        </is>
+      </c>
       <c r="BB32" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -9577,7 +9617,7 @@
       </c>
       <c r="AF34" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG34" s="16" t="inlineStr">
@@ -9674,7 +9714,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA34" s="16" t="n"/>
+      <c r="BA34" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了primary/secondary WM) | oo核查修正[设计]:准RCT→单组前后测(养老院居民，无对照组，只有训练组前后比较)</t>
+        </is>
+      </c>
       <c r="BB34" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -9682,7 +9726,7 @@
       </c>
       <c r="BC34" s="16" t="inlineStr">
         <is>
-          <t>准RCT</t>
+          <t>单组前后测</t>
         </is>
       </c>
       <c r="BD34" s="20" t="inlineStr">
@@ -9842,7 +9886,7 @@
       </c>
       <c r="AF35" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG35" s="15" t="inlineStr">
@@ -9941,7 +9985,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA35" s="15" t="n"/>
+      <c r="BA35" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了WM等认知测量)</t>
+        </is>
+      </c>
       <c r="BB35" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -11157,7 +11205,7 @@
       </c>
       <c r="AF40" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -11248,7 +11296,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA40" s="16" t="n"/>
+      <c r="BA40" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）)</t>
+        </is>
+      </c>
       <c r="BB40" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -12201,7 +12253,7 @@
       </c>
       <c r="AF44" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG44" s="16" t="inlineStr">
@@ -12302,7 +12354,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA44" s="16" t="n"/>
+      <c r="BA44" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(CWMS criterion task = 近迁移)</t>
+        </is>
+      </c>
       <c r="BB44" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -12732,7 +12788,7 @@
       </c>
       <c r="AF46" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG46" s="16" t="inlineStr">
@@ -12831,7 +12887,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA46" s="16" t="n"/>
+      <c r="BA46" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(测了spatial WM（训练为verbal WM）)</t>
+        </is>
+      </c>
       <c r="BB46" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -14300,7 +14360,7 @@
       </c>
       <c r="AF52" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG52" s="16" t="inlineStr">
@@ -14397,7 +14457,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA52" s="16" t="n"/>
+      <c r="BA52" s="16" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(研究主题即训练→untrained outcomes，有近迁移测量)</t>
+        </is>
+      </c>
       <c r="BB52" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -15090,7 +15154,7 @@
       </c>
       <c r="AF55" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AG55" s="15" t="inlineStr">
@@ -15187,7 +15251,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA55" s="15" t="n"/>
+      <c r="BA55" s="15" t="inlineStr">
+        <is>
+          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移)</t>
+        </is>
+      </c>
       <c r="BB55" s="15" t="inlineStr">
         <is>
           <t>未评估</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AW4" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX4" s="16" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="BA4" s="16" t="inlineStr">
         <is>
-          <t>音乐条件调节效应：Albinoni组&gt;Mozart组在部分任务；White noise=Music组总体</t>
+          <t>音乐条件调节效应：Albinoni组&gt;Mozart组在部分任务；White noise=Music组总体 | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB4" s="16" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AW6" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX6" s="16" t="inlineStr">
@@ -2302,7 +2302,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA6" s="16" t="n"/>
+      <c r="BA6" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB6" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -2547,7 +2551,7 @@
       </c>
       <c r="AW7" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX7" s="15" t="inlineStr">
@@ -2565,7 +2569,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA7" s="15" t="n"/>
+      <c r="BA7" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB7" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -2816,7 +2824,7 @@
       </c>
       <c r="AW8" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX8" s="16" t="inlineStr">
@@ -2834,7 +2842,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA8" s="16" t="n"/>
+      <c r="BA8" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB8" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -3330,7 +3342,7 @@
       </c>
       <c r="AW10" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX10" s="16" t="inlineStr">
@@ -3350,7 +3362,7 @@
       </c>
       <c r="BA10" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Abstract明确near transfer，测了untrained WM tasks) | oo核查修正[远迁移]:否→是(Abstract明确far transfer，Bayesian evidence)</t>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确near transfer，测了untrained WM tasks) | oo核查修正[远迁移]:否→是(Abstract明确far transfer，Bayesian evidence) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB10" s="16" t="inlineStr">
@@ -3591,7 +3603,7 @@
       </c>
       <c r="AW11" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX11" s="15" t="inlineStr">
@@ -3609,7 +3621,11 @@
           <t>预印本</t>
         </is>
       </c>
-      <c r="BA11" s="15" t="n"/>
+      <c r="BA11" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB11" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -4123,7 +4139,7 @@
       </c>
       <c r="AW13" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX13" s="15" t="inlineStr">
@@ -4141,7 +4157,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA13" s="15" t="n"/>
+      <c r="BA13" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB13" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -4388,7 +4408,7 @@
       </c>
       <c r="AW14" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX14" s="16" t="inlineStr">
@@ -4408,7 +4428,7 @@
       </c>
       <c r="BA14" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[设计]:准RCT→RCT("randomly divided into two training groups")</t>
+          <t>oo核查修正[设计]:准RCT→RCT("randomly divided into two training groups") | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB14" s="16" t="inlineStr">
@@ -4929,7 +4949,7 @@
       </c>
       <c r="AW16" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX16" s="16" t="inlineStr">
@@ -4949,7 +4969,7 @@
       </c>
       <c r="BA16" s="16" t="inlineStr">
         <is>
-          <t>：需人工判断 | ：需人工判断 | oo核查修正[近迁移]:否→是(criterion task（类训练WM任务）= 近迁移)</t>
+          <t>：需人工判断 | ：需人工判断 | oo核查修正[近迁移]:否→是(criterion task（类训练WM任务）= 近迁移) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB16" s="16" t="inlineStr">
@@ -5198,7 +5218,7 @@
       </c>
       <c r="AW17" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX17" s="15" t="inlineStr">
@@ -5218,7 +5238,7 @@
       </c>
       <c r="BA17" s="15" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Results测了memory updating/inhibition/STM) | oo核查修正[设计]:准RCT→RCT(randomly assigned明确)</t>
+          <t>oo核查修正[近迁移]:否→是(Results测了memory updating/inhibition/STM) | oo核查修正[设计]:准RCT→RCT(randomly assigned明确) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB17" s="15" t="inlineStr">
@@ -5733,7 +5753,7 @@
       </c>
       <c r="AW19" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX19" s="15" t="inlineStr">
@@ -5751,7 +5771,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA19" s="15" t="n"/>
+      <c r="BA19" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB19" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -5998,7 +6022,7 @@
       </c>
       <c r="AW20" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX20" s="16" t="inlineStr">
@@ -6018,7 +6042,7 @@
       </c>
       <c r="BA20" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(测了Corsi Block + Digit Span（未训练WM任务）)</t>
+          <t>oo核查修正[近迁移]:否→是(测了Corsi Block + Digit Span（未训练WM任务）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB20" s="16" t="inlineStr">
@@ -6534,7 +6558,7 @@
       </c>
       <c r="AW22" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX22" s="16" t="inlineStr">
@@ -6552,7 +6576,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA22" s="16" t="n"/>
+      <c r="BA22" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB22" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -6799,7 +6827,7 @@
       </c>
       <c r="AW23" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX23" s="15" t="inlineStr">
@@ -6817,7 +6845,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA23" s="15" t="n"/>
+      <c r="BA23" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB23" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -7584,7 +7616,7 @@
       </c>
       <c r="AW26" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX26" s="16" t="inlineStr">
@@ -7602,7 +7634,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA26" s="16" t="n"/>
+      <c r="BA26" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB26" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -7852,7 +7888,7 @@
       </c>
       <c r="AW27" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX27" s="15" t="inlineStr">
@@ -7870,7 +7906,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA27" s="15" t="n"/>
+      <c r="BA27" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB27" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -8119,7 +8159,7 @@
       </c>
       <c r="AW28" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX28" s="16" t="inlineStr">
@@ -8137,7 +8177,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA28" s="16" t="n"/>
+      <c r="BA28" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB28" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -8647,7 +8691,7 @@
       </c>
       <c r="AW30" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX30" s="16" t="inlineStr">
@@ -8667,7 +8711,7 @@
       </c>
       <c r="BA30" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移)</t>
+          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB30" s="16" t="inlineStr">
@@ -9435,7 +9479,7 @@
       </c>
       <c r="AW33" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX33" s="15" t="inlineStr">
@@ -9453,7 +9497,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA33" s="15" t="n"/>
+      <c r="BA33" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB33" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -10240,7 +10288,7 @@
       </c>
       <c r="AW36" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX36" s="16" t="inlineStr">
@@ -10258,7 +10306,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA36" s="16" t="n"/>
+      <c r="BA36" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB36" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -10508,7 +10560,7 @@
       </c>
       <c r="AW37" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX37" s="15" t="inlineStr">
@@ -10526,7 +10578,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA37" s="15" t="n"/>
+      <c r="BA37" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB37" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -10762,7 +10818,7 @@
       </c>
       <c r="AW38" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX38" s="16" t="inlineStr">
@@ -10780,7 +10836,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA38" s="16" t="n"/>
+      <c r="BA38" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB38" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -11023,7 +11083,7 @@
       </c>
       <c r="AW39" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX39" s="15" t="inlineStr">
@@ -11041,7 +11101,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA39" s="15" t="n"/>
+      <c r="BA39" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB39" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -11278,7 +11342,7 @@
       </c>
       <c r="AW40" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX40" s="16" t="inlineStr">
@@ -11298,7 +11362,7 @@
       </c>
       <c r="BA40" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）)</t>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB40" s="16" t="inlineStr">
@@ -11537,7 +11601,7 @@
       </c>
       <c r="AW41" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX41" s="15" t="inlineStr">
@@ -11555,7 +11619,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA41" s="15" t="n"/>
+      <c r="BA41" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB41" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -11802,7 +11870,7 @@
       </c>
       <c r="AW42" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX42" s="16" t="inlineStr">
@@ -11820,7 +11888,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA42" s="16" t="n"/>
+      <c r="BA42" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB42" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -12869,7 +12941,7 @@
       </c>
       <c r="AW46" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX46" s="16" t="inlineStr">
@@ -12889,7 +12961,7 @@
       </c>
       <c r="BA46" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(测了spatial WM（训练为verbal WM）)</t>
+          <t>oo核查修正[近迁移]:否→是(测了spatial WM（训练为verbal WM）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
         </is>
       </c>
       <c r="BB46" s="16" t="inlineStr">
@@ -13140,7 +13212,7 @@
       </c>
       <c r="AW47" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX47" s="15" t="inlineStr">
@@ -13158,7 +13230,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA47" s="15" t="n"/>
+      <c r="BA47" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB47" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -13397,7 +13473,7 @@
       </c>
       <c r="AW48" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX48" s="16" t="inlineStr">
@@ -13415,7 +13491,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA48" s="16" t="n"/>
+      <c r="BA48" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB48" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -13656,7 +13736,7 @@
       </c>
       <c r="AW49" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX49" s="15" t="inlineStr">
@@ -13674,7 +13754,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA49" s="15" t="n"/>
+      <c r="BA49" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB49" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -14964,7 +15048,7 @@
       </c>
       <c r="AW54" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX54" s="16" t="inlineStr">
@@ -14982,7 +15066,11 @@
           <t>预印本</t>
         </is>
       </c>
-      <c r="BA54" s="16" t="n"/>
+      <c r="BA54" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB54" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -15761,7 +15849,7 @@
       </c>
       <c r="AW57" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AX57" s="15" t="inlineStr">
@@ -15779,7 +15867,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA57" s="15" t="n"/>
+      <c r="BA57" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+        </is>
+      </c>
       <c r="BB57" s="15" t="inlineStr">
         <is>
           <t>未评估</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -9665,7 +9665,7 @@
       </c>
       <c r="AF34" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AG34" s="16" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="BA34" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(测了primary/secondary WM) | oo核查修正[设计]:准RCT→单组前后测(养老院居民，无对照组，只有训练组前后比较)</t>
+          <t>oo核查修正[近迁移]:否→是(测了primary/secondary WM) | oo核查修正[设计]:准RCT→单组前后测(养老院居民，无对照组，只有训练组前后比较) | oo核查：测量工具为Nürnberg Aging Inventory + CVLT，非标准WM任务，改为否</t>
         </is>
       </c>
       <c r="BB34" s="16" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="AF35" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AG35" s="15" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="BA35" s="15" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(测了WM等认知测量)</t>
+          <t>oo核查修正[近迁移]:否→是(测了WM等认知测量) | oo核查：TV训练内容本身含WM，无独立近迁移WM任务，改为否</t>
         </is>
       </c>
       <c r="BB35" s="15" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="AF40" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="BA40" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：训练任务=Digit Span+N-back，测量任务相同，Results明确no transfer evidence</t>
         </is>
       </c>
       <c r="BB40" s="16" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AW13" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX13" s="15" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="BA13" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有young-old亚组比较</t>
         </is>
       </c>
       <c r="BB13" s="15" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AW26" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX26" s="16" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="BA26" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析</t>
         </is>
       </c>
       <c r="BB26" s="16" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="AW28" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX28" s="16" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="BA28" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析</t>
         </is>
       </c>
       <c r="BB28" s="16" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AW38" s="16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX38" s="16" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="BA38" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析</t>
         </is>
       </c>
       <c r="BB38" s="16" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AW39" s="15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AX39" s="15" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="BA39" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有young-old亚组分析</t>
         </is>
       </c>
       <c r="BB39" s="15" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -6498,7 +6498,7 @@
       <c r="AJ22" s="16" t="n"/>
       <c r="AK22" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AL22" s="16" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="BA22" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：自身无follow-up测量，改为否</t>
         </is>
       </c>
       <c r="BB22" s="16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       <c r="AJ24" s="16" t="n"/>
       <c r="AK24" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AL24" s="16" t="inlineStr">
@@ -7106,7 +7106,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA24" s="16" t="n"/>
+      <c r="BA24" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：自身无follow-up测量，改为否</t>
+        </is>
+      </c>
       <c r="BB24" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -9419,7 +9423,7 @@
       <c r="AJ33" s="15" t="n"/>
       <c r="AK33" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AL33" s="15" t="inlineStr">
@@ -9499,7 +9503,7 @@
       </c>
       <c r="BA33" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：自身无follow-up测量，改为否</t>
         </is>
       </c>
       <c r="BB33" s="15" t="inlineStr">
@@ -14206,7 +14210,7 @@
       </c>
       <c r="AK51" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AL51" s="15" t="n">
@@ -14278,7 +14282,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA51" s="15" t="n"/>
+      <c r="BA51" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：自身无follow-up测量，改为否</t>
+        </is>
+      </c>
       <c r="BB51" s="15" t="inlineStr">
         <is>
           <t>未评估</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AT5" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU5" s="15" t="inlineStr">
@@ -2031,7 +2031,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA5" s="15" t="n"/>
+      <c r="BA5" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：Results段无显式调节效应检验，改为否</t>
+        </is>
+      </c>
       <c r="BB5" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -3078,7 +3082,7 @@
       </c>
       <c r="AT9" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU9" s="15" t="inlineStr">
@@ -3111,7 +3115,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA9" s="15" t="n"/>
+      <c r="BA9" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：Results段无显式调节效应检验，改为否</t>
+        </is>
+      </c>
       <c r="BB9" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -3327,7 +3335,7 @@
       </c>
       <c r="AT10" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU10" s="16" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="BA10" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Abstract明确near transfer，测了untrained WM tasks) | oo核查修正[远迁移]:否→是(Abstract明确far transfer，Bayesian evidence) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确near transfer，测了untrained WM tasks) | oo核查修正[远迁移]:否→是(Abstract明确far transfer，Bayesian evidence) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB10" s="16" t="inlineStr">
@@ -3588,7 +3596,7 @@
       </c>
       <c r="AT11" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU11" s="15" t="inlineStr">
@@ -3623,7 +3631,7 @@
       </c>
       <c r="BA11" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB11" s="15" t="inlineStr">
@@ -3859,7 +3867,7 @@
       </c>
       <c r="AT12" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU12" s="16" t="inlineStr">
@@ -3894,7 +3902,7 @@
       </c>
       <c r="BA12" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[设计]:交叉→RCT("randomized active control trial"，有crossover但主设计是RCT)</t>
+          <t>oo核查修正[设计]:交叉→RCT("randomized active control trial"，有crossover但主设计是RCT) | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB12" s="16" t="inlineStr">
@@ -4124,7 +4132,7 @@
       </c>
       <c r="AT13" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU13" s="15" t="inlineStr">
@@ -4159,7 +4167,7 @@
       </c>
       <c r="BA13" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有young-old亚组比较</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有young-old亚组比较 | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB13" s="15" t="inlineStr">
@@ -4656,7 +4664,7 @@
       </c>
       <c r="AT15" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU15" s="15" t="inlineStr">
@@ -4691,7 +4699,7 @@
       </c>
       <c r="BA15" s="15" t="inlineStr">
         <is>
-          <t>oo核查修正[设计]:RCT→交叉("randomized double-blind crossover study")</t>
+          <t>oo核查修正[设计]:RCT→交叉("randomized double-blind crossover study") | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB15" s="15" t="inlineStr">
@@ -5203,7 +5211,7 @@
       </c>
       <c r="AT17" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU17" s="15" t="inlineStr">
@@ -5238,7 +5246,7 @@
       </c>
       <c r="BA17" s="15" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Results测了memory updating/inhibition/STM) | oo核查修正[设计]:准RCT→RCT(randomly assigned明确) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查修正[近迁移]:否→是(Results测了memory updating/inhibition/STM) | oo核查修正[设计]:准RCT→RCT(randomly assigned明确) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB17" s="15" t="inlineStr">
@@ -6812,7 +6820,7 @@
       </c>
       <c r="AT23" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU23" s="15" t="inlineStr">
@@ -6847,7 +6855,7 @@
       </c>
       <c r="BA23" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB23" s="15" t="inlineStr">
@@ -7605,7 +7613,7 @@
       </c>
       <c r="AT26" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU26" s="16" t="inlineStr">
@@ -7640,7 +7648,7 @@
       </c>
       <c r="BA26" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析 | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB26" s="16" t="inlineStr">
@@ -7877,7 +7885,7 @@
       </c>
       <c r="AT27" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU27" s="15" t="inlineStr">
@@ -7912,7 +7920,7 @@
       </c>
       <c r="BA27" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB27" s="15" t="inlineStr">
@@ -8148,7 +8156,7 @@
       </c>
       <c r="AT28" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU28" s="16" t="inlineStr">
@@ -8183,7 +8191,7 @@
       </c>
       <c r="BA28" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo严格核查：Results段有old-old亚组分析 | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB28" s="16" t="inlineStr">
@@ -8950,7 +8958,7 @@
       </c>
       <c r="AT31" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU31" s="15" t="inlineStr">
@@ -8983,7 +8991,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA31" s="15" t="n"/>
+      <c r="BA31" s="15" t="inlineStr">
+        <is>
+          <t>oo核查：Results段无显式调节效应检验，改为否</t>
+        </is>
+      </c>
       <c r="BB31" s="15" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -9468,7 +9480,7 @@
       </c>
       <c r="AT33" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU33" s="15" t="inlineStr">
@@ -9503,7 +9515,7 @@
       </c>
       <c r="BA33" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：自身无follow-up测量，改为否</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：自身无follow-up测量，改为否 | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB33" s="15" t="inlineStr">
@@ -11331,7 +11343,7 @@
       </c>
       <c r="AT40" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU40" s="16" t="inlineStr">
@@ -11366,7 +11378,7 @@
       </c>
       <c r="BA40" s="16" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：训练任务=Digit Span+N-back，测量任务相同，Results明确no transfer evidence</t>
+          <t>oo核查修正[近迁移]:否→是(Abstract明确测了WM任务（trained + untrained domain）) | oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：训练任务=Digit Span+N-back，测量任务相同，Results明确no transfer evidence | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB40" s="16" t="inlineStr">
@@ -13201,7 +13213,7 @@
       </c>
       <c r="AT47" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU47" s="15" t="inlineStr">
@@ -13236,7 +13248,7 @@
       </c>
       <c r="BA47" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB47" s="15" t="inlineStr">
@@ -13462,7 +13474,7 @@
       </c>
       <c r="AT48" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU48" s="16" t="inlineStr">
@@ -13497,7 +13509,7 @@
       </c>
       <c r="BA48" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB48" s="16" t="inlineStr">
@@ -13990,7 +14002,7 @@
       </c>
       <c r="AT50" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU50" s="16" t="inlineStr">
@@ -14023,7 +14035,11 @@
           <t>预印本</t>
         </is>
       </c>
-      <c r="BA50" s="16" t="n"/>
+      <c r="BA50" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：Results段无显式调节效应检验，改为否</t>
+        </is>
+      </c>
       <c r="BB50" s="16" t="inlineStr">
         <is>
           <t>未评估</t>
@@ -15041,7 +15057,7 @@
       </c>
       <c r="AT54" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU54" s="16" t="inlineStr">
@@ -15076,7 +15092,7 @@
       </c>
       <c r="BA54" s="16" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB54" s="16" t="inlineStr">
@@ -15314,7 +15330,7 @@
       </c>
       <c r="AT55" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU55" s="15" t="inlineStr">
@@ -15349,7 +15365,7 @@
       </c>
       <c r="BA55" s="15" t="inlineStr">
         <is>
-          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移)</t>
+          <t>oo核查修正[近迁移]:否→是(criterion WM task = 近迁移) | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB55" s="15" t="inlineStr">
@@ -15842,7 +15858,7 @@
       </c>
       <c r="AT57" s="15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU57" s="15" t="inlineStr">
@@ -15877,7 +15893,7 @@
       </c>
       <c r="BA57" s="15" t="inlineStr">
         <is>
-          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献）</t>
+          <t>oo核查：年龄亚组分析→否（全文Results段无实质亚组比较，仅引用文献） | oo核查：Results段无显式调节效应检验，改为否</t>
         </is>
       </c>
       <c r="BB57" s="15" t="inlineStr">
@@ -16110,7 +16126,7 @@
       </c>
       <c r="AT58" s="16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AU58" s="16" t="inlineStr">
@@ -16143,7 +16159,11 @@
           <t>期刊</t>
         </is>
       </c>
-      <c r="BA58" s="16" t="n"/>
+      <c r="BA58" s="16" t="inlineStr">
+        <is>
+          <t>oo核查：Results段无显式调节效应检验，改为否</t>
+        </is>
+      </c>
       <c r="BB58" s="16" t="inlineStr">
         <is>
           <t>未评估</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -3284,7 +3284,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="AG10" s="16" t="n"/>
+      <c r="AG10" s="16" t="inlineStr">
+        <is>
+          <t>Updating task; Binding task; Complex span task（均为未训练WM任务）</t>
+        </is>
+      </c>
       <c r="AH10" s="16" t="inlineStr">
         <is>
           <t>是</t>
@@ -4611,7 +4615,7 @@
       </c>
       <c r="AG15" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH15" s="15" t="inlineStr">
@@ -4879,7 +4883,7 @@
       </c>
       <c r="AG16" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Categorization Working Memory Span (CWMS)</t>
         </is>
       </c>
       <c r="AH16" s="16" t="inlineStr">
@@ -5150,7 +5154,7 @@
       </c>
       <c r="AG17" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Operation Span (OSPAN); Dual N-back（作为独立近迁移测量）</t>
         </is>
       </c>
       <c r="AH17" s="15" t="inlineStr">
@@ -5962,7 +5966,7 @@
       </c>
       <c r="AG20" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Corsi Block Task; Digit Span（Forward and Backward）</t>
         </is>
       </c>
       <c r="AH20" s="16" t="inlineStr">
@@ -6759,7 +6763,7 @@
       </c>
       <c r="AG23" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH23" s="15" t="inlineStr">
@@ -7028,7 +7032,7 @@
       </c>
       <c r="AG24" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH24" s="16" t="inlineStr">
@@ -8365,7 +8369,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AG29" s="15" t="n"/>
+      <c r="AG29" s="15" t="inlineStr">
+        <is>
+          <t>未测量（无近迁移）</t>
+        </is>
+      </c>
       <c r="AH29" s="15" t="inlineStr">
         <is>
           <t>否</t>
@@ -8623,7 +8631,7 @@
       </c>
       <c r="AG30" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Working Memory Span task (CWMS)</t>
         </is>
       </c>
       <c r="AH30" s="16" t="inlineStr">
@@ -9166,7 +9174,7 @@
       </c>
       <c r="AG32" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Digit Span Forward; Verbal WM task</t>
         </is>
       </c>
       <c r="AH32" s="16" t="inlineStr">
@@ -9686,7 +9694,7 @@
       </c>
       <c r="AG34" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH34" s="16" t="inlineStr">
@@ -9955,7 +9963,7 @@
       </c>
       <c r="AG35" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH35" s="15" t="inlineStr">
@@ -11288,7 +11296,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AG40" s="16" t="n"/>
+      <c r="AG40" s="16" t="inlineStr">
+        <is>
+          <t>未测量（无近迁移）</t>
+        </is>
+      </c>
       <c r="AH40" s="16" t="inlineStr">
         <is>
           <t>否</t>
@@ -11545,7 +11557,7 @@
       </c>
       <c r="AG41" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH41" s="15" t="inlineStr">
@@ -12346,7 +12358,7 @@
       </c>
       <c r="AG44" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Forward Digit Span; N-back（作为独立近迁移测量）</t>
         </is>
       </c>
       <c r="AH44" s="16" t="inlineStr">
@@ -12881,7 +12893,7 @@
       </c>
       <c r="AG46" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Digit Span Forward; Corsi Block Forward; K-ABC Icons（verbal+visuospatial）</t>
         </is>
       </c>
       <c r="AH46" s="16" t="inlineStr">
@@ -14473,7 +14485,7 @@
       </c>
       <c r="AG52" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Backward Digit Span; Letter-Number Sequencing</t>
         </is>
       </c>
       <c r="AH52" s="16" t="inlineStr">
@@ -14738,7 +14750,7 @@
       </c>
       <c r="AG53" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未测量（无近迁移）</t>
         </is>
       </c>
       <c r="AH53" s="15" t="inlineStr">
@@ -15271,7 +15283,7 @@
       </c>
       <c r="AG55" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Forward/Backward Corsi Span; Categorization WM Span (CWMS)</t>
         </is>
       </c>
       <c r="AH55" s="15" t="inlineStr">
@@ -16063,7 +16075,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="AG58" s="16" t="n"/>
+      <c r="AG58" s="16" t="inlineStr">
+        <is>
+          <t>未测量（无近迁移）</t>
+        </is>
+      </c>
       <c r="AH58" s="16" t="inlineStr">
         <is>
           <t>是</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AE4" s="19" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" s="16" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AE20" s="21" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF20" s="16" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AE22" s="21" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF22" s="16" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="V39" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W39" s="15" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="U46" s="16" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V46" s="16" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AE46" s="21" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF46" s="16" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="X47" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y47" s="15" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="U49" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V49" s="15" t="n">

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1333,10 +1333,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U3" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U3" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="V3" s="15" t="inlineStr">
         <is>
@@ -1607,10 +1605,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U4" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U4" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="V4" s="16" t="n">
         <v>60</v>
@@ -1620,10 +1616,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X4" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X4" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="Y4" s="16" t="inlineStr">
         <is>
@@ -1876,10 +1870,8 @@
       <c r="U5" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="V5" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V5" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="W5" s="15" t="inlineStr">
         <is>
@@ -2161,10 +2153,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X6" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X6" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="Y6" s="16" t="inlineStr">
         <is>
@@ -2196,10 +2186,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE6" s="19" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE6" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="AF6" s="16" t="inlineStr">
         <is>
@@ -2693,10 +2681,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U8" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U8" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="V8" s="16" t="n">
         <v>40</v>
@@ -2706,10 +2692,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X8" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X8" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="Y8" s="16" t="inlineStr">
         <is>
@@ -2742,10 +2726,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE8" s="19" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE8" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="AF8" s="16" t="inlineStr">
         <is>
@@ -2961,10 +2943,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U9" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U9" s="15" t="n">
+        <v>12</v>
       </c>
       <c r="V9" s="15" t="n">
         <v>50</v>
@@ -3007,10 +2987,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE9" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE9" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="AF9" s="15" t="inlineStr">
         <is>
@@ -3239,10 +3217,8 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="X10" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X10" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="Y10" s="16" t="inlineStr">
         <is>
@@ -3274,10 +3250,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE10" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF10" s="16" t="inlineStr">
         <is>
@@ -4018,20 +3992,16 @@
       <c r="U13" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V13" s="15" t="n">
+        <v>45</v>
       </c>
       <c r="W13" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X13" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X13" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="Y13" s="15" t="inlineStr">
         <is>
@@ -4063,10 +4033,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE13" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE13" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF13" s="15" t="inlineStr">
         <is>
@@ -4553,10 +4521,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U15" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U15" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="V15" s="15" t="inlineStr">
         <is>
@@ -4568,10 +4534,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X15" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X15" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="Y15" s="15" t="inlineStr">
         <is>
@@ -4821,25 +4785,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U16" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V16" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U16" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="16" t="n">
+        <v>40</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X16" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X16" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="Y16" s="16" t="inlineStr">
         <is>
@@ -5094,10 +5052,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U17" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U17" s="15" t="n">
+        <v>25</v>
       </c>
       <c r="V17" s="15" t="inlineStr">
         <is>
@@ -5142,10 +5098,8 @@
           <t>居家</t>
         </is>
       </c>
-      <c r="AE17" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE17" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF17" s="15" t="inlineStr">
         <is>
@@ -5361,15 +5315,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U18" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V18" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U18" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="V18" s="16" t="n">
+        <v>45</v>
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
@@ -5631,10 +5581,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U19" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U19" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="V19" s="15" t="n">
         <v>45</v>
@@ -5644,10 +5592,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X19" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X19" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="Y19" s="15" t="inlineStr">
         <is>
@@ -5907,10 +5853,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U20" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="V20" s="16" t="n">
         <v>45</v>
@@ -6173,15 +6117,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U21" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V21" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U21" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" s="15" t="n">
+        <v>60</v>
       </c>
       <c r="W21" s="15" t="inlineStr">
         <is>
@@ -6221,10 +6161,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE21" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE21" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="AF21" s="15" t="inlineStr">
         <is>
@@ -6233,7 +6171,7 @@
       </c>
       <c r="AG21" s="15" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Spatial working memory (matrix pattern task), Numerical working memory (number sequence recall)</t>
         </is>
       </c>
       <c r="AH21" s="15" t="inlineStr">
@@ -6443,10 +6381,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="V22" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V22" s="16" t="n">
+        <v>40</v>
       </c>
       <c r="W22" s="16" t="inlineStr">
         <is>
@@ -6701,25 +6637,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U23" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V23" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U23" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="V23" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="W23" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X23" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X23" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Y23" s="15" t="inlineStr">
         <is>
@@ -6751,10 +6681,8 @@
           <t>居家</t>
         </is>
       </c>
-      <c r="AE23" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE23" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF23" s="15" t="inlineStr">
         <is>
@@ -7244,10 +7172,8 @@
       <c r="U25" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="V25" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="V25" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="W25" s="15" t="inlineStr">
         <is>
@@ -7544,10 +7470,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE26" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE26" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF26" s="16" t="inlineStr">
         <is>
@@ -7777,10 +7701,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X27" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X27" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Y27" s="15" t="inlineStr">
         <is>
@@ -7812,10 +7734,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE27" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE27" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF27" s="15" t="inlineStr">
         <is>
@@ -8571,10 +8491,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U30" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U30" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="V30" s="16" t="n">
         <v>40</v>
@@ -8584,10 +8502,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X30" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X30" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="Y30" s="16" t="inlineStr">
         <is>
@@ -8845,10 +8761,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U31" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U31" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="V31" s="15" t="n">
         <v>40</v>
@@ -8858,10 +8772,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X31" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X31" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="Y31" s="15" t="inlineStr">
         <is>
@@ -9384,10 +9296,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X33" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X33" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="Y33" s="15" t="inlineStr">
         <is>
@@ -9419,10 +9329,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE33" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE33" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF33" s="15" t="inlineStr">
         <is>
@@ -9638,10 +9546,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U34" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U34" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="V34" s="16" t="n">
         <v>45</v>
@@ -9901,25 +9807,19 @@
           <t>否</t>
         </is>
       </c>
-      <c r="U35" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V35" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U35" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="V35" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X35" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X35" s="15" t="n">
+        <v>8</v>
       </c>
       <c r="Y35" s="15" t="inlineStr">
         <is>
@@ -9951,10 +9851,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE35" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE35" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF35" s="15" t="inlineStr">
         <is>
@@ -10178,10 +10076,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U36" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U36" s="16" t="n">
+        <v>23</v>
       </c>
       <c r="V36" s="16" t="n">
         <v>45</v>
@@ -10224,10 +10120,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE36" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE36" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="AF36" s="16" t="inlineStr">
         <is>
@@ -11027,10 +10921,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE39" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE39" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF39" s="15" t="inlineStr">
         <is>
@@ -11251,10 +11143,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X40" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X40" s="16" t="n">
+        <v>13</v>
       </c>
       <c r="Y40" s="16" t="inlineStr">
         <is>
@@ -11286,10 +11176,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE40" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE40" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="AF40" s="16" t="inlineStr">
         <is>
@@ -11499,10 +11387,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U41" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U41" s="15" t="n">
+        <v>25</v>
       </c>
       <c r="V41" s="15" t="n">
         <v>40</v>
@@ -11545,10 +11431,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE41" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE41" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF41" s="15" t="inlineStr">
         <is>
@@ -11764,10 +11648,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U42" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U42" s="16" t="n">
+        <v>25</v>
       </c>
       <c r="V42" s="16" t="n">
         <v>30</v>
@@ -12037,10 +11919,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U43" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U43" s="15" t="n">
+        <v>40</v>
       </c>
       <c r="V43" s="15" t="n">
         <v>30</v>
@@ -12298,10 +12178,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U44" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U44" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="V44" s="16" t="n">
         <v>40</v>
@@ -12311,10 +12189,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X44" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X44" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="Y44" s="16" t="inlineStr">
         <is>
@@ -12576,10 +12452,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U45" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U45" s="15" t="n">
+        <v>40</v>
       </c>
       <c r="V45" s="15" t="n">
         <v>30</v>
@@ -13100,10 +12974,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U47" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U47" s="15" t="n">
+        <v>5</v>
       </c>
       <c r="V47" s="15" t="n">
         <v>30</v>
@@ -13643,10 +13515,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X49" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X49" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="Y49" s="15" t="inlineStr">
         <is>
@@ -13893,10 +13763,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U50" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U50" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="V50" s="16" t="n">
         <v>30</v>
@@ -14423,15 +14291,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U52" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V52" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U52" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="V52" s="16" t="n">
+        <v>60</v>
       </c>
       <c r="W52" s="16" t="inlineStr">
         <is>
@@ -14473,10 +14337,8 @@
           <t>混合</t>
         </is>
       </c>
-      <c r="AE52" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE52" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="AF52" s="16" t="inlineStr">
         <is>
@@ -14692,10 +14554,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U53" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U53" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="V53" s="15" t="n">
         <v>40</v>
@@ -14950,15 +14810,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U54" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V54" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U54" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="V54" s="16" t="n">
+        <v>45</v>
       </c>
       <c r="W54" s="16" t="inlineStr">
         <is>
@@ -14998,10 +14854,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE54" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE54" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="AF54" s="16" t="inlineStr">
         <is>
@@ -15221,25 +15075,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U55" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="V55" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U55" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V55" s="15" t="n">
+        <v>60</v>
       </c>
       <c r="W55" s="15" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="X55" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X55" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="Y55" s="15" t="inlineStr">
         <is>
@@ -15501,10 +15349,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X56" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X56" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="Y56" s="16" t="inlineStr">
         <is>
@@ -15746,10 +15592,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U57" s="15" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U57" s="15" t="n">
+        <v>12</v>
       </c>
       <c r="V57" s="15" t="n">
         <v>60</v>
@@ -15793,10 +15637,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE57" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE57" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="AF57" s="15" t="inlineStr">
         <is>
@@ -16014,10 +15856,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U58" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="U58" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="V58" s="16" t="inlineStr">
         <is>
@@ -16029,10 +15869,8 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="X58" s="16" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="X58" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="Y58" s="16" t="inlineStr">
         <is>
@@ -16065,10 +15903,8 @@
           <t>实验室</t>
         </is>
       </c>
-      <c r="AE58" s="21" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AE58" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="AF58" s="16" t="inlineStr">
         <is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v3_research.xlsx
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AE4" s="19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AF4" s="16" t="inlineStr">
@@ -5856,8 +5856,10 @@
       <c r="U20" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="V20" s="16" t="n">
-        <v>45</v>
+      <c r="V20" s="16" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
@@ -5865,7 +5867,7 @@
         </is>
       </c>
       <c r="X20" s="16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="16" t="inlineStr">
         <is>
@@ -9286,7 +9288,7 @@
         </is>
       </c>
       <c r="U33" s="15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V33" s="15" t="n">
         <v>20</v>
@@ -12714,8 +12716,10 @@
           <t>10</t>
         </is>
       </c>
-      <c r="V46" s="16" t="n">
-        <v>30</v>
+      <c r="V46" s="16" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="W46" s="16" t="inlineStr">
         <is>
@@ -12723,7 +12727,7 @@
         </is>
       </c>
       <c r="X46" s="16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y46" s="16" t="inlineStr">
         <is>
